--- a/VM2026_Tipping - Martin.xlsx
+++ b/VM2026_Tipping - Martin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/Tipping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{93E9AAE6-D14F-4877-B081-BFF986B62DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F3F6298-94B9-419A-B3A0-D1F61A7DB768}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="8_{93E9AAE6-D14F-4877-B081-BFF986B62DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CACE6077-60F6-472C-96DB-8DE6FAA71042}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="8172" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1492,17 +1492,26 @@
     <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1522,26 +1531,17 @@
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2104,111 +2104,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="M1" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
+      <c r="A1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="M1" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
     </row>
     <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="68" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="M2" s="69" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="M2" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
     </row>
     <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="M3" s="64" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="M3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
     </row>
     <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="M5" s="58" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="M5" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
     </row>
     <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2281,13 +2281,13 @@
         <v>28</v>
       </c>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="M7" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,W7,IF(AF8=1,W8,IF(AF9=1,W9,IF(AF10=1,W10,"")))),"")</f>
-        <v>Sør-Afrika</v>
+        <v>Mexico</v>
       </c>
       <c r="N7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,X7,IF(AF8=1,X8,IF(AF9=1,X9,IF(AF10=1,X10,"")))),"")</f>
@@ -2318,11 +2318,11 @@
       </c>
       <c r="P7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,Z7,IF(AF8=1,Z8,IF(AF9=1,Z9,IF(AF10=1,Z10,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,AA7,IF(AF8=1,AA8,IF(AF9=1,AA9,IF(AF10=1,AA10,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,AB7,IF(AF8=1,AB8,IF(AF9=1,AB9,IF(AF10=1,AB10,"")))),"")</f>
@@ -2330,15 +2330,15 @@
       </c>
       <c r="S7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,AC7,IF(AF8=1,AC8,IF(AF9=1,AC9,IF(AF10=1,AC10,"")))),"")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,AD7,IF(AF8=1,AD8,IF(AF9=1,AD9,IF(AF10=1,AD10,"")))),"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U7" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,AE7,IF(AF8=1,AE8,IF(AF9=1,AE9,IF(AF10=1,AE10,"")))),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7" t="s">
         <v>28</v>
@@ -2349,35 +2349,35 @@
       </c>
       <c r="Y7">
         <f>((C7="Mexico")*ISNUMBER(D7)*(D7&gt;F7))+((G7="Mexico")*ISNUMBER(D7)*(F7&gt;D7))+((C8="Mexico")*ISNUMBER(D8)*(D8&gt;F8))+((G8="Mexico")*ISNUMBER(D8)*(F8&gt;D8))+((C9="Mexico")*ISNUMBER(D9)*(D9&gt;F9))+((G9="Mexico")*ISNUMBER(D9)*(F9&gt;D9))+((C10="Mexico")*ISNUMBER(D10)*(D10&gt;F10))+((G10="Mexico")*ISNUMBER(D10)*(F10&gt;D10))+((C11="Mexico")*ISNUMBER(D11)*(D11&gt;F11))+((G11="Mexico")*ISNUMBER(D11)*(F11&gt;D11))+((C12="Mexico")*ISNUMBER(D12)*(D12&gt;F12))+((G12="Mexico")*ISNUMBER(D12)*(F12&gt;D12))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z7">
         <f>((C7="Mexico")*ISNUMBER(D7)*(D7=F7))+((G7="Mexico")*ISNUMBER(D7)*(F7=D7))+((C8="Mexico")*ISNUMBER(D8)*(D8=F8))+((G8="Mexico")*ISNUMBER(D8)*(F8=D8))+((C9="Mexico")*ISNUMBER(D9)*(D9=F9))+((G9="Mexico")*ISNUMBER(D9)*(F9=D9))+((C10="Mexico")*ISNUMBER(D10)*(D10=F10))+((G10="Mexico")*ISNUMBER(D10)*(F10=D10))+((C11="Mexico")*ISNUMBER(D11)*(D11=F11))+((G11="Mexico")*ISNUMBER(D11)*(F11=D11))+((C12="Mexico")*ISNUMBER(D12)*(D12=F12))+((G12="Mexico")*ISNUMBER(D12)*(F12=D12))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f>((C7="Mexico")*ISNUMBER(D7)*(D7&lt;F7))+((G7="Mexico")*ISNUMBER(D7)*(F7&lt;D7))+((C8="Mexico")*ISNUMBER(D8)*(D8&lt;F8))+((G8="Mexico")*ISNUMBER(D8)*(F8&lt;D8))+((C9="Mexico")*ISNUMBER(D9)*(D9&lt;F9))+((G9="Mexico")*ISNUMBER(D9)*(F9&lt;D9))+((C10="Mexico")*ISNUMBER(D10)*(D10&lt;F10))+((G10="Mexico")*ISNUMBER(D10)*(F10&lt;D10))+((C11="Mexico")*ISNUMBER(D11)*(D11&lt;F11))+((G11="Mexico")*ISNUMBER(D11)*(F11&lt;D11))+((C12="Mexico")*ISNUMBER(D12)*(D12&lt;F12))+((G12="Mexico")*ISNUMBER(D12)*(F12&lt;D12))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7">
         <f>IF((C7="Mexico")*ISNUMBER(D7),D7,0)+IF((G7="Mexico")*ISNUMBER(D7),F7,0)+IF((C8="Mexico")*ISNUMBER(D8),D8,0)+IF((G8="Mexico")*ISNUMBER(D8),F8,0)+IF((C9="Mexico")*ISNUMBER(D9),D9,0)+IF((G9="Mexico")*ISNUMBER(D9),F9,0)+IF((C10="Mexico")*ISNUMBER(D10),D10,0)+IF((G10="Mexico")*ISNUMBER(D10),F10,0)+IF((C11="Mexico")*ISNUMBER(D11),D11,0)+IF((G11="Mexico")*ISNUMBER(D11),F11,0)+IF((C12="Mexico")*ISNUMBER(D12),D12,0)+IF((G12="Mexico")*ISNUMBER(D12),F12,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <f>IF((C7="Mexico")*ISNUMBER(D7),F7,0)+IF((G7="Mexico")*ISNUMBER(D7),D7,0)+IF((C8="Mexico")*ISNUMBER(D8),F8,0)+IF((G8="Mexico")*ISNUMBER(D8),D8,0)+IF((C9="Mexico")*ISNUMBER(D9),F9,0)+IF((G9="Mexico")*ISNUMBER(D9),D9,0)+IF((C10="Mexico")*ISNUMBER(D10),F10,0)+IF((G10="Mexico")*ISNUMBER(D10),D10,0)+IF((C11="Mexico")*ISNUMBER(D11),F11,0)+IF((G11="Mexico")*ISNUMBER(D11),D11,0)+IF((C12="Mexico")*ISNUMBER(D12),F12,0)+IF((G12="Mexico")*ISNUMBER(D12),D12,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f>AB7-AC7</f>
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="AE7">
         <f>3*Y7+Z7</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <f>1+((AE8&gt;AE7)+(AE8=AE7)*(AD8&gt;AD7)+(AE8=AE7)*(AD8=AD7)*(AB8&gt;AB7)&gt;0)*1+((AE9&gt;AE7)+(AE9=AE7)*(AD9&gt;AD7)+(AE9=AE7)*(AD9=AD7)*(AB9&gt;AB7)&gt;0)*1+((AE10&gt;AE7)+(AE10=AE7)*(AD10&gt;AD7)+(AE10=AE7)*(AD10=AD7)*(AB10&gt;AB7)&gt;0)*1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2391,13 +2391,13 @@
         <v>35</v>
       </c>
       <c r="D8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="M8" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,W7,IF(AF8=2,W8,IF(AF9=2,W9,IF(AF10=2,W10,"")))),"")</f>
-        <v>Tsjekkia</v>
+        <v>Sør-Korea</v>
       </c>
       <c r="N8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,X7,IF(AF8=2,X8,IF(AF9=2,X9,IF(AF10=2,X10,"")))),"")</f>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="O8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,Y7,IF(AF8=2,Y8,IF(AF9=2,Y9,IF(AF10=2,Y10,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,Z7,IF(AF8=2,Z8,IF(AF9=2,Z9,IF(AF10=2,Z10,"")))),"")</f>
@@ -2432,15 +2432,15 @@
       </c>
       <c r="Q8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,AA7,IF(AF8=2,AA8,IF(AF9=2,AA9,IF(AF10=2,AA10,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,AB7,IF(AF8=2,AB8,IF(AF9=2,AB9,IF(AF10=2,AB10,"")))),"")</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,AC7,IF(AF8=2,AC8,IF(AF9=2,AC9,IF(AF10=2,AC10,"")))),"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,AD7,IF(AF8=2,AD8,IF(AF9=2,AD9,IF(AF10=2,AD10,"")))),"")</f>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="U8" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,AE7,IF(AF8=2,AE8,IF(AF9=2,AE9,IF(AF10=2,AE10,"")))),"")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W8" t="s">
         <v>30</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Y8">
         <f>((C7="Sør-Afrika")*ISNUMBER(D7)*(D7&gt;F7))+((G7="Sør-Afrika")*ISNUMBER(D7)*(F7&gt;D7))+((C8="Sør-Afrika")*ISNUMBER(D8)*(D8&gt;F8))+((G8="Sør-Afrika")*ISNUMBER(D8)*(F8&gt;D8))+((C9="Sør-Afrika")*ISNUMBER(D9)*(D9&gt;F9))+((G9="Sør-Afrika")*ISNUMBER(D9)*(F9&gt;D9))+((C10="Sør-Afrika")*ISNUMBER(D10)*(D10&gt;F10))+((G10="Sør-Afrika")*ISNUMBER(D10)*(F10&gt;D10))+((C11="Sør-Afrika")*ISNUMBER(D11)*(D11&gt;F11))+((G11="Sør-Afrika")*ISNUMBER(D11)*(F11&gt;D11))+((C12="Sør-Afrika")*ISNUMBER(D12)*(D12&gt;F12))+((G12="Sør-Afrika")*ISNUMBER(D12)*(F12&gt;D12))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z8">
         <f>((C7="Sør-Afrika")*ISNUMBER(D7)*(D7=F7))+((G7="Sør-Afrika")*ISNUMBER(D7)*(F7=D7))+((C8="Sør-Afrika")*ISNUMBER(D8)*(D8=F8))+((G8="Sør-Afrika")*ISNUMBER(D8)*(F8=D8))+((C9="Sør-Afrika")*ISNUMBER(D9)*(D9=F9))+((G9="Sør-Afrika")*ISNUMBER(D9)*(F9=D9))+((C10="Sør-Afrika")*ISNUMBER(D10)*(D10=F10))+((G10="Sør-Afrika")*ISNUMBER(D10)*(F10=D10))+((C11="Sør-Afrika")*ISNUMBER(D11)*(D11=F11))+((G11="Sør-Afrika")*ISNUMBER(D11)*(F11=D11))+((C12="Sør-Afrika")*ISNUMBER(D12)*(D12=F12))+((G12="Sør-Afrika")*ISNUMBER(D12)*(F12=D12))</f>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="AA8">
         <f>((C7="Sør-Afrika")*ISNUMBER(D7)*(D7&lt;F7))+((G7="Sør-Afrika")*ISNUMBER(D7)*(F7&lt;D7))+((C8="Sør-Afrika")*ISNUMBER(D8)*(D8&lt;F8))+((G8="Sør-Afrika")*ISNUMBER(D8)*(F8&lt;D8))+((C9="Sør-Afrika")*ISNUMBER(D9)*(D9&lt;F9))+((G9="Sør-Afrika")*ISNUMBER(D9)*(F9&lt;D9))+((C10="Sør-Afrika")*ISNUMBER(D10)*(D10&lt;F10))+((G10="Sør-Afrika")*ISNUMBER(D10)*(F10&lt;D10))+((C11="Sør-Afrika")*ISNUMBER(D11)*(D11&lt;F11))+((G11="Sør-Afrika")*ISNUMBER(D11)*(F11&lt;D11))+((C12="Sør-Afrika")*ISNUMBER(D12)*(D12&lt;F12))+((G12="Sør-Afrika")*ISNUMBER(D12)*(F12&lt;D12))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB8">
         <f>IF((C7="Sør-Afrika")*ISNUMBER(D7),D7,0)+IF((G7="Sør-Afrika")*ISNUMBER(D7),F7,0)+IF((C8="Sør-Afrika")*ISNUMBER(D8),D8,0)+IF((G8="Sør-Afrika")*ISNUMBER(D8),F8,0)+IF((C9="Sør-Afrika")*ISNUMBER(D9),D9,0)+IF((G9="Sør-Afrika")*ISNUMBER(D9),F9,0)+IF((C10="Sør-Afrika")*ISNUMBER(D10),D10,0)+IF((G10="Sør-Afrika")*ISNUMBER(D10),F10,0)+IF((C11="Sør-Afrika")*ISNUMBER(D11),D11,0)+IF((G11="Sør-Afrika")*ISNUMBER(D11),F11,0)+IF((C12="Sør-Afrika")*ISNUMBER(D12),D12,0)+IF((G12="Sør-Afrika")*ISNUMBER(D12),F12,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <f>IF((C7="Sør-Afrika")*ISNUMBER(D7),F7,0)+IF((G7="Sør-Afrika")*ISNUMBER(D7),D7,0)+IF((C8="Sør-Afrika")*ISNUMBER(D8),F8,0)+IF((G8="Sør-Afrika")*ISNUMBER(D8),D8,0)+IF((C9="Sør-Afrika")*ISNUMBER(D9),F9,0)+IF((G9="Sør-Afrika")*ISNUMBER(D9),D9,0)+IF((C10="Sør-Afrika")*ISNUMBER(D10),F10,0)+IF((G10="Sør-Afrika")*ISNUMBER(D10),D10,0)+IF((C11="Sør-Afrika")*ISNUMBER(D11),F11,0)+IF((G11="Sør-Afrika")*ISNUMBER(D11),D11,0)+IF((C12="Sør-Afrika")*ISNUMBER(D12),F12,0)+IF((G12="Sør-Afrika")*ISNUMBER(D12),D12,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8">
         <f>AB8-AC8</f>
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AE8">
         <f>3*Y8+Z8</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF8">
         <f>1+((AE7&gt;AE8)+(AE7=AE8)*(AD7&gt;AD8)+(AE7=AE8)*(AD7=AD8)*(AB7&gt;AB8)&gt;0)*1+((AE9&gt;AE8)+(AE9=AE8)*(AD9&gt;AD8)+(AE9=AE8)*(AD9=AD8)*(AB9&gt;AB8)&gt;0)*1+((AE10&gt;AE8)+(AE10=AE8)*(AD10&gt;AD8)+(AE10=AE8)*(AD10=AD8)*(AB10&gt;AB8)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2501,7 +2501,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>29</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="M9" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,W7,IF(AF8=3,W8,IF(AF9=3,W9,IF(AF10=3,W10,"")))),"")</f>
-        <v>Sør-Korea</v>
+        <v>Sør-Afrika</v>
       </c>
       <c r="N9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,X7,IF(AF8=3,X8,IF(AF9=3,X9,IF(AF10=3,X10,"")))),"")</f>
@@ -2538,27 +2538,27 @@
       </c>
       <c r="P9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,Z7,IF(AF8=3,Z8,IF(AF9=3,Z9,IF(AF10=3,Z10,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,AA7,IF(AF8=3,AA8,IF(AF9=3,AA9,IF(AF10=3,AA10,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,AB7,IF(AF8=3,AB8,IF(AF9=3,AB9,IF(AF10=3,AB10,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,AC7,IF(AF8=3,AC8,IF(AF9=3,AC9,IF(AF10=3,AC10,"")))),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,AD7,IF(AF8=3,AD8,IF(AF9=3,AD9,IF(AF10=3,AD10,"")))),"")</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U9" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,AE7,IF(AF8=3,AE8,IF(AF9=3,AE9,IF(AF10=3,AE10,"")))),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W9" t="s">
         <v>35</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Y9">
         <f>((C7="Sør-Korea")*ISNUMBER(D7)*(D7&gt;F7))+((G7="Sør-Korea")*ISNUMBER(D7)*(F7&gt;D7))+((C8="Sør-Korea")*ISNUMBER(D8)*(D8&gt;F8))+((G8="Sør-Korea")*ISNUMBER(D8)*(F8&gt;D8))+((C9="Sør-Korea")*ISNUMBER(D9)*(D9&gt;F9))+((G9="Sør-Korea")*ISNUMBER(D9)*(F9&gt;D9))+((C10="Sør-Korea")*ISNUMBER(D10)*(D10&gt;F10))+((G10="Sør-Korea")*ISNUMBER(D10)*(F10&gt;D10))+((C11="Sør-Korea")*ISNUMBER(D11)*(D11&gt;F11))+((G11="Sør-Korea")*ISNUMBER(D11)*(F11&gt;D11))+((C12="Sør-Korea")*ISNUMBER(D12)*(D12&gt;F12))+((G12="Sør-Korea")*ISNUMBER(D12)*(F12&gt;D12))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z9">
         <f>((C7="Sør-Korea")*ISNUMBER(D7)*(D7=F7))+((G7="Sør-Korea")*ISNUMBER(D7)*(F7=D7))+((C8="Sør-Korea")*ISNUMBER(D8)*(D8=F8))+((G8="Sør-Korea")*ISNUMBER(D8)*(F8=D8))+((C9="Sør-Korea")*ISNUMBER(D9)*(D9=F9))+((G9="Sør-Korea")*ISNUMBER(D9)*(F9=D9))+((C10="Sør-Korea")*ISNUMBER(D10)*(D10=F10))+((G10="Sør-Korea")*ISNUMBER(D10)*(F10=D10))+((C11="Sør-Korea")*ISNUMBER(D11)*(D11=F11))+((G11="Sør-Korea")*ISNUMBER(D11)*(F11=D11))+((C12="Sør-Korea")*ISNUMBER(D12)*(D12=F12))+((G12="Sør-Korea")*ISNUMBER(D12)*(F12=D12))</f>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AA9">
         <f>((C7="Sør-Korea")*ISNUMBER(D7)*(D7&lt;F7))+((G7="Sør-Korea")*ISNUMBER(D7)*(F7&lt;D7))+((C8="Sør-Korea")*ISNUMBER(D8)*(D8&lt;F8))+((G8="Sør-Korea")*ISNUMBER(D8)*(F8&lt;D8))+((C9="Sør-Korea")*ISNUMBER(D9)*(D9&lt;F9))+((G9="Sør-Korea")*ISNUMBER(D9)*(F9&lt;D9))+((C10="Sør-Korea")*ISNUMBER(D10)*(D10&lt;F10))+((G10="Sør-Korea")*ISNUMBER(D10)*(F10&lt;D10))+((C11="Sør-Korea")*ISNUMBER(D11)*(D11&lt;F11))+((G11="Sør-Korea")*ISNUMBER(D11)*(F11&lt;D11))+((C12="Sør-Korea")*ISNUMBER(D12)*(D12&lt;F12))+((G12="Sør-Korea")*ISNUMBER(D12)*(F12&lt;D12))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <f>IF((C7="Sør-Korea")*ISNUMBER(D7),D7,0)+IF((G7="Sør-Korea")*ISNUMBER(D7),F7,0)+IF((C8="Sør-Korea")*ISNUMBER(D8),D8,0)+IF((G8="Sør-Korea")*ISNUMBER(D8),F8,0)+IF((C9="Sør-Korea")*ISNUMBER(D9),D9,0)+IF((G9="Sør-Korea")*ISNUMBER(D9),F9,0)+IF((C10="Sør-Korea")*ISNUMBER(D10),D10,0)+IF((G10="Sør-Korea")*ISNUMBER(D10),F10,0)+IF((C11="Sør-Korea")*ISNUMBER(D11),D11,0)+IF((G11="Sør-Korea")*ISNUMBER(D11),F11,0)+IF((C12="Sør-Korea")*ISNUMBER(D12),D12,0)+IF((G12="Sør-Korea")*ISNUMBER(D12),F12,0)</f>
@@ -2585,19 +2585,19 @@
       </c>
       <c r="AC9">
         <f>IF((C7="Sør-Korea")*ISNUMBER(D7),F7,0)+IF((G7="Sør-Korea")*ISNUMBER(D7),D7,0)+IF((C8="Sør-Korea")*ISNUMBER(D8),F8,0)+IF((G8="Sør-Korea")*ISNUMBER(D8),D8,0)+IF((C9="Sør-Korea")*ISNUMBER(D9),F9,0)+IF((G9="Sør-Korea")*ISNUMBER(D9),D9,0)+IF((C10="Sør-Korea")*ISNUMBER(D10),F10,0)+IF((G10="Sør-Korea")*ISNUMBER(D10),D10,0)+IF((C11="Sør-Korea")*ISNUMBER(D11),F11,0)+IF((G11="Sør-Korea")*ISNUMBER(D11),D11,0)+IF((C12="Sør-Korea")*ISNUMBER(D12),F12,0)+IF((G12="Sør-Korea")*ISNUMBER(D12),D12,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD9">
         <f>AB9-AC9</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AE9">
         <f>3*Y9+Z9</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF9">
         <f>1+((AE7&gt;AE9)+(AE7=AE9)*(AD7&gt;AD9)+(AE7=AE9)*(AD7=AD9)*(AB7&gt;AB9)&gt;0)*1+((AE8&gt;AE9)+(AE8=AE9)*(AD8&gt;AD9)+(AE8=AE9)*(AD8=AD9)*(AB8&gt;AB9)&gt;0)*1+((AE10&gt;AE9)+(AE10=AE9)*(AD10&gt;AD9)+(AE10=AE9)*(AD10=AD9)*(AB10&gt;AB9)&gt;0)*1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,7 +2617,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>35</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="M10" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,W7,IF(AF8=4,W8,IF(AF9=4,W9,IF(AF10=4,W10,"")))),"")</f>
-        <v>Mexico</v>
+        <v>Tsjekkia</v>
       </c>
       <c r="N10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,X7,IF(AF8=4,X8,IF(AF9=4,X9,IF(AF10=4,X10,"")))),"")</f>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,Y7,IF(AF8=4,Y8,IF(AF9=4,Y9,IF(AF10=4,Y10,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,Z7,IF(AF8=4,Z8,IF(AF9=4,Z9,IF(AF10=4,Z10,"")))),"")</f>
@@ -2652,23 +2652,23 @@
       </c>
       <c r="Q10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,AA7,IF(AF8=4,AA8,IF(AF9=4,AA9,IF(AF10=4,AA10,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,AB7,IF(AF8=4,AB8,IF(AF9=4,AB9,IF(AF10=4,AB10,"")))),"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,AC7,IF(AF8=4,AC8,IF(AF9=4,AC9,IF(AF10=4,AC10,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,AD7,IF(AF8=4,AD8,IF(AF9=4,AD9,IF(AF10=4,AD10,"")))),"")</f>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="U10" s="3">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,AE7,IF(AF8=4,AE8,IF(AF9=4,AE9,IF(AF10=4,AE10,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="s">
         <v>36</v>
@@ -2679,19 +2679,19 @@
       </c>
       <c r="Y10">
         <f>((C7="Tsjekkia")*ISNUMBER(D7)*(D7&gt;F7))+((G7="Tsjekkia")*ISNUMBER(D7)*(F7&gt;D7))+((C8="Tsjekkia")*ISNUMBER(D8)*(D8&gt;F8))+((G8="Tsjekkia")*ISNUMBER(D8)*(F8&gt;D8))+((C9="Tsjekkia")*ISNUMBER(D9)*(D9&gt;F9))+((G9="Tsjekkia")*ISNUMBER(D9)*(F9&gt;D9))+((C10="Tsjekkia")*ISNUMBER(D10)*(D10&gt;F10))+((G10="Tsjekkia")*ISNUMBER(D10)*(F10&gt;D10))+((C11="Tsjekkia")*ISNUMBER(D11)*(D11&gt;F11))+((G11="Tsjekkia")*ISNUMBER(D11)*(F11&gt;D11))+((C12="Tsjekkia")*ISNUMBER(D12)*(D12&gt;F12))+((G12="Tsjekkia")*ISNUMBER(D12)*(F12&gt;D12))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
         <f>((C7="Tsjekkia")*ISNUMBER(D7)*(D7=F7))+((G7="Tsjekkia")*ISNUMBER(D7)*(F7=D7))+((C8="Tsjekkia")*ISNUMBER(D8)*(D8=F8))+((G8="Tsjekkia")*ISNUMBER(D8)*(F8=D8))+((C9="Tsjekkia")*ISNUMBER(D9)*(D9=F9))+((G9="Tsjekkia")*ISNUMBER(D9)*(F9=D9))+((C10="Tsjekkia")*ISNUMBER(D10)*(D10=F10))+((G10="Tsjekkia")*ISNUMBER(D10)*(F10=D10))+((C11="Tsjekkia")*ISNUMBER(D11)*(D11=F11))+((G11="Tsjekkia")*ISNUMBER(D11)*(F11=D11))+((C12="Tsjekkia")*ISNUMBER(D12)*(D12=F12))+((G12="Tsjekkia")*ISNUMBER(D12)*(F12=D12))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <f>((C7="Tsjekkia")*ISNUMBER(D7)*(D7&lt;F7))+((G7="Tsjekkia")*ISNUMBER(D7)*(F7&lt;D7))+((C8="Tsjekkia")*ISNUMBER(D8)*(D8&lt;F8))+((G8="Tsjekkia")*ISNUMBER(D8)*(F8&lt;D8))+((C9="Tsjekkia")*ISNUMBER(D9)*(D9&lt;F9))+((G9="Tsjekkia")*ISNUMBER(D9)*(F9&lt;D9))+((C10="Tsjekkia")*ISNUMBER(D10)*(D10&lt;F10))+((G10="Tsjekkia")*ISNUMBER(D10)*(F10&lt;D10))+((C11="Tsjekkia")*ISNUMBER(D11)*(D11&lt;F11))+((G11="Tsjekkia")*ISNUMBER(D11)*(F11&lt;D11))+((C12="Tsjekkia")*ISNUMBER(D12)*(D12&lt;F12))+((G12="Tsjekkia")*ISNUMBER(D12)*(F12&lt;D12))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB10">
         <f>IF((C7="Tsjekkia")*ISNUMBER(D7),D7,0)+IF((G7="Tsjekkia")*ISNUMBER(D7),F7,0)+IF((C8="Tsjekkia")*ISNUMBER(D8),D8,0)+IF((G8="Tsjekkia")*ISNUMBER(D8),F8,0)+IF((C9="Tsjekkia")*ISNUMBER(D9),D9,0)+IF((G9="Tsjekkia")*ISNUMBER(D9),F9,0)+IF((C10="Tsjekkia")*ISNUMBER(D10),D10,0)+IF((G10="Tsjekkia")*ISNUMBER(D10),F10,0)+IF((C11="Tsjekkia")*ISNUMBER(D11),D11,0)+IF((G11="Tsjekkia")*ISNUMBER(D11),F11,0)+IF((C12="Tsjekkia")*ISNUMBER(D12),D12,0)+IF((G12="Tsjekkia")*ISNUMBER(D12),F12,0)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <f>IF((C7="Tsjekkia")*ISNUMBER(D7),F7,0)+IF((G7="Tsjekkia")*ISNUMBER(D7),D7,0)+IF((C8="Tsjekkia")*ISNUMBER(D8),F8,0)+IF((G8="Tsjekkia")*ISNUMBER(D8),D8,0)+IF((C9="Tsjekkia")*ISNUMBER(D9),F9,0)+IF((G9="Tsjekkia")*ISNUMBER(D9),D9,0)+IF((C10="Tsjekkia")*ISNUMBER(D10),F10,0)+IF((G10="Tsjekkia")*ISNUMBER(D10),D10,0)+IF((C11="Tsjekkia")*ISNUMBER(D11),F11,0)+IF((G11="Tsjekkia")*ISNUMBER(D11),D11,0)+IF((C12="Tsjekkia")*ISNUMBER(D12),F12,0)+IF((G12="Tsjekkia")*ISNUMBER(D12),D12,0)</f>
@@ -2699,15 +2699,15 @@
       </c>
       <c r="AD10">
         <f>AB10-AC10</f>
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="AE10">
         <f>3*Y10+Z10</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <f>1+((AE7&gt;AE10)+(AE7=AE10)*(AD7&gt;AD10)+(AE7=AE10)*(AD7=AD10)*(AB7&gt;AB10)&gt;0)*1+((AE8&gt;AE10)+(AE8=AE10)*(AD8&gt;AD10)+(AE8=AE10)*(AD8=AD10)*(AB8&gt;AB10)&gt;0)*1+((AE9&gt;AE10)+(AE9=AE10)*(AD9&gt;AD10)+(AE9=AE10)*(AD9=AD10)*(AB9&gt;AB10)&gt;0)*1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2721,13 +2721,13 @@
         <v>28</v>
       </c>
       <c r="D11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>36</v>
@@ -2756,13 +2756,13 @@
         <v>30</v>
       </c>
       <c r="D12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>35</v>
@@ -2781,30 +2781,30 @@
       </c>
     </row>
     <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="M13" s="58" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="M13" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="61"/>
+      <c r="U13" s="61"/>
     </row>
     <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2877,7 +2877,7 @@
         <v>51</v>
       </c>
       <c r="D15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="M15" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,W15,IF(AF16=1,W16,IF(AF17=1,W17,IF(AF18=1,W18,"")))),"")</f>
-        <v>Sveits</v>
+        <v>Bosnia-Hercegovina</v>
       </c>
       <c r="N15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,X15,IF(AF16=1,X16,IF(AF17=1,X17,IF(AF18=1,X18,"")))),"")</f>
@@ -2910,11 +2910,11 @@
       </c>
       <c r="O15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,Y15,IF(AF16=1,Y16,IF(AF17=1,Y17,IF(AF18=1,Y18,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,Z15,IF(AF16=1,Z16,IF(AF17=1,Z17,IF(AF18=1,Z18,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,AA15,IF(AF16=1,AA16,IF(AF17=1,AA17,IF(AF18=1,AA18,"")))),"")</f>
@@ -2922,19 +2922,19 @@
       </c>
       <c r="R15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,AB15,IF(AF16=1,AB16,IF(AF17=1,AB17,IF(AF18=1,AB18,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,AC15,IF(AF16=1,AC16,IF(AF17=1,AC17,IF(AF18=1,AC18,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,AD15,IF(AF16=1,AD16,IF(AF17=1,AD17,IF(AF18=1,AD18,"")))),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,AE15,IF(AF16=1,AE16,IF(AF17=1,AE17,IF(AF18=1,AE18,"")))),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="s">
         <v>51</v>
@@ -2957,15 +2957,15 @@
       </c>
       <c r="AB15">
         <f>IF((C15="Canada")*ISNUMBER(D15),D15,0)+IF((G15="Canada")*ISNUMBER(D15),F15,0)+IF((C16="Canada")*ISNUMBER(D16),D16,0)+IF((G16="Canada")*ISNUMBER(D16),F16,0)+IF((C17="Canada")*ISNUMBER(D17),D17,0)+IF((G17="Canada")*ISNUMBER(D17),F17,0)+IF((C18="Canada")*ISNUMBER(D18),D18,0)+IF((G18="Canada")*ISNUMBER(D18),F18,0)+IF((C19="Canada")*ISNUMBER(D19),D19,0)+IF((G19="Canada")*ISNUMBER(D19),F19,0)+IF((C20="Canada")*ISNUMBER(D20),D20,0)+IF((G20="Canada")*ISNUMBER(D20),F20,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC15">
         <f>IF((C15="Canada")*ISNUMBER(D15),F15,0)+IF((G15="Canada")*ISNUMBER(D15),D15,0)+IF((C16="Canada")*ISNUMBER(D16),F16,0)+IF((G16="Canada")*ISNUMBER(D16),D16,0)+IF((C17="Canada")*ISNUMBER(D17),F17,0)+IF((G17="Canada")*ISNUMBER(D17),D17,0)+IF((C18="Canada")*ISNUMBER(D18),F18,0)+IF((G18="Canada")*ISNUMBER(D18),D18,0)+IF((C19="Canada")*ISNUMBER(D19),F19,0)+IF((G19="Canada")*ISNUMBER(D19),D19,0)+IF((C20="Canada")*ISNUMBER(D20),F20,0)+IF((G20="Canada")*ISNUMBER(D20),D20,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD15">
         <f>AB15-AC15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15">
         <f>3*Y15+Z15</f>
@@ -2987,13 +2987,13 @@
         <v>54</v>
       </c>
       <c r="D16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>55</v>
@@ -3032,15 +3032,15 @@
       </c>
       <c r="R16" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=2,AB15,IF(AF16=2,AB16,IF(AF17=2,AB17,IF(AF18=2,AB18,"")))),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S16" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=2,AC15,IF(AF16=2,AC16,IF(AF17=2,AC17,IF(AF18=2,AC18,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T16" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=2,AD15,IF(AF16=2,AD16,IF(AF17=2,AD17,IF(AF18=2,AD18,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=2,AE15,IF(AF16=2,AE16,IF(AF17=2,AE17,IF(AF18=2,AE18,"")))),"")</f>
@@ -3055,15 +3055,15 @@
       </c>
       <c r="Y16">
         <f>((C15="Bosnia-Hercegovina")*ISNUMBER(D15)*(D15&gt;F15))+((G15="Bosnia-Hercegovina")*ISNUMBER(D15)*(F15&gt;D15))+((C16="Bosnia-Hercegovina")*ISNUMBER(D16)*(D16&gt;F16))+((G16="Bosnia-Hercegovina")*ISNUMBER(D16)*(F16&gt;D16))+((C17="Bosnia-Hercegovina")*ISNUMBER(D17)*(D17&gt;F17))+((G17="Bosnia-Hercegovina")*ISNUMBER(D17)*(F17&gt;D17))+((C18="Bosnia-Hercegovina")*ISNUMBER(D18)*(D18&gt;F18))+((G18="Bosnia-Hercegovina")*ISNUMBER(D18)*(F18&gt;D18))+((C19="Bosnia-Hercegovina")*ISNUMBER(D19)*(D19&gt;F19))+((G19="Bosnia-Hercegovina")*ISNUMBER(D19)*(F19&gt;D19))+((C20="Bosnia-Hercegovina")*ISNUMBER(D20)*(D20&gt;F20))+((G20="Bosnia-Hercegovina")*ISNUMBER(D20)*(F20&gt;D20))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z16">
         <f>((C15="Bosnia-Hercegovina")*ISNUMBER(D15)*(D15=F15))+((G15="Bosnia-Hercegovina")*ISNUMBER(D15)*(F15=D15))+((C16="Bosnia-Hercegovina")*ISNUMBER(D16)*(D16=F16))+((G16="Bosnia-Hercegovina")*ISNUMBER(D16)*(F16=D16))+((C17="Bosnia-Hercegovina")*ISNUMBER(D17)*(D17=F17))+((G17="Bosnia-Hercegovina")*ISNUMBER(D17)*(F17=D17))+((C18="Bosnia-Hercegovina")*ISNUMBER(D18)*(D18=F18))+((G18="Bosnia-Hercegovina")*ISNUMBER(D18)*(F18=D18))+((C19="Bosnia-Hercegovina")*ISNUMBER(D19)*(D19=F19))+((G19="Bosnia-Hercegovina")*ISNUMBER(D19)*(F19=D19))+((C20="Bosnia-Hercegovina")*ISNUMBER(D20)*(D20=F20))+((G20="Bosnia-Hercegovina")*ISNUMBER(D20)*(F20=D20))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16">
         <f>((C15="Bosnia-Hercegovina")*ISNUMBER(D15)*(D15&lt;F15))+((G15="Bosnia-Hercegovina")*ISNUMBER(D15)*(F15&lt;D15))+((C16="Bosnia-Hercegovina")*ISNUMBER(D16)*(D16&lt;F16))+((G16="Bosnia-Hercegovina")*ISNUMBER(D16)*(F16&lt;D16))+((C17="Bosnia-Hercegovina")*ISNUMBER(D17)*(D17&lt;F17))+((G17="Bosnia-Hercegovina")*ISNUMBER(D17)*(F17&lt;D17))+((C18="Bosnia-Hercegovina")*ISNUMBER(D18)*(D18&lt;F18))+((G18="Bosnia-Hercegovina")*ISNUMBER(D18)*(F18&lt;D18))+((C19="Bosnia-Hercegovina")*ISNUMBER(D19)*(D19&lt;F19))+((G19="Bosnia-Hercegovina")*ISNUMBER(D19)*(F19&lt;D19))+((C20="Bosnia-Hercegovina")*ISNUMBER(D20)*(D20&lt;F20))+((G20="Bosnia-Hercegovina")*ISNUMBER(D20)*(F20&lt;D20))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16">
         <f>IF((C15="Bosnia-Hercegovina")*ISNUMBER(D15),D15,0)+IF((G15="Bosnia-Hercegovina")*ISNUMBER(D15),F15,0)+IF((C16="Bosnia-Hercegovina")*ISNUMBER(D16),D16,0)+IF((G16="Bosnia-Hercegovina")*ISNUMBER(D16),F16,0)+IF((C17="Bosnia-Hercegovina")*ISNUMBER(D17),D17,0)+IF((G17="Bosnia-Hercegovina")*ISNUMBER(D17),F17,0)+IF((C18="Bosnia-Hercegovina")*ISNUMBER(D18),D18,0)+IF((G18="Bosnia-Hercegovina")*ISNUMBER(D18),F18,0)+IF((C19="Bosnia-Hercegovina")*ISNUMBER(D19),D19,0)+IF((G19="Bosnia-Hercegovina")*ISNUMBER(D19),F19,0)+IF((C20="Bosnia-Hercegovina")*ISNUMBER(D20),D20,0)+IF((G20="Bosnia-Hercegovina")*ISNUMBER(D20),F20,0)</f>
@@ -3071,19 +3071,19 @@
       </c>
       <c r="AC16">
         <f>IF((C15="Bosnia-Hercegovina")*ISNUMBER(D15),F15,0)+IF((G15="Bosnia-Hercegovina")*ISNUMBER(D15),D15,0)+IF((C16="Bosnia-Hercegovina")*ISNUMBER(D16),F16,0)+IF((G16="Bosnia-Hercegovina")*ISNUMBER(D16),D16,0)+IF((C17="Bosnia-Hercegovina")*ISNUMBER(D17),F17,0)+IF((G17="Bosnia-Hercegovina")*ISNUMBER(D17),D17,0)+IF((C18="Bosnia-Hercegovina")*ISNUMBER(D18),F18,0)+IF((G18="Bosnia-Hercegovina")*ISNUMBER(D18),D18,0)+IF((C19="Bosnia-Hercegovina")*ISNUMBER(D19),F19,0)+IF((G19="Bosnia-Hercegovina")*ISNUMBER(D19),D19,0)+IF((C20="Bosnia-Hercegovina")*ISNUMBER(D20),F20,0)+IF((G20="Bosnia-Hercegovina")*ISNUMBER(D20),D20,0)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AD16">
         <f>AB16-AC16</f>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AE16">
         <f>3*Y16+Z16</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <f>1+((AE15&gt;AE16)+(AE15=AE16)*(AD15&gt;AD16)+(AE15=AE16)*(AD15=AD16)*(AB15&gt;AB16)&gt;0)*1+((AE17&gt;AE16)+(AE17=AE16)*(AD17&gt;AD16)+(AE17=AE16)*(AD17=AD16)*(AB17&gt;AB16)&gt;0)*1+((AE18&gt;AE16)+(AE18=AE16)*(AD18&gt;AD16)+(AE18=AE16)*(AD18=AD16)*(AB18&gt;AB16)&gt;0)*1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3097,13 +3097,13 @@
         <v>55</v>
       </c>
       <c r="D17" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>52</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="M17" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,W15,IF(AF16=3,W16,IF(AF17=3,W17,IF(AF18=3,W18,"")))),"")</f>
-        <v>Bosnia-Hercegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="N17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,X15,IF(AF16=3,X16,IF(AF17=3,X17,IF(AF18=3,X18,"")))),"")</f>
@@ -3130,31 +3130,31 @@
       </c>
       <c r="O17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,Y15,IF(AF16=3,Y16,IF(AF17=3,Y17,IF(AF18=3,Y18,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,Z15,IF(AF16=3,Z16,IF(AF17=3,Z17,IF(AF18=3,Z18,"")))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,AA15,IF(AF16=3,AA16,IF(AF17=3,AA17,IF(AF18=3,AA18,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,AB15,IF(AF16=3,AB16,IF(AF17=3,AB17,IF(AF18=3,AB18,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,AC15,IF(AF16=3,AC16,IF(AF17=3,AC17,IF(AF18=3,AC18,"")))),"")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,AD15,IF(AF16=3,AD16,IF(AF17=3,AD17,IF(AF18=3,AD18,"")))),"")</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="U17" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,AE15,IF(AF16=3,AE16,IF(AF17=3,AE17,IF(AF18=3,AE18,"")))),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W17" t="s">
         <v>54</v>
@@ -3177,11 +3177,11 @@
       </c>
       <c r="AB17">
         <f>IF((C15="Qatar")*ISNUMBER(D15),D15,0)+IF((G15="Qatar")*ISNUMBER(D15),F15,0)+IF((C16="Qatar")*ISNUMBER(D16),D16,0)+IF((G16="Qatar")*ISNUMBER(D16),F16,0)+IF((C17="Qatar")*ISNUMBER(D17),D17,0)+IF((G17="Qatar")*ISNUMBER(D17),F17,0)+IF((C18="Qatar")*ISNUMBER(D18),D18,0)+IF((G18="Qatar")*ISNUMBER(D18),F18,0)+IF((C19="Qatar")*ISNUMBER(D19),D19,0)+IF((G19="Qatar")*ISNUMBER(D19),F19,0)+IF((C20="Qatar")*ISNUMBER(D20),D20,0)+IF((G20="Qatar")*ISNUMBER(D20),F20,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC17">
         <f>IF((C15="Qatar")*ISNUMBER(D15),F15,0)+IF((G15="Qatar")*ISNUMBER(D15),D15,0)+IF((C16="Qatar")*ISNUMBER(D16),F16,0)+IF((G16="Qatar")*ISNUMBER(D16),D16,0)+IF((C17="Qatar")*ISNUMBER(D17),F17,0)+IF((G17="Qatar")*ISNUMBER(D17),D17,0)+IF((C18="Qatar")*ISNUMBER(D18),F18,0)+IF((G18="Qatar")*ISNUMBER(D18),D18,0)+IF((C19="Qatar")*ISNUMBER(D19),F19,0)+IF((G19="Qatar")*ISNUMBER(D19),D19,0)+IF((C20="Qatar")*ISNUMBER(D20),F20,0)+IF((G20="Qatar")*ISNUMBER(D20),D20,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD17">
         <f>AB17-AC17</f>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AF17">
         <f>1+((AE15&gt;AE17)+(AE15=AE17)*(AD15&gt;AD17)+(AE15=AE17)*(AD15=AD17)*(AB15&gt;AB17)&gt;0)*1+((AE16&gt;AE17)+(AE16=AE17)*(AD16&gt;AD17)+(AE16=AE17)*(AD16=AD17)*(AB16&gt;AB17)&gt;0)*1+((AE18&gt;AE17)+(AE18=AE17)*(AD18&gt;AD17)+(AE18=AE17)*(AD18=AD17)*(AB18&gt;AB17)&gt;0)*1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3207,13 +3207,13 @@
         <v>51</v>
       </c>
       <c r="D18" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>54</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="M18" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,W15,IF(AF16=4,W16,IF(AF17=4,W17,IF(AF18=4,W18,"")))),"")</f>
-        <v>Qatar</v>
+        <v>Sveits</v>
       </c>
       <c r="N18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,X15,IF(AF16=4,X16,IF(AF17=4,X17,IF(AF18=4,X18,"")))),"")</f>
@@ -3244,27 +3244,27 @@
       </c>
       <c r="P18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,Z15,IF(AF16=4,Z16,IF(AF17=4,Z17,IF(AF18=4,Z18,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,AA15,IF(AF16=4,AA16,IF(AF17=4,AA17,IF(AF18=4,AA18,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,AB15,IF(AF16=4,AB16,IF(AF17=4,AB17,IF(AF18=4,AB18,"")))),"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,AC15,IF(AF16=4,AC16,IF(AF17=4,AC17,IF(AF18=4,AC18,"")))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,AD15,IF(AF16=4,AD16,IF(AF17=4,AD17,IF(AF18=4,AD18,"")))),"")</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="U18" s="3">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,AE15,IF(AF16=4,AE16,IF(AF17=4,AE17,IF(AF18=4,AE18,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18" t="s">
         <v>55</v>
@@ -3275,35 +3275,35 @@
       </c>
       <c r="Y18">
         <f>((C15="Sveits")*ISNUMBER(D15)*(D15&gt;F15))+((G15="Sveits")*ISNUMBER(D15)*(F15&gt;D15))+((C16="Sveits")*ISNUMBER(D16)*(D16&gt;F16))+((G16="Sveits")*ISNUMBER(D16)*(F16&gt;D16))+((C17="Sveits")*ISNUMBER(D17)*(D17&gt;F17))+((G17="Sveits")*ISNUMBER(D17)*(F17&gt;D17))+((C18="Sveits")*ISNUMBER(D18)*(D18&gt;F18))+((G18="Sveits")*ISNUMBER(D18)*(F18&gt;D18))+((C19="Sveits")*ISNUMBER(D19)*(D19&gt;F19))+((G19="Sveits")*ISNUMBER(D19)*(F19&gt;D19))+((C20="Sveits")*ISNUMBER(D20)*(D20&gt;F20))+((G20="Sveits")*ISNUMBER(D20)*(F20&gt;D20))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18">
         <f>((C15="Sveits")*ISNUMBER(D15)*(D15=F15))+((G15="Sveits")*ISNUMBER(D15)*(F15=D15))+((C16="Sveits")*ISNUMBER(D16)*(D16=F16))+((G16="Sveits")*ISNUMBER(D16)*(F16=D16))+((C17="Sveits")*ISNUMBER(D17)*(D17=F17))+((G17="Sveits")*ISNUMBER(D17)*(F17=D17))+((C18="Sveits")*ISNUMBER(D18)*(D18=F18))+((G18="Sveits")*ISNUMBER(D18)*(F18=D18))+((C19="Sveits")*ISNUMBER(D19)*(D19=F19))+((G19="Sveits")*ISNUMBER(D19)*(F19=D19))+((C20="Sveits")*ISNUMBER(D20)*(D20=F20))+((G20="Sveits")*ISNUMBER(D20)*(F20=D20))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA18">
         <f>((C15="Sveits")*ISNUMBER(D15)*(D15&lt;F15))+((G15="Sveits")*ISNUMBER(D15)*(F15&lt;D15))+((C16="Sveits")*ISNUMBER(D16)*(D16&lt;F16))+((G16="Sveits")*ISNUMBER(D16)*(F16&lt;D16))+((C17="Sveits")*ISNUMBER(D17)*(D17&lt;F17))+((G17="Sveits")*ISNUMBER(D17)*(F17&lt;D17))+((C18="Sveits")*ISNUMBER(D18)*(D18&lt;F18))+((G18="Sveits")*ISNUMBER(D18)*(F18&lt;D18))+((C19="Sveits")*ISNUMBER(D19)*(D19&lt;F19))+((G19="Sveits")*ISNUMBER(D19)*(F19&lt;D19))+((C20="Sveits")*ISNUMBER(D20)*(D20&lt;F20))+((G20="Sveits")*ISNUMBER(D20)*(F20&lt;D20))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18">
         <f>IF((C15="Sveits")*ISNUMBER(D15),D15,0)+IF((G15="Sveits")*ISNUMBER(D15),F15,0)+IF((C16="Sveits")*ISNUMBER(D16),D16,0)+IF((G16="Sveits")*ISNUMBER(D16),F16,0)+IF((C17="Sveits")*ISNUMBER(D17),D17,0)+IF((G17="Sveits")*ISNUMBER(D17),F17,0)+IF((C18="Sveits")*ISNUMBER(D18),D18,0)+IF((G18="Sveits")*ISNUMBER(D18),F18,0)+IF((C19="Sveits")*ISNUMBER(D19),D19,0)+IF((G19="Sveits")*ISNUMBER(D19),F19,0)+IF((C20="Sveits")*ISNUMBER(D20),D20,0)+IF((G20="Sveits")*ISNUMBER(D20),F20,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC18">
         <f>IF((C15="Sveits")*ISNUMBER(D15),F15,0)+IF((G15="Sveits")*ISNUMBER(D15),D15,0)+IF((C16="Sveits")*ISNUMBER(D16),F16,0)+IF((G16="Sveits")*ISNUMBER(D16),D16,0)+IF((C17="Sveits")*ISNUMBER(D17),F17,0)+IF((G17="Sveits")*ISNUMBER(D17),D17,0)+IF((C18="Sveits")*ISNUMBER(D18),F18,0)+IF((G18="Sveits")*ISNUMBER(D18),D18,0)+IF((C19="Sveits")*ISNUMBER(D19),F19,0)+IF((G19="Sveits")*ISNUMBER(D19),D19,0)+IF((C20="Sveits")*ISNUMBER(D20),F20,0)+IF((G20="Sveits")*ISNUMBER(D20),D20,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD18">
         <f>AB18-AC18</f>
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="AE18">
         <f>3*Y18+Z18</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF18">
         <f>1+((AE15&gt;AE18)+(AE15=AE18)*(AD15&gt;AD18)+(AE15=AE18)*(AD15=AD18)*(AB15&gt;AB18)&gt;0)*1+((AE16&gt;AE18)+(AE16=AE18)*(AD16&gt;AD18)+(AE16=AE18)*(AD16=AD18)*(AB16&gt;AB18)&gt;0)*1+((AE17&gt;AE18)+(AE17=AE18)*(AD17&gt;AD18)+(AE17=AE18)*(AD17=AD18)*(AB17&gt;AB18)&gt;0)*1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3317,13 +3317,13 @@
         <v>55</v>
       </c>
       <c r="D19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>51</v>
@@ -3352,13 +3352,13 @@
         <v>52</v>
       </c>
       <c r="D20" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>54</v>
@@ -3377,30 +3377,30 @@
       </c>
     </row>
     <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="M21" s="58" t="s">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="M21" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
     </row>
     <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -3473,7 +3473,7 @@
         <v>66</v>
       </c>
       <c r="D23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>29</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M23" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,W23,IF(AF24=1,W24,IF(AF25=1,W25,IF(AF26=1,W26,"")))),"")</f>
-        <v>Skottland</v>
+        <v>Brasil</v>
       </c>
       <c r="N23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,X23,IF(AF24=1,X24,IF(AF25=1,X25,IF(AF26=1,X26,"")))),"")</f>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,Y23,IF(AF24=1,Y24,IF(AF25=1,Y25,IF(AF26=1,Y26,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,Z23,IF(AF24=1,Z24,IF(AF25=1,Z25,IF(AF26=1,Z26,"")))),"")</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Q23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,AA23,IF(AF24=1,AA24,IF(AF25=1,AA25,IF(AF26=1,AA26,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,AB23,IF(AF24=1,AB24,IF(AF25=1,AB25,IF(AF26=1,AB26,"")))),"")</f>
@@ -3522,15 +3522,15 @@
       </c>
       <c r="S23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,AC23,IF(AF24=1,AC24,IF(AF25=1,AC25,IF(AF26=1,AC26,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,AD23,IF(AF24=1,AD24,IF(AF25=1,AD25,IF(AF26=1,AD26,"")))),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,AE23,IF(AF24=1,AE24,IF(AF25=1,AE25,IF(AF26=1,AE26,"")))),"")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W23" t="s">
         <v>66</v>
@@ -3541,35 +3541,35 @@
       </c>
       <c r="Y23">
         <f>((C23="Brasil")*ISNUMBER(D23)*(D23&gt;F23))+((G23="Brasil")*ISNUMBER(D23)*(F23&gt;D23))+((C24="Brasil")*ISNUMBER(D24)*(D24&gt;F24))+((G24="Brasil")*ISNUMBER(D24)*(F24&gt;D24))+((C25="Brasil")*ISNUMBER(D25)*(D25&gt;F25))+((G25="Brasil")*ISNUMBER(D25)*(F25&gt;D25))+((C26="Brasil")*ISNUMBER(D26)*(D26&gt;F26))+((G26="Brasil")*ISNUMBER(D26)*(F26&gt;D26))+((C27="Brasil")*ISNUMBER(D27)*(D27&gt;F27))+((G27="Brasil")*ISNUMBER(D27)*(F27&gt;D27))+((C28="Brasil")*ISNUMBER(D28)*(D28&gt;F28))+((G28="Brasil")*ISNUMBER(D28)*(F28&gt;D28))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z23">
         <f>((C23="Brasil")*ISNUMBER(D23)*(D23=F23))+((G23="Brasil")*ISNUMBER(D23)*(F23=D23))+((C24="Brasil")*ISNUMBER(D24)*(D24=F24))+((G24="Brasil")*ISNUMBER(D24)*(F24=D24))+((C25="Brasil")*ISNUMBER(D25)*(D25=F25))+((G25="Brasil")*ISNUMBER(D25)*(F25=D25))+((C26="Brasil")*ISNUMBER(D26)*(D26=F26))+((G26="Brasil")*ISNUMBER(D26)*(F26=D26))+((C27="Brasil")*ISNUMBER(D27)*(D27=F27))+((G27="Brasil")*ISNUMBER(D27)*(F27=D27))+((C28="Brasil")*ISNUMBER(D28)*(D28=F28))+((G28="Brasil")*ISNUMBER(D28)*(F28=D28))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <f>((C23="Brasil")*ISNUMBER(D23)*(D23&lt;F23))+((G23="Brasil")*ISNUMBER(D23)*(F23&lt;D23))+((C24="Brasil")*ISNUMBER(D24)*(D24&lt;F24))+((G24="Brasil")*ISNUMBER(D24)*(F24&lt;D24))+((C25="Brasil")*ISNUMBER(D25)*(D25&lt;F25))+((G25="Brasil")*ISNUMBER(D25)*(F25&lt;D25))+((C26="Brasil")*ISNUMBER(D26)*(D26&lt;F26))+((G26="Brasil")*ISNUMBER(D26)*(F26&lt;D26))+((C27="Brasil")*ISNUMBER(D27)*(D27&lt;F27))+((G27="Brasil")*ISNUMBER(D27)*(F27&lt;D27))+((C28="Brasil")*ISNUMBER(D28)*(D28&lt;F28))+((G28="Brasil")*ISNUMBER(D28)*(F28&lt;D28))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB23">
         <f>IF((C23="Brasil")*ISNUMBER(D23),D23,0)+IF((G23="Brasil")*ISNUMBER(D23),F23,0)+IF((C24="Brasil")*ISNUMBER(D24),D24,0)+IF((G24="Brasil")*ISNUMBER(D24),F24,0)+IF((C25="Brasil")*ISNUMBER(D25),D25,0)+IF((G25="Brasil")*ISNUMBER(D25),F25,0)+IF((C26="Brasil")*ISNUMBER(D26),D26,0)+IF((G26="Brasil")*ISNUMBER(D26),F26,0)+IF((C27="Brasil")*ISNUMBER(D27),D27,0)+IF((G27="Brasil")*ISNUMBER(D27),F27,0)+IF((C28="Brasil")*ISNUMBER(D28),D28,0)+IF((G28="Brasil")*ISNUMBER(D28),F28,0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <f>IF((C23="Brasil")*ISNUMBER(D23),F23,0)+IF((G23="Brasil")*ISNUMBER(D23),D23,0)+IF((C24="Brasil")*ISNUMBER(D24),F24,0)+IF((G24="Brasil")*ISNUMBER(D24),D24,0)+IF((C25="Brasil")*ISNUMBER(D25),F25,0)+IF((G25="Brasil")*ISNUMBER(D25),D25,0)+IF((C26="Brasil")*ISNUMBER(D26),F26,0)+IF((G26="Brasil")*ISNUMBER(D26),D26,0)+IF((C27="Brasil")*ISNUMBER(D27),F27,0)+IF((G27="Brasil")*ISNUMBER(D27),D27,0)+IF((C28="Brasil")*ISNUMBER(D28),F28,0)+IF((G28="Brasil")*ISNUMBER(D28),D28,0)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AD23">
         <f>AB23-AC23</f>
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="AE23">
         <f>3*Y23+Z23</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AF23">
         <f>1+((AE24&gt;AE23)+(AE24=AE23)*(AD24&gt;AD23)+(AE24=AE23)*(AD24=AD23)*(AB24&gt;AB23)&gt;0)*1+((AE25&gt;AE23)+(AE25=AE23)*(AD25&gt;AD23)+(AE25=AE23)*(AD25=AD23)*(AB25&gt;AB23)&gt;0)*1+((AE26&gt;AE23)+(AE26=AE23)*(AD26&gt;AD23)+(AE26=AE23)*(AD26=AD23)*(AB26&gt;AB23)&gt;0)*1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3583,13 +3583,13 @@
         <v>70</v>
       </c>
       <c r="D24" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>71</v>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="M24" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,W23,IF(AF24=2,W24,IF(AF25=2,W25,IF(AF26=2,W26,"")))),"")</f>
-        <v>Haiti</v>
+        <v>Skottland</v>
       </c>
       <c r="N24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,X23,IF(AF24=2,X24,IF(AF25=2,X25,IF(AF26=2,X26,"")))),"")</f>
@@ -3616,11 +3616,11 @@
       </c>
       <c r="O24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,Y23,IF(AF24=2,Y24,IF(AF25=2,Y25,IF(AF26=2,Y26,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,Z23,IF(AF24=2,Z24,IF(AF25=2,Z25,IF(AF26=2,Z26,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,AA23,IF(AF24=2,AA24,IF(AF25=2,AA25,IF(AF26=2,AA26,"")))),"")</f>
@@ -3628,19 +3628,19 @@
       </c>
       <c r="R24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,AB23,IF(AF24=2,AB24,IF(AF25=2,AB25,IF(AF26=2,AB26,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,AC23,IF(AF24=2,AC24,IF(AF25=2,AC25,IF(AF26=2,AC26,"")))),"")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,AD23,IF(AF24=2,AD24,IF(AF25=2,AD25,IF(AF26=2,AD26,"")))),"")</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U24" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,AE23,IF(AF24=2,AE24,IF(AF25=2,AE25,IF(AF26=2,AE26,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W24" t="s">
         <v>67</v>
@@ -3663,15 +3663,15 @@
       </c>
       <c r="AB24">
         <f>IF((C23="Marokko")*ISNUMBER(D23),D23,0)+IF((G23="Marokko")*ISNUMBER(D23),F23,0)+IF((C24="Marokko")*ISNUMBER(D24),D24,0)+IF((G24="Marokko")*ISNUMBER(D24),F24,0)+IF((C25="Marokko")*ISNUMBER(D25),D25,0)+IF((G25="Marokko")*ISNUMBER(D25),F25,0)+IF((C26="Marokko")*ISNUMBER(D26),D26,0)+IF((G26="Marokko")*ISNUMBER(D26),F26,0)+IF((C27="Marokko")*ISNUMBER(D27),D27,0)+IF((G27="Marokko")*ISNUMBER(D27),F27,0)+IF((C28="Marokko")*ISNUMBER(D28),D28,0)+IF((G28="Marokko")*ISNUMBER(D28),F28,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <f>IF((C23="Marokko")*ISNUMBER(D23),F23,0)+IF((G23="Marokko")*ISNUMBER(D23),D23,0)+IF((C24="Marokko")*ISNUMBER(D24),F24,0)+IF((G24="Marokko")*ISNUMBER(D24),D24,0)+IF((C25="Marokko")*ISNUMBER(D25),F25,0)+IF((G25="Marokko")*ISNUMBER(D25),D25,0)+IF((C26="Marokko")*ISNUMBER(D26),F26,0)+IF((G26="Marokko")*ISNUMBER(D26),D26,0)+IF((C27="Marokko")*ISNUMBER(D27),F27,0)+IF((G27="Marokko")*ISNUMBER(D27),D27,0)+IF((C28="Marokko")*ISNUMBER(D28),F28,0)+IF((G28="Marokko")*ISNUMBER(D28),D28,0)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD24">
         <f>AB24-AC24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24">
         <f>3*Y24+Z24</f>
@@ -3693,13 +3693,13 @@
         <v>71</v>
       </c>
       <c r="D25" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>67</v>
@@ -3738,15 +3738,15 @@
       </c>
       <c r="R25" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=3,AB23,IF(AF24=3,AB24,IF(AF25=3,AB25,IF(AF26=3,AB26,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S25" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=3,AC23,IF(AF24=3,AC24,IF(AF25=3,AC25,IF(AF26=3,AC26,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=3,AD23,IF(AF24=3,AD24,IF(AF25=3,AD25,IF(AF26=3,AD26,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=3,AE23,IF(AF24=3,AE24,IF(AF25=3,AE25,IF(AF26=3,AE26,"")))),"")</f>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Y25">
         <f>((C23="Haiti")*ISNUMBER(D23)*(D23&gt;F23))+((G23="Haiti")*ISNUMBER(D23)*(F23&gt;D23))+((C24="Haiti")*ISNUMBER(D24)*(D24&gt;F24))+((G24="Haiti")*ISNUMBER(D24)*(F24&gt;D24))+((C25="Haiti")*ISNUMBER(D25)*(D25&gt;F25))+((G25="Haiti")*ISNUMBER(D25)*(F25&gt;D25))+((C26="Haiti")*ISNUMBER(D26)*(D26&gt;F26))+((G26="Haiti")*ISNUMBER(D26)*(F26&gt;D26))+((C27="Haiti")*ISNUMBER(D27)*(D27&gt;F27))+((G27="Haiti")*ISNUMBER(D27)*(F27&gt;D27))+((C28="Haiti")*ISNUMBER(D28)*(D28&gt;F28))+((G28="Haiti")*ISNUMBER(D28)*(F28&gt;D28))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25">
         <f>((C23="Haiti")*ISNUMBER(D23)*(D23=F23))+((G23="Haiti")*ISNUMBER(D23)*(F23=D23))+((C24="Haiti")*ISNUMBER(D24)*(D24=F24))+((G24="Haiti")*ISNUMBER(D24)*(F24=D24))+((C25="Haiti")*ISNUMBER(D25)*(D25=F25))+((G25="Haiti")*ISNUMBER(D25)*(F25=D25))+((C26="Haiti")*ISNUMBER(D26)*(D26=F26))+((G26="Haiti")*ISNUMBER(D26)*(F26=D26))+((C27="Haiti")*ISNUMBER(D27)*(D27=F27))+((G27="Haiti")*ISNUMBER(D27)*(F27=D27))+((C28="Haiti")*ISNUMBER(D28)*(D28=F28))+((G28="Haiti")*ISNUMBER(D28)*(F28=D28))</f>
@@ -3769,27 +3769,27 @@
       </c>
       <c r="AA25">
         <f>((C23="Haiti")*ISNUMBER(D23)*(D23&lt;F23))+((G23="Haiti")*ISNUMBER(D23)*(F23&lt;D23))+((C24="Haiti")*ISNUMBER(D24)*(D24&lt;F24))+((G24="Haiti")*ISNUMBER(D24)*(F24&lt;D24))+((C25="Haiti")*ISNUMBER(D25)*(D25&lt;F25))+((G25="Haiti")*ISNUMBER(D25)*(F25&lt;D25))+((C26="Haiti")*ISNUMBER(D26)*(D26&lt;F26))+((G26="Haiti")*ISNUMBER(D26)*(F26&lt;D26))+((C27="Haiti")*ISNUMBER(D27)*(D27&lt;F27))+((G27="Haiti")*ISNUMBER(D27)*(F27&lt;D27))+((C28="Haiti")*ISNUMBER(D28)*(D28&lt;F28))+((G28="Haiti")*ISNUMBER(D28)*(F28&lt;D28))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB25">
         <f>IF((C23="Haiti")*ISNUMBER(D23),D23,0)+IF((G23="Haiti")*ISNUMBER(D23),F23,0)+IF((C24="Haiti")*ISNUMBER(D24),D24,0)+IF((G24="Haiti")*ISNUMBER(D24),F24,0)+IF((C25="Haiti")*ISNUMBER(D25),D25,0)+IF((G25="Haiti")*ISNUMBER(D25),F25,0)+IF((C26="Haiti")*ISNUMBER(D26),D26,0)+IF((G26="Haiti")*ISNUMBER(D26),F26,0)+IF((C27="Haiti")*ISNUMBER(D27),D27,0)+IF((G27="Haiti")*ISNUMBER(D27),F27,0)+IF((C28="Haiti")*ISNUMBER(D28),D28,0)+IF((G28="Haiti")*ISNUMBER(D28),F28,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <f>IF((C23="Haiti")*ISNUMBER(D23),F23,0)+IF((G23="Haiti")*ISNUMBER(D23),D23,0)+IF((C24="Haiti")*ISNUMBER(D24),F24,0)+IF((G24="Haiti")*ISNUMBER(D24),D24,0)+IF((C25="Haiti")*ISNUMBER(D25),F25,0)+IF((G25="Haiti")*ISNUMBER(D25),D25,0)+IF((C26="Haiti")*ISNUMBER(D26),F26,0)+IF((G26="Haiti")*ISNUMBER(D26),D26,0)+IF((C27="Haiti")*ISNUMBER(D27),F27,0)+IF((G27="Haiti")*ISNUMBER(D27),D27,0)+IF((C28="Haiti")*ISNUMBER(D28),F28,0)+IF((G28="Haiti")*ISNUMBER(D28),D28,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <f>AB25-AC25</f>
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="AE25">
         <f>3*Y25+Z25</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF25">
         <f>1+((AE23&gt;AE25)+(AE23=AE25)*(AD23&gt;AD25)+(AE23=AE25)*(AD23=AD25)*(AB23&gt;AB25)&gt;0)*1+((AE24&gt;AE25)+(AE24=AE25)*(AD24&gt;AD25)+(AE24=AE25)*(AD24=AD25)*(AB24&gt;AB25)&gt;0)*1+((AE26&gt;AE25)+(AE26=AE25)*(AD26&gt;AD25)+(AE26=AE25)*(AD26=AD25)*(AB26&gt;AB25)&gt;0)*1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3803,13 +3803,13 @@
         <v>66</v>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F26" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>70</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M26" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,W23,IF(AF24=4,W24,IF(AF25=4,W25,IF(AF26=4,W26,"")))),"")</f>
-        <v>Brasil</v>
+        <v>Haiti</v>
       </c>
       <c r="N26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,X23,IF(AF24=4,X24,IF(AF25=4,X25,IF(AF26=4,X26,"")))),"")</f>
@@ -3840,27 +3840,27 @@
       </c>
       <c r="P26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,Z23,IF(AF24=4,Z24,IF(AF25=4,Z25,IF(AF26=4,Z26,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,AA23,IF(AF24=4,AA24,IF(AF25=4,AA25,IF(AF26=4,AA26,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,AB23,IF(AF24=4,AB24,IF(AF25=4,AB25,IF(AF26=4,AB26,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,AC23,IF(AF24=4,AC24,IF(AF25=4,AC25,IF(AF26=4,AC26,"")))),"")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,AD23,IF(AF24=4,AD24,IF(AF25=4,AD25,IF(AF26=4,AD26,"")))),"")</f>
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="U26" s="3">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,AE23,IF(AF24=4,AE24,IF(AF25=4,AE25,IF(AF26=4,AE26,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="s">
         <v>71</v>
@@ -3871,11 +3871,11 @@
       </c>
       <c r="Y26">
         <f>((C23="Skottland")*ISNUMBER(D23)*(D23&gt;F23))+((G23="Skottland")*ISNUMBER(D23)*(F23&gt;D23))+((C24="Skottland")*ISNUMBER(D24)*(D24&gt;F24))+((G24="Skottland")*ISNUMBER(D24)*(F24&gt;D24))+((C25="Skottland")*ISNUMBER(D25)*(D25&gt;F25))+((G25="Skottland")*ISNUMBER(D25)*(F25&gt;D25))+((C26="Skottland")*ISNUMBER(D26)*(D26&gt;F26))+((G26="Skottland")*ISNUMBER(D26)*(F26&gt;D26))+((C27="Skottland")*ISNUMBER(D27)*(D27&gt;F27))+((G27="Skottland")*ISNUMBER(D27)*(F27&gt;D27))+((C28="Skottland")*ISNUMBER(D28)*(D28&gt;F28))+((G28="Skottland")*ISNUMBER(D28)*(F28&gt;D28))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z26">
         <f>((C23="Skottland")*ISNUMBER(D23)*(D23=F23))+((G23="Skottland")*ISNUMBER(D23)*(F23=D23))+((C24="Skottland")*ISNUMBER(D24)*(D24=F24))+((G24="Skottland")*ISNUMBER(D24)*(F24=D24))+((C25="Skottland")*ISNUMBER(D25)*(D25=F25))+((G25="Skottland")*ISNUMBER(D25)*(F25=D25))+((C26="Skottland")*ISNUMBER(D26)*(D26=F26))+((G26="Skottland")*ISNUMBER(D26)*(F26=D26))+((C27="Skottland")*ISNUMBER(D27)*(D27=F27))+((G27="Skottland")*ISNUMBER(D27)*(F27=D27))+((C28="Skottland")*ISNUMBER(D28)*(D28=F28))+((G28="Skottland")*ISNUMBER(D28)*(F28=D28))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26">
         <f>((C23="Skottland")*ISNUMBER(D23)*(D23&lt;F23))+((G23="Skottland")*ISNUMBER(D23)*(F23&lt;D23))+((C24="Skottland")*ISNUMBER(D24)*(D24&lt;F24))+((G24="Skottland")*ISNUMBER(D24)*(F24&lt;D24))+((C25="Skottland")*ISNUMBER(D25)*(D25&lt;F25))+((G25="Skottland")*ISNUMBER(D25)*(F25&lt;D25))+((C26="Skottland")*ISNUMBER(D26)*(D26&lt;F26))+((G26="Skottland")*ISNUMBER(D26)*(F26&lt;D26))+((C27="Skottland")*ISNUMBER(D27)*(D27&lt;F27))+((G27="Skottland")*ISNUMBER(D27)*(F27&lt;D27))+((C28="Skottland")*ISNUMBER(D28)*(D28&lt;F28))+((G28="Skottland")*ISNUMBER(D28)*(F28&lt;D28))</f>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB26">
         <f>IF((C23="Skottland")*ISNUMBER(D23),D23,0)+IF((G23="Skottland")*ISNUMBER(D23),F23,0)+IF((C24="Skottland")*ISNUMBER(D24),D24,0)+IF((G24="Skottland")*ISNUMBER(D24),F24,0)+IF((C25="Skottland")*ISNUMBER(D25),D25,0)+IF((G25="Skottland")*ISNUMBER(D25),F25,0)+IF((C26="Skottland")*ISNUMBER(D26),D26,0)+IF((G26="Skottland")*ISNUMBER(D26),F26,0)+IF((C27="Skottland")*ISNUMBER(D27),D27,0)+IF((G27="Skottland")*ISNUMBER(D27),F27,0)+IF((C28="Skottland")*ISNUMBER(D28),D28,0)+IF((G28="Skottland")*ISNUMBER(D28),F28,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <f>IF((C23="Skottland")*ISNUMBER(D23),F23,0)+IF((G23="Skottland")*ISNUMBER(D23),D23,0)+IF((C24="Skottland")*ISNUMBER(D24),F24,0)+IF((G24="Skottland")*ISNUMBER(D24),D24,0)+IF((C25="Skottland")*ISNUMBER(D25),F25,0)+IF((G25="Skottland")*ISNUMBER(D25),D25,0)+IF((C26="Skottland")*ISNUMBER(D26),F26,0)+IF((G26="Skottland")*ISNUMBER(D26),D26,0)+IF((C27="Skottland")*ISNUMBER(D27),F27,0)+IF((G27="Skottland")*ISNUMBER(D27),D27,0)+IF((C28="Skottland")*ISNUMBER(D28),F28,0)+IF((G28="Skottland")*ISNUMBER(D28),D28,0)</f>
@@ -3891,15 +3891,15 @@
       </c>
       <c r="AD26">
         <f>AB26-AC26</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE26">
         <f>3*Y26+Z26</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF26">
         <f>1+((AE23&gt;AE26)+(AE23=AE26)*(AD23&gt;AD26)+(AE23=AE26)*(AD23=AD26)*(AB23&gt;AB26)&gt;0)*1+((AE24&gt;AE26)+(AE24=AE26)*(AD24&gt;AD26)+(AE24=AE26)*(AD24=AD26)*(AB24&gt;AB26)&gt;0)*1+((AE25&gt;AE26)+(AE25=AE26)*(AD25&gt;AD26)+(AE25=AE26)*(AD25=AD26)*(AB25&gt;AB26)&gt;0)*1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3913,13 +3913,13 @@
         <v>71</v>
       </c>
       <c r="D27" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>66</v>
@@ -3948,13 +3948,13 @@
         <v>67</v>
       </c>
       <c r="D28" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>70</v>
@@ -3973,30 +3973,30 @@
       </c>
     </row>
     <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="M29" s="58" t="s">
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="M29" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="58"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="61"/>
     </row>
     <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -4069,7 +4069,7 @@
         <v>79</v>
       </c>
       <c r="D31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M31" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,W31,IF(AF32=1,W32,IF(AF33=1,W33,IF(AF34=1,W34,"")))),"")</f>
-        <v>Paraguay</v>
+        <v>Tyrkia</v>
       </c>
       <c r="N31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,X31,IF(AF32=1,X32,IF(AF33=1,X33,IF(AF34=1,X34,"")))),"")</f>
@@ -4102,11 +4102,11 @@
       </c>
       <c r="O31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,Y31,IF(AF32=1,Y32,IF(AF33=1,Y33,IF(AF34=1,Y34,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,Z31,IF(AF32=1,Z32,IF(AF33=1,Z33,IF(AF34=1,Z34,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,AA31,IF(AF32=1,AA32,IF(AF33=1,AA33,IF(AF34=1,AA34,"")))),"")</f>
@@ -4114,19 +4114,19 @@
       </c>
       <c r="R31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,AB31,IF(AF32=1,AB32,IF(AF33=1,AB33,IF(AF34=1,AB34,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,AC31,IF(AF32=1,AC32,IF(AF33=1,AC33,IF(AF34=1,AC34,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,AD31,IF(AF32=1,AD32,IF(AF33=1,AD33,IF(AF34=1,AD34,"")))),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U31" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,AE31,IF(AF32=1,AE32,IF(AF33=1,AE33,IF(AF34=1,AE34,"")))),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W31" t="s">
         <v>79</v>
@@ -4137,11 +4137,11 @@
       </c>
       <c r="Y31">
         <f>((C31="USA")*ISNUMBER(D31)*(D31&gt;F31))+((G31="USA")*ISNUMBER(D31)*(F31&gt;D31))+((C32="USA")*ISNUMBER(D32)*(D32&gt;F32))+((G32="USA")*ISNUMBER(D32)*(F32&gt;D32))+((C33="USA")*ISNUMBER(D33)*(D33&gt;F33))+((G33="USA")*ISNUMBER(D33)*(F33&gt;D33))+((C34="USA")*ISNUMBER(D34)*(D34&gt;F34))+((G34="USA")*ISNUMBER(D34)*(F34&gt;D34))+((C35="USA")*ISNUMBER(D35)*(D35&gt;F35))+((G35="USA")*ISNUMBER(D35)*(F35&gt;D35))+((C36="USA")*ISNUMBER(D36)*(D36&gt;F36))+((G36="USA")*ISNUMBER(D36)*(F36&gt;D36))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31">
         <f>((C31="USA")*ISNUMBER(D31)*(D31=F31))+((G31="USA")*ISNUMBER(D31)*(F31=D31))+((C32="USA")*ISNUMBER(D32)*(D32=F32))+((G32="USA")*ISNUMBER(D32)*(F32=D32))+((C33="USA")*ISNUMBER(D33)*(D33=F33))+((G33="USA")*ISNUMBER(D33)*(F33=D33))+((C34="USA")*ISNUMBER(D34)*(D34=F34))+((G34="USA")*ISNUMBER(D34)*(F34=D34))+((C35="USA")*ISNUMBER(D35)*(D35=F35))+((G35="USA")*ISNUMBER(D35)*(F35=D35))+((C36="USA")*ISNUMBER(D36)*(D36=F36))+((G36="USA")*ISNUMBER(D36)*(F36=D36))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA31">
         <f>((C31="USA")*ISNUMBER(D31)*(D31&lt;F31))+((G31="USA")*ISNUMBER(D31)*(F31&lt;D31))+((C32="USA")*ISNUMBER(D32)*(D32&lt;F32))+((G32="USA")*ISNUMBER(D32)*(F32&lt;D32))+((C33="USA")*ISNUMBER(D33)*(D33&lt;F33))+((G33="USA")*ISNUMBER(D33)*(F33&lt;D33))+((C34="USA")*ISNUMBER(D34)*(D34&lt;F34))+((G34="USA")*ISNUMBER(D34)*(F34&lt;D34))+((C35="USA")*ISNUMBER(D35)*(D35&lt;F35))+((G35="USA")*ISNUMBER(D35)*(F35&lt;D35))+((C36="USA")*ISNUMBER(D36)*(D36&lt;F36))+((G36="USA")*ISNUMBER(D36)*(F36&lt;D36))</f>
@@ -4149,11 +4149,11 @@
       </c>
       <c r="AB31">
         <f>IF((C31="USA")*ISNUMBER(D31),D31,0)+IF((G31="USA")*ISNUMBER(D31),F31,0)+IF((C32="USA")*ISNUMBER(D32),D32,0)+IF((G32="USA")*ISNUMBER(D32),F32,0)+IF((C33="USA")*ISNUMBER(D33),D33,0)+IF((G33="USA")*ISNUMBER(D33),F33,0)+IF((C34="USA")*ISNUMBER(D34),D34,0)+IF((G34="USA")*ISNUMBER(D34),F34,0)+IF((C35="USA")*ISNUMBER(D35),D35,0)+IF((G35="USA")*ISNUMBER(D35),F35,0)+IF((C36="USA")*ISNUMBER(D36),D36,0)+IF((G36="USA")*ISNUMBER(D36),F36,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC31">
         <f>IF((C31="USA")*ISNUMBER(D31),F31,0)+IF((G31="USA")*ISNUMBER(D31),D31,0)+IF((C32="USA")*ISNUMBER(D32),F32,0)+IF((G32="USA")*ISNUMBER(D32),D32,0)+IF((C33="USA")*ISNUMBER(D33),F33,0)+IF((G33="USA")*ISNUMBER(D33),D33,0)+IF((C34="USA")*ISNUMBER(D34),F34,0)+IF((G34="USA")*ISNUMBER(D34),D34,0)+IF((C35="USA")*ISNUMBER(D35),F35,0)+IF((G35="USA")*ISNUMBER(D35),D35,0)+IF((C36="USA")*ISNUMBER(D36),F36,0)+IF((G36="USA")*ISNUMBER(D36),D36,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD31">
         <f>AB31-AC31</f>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AE31">
         <f>3*Y31+Z31</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF31">
         <f>1+((AE32&gt;AE31)+(AE32=AE31)*(AD32&gt;AD31)+(AE32=AE31)*(AD32=AD31)*(AB32&gt;AB31)&gt;0)*1+((AE33&gt;AE31)+(AE33=AE31)*(AD33&gt;AD31)+(AE33=AE31)*(AD33=AD31)*(AB33&gt;AB31)&gt;0)*1+((AE34&gt;AE31)+(AE34=AE31)*(AD34&gt;AD31)+(AE34=AE31)*(AD34=AD31)*(AB34&gt;AB31)&gt;0)*1</f>
@@ -4179,7 +4179,7 @@
         <v>81</v>
       </c>
       <c r="D32" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>29</v>
@@ -4212,11 +4212,11 @@
       </c>
       <c r="O32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,Y31,IF(AF32=2,Y32,IF(AF33=2,Y33,IF(AF34=2,Y34,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,Z31,IF(AF32=2,Z32,IF(AF33=2,Z33,IF(AF34=2,Z34,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,AA31,IF(AF32=2,AA32,IF(AF33=2,AA33,IF(AF34=2,AA34,"")))),"")</f>
@@ -4224,11 +4224,11 @@
       </c>
       <c r="R32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,AB31,IF(AF32=2,AB32,IF(AF33=2,AB33,IF(AF34=2,AB34,"")))),"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,AC31,IF(AF32=2,AC32,IF(AF33=2,AC33,IF(AF34=2,AC34,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,AD31,IF(AF32=2,AD32,IF(AF33=2,AD33,IF(AF34=2,AD34,"")))),"")</f>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="U32" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,AE31,IF(AF32=2,AE32,IF(AF33=2,AE33,IF(AF34=2,AE34,"")))),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W32" t="s">
         <v>80</v>
@@ -4251,31 +4251,31 @@
       </c>
       <c r="Z32">
         <f>((C31="Paraguay")*ISNUMBER(D31)*(D31=F31))+((G31="Paraguay")*ISNUMBER(D31)*(F31=D31))+((C32="Paraguay")*ISNUMBER(D32)*(D32=F32))+((G32="Paraguay")*ISNUMBER(D32)*(F32=D32))+((C33="Paraguay")*ISNUMBER(D33)*(D33=F33))+((G33="Paraguay")*ISNUMBER(D33)*(F33=D33))+((C34="Paraguay")*ISNUMBER(D34)*(D34=F34))+((G34="Paraguay")*ISNUMBER(D34)*(F34=D34))+((C35="Paraguay")*ISNUMBER(D35)*(D35=F35))+((G35="Paraguay")*ISNUMBER(D35)*(F35=D35))+((C36="Paraguay")*ISNUMBER(D36)*(D36=F36))+((G36="Paraguay")*ISNUMBER(D36)*(F36=D36))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA32">
         <f>((C31="Paraguay")*ISNUMBER(D31)*(D31&lt;F31))+((G31="Paraguay")*ISNUMBER(D31)*(F31&lt;D31))+((C32="Paraguay")*ISNUMBER(D32)*(D32&lt;F32))+((G32="Paraguay")*ISNUMBER(D32)*(F32&lt;D32))+((C33="Paraguay")*ISNUMBER(D33)*(D33&lt;F33))+((G33="Paraguay")*ISNUMBER(D33)*(F33&lt;D33))+((C34="Paraguay")*ISNUMBER(D34)*(D34&lt;F34))+((G34="Paraguay")*ISNUMBER(D34)*(F34&lt;D34))+((C35="Paraguay")*ISNUMBER(D35)*(D35&lt;F35))+((G35="Paraguay")*ISNUMBER(D35)*(F35&lt;D35))+((C36="Paraguay")*ISNUMBER(D36)*(D36&lt;F36))+((G36="Paraguay")*ISNUMBER(D36)*(F36&lt;D36))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB32">
         <f>IF((C31="Paraguay")*ISNUMBER(D31),D31,0)+IF((G31="Paraguay")*ISNUMBER(D31),F31,0)+IF((C32="Paraguay")*ISNUMBER(D32),D32,0)+IF((G32="Paraguay")*ISNUMBER(D32),F32,0)+IF((C33="Paraguay")*ISNUMBER(D33),D33,0)+IF((G33="Paraguay")*ISNUMBER(D33),F33,0)+IF((C34="Paraguay")*ISNUMBER(D34),D34,0)+IF((G34="Paraguay")*ISNUMBER(D34),F34,0)+IF((C35="Paraguay")*ISNUMBER(D35),D35,0)+IF((G35="Paraguay")*ISNUMBER(D35),F35,0)+IF((C36="Paraguay")*ISNUMBER(D36),D36,0)+IF((G36="Paraguay")*ISNUMBER(D36),F36,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <f>IF((C31="Paraguay")*ISNUMBER(D31),F31,0)+IF((G31="Paraguay")*ISNUMBER(D31),D31,0)+IF((C32="Paraguay")*ISNUMBER(D32),F32,0)+IF((G32="Paraguay")*ISNUMBER(D32),D32,0)+IF((C33="Paraguay")*ISNUMBER(D33),F33,0)+IF((G33="Paraguay")*ISNUMBER(D33),D33,0)+IF((C34="Paraguay")*ISNUMBER(D34),F34,0)+IF((G34="Paraguay")*ISNUMBER(D34),D34,0)+IF((C35="Paraguay")*ISNUMBER(D35),F35,0)+IF((G35="Paraguay")*ISNUMBER(D35),D35,0)+IF((C36="Paraguay")*ISNUMBER(D36),F36,0)+IF((G36="Paraguay")*ISNUMBER(D36),D36,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD32">
         <f>AB32-AC32</f>
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AE32">
         <f>3*Y32+Z32</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF32">
         <f>1+((AE31&gt;AE32)+(AE31=AE32)*(AD31&gt;AD32)+(AE31=AE32)*(AD31=AD32)*(AB31&gt;AB32)&gt;0)*1+((AE33&gt;AE32)+(AE33=AE32)*(AD33&gt;AD32)+(AE33=AE32)*(AD33=AD32)*(AB33&gt;AB32)&gt;0)*1+((AE34&gt;AE32)+(AE34=AE32)*(AD34&gt;AD32)+(AE34=AE32)*(AD34=AD32)*(AB34&gt;AB32)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4289,13 +4289,13 @@
         <v>79</v>
       </c>
       <c r="D33" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>81</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="M33" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,W31,IF(AF32=3,W32,IF(AF33=3,W33,IF(AF34=3,W34,"")))),"")</f>
-        <v>Australia</v>
+        <v>Paraguay</v>
       </c>
       <c r="N33" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,X31,IF(AF32=3,X32,IF(AF33=3,X33,IF(AF34=3,X34,"")))),"")</f>
@@ -4334,15 +4334,15 @@
       </c>
       <c r="R33" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,AB31,IF(AF32=3,AB32,IF(AF33=3,AB33,IF(AF34=3,AB34,"")))),"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S33" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,AC31,IF(AF32=3,AC32,IF(AF33=3,AC33,IF(AF34=3,AC34,"")))),"")</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,AD31,IF(AF32=3,AD32,IF(AF33=3,AD33,IF(AF34=3,AD34,"")))),"")</f>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="U33" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,AE31,IF(AF32=3,AE32,IF(AF33=3,AE33,IF(AF34=3,AE34,"")))),"")</f>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Y33">
         <f>((C31="Australia")*ISNUMBER(D31)*(D31&gt;F31))+((G31="Australia")*ISNUMBER(D31)*(F31&gt;D31))+((C32="Australia")*ISNUMBER(D32)*(D32&gt;F32))+((G32="Australia")*ISNUMBER(D32)*(F32&gt;D32))+((C33="Australia")*ISNUMBER(D33)*(D33&gt;F33))+((G33="Australia")*ISNUMBER(D33)*(F33&gt;D33))+((C34="Australia")*ISNUMBER(D34)*(D34&gt;F34))+((G34="Australia")*ISNUMBER(D34)*(F34&gt;D34))+((C35="Australia")*ISNUMBER(D35)*(D35&gt;F35))+((G35="Australia")*ISNUMBER(D35)*(F35&gt;D35))+((C36="Australia")*ISNUMBER(D36)*(D36&gt;F36))+((G36="Australia")*ISNUMBER(D36)*(F36&gt;D36))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33">
         <f>((C31="Australia")*ISNUMBER(D31)*(D31=F31))+((G31="Australia")*ISNUMBER(D31)*(F31=D31))+((C32="Australia")*ISNUMBER(D32)*(D32=F32))+((G32="Australia")*ISNUMBER(D32)*(F32=D32))+((C33="Australia")*ISNUMBER(D33)*(D33=F33))+((G33="Australia")*ISNUMBER(D33)*(F33=D33))+((C34="Australia")*ISNUMBER(D34)*(D34=F34))+((G34="Australia")*ISNUMBER(D34)*(F34=D34))+((C35="Australia")*ISNUMBER(D35)*(D35=F35))+((G35="Australia")*ISNUMBER(D35)*(F35=D35))+((C36="Australia")*ISNUMBER(D36)*(D36=F36))+((G36="Australia")*ISNUMBER(D36)*(F36=D36))</f>
@@ -4365,27 +4365,27 @@
       </c>
       <c r="AA33">
         <f>((C31="Australia")*ISNUMBER(D31)*(D31&lt;F31))+((G31="Australia")*ISNUMBER(D31)*(F31&lt;D31))+((C32="Australia")*ISNUMBER(D32)*(D32&lt;F32))+((G32="Australia")*ISNUMBER(D32)*(F32&lt;D32))+((C33="Australia")*ISNUMBER(D33)*(D33&lt;F33))+((G33="Australia")*ISNUMBER(D33)*(F33&lt;D33))+((C34="Australia")*ISNUMBER(D34)*(D34&lt;F34))+((G34="Australia")*ISNUMBER(D34)*(F34&lt;D34))+((C35="Australia")*ISNUMBER(D35)*(D35&lt;F35))+((G35="Australia")*ISNUMBER(D35)*(F35&lt;D35))+((C36="Australia")*ISNUMBER(D36)*(D36&lt;F36))+((G36="Australia")*ISNUMBER(D36)*(F36&lt;D36))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB33">
         <f>IF((C31="Australia")*ISNUMBER(D31),D31,0)+IF((G31="Australia")*ISNUMBER(D31),F31,0)+IF((C32="Australia")*ISNUMBER(D32),D32,0)+IF((G32="Australia")*ISNUMBER(D32),F32,0)+IF((C33="Australia")*ISNUMBER(D33),D33,0)+IF((G33="Australia")*ISNUMBER(D33),F33,0)+IF((C34="Australia")*ISNUMBER(D34),D34,0)+IF((G34="Australia")*ISNUMBER(D34),F34,0)+IF((C35="Australia")*ISNUMBER(D35),D35,0)+IF((G35="Australia")*ISNUMBER(D35),F35,0)+IF((C36="Australia")*ISNUMBER(D36),D36,0)+IF((G36="Australia")*ISNUMBER(D36),F36,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC33">
         <f>IF((C31="Australia")*ISNUMBER(D31),F31,0)+IF((G31="Australia")*ISNUMBER(D31),D31,0)+IF((C32="Australia")*ISNUMBER(D32),F32,0)+IF((G32="Australia")*ISNUMBER(D32),D32,0)+IF((C33="Australia")*ISNUMBER(D33),F33,0)+IF((G33="Australia")*ISNUMBER(D33),D33,0)+IF((C34="Australia")*ISNUMBER(D34),F34,0)+IF((G34="Australia")*ISNUMBER(D34),D34,0)+IF((C35="Australia")*ISNUMBER(D35),F35,0)+IF((G35="Australia")*ISNUMBER(D35),D35,0)+IF((C36="Australia")*ISNUMBER(D36),F36,0)+IF((G36="Australia")*ISNUMBER(D36),D36,0)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AD33">
         <f>AB33-AC33</f>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="AE33">
         <f>3*Y33+Z33</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <f>1+((AE31&gt;AE33)+(AE31=AE33)*(AD31&gt;AD33)+(AE31=AE33)*(AD31=AD33)*(AB31&gt;AB33)&gt;0)*1+((AE32&gt;AE33)+(AE32=AE33)*(AD32&gt;AD33)+(AE32=AE33)*(AD32=AD33)*(AB32&gt;AB33)&gt;0)*1+((AE34&gt;AE33)+(AE34=AE33)*(AD34&gt;AD33)+(AE34=AE33)*(AD34=AD33)*(AB34&gt;AB33)&gt;0)*1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4399,7 +4399,7 @@
         <v>82</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>29</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M34" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,W31,IF(AF32=4,W32,IF(AF33=4,W33,IF(AF34=4,W34,"")))),"")</f>
-        <v>Tyrkia</v>
+        <v>Australia</v>
       </c>
       <c r="N34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,X31,IF(AF32=4,X32,IF(AF33=4,X33,IF(AF34=4,X34,"")))),"")</f>
@@ -4436,27 +4436,27 @@
       </c>
       <c r="P34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,Z31,IF(AF32=4,Z32,IF(AF33=4,Z33,IF(AF34=4,Z34,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,AA31,IF(AF32=4,AA32,IF(AF33=4,AA33,IF(AF34=4,AA34,"")))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,AB31,IF(AF32=4,AB32,IF(AF33=4,AB33,IF(AF34=4,AB34,"")))),"")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,AC31,IF(AF32=4,AC32,IF(AF33=4,AC33,IF(AF34=4,AC34,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,AD31,IF(AF32=4,AD32,IF(AF33=4,AD33,IF(AF34=4,AD34,"")))),"")</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="U34" s="3">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,AE31,IF(AF32=4,AE32,IF(AF33=4,AE33,IF(AF34=4,AE34,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W34" t="s">
         <v>82</v>
@@ -4467,35 +4467,35 @@
       </c>
       <c r="Y34">
         <f>((C31="Tyrkia")*ISNUMBER(D31)*(D31&gt;F31))+((G31="Tyrkia")*ISNUMBER(D31)*(F31&gt;D31))+((C32="Tyrkia")*ISNUMBER(D32)*(D32&gt;F32))+((G32="Tyrkia")*ISNUMBER(D32)*(F32&gt;D32))+((C33="Tyrkia")*ISNUMBER(D33)*(D33&gt;F33))+((G33="Tyrkia")*ISNUMBER(D33)*(F33&gt;D33))+((C34="Tyrkia")*ISNUMBER(D34)*(D34&gt;F34))+((G34="Tyrkia")*ISNUMBER(D34)*(F34&gt;D34))+((C35="Tyrkia")*ISNUMBER(D35)*(D35&gt;F35))+((G35="Tyrkia")*ISNUMBER(D35)*(F35&gt;D35))+((C36="Tyrkia")*ISNUMBER(D36)*(D36&gt;F36))+((G36="Tyrkia")*ISNUMBER(D36)*(F36&gt;D36))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34">
         <f>((C31="Tyrkia")*ISNUMBER(D31)*(D31=F31))+((G31="Tyrkia")*ISNUMBER(D31)*(F31=D31))+((C32="Tyrkia")*ISNUMBER(D32)*(D32=F32))+((G32="Tyrkia")*ISNUMBER(D32)*(F32=D32))+((C33="Tyrkia")*ISNUMBER(D33)*(D33=F33))+((G33="Tyrkia")*ISNUMBER(D33)*(F33=D33))+((C34="Tyrkia")*ISNUMBER(D34)*(D34=F34))+((G34="Tyrkia")*ISNUMBER(D34)*(F34=D34))+((C35="Tyrkia")*ISNUMBER(D35)*(D35=F35))+((G35="Tyrkia")*ISNUMBER(D35)*(F35=D35))+((C36="Tyrkia")*ISNUMBER(D36)*(D36=F36))+((G36="Tyrkia")*ISNUMBER(D36)*(F36=D36))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA34">
         <f>((C31="Tyrkia")*ISNUMBER(D31)*(D31&lt;F31))+((G31="Tyrkia")*ISNUMBER(D31)*(F31&lt;D31))+((C32="Tyrkia")*ISNUMBER(D32)*(D32&lt;F32))+((G32="Tyrkia")*ISNUMBER(D32)*(F32&lt;D32))+((C33="Tyrkia")*ISNUMBER(D33)*(D33&lt;F33))+((G33="Tyrkia")*ISNUMBER(D33)*(F33&lt;D33))+((C34="Tyrkia")*ISNUMBER(D34)*(D34&lt;F34))+((G34="Tyrkia")*ISNUMBER(D34)*(F34&lt;D34))+((C35="Tyrkia")*ISNUMBER(D35)*(D35&lt;F35))+((G35="Tyrkia")*ISNUMBER(D35)*(F35&lt;D35))+((C36="Tyrkia")*ISNUMBER(D36)*(D36&lt;F36))+((G36="Tyrkia")*ISNUMBER(D36)*(F36&lt;D36))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34">
         <f>IF((C31="Tyrkia")*ISNUMBER(D31),D31,0)+IF((G31="Tyrkia")*ISNUMBER(D31),F31,0)+IF((C32="Tyrkia")*ISNUMBER(D32),D32,0)+IF((G32="Tyrkia")*ISNUMBER(D32),F32,0)+IF((C33="Tyrkia")*ISNUMBER(D33),D33,0)+IF((G33="Tyrkia")*ISNUMBER(D33),F33,0)+IF((C34="Tyrkia")*ISNUMBER(D34),D34,0)+IF((G34="Tyrkia")*ISNUMBER(D34),F34,0)+IF((C35="Tyrkia")*ISNUMBER(D35),D35,0)+IF((G35="Tyrkia")*ISNUMBER(D35),F35,0)+IF((C36="Tyrkia")*ISNUMBER(D36),D36,0)+IF((G36="Tyrkia")*ISNUMBER(D36),F36,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC34">
         <f>IF((C31="Tyrkia")*ISNUMBER(D31),F31,0)+IF((G31="Tyrkia")*ISNUMBER(D31),D31,0)+IF((C32="Tyrkia")*ISNUMBER(D32),F32,0)+IF((G32="Tyrkia")*ISNUMBER(D32),D32,0)+IF((C33="Tyrkia")*ISNUMBER(D33),F33,0)+IF((G33="Tyrkia")*ISNUMBER(D33),D33,0)+IF((C34="Tyrkia")*ISNUMBER(D34),F34,0)+IF((G34="Tyrkia")*ISNUMBER(D34),D34,0)+IF((C35="Tyrkia")*ISNUMBER(D35),F35,0)+IF((G35="Tyrkia")*ISNUMBER(D35),D35,0)+IF((C36="Tyrkia")*ISNUMBER(D36),F36,0)+IF((G36="Tyrkia")*ISNUMBER(D36),D36,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD34">
         <f>AB34-AC34</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AE34">
         <f>3*Y34+Z34</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AF34">
         <f>1+((AE31&gt;AE34)+(AE31=AE34)*(AD31&gt;AD34)+(AE31=AE34)*(AD31=AD34)*(AB31&gt;AB34)&gt;0)*1+((AE32&gt;AE34)+(AE32=AE34)*(AD32&gt;AD34)+(AE32=AE34)*(AD32=AD34)*(AB32&gt;AB34)&gt;0)*1+((AE33&gt;AE34)+(AE33=AE34)*(AD33&gt;AD34)+(AE33=AE34)*(AD33=AD34)*(AB33&gt;AB34)&gt;0)*1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4509,13 +4509,13 @@
         <v>82</v>
       </c>
       <c r="D35" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>79</v>
@@ -4544,13 +4544,13 @@
         <v>80</v>
       </c>
       <c r="D36" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>81</v>
@@ -4569,30 +4569,30 @@
       </c>
     </row>
     <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="M37" s="58" t="s">
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="M37" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="N37" s="58"/>
-      <c r="O37" s="58"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="58"/>
-      <c r="S37" s="58"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="58"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="61"/>
     </row>
     <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -4665,13 +4665,13 @@
         <v>88</v>
       </c>
       <c r="D39" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F39" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>89</v>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="M39" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,W39,IF(AF40=1,W40,IF(AF41=1,W41,IF(AF42=1,W42,"")))),"")</f>
-        <v>Elfenbenskysten</v>
+        <v>Tyskland</v>
       </c>
       <c r="N39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,X39,IF(AF40=1,X40,IF(AF41=1,X41,IF(AF42=1,X42,"")))),"")</f>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="O39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,Y39,IF(AF40=1,Y40,IF(AF41=1,Y41,IF(AF42=1,Y42,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,Z39,IF(AF40=1,Z40,IF(AF41=1,Z41,IF(AF42=1,Z42,"")))),"")</f>
@@ -4706,23 +4706,23 @@
       </c>
       <c r="Q39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,AA39,IF(AF40=1,AA40,IF(AF41=1,AA41,IF(AF42=1,AA42,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,AB39,IF(AF40=1,AB40,IF(AF41=1,AB41,IF(AF42=1,AB42,"")))),"")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,AC39,IF(AF40=1,AC40,IF(AF41=1,AC41,IF(AF42=1,AC42,"")))),"")</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,AD39,IF(AF40=1,AD40,IF(AF41=1,AD41,IF(AF42=1,AD42,"")))),"")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U39" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,AE39,IF(AF40=1,AE40,IF(AF41=1,AE41,IF(AF42=1,AE42,"")))),"")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W39" t="s">
         <v>88</v>
@@ -4733,35 +4733,35 @@
       </c>
       <c r="Y39">
         <f>((C39="Tyskland")*ISNUMBER(D39)*(D39&gt;F39))+((G39="Tyskland")*ISNUMBER(D39)*(F39&gt;D39))+((C40="Tyskland")*ISNUMBER(D40)*(D40&gt;F40))+((G40="Tyskland")*ISNUMBER(D40)*(F40&gt;D40))+((C41="Tyskland")*ISNUMBER(D41)*(D41&gt;F41))+((G41="Tyskland")*ISNUMBER(D41)*(F41&gt;D41))+((C42="Tyskland")*ISNUMBER(D42)*(D42&gt;F42))+((G42="Tyskland")*ISNUMBER(D42)*(F42&gt;D42))+((C43="Tyskland")*ISNUMBER(D43)*(D43&gt;F43))+((G43="Tyskland")*ISNUMBER(D43)*(F43&gt;D43))+((C44="Tyskland")*ISNUMBER(D44)*(D44&gt;F44))+((G44="Tyskland")*ISNUMBER(D44)*(F44&gt;D44))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z39">
         <f>((C39="Tyskland")*ISNUMBER(D39)*(D39=F39))+((G39="Tyskland")*ISNUMBER(D39)*(F39=D39))+((C40="Tyskland")*ISNUMBER(D40)*(D40=F40))+((G40="Tyskland")*ISNUMBER(D40)*(F40=D40))+((C41="Tyskland")*ISNUMBER(D41)*(D41=F41))+((G41="Tyskland")*ISNUMBER(D41)*(F41=D41))+((C42="Tyskland")*ISNUMBER(D42)*(D42=F42))+((G42="Tyskland")*ISNUMBER(D42)*(F42=D42))+((C43="Tyskland")*ISNUMBER(D43)*(D43=F43))+((G43="Tyskland")*ISNUMBER(D43)*(F43=D43))+((C44="Tyskland")*ISNUMBER(D44)*(D44=F44))+((G44="Tyskland")*ISNUMBER(D44)*(F44=D44))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39">
         <f>((C39="Tyskland")*ISNUMBER(D39)*(D39&lt;F39))+((G39="Tyskland")*ISNUMBER(D39)*(F39&lt;D39))+((C40="Tyskland")*ISNUMBER(D40)*(D40&lt;F40))+((G40="Tyskland")*ISNUMBER(D40)*(F40&lt;D40))+((C41="Tyskland")*ISNUMBER(D41)*(D41&lt;F41))+((G41="Tyskland")*ISNUMBER(D41)*(F41&lt;D41))+((C42="Tyskland")*ISNUMBER(D42)*(D42&lt;F42))+((G42="Tyskland")*ISNUMBER(D42)*(F42&lt;D42))+((C43="Tyskland")*ISNUMBER(D43)*(D43&lt;F43))+((G43="Tyskland")*ISNUMBER(D43)*(F43&lt;D43))+((C44="Tyskland")*ISNUMBER(D44)*(D44&lt;F44))+((G44="Tyskland")*ISNUMBER(D44)*(F44&lt;D44))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39">
         <f>IF((C39="Tyskland")*ISNUMBER(D39),D39,0)+IF((G39="Tyskland")*ISNUMBER(D39),F39,0)+IF((C40="Tyskland")*ISNUMBER(D40),D40,0)+IF((G40="Tyskland")*ISNUMBER(D40),F40,0)+IF((C41="Tyskland")*ISNUMBER(D41),D41,0)+IF((G41="Tyskland")*ISNUMBER(D41),F41,0)+IF((C42="Tyskland")*ISNUMBER(D42),D42,0)+IF((G42="Tyskland")*ISNUMBER(D42),F42,0)+IF((C43="Tyskland")*ISNUMBER(D43),D43,0)+IF((G43="Tyskland")*ISNUMBER(D43),F43,0)+IF((C44="Tyskland")*ISNUMBER(D44),D44,0)+IF((G44="Tyskland")*ISNUMBER(D44),F44,0)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC39">
         <f>IF((C39="Tyskland")*ISNUMBER(D39),F39,0)+IF((G39="Tyskland")*ISNUMBER(D39),D39,0)+IF((C40="Tyskland")*ISNUMBER(D40),F40,0)+IF((G40="Tyskland")*ISNUMBER(D40),D40,0)+IF((C41="Tyskland")*ISNUMBER(D41),F41,0)+IF((G41="Tyskland")*ISNUMBER(D41),D41,0)+IF((C42="Tyskland")*ISNUMBER(D42),F42,0)+IF((G42="Tyskland")*ISNUMBER(D42),D42,0)+IF((C43="Tyskland")*ISNUMBER(D43),F43,0)+IF((G43="Tyskland")*ISNUMBER(D43),D43,0)+IF((C44="Tyskland")*ISNUMBER(D44),F44,0)+IF((G44="Tyskland")*ISNUMBER(D44),D44,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD39">
         <f>AB39-AC39</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE39">
         <f>3*Y39+Z39</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AF39">
         <f>1+((AE40&gt;AE39)+(AE40=AE39)*(AD40&gt;AD39)+(AE40=AE39)*(AD40=AD39)*(AB40&gt;AB39)&gt;0)*1+((AE41&gt;AE39)+(AE41=AE39)*(AD41&gt;AD39)+(AE41=AE39)*(AD41=AD39)*(AB41&gt;AB39)&gt;0)*1+((AE42&gt;AE39)+(AE42=AE39)*(AD42&gt;AD39)+(AE42=AE39)*(AD42=AD39)*(AB42&gt;AB39)&gt;0)*1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4775,13 +4775,13 @@
         <v>92</v>
       </c>
       <c r="D40" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>93</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="M40" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,W39,IF(AF40=2,W40,IF(AF41=2,W41,IF(AF42=2,W42,"")))),"")</f>
-        <v>Tyskland</v>
+        <v>Elfenbenskysten</v>
       </c>
       <c r="N40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,X39,IF(AF40=2,X40,IF(AF41=2,X41,IF(AF42=2,X42,"")))),"")</f>
@@ -4808,11 +4808,11 @@
       </c>
       <c r="O40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,Y39,IF(AF40=2,Y40,IF(AF41=2,Y41,IF(AF42=2,Y42,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,Z39,IF(AF40=2,Z40,IF(AF41=2,Z41,IF(AF42=2,Z42,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,AA39,IF(AF40=2,AA40,IF(AF41=2,AA41,IF(AF42=2,AA42,"")))),"")</f>
@@ -4820,19 +4820,19 @@
       </c>
       <c r="R40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,AB39,IF(AF40=2,AB40,IF(AF41=2,AB41,IF(AF42=2,AB42,"")))),"")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,AC39,IF(AF40=2,AC40,IF(AF41=2,AC41,IF(AF42=2,AC42,"")))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,AD39,IF(AF40=2,AD40,IF(AF41=2,AD41,IF(AF42=2,AD42,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,AE39,IF(AF40=2,AE40,IF(AF41=2,AE41,IF(AF42=2,AE42,"")))),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W40" t="s">
         <v>89</v>
@@ -4847,27 +4847,27 @@
       </c>
       <c r="Z40">
         <f>((C39="Curaçao")*ISNUMBER(D39)*(D39=F39))+((G39="Curaçao")*ISNUMBER(D39)*(F39=D39))+((C40="Curaçao")*ISNUMBER(D40)*(D40=F40))+((G40="Curaçao")*ISNUMBER(D40)*(F40=D40))+((C41="Curaçao")*ISNUMBER(D41)*(D41=F41))+((G41="Curaçao")*ISNUMBER(D41)*(F41=D41))+((C42="Curaçao")*ISNUMBER(D42)*(D42=F42))+((G42="Curaçao")*ISNUMBER(D42)*(F42=D42))+((C43="Curaçao")*ISNUMBER(D43)*(D43=F43))+((G43="Curaçao")*ISNUMBER(D43)*(F43=D43))+((C44="Curaçao")*ISNUMBER(D44)*(D44=F44))+((G44="Curaçao")*ISNUMBER(D44)*(F44=D44))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA40">
         <f>((C39="Curaçao")*ISNUMBER(D39)*(D39&lt;F39))+((G39="Curaçao")*ISNUMBER(D39)*(F39&lt;D39))+((C40="Curaçao")*ISNUMBER(D40)*(D40&lt;F40))+((G40="Curaçao")*ISNUMBER(D40)*(F40&lt;D40))+((C41="Curaçao")*ISNUMBER(D41)*(D41&lt;F41))+((G41="Curaçao")*ISNUMBER(D41)*(F41&lt;D41))+((C42="Curaçao")*ISNUMBER(D42)*(D42&lt;F42))+((G42="Curaçao")*ISNUMBER(D42)*(F42&lt;D42))+((C43="Curaçao")*ISNUMBER(D43)*(D43&lt;F43))+((G43="Curaçao")*ISNUMBER(D43)*(F43&lt;D43))+((C44="Curaçao")*ISNUMBER(D44)*(D44&lt;F44))+((G44="Curaçao")*ISNUMBER(D44)*(F44&lt;D44))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB40">
         <f>IF((C39="Curaçao")*ISNUMBER(D39),D39,0)+IF((G39="Curaçao")*ISNUMBER(D39),F39,0)+IF((C40="Curaçao")*ISNUMBER(D40),D40,0)+IF((G40="Curaçao")*ISNUMBER(D40),F40,0)+IF((C41="Curaçao")*ISNUMBER(D41),D41,0)+IF((G41="Curaçao")*ISNUMBER(D41),F41,0)+IF((C42="Curaçao")*ISNUMBER(D42),D42,0)+IF((G42="Curaçao")*ISNUMBER(D42),F42,0)+IF((C43="Curaçao")*ISNUMBER(D43),D43,0)+IF((G43="Curaçao")*ISNUMBER(D43),F43,0)+IF((C44="Curaçao")*ISNUMBER(D44),D44,0)+IF((G44="Curaçao")*ISNUMBER(D44),F44,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC40">
         <f>IF((C39="Curaçao")*ISNUMBER(D39),F39,0)+IF((G39="Curaçao")*ISNUMBER(D39),D39,0)+IF((C40="Curaçao")*ISNUMBER(D40),F40,0)+IF((G40="Curaçao")*ISNUMBER(D40),D40,0)+IF((C41="Curaçao")*ISNUMBER(D41),F41,0)+IF((G41="Curaçao")*ISNUMBER(D41),D41,0)+IF((C42="Curaçao")*ISNUMBER(D42),F42,0)+IF((G42="Curaçao")*ISNUMBER(D42),D42,0)+IF((C43="Curaçao")*ISNUMBER(D43),F43,0)+IF((G43="Curaçao")*ISNUMBER(D43),D43,0)+IF((C44="Curaçao")*ISNUMBER(D44),F44,0)+IF((G44="Curaçao")*ISNUMBER(D44),D44,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD40">
         <f>AB40-AC40</f>
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="AE40">
         <f>3*Y40+Z40</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF40">
         <f>1+((AE39&gt;AE40)+(AE39=AE40)*(AD39&gt;AD40)+(AE39=AE40)*(AD39=AD40)*(AB39&gt;AB40)&gt;0)*1+((AE41&gt;AE40)+(AE41=AE40)*(AD41&gt;AD40)+(AE41=AE40)*(AD41=AD40)*(AB41&gt;AB40)&gt;0)*1+((AE42&gt;AE40)+(AE42=AE40)*(AD42&gt;AD40)+(AE42=AE40)*(AD42=AD40)*(AB42&gt;AB40)&gt;0)*1</f>
@@ -4885,13 +4885,13 @@
         <v>88</v>
       </c>
       <c r="D41" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>92</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="O41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,Y39,IF(AF40=3,Y40,IF(AF41=3,Y41,IF(AF42=3,Y42,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,Z39,IF(AF40=3,Z40,IF(AF41=3,Z41,IF(AF42=3,Z42,"")))),"")</f>
@@ -4926,23 +4926,23 @@
       </c>
       <c r="Q41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,AA39,IF(AF40=3,AA40,IF(AF41=3,AA41,IF(AF42=3,AA42,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,AB39,IF(AF40=3,AB40,IF(AF41=3,AB41,IF(AF42=3,AB42,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,AC39,IF(AF40=3,AC40,IF(AF41=3,AC41,IF(AF42=3,AC42,"")))),"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,AD39,IF(AF40=3,AD40,IF(AF41=3,AD41,IF(AF42=3,AD42,"")))),"")</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="U41" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,AE39,IF(AF40=3,AE40,IF(AF41=3,AE41,IF(AF42=3,AE42,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W41" t="s">
         <v>92</v>
@@ -4965,15 +4965,15 @@
       </c>
       <c r="AB41">
         <f>IF((C39="Elfenbenskysten")*ISNUMBER(D39),D39,0)+IF((G39="Elfenbenskysten")*ISNUMBER(D39),F39,0)+IF((C40="Elfenbenskysten")*ISNUMBER(D40),D40,0)+IF((G40="Elfenbenskysten")*ISNUMBER(D40),F40,0)+IF((C41="Elfenbenskysten")*ISNUMBER(D41),D41,0)+IF((G41="Elfenbenskysten")*ISNUMBER(D41),F41,0)+IF((C42="Elfenbenskysten")*ISNUMBER(D42),D42,0)+IF((G42="Elfenbenskysten")*ISNUMBER(D42),F42,0)+IF((C43="Elfenbenskysten")*ISNUMBER(D43),D43,0)+IF((G43="Elfenbenskysten")*ISNUMBER(D43),F43,0)+IF((C44="Elfenbenskysten")*ISNUMBER(D44),D44,0)+IF((G44="Elfenbenskysten")*ISNUMBER(D44),F44,0)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC41">
         <f>IF((C39="Elfenbenskysten")*ISNUMBER(D39),F39,0)+IF((G39="Elfenbenskysten")*ISNUMBER(D39),D39,0)+IF((C40="Elfenbenskysten")*ISNUMBER(D40),F40,0)+IF((G40="Elfenbenskysten")*ISNUMBER(D40),D40,0)+IF((C41="Elfenbenskysten")*ISNUMBER(D41),F41,0)+IF((G41="Elfenbenskysten")*ISNUMBER(D41),D41,0)+IF((C42="Elfenbenskysten")*ISNUMBER(D42),F42,0)+IF((G42="Elfenbenskysten")*ISNUMBER(D42),D42,0)+IF((C43="Elfenbenskysten")*ISNUMBER(D43),F43,0)+IF((G43="Elfenbenskysten")*ISNUMBER(D43),D43,0)+IF((C44="Elfenbenskysten")*ISNUMBER(D44),F44,0)+IF((G44="Elfenbenskysten")*ISNUMBER(D44),D44,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD41">
         <f>AB41-AC41</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE41">
         <f>3*Y41+Z41</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="AF41">
         <f>1+((AE39&gt;AE41)+(AE39=AE41)*(AD39&gt;AD41)+(AE39=AE41)*(AD39=AD41)*(AB39&gt;AB41)&gt;0)*1+((AE40&gt;AE41)+(AE40=AE41)*(AD40&gt;AD41)+(AE40=AE41)*(AD40=AD41)*(AB40&gt;AB41)&gt;0)*1+((AE42&gt;AE41)+(AE42=AE41)*(AD42&gt;AD41)+(AE42=AE41)*(AD42=AD41)*(AB42&gt;AB41)&gt;0)*1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5032,27 +5032,27 @@
       </c>
       <c r="P42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,Z39,IF(AF40=4,Z40,IF(AF41=4,Z41,IF(AF42=4,Z42,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,AA39,IF(AF40=4,AA40,IF(AF41=4,AA41,IF(AF42=4,AA42,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,AB39,IF(AF40=4,AB40,IF(AF41=4,AB41,IF(AF42=4,AB42,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,AC39,IF(AF40=4,AC40,IF(AF41=4,AC41,IF(AF42=4,AC42,"")))),"")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,AD39,IF(AF40=4,AD40,IF(AF41=4,AD41,IF(AF42=4,AD42,"")))),"")</f>
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="U42" s="3">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,AE39,IF(AF40=4,AE40,IF(AF41=4,AE41,IF(AF42=4,AE42,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W42" t="s">
         <v>93</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Y42">
         <f>((C39="Ecuador")*ISNUMBER(D39)*(D39&gt;F39))+((G39="Ecuador")*ISNUMBER(D39)*(F39&gt;D39))+((C40="Ecuador")*ISNUMBER(D40)*(D40&gt;F40))+((G40="Ecuador")*ISNUMBER(D40)*(F40&gt;D40))+((C41="Ecuador")*ISNUMBER(D41)*(D41&gt;F41))+((G41="Ecuador")*ISNUMBER(D41)*(F41&gt;D41))+((C42="Ecuador")*ISNUMBER(D42)*(D42&gt;F42))+((G42="Ecuador")*ISNUMBER(D42)*(F42&gt;D42))+((C43="Ecuador")*ISNUMBER(D43)*(D43&gt;F43))+((G43="Ecuador")*ISNUMBER(D43)*(F43&gt;D43))+((C44="Ecuador")*ISNUMBER(D44)*(D44&gt;F44))+((G44="Ecuador")*ISNUMBER(D44)*(F44&gt;D44))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42">
         <f>((C39="Ecuador")*ISNUMBER(D39)*(D39=F39))+((G39="Ecuador")*ISNUMBER(D39)*(F39=D39))+((C40="Ecuador")*ISNUMBER(D40)*(D40=F40))+((G40="Ecuador")*ISNUMBER(D40)*(F40=D40))+((C41="Ecuador")*ISNUMBER(D41)*(D41=F41))+((G41="Ecuador")*ISNUMBER(D41)*(F41=D41))+((C42="Ecuador")*ISNUMBER(D42)*(D42=F42))+((G42="Ecuador")*ISNUMBER(D42)*(F42=D42))+((C43="Ecuador")*ISNUMBER(D43)*(D43=F43))+((G43="Ecuador")*ISNUMBER(D43)*(F43=D43))+((C44="Ecuador")*ISNUMBER(D44)*(D44=F44))+((G44="Ecuador")*ISNUMBER(D44)*(F44=D44))</f>
@@ -5071,23 +5071,23 @@
       </c>
       <c r="AA42">
         <f>((C39="Ecuador")*ISNUMBER(D39)*(D39&lt;F39))+((G39="Ecuador")*ISNUMBER(D39)*(F39&lt;D39))+((C40="Ecuador")*ISNUMBER(D40)*(D40&lt;F40))+((G40="Ecuador")*ISNUMBER(D40)*(F40&lt;D40))+((C41="Ecuador")*ISNUMBER(D41)*(D41&lt;F41))+((G41="Ecuador")*ISNUMBER(D41)*(F41&lt;D41))+((C42="Ecuador")*ISNUMBER(D42)*(D42&lt;F42))+((G42="Ecuador")*ISNUMBER(D42)*(F42&lt;D42))+((C43="Ecuador")*ISNUMBER(D43)*(D43&lt;F43))+((G43="Ecuador")*ISNUMBER(D43)*(F43&lt;D43))+((C44="Ecuador")*ISNUMBER(D44)*(D44&lt;F44))+((G44="Ecuador")*ISNUMBER(D44)*(F44&lt;D44))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB42">
         <f>IF((C39="Ecuador")*ISNUMBER(D39),D39,0)+IF((G39="Ecuador")*ISNUMBER(D39),F39,0)+IF((C40="Ecuador")*ISNUMBER(D40),D40,0)+IF((G40="Ecuador")*ISNUMBER(D40),F40,0)+IF((C41="Ecuador")*ISNUMBER(D41),D41,0)+IF((G41="Ecuador")*ISNUMBER(D41),F41,0)+IF((C42="Ecuador")*ISNUMBER(D42),D42,0)+IF((G42="Ecuador")*ISNUMBER(D42),F42,0)+IF((C43="Ecuador")*ISNUMBER(D43),D43,0)+IF((G43="Ecuador")*ISNUMBER(D43),F43,0)+IF((C44="Ecuador")*ISNUMBER(D44),D44,0)+IF((G44="Ecuador")*ISNUMBER(D44),F44,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC42">
         <f>IF((C39="Ecuador")*ISNUMBER(D39),F39,0)+IF((G39="Ecuador")*ISNUMBER(D39),D39,0)+IF((C40="Ecuador")*ISNUMBER(D40),F40,0)+IF((G40="Ecuador")*ISNUMBER(D40),D40,0)+IF((C41="Ecuador")*ISNUMBER(D41),F41,0)+IF((G41="Ecuador")*ISNUMBER(D41),D41,0)+IF((C42="Ecuador")*ISNUMBER(D42),F42,0)+IF((G42="Ecuador")*ISNUMBER(D42),D42,0)+IF((C43="Ecuador")*ISNUMBER(D43),F43,0)+IF((G43="Ecuador")*ISNUMBER(D43),D43,0)+IF((C44="Ecuador")*ISNUMBER(D44),F44,0)+IF((G44="Ecuador")*ISNUMBER(D44),D44,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD42">
         <f>AB42-AC42</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="AE42">
         <f>3*Y42+Z42</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF42">
         <f>1+((AE39&gt;AE42)+(AE39=AE42)*(AD39&gt;AD42)+(AE39=AE42)*(AD39=AD42)*(AB39&gt;AB42)&gt;0)*1+((AE40&gt;AE42)+(AE40=AE42)*(AD40&gt;AD42)+(AE40=AE42)*(AD40=AD42)*(AB40&gt;AB42)&gt;0)*1+((AE41&gt;AE42)+(AE41=AE42)*(AD41&gt;AD42)+(AE41=AE42)*(AD41=AD42)*(AB41&gt;AB42)&gt;0)*1</f>
@@ -5105,7 +5105,7 @@
         <v>89</v>
       </c>
       <c r="D43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>29</v>
@@ -5140,13 +5140,13 @@
         <v>93</v>
       </c>
       <c r="D44" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>88</v>
@@ -5165,30 +5165,30 @@
       </c>
     </row>
     <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="57" t="s">
+      <c r="A45" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="M45" s="58" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="60"/>
+      <c r="M45" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="N45" s="58"/>
-      <c r="O45" s="58"/>
-      <c r="P45" s="58"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="58"/>
-      <c r="S45" s="58"/>
-      <c r="T45" s="58"/>
-      <c r="U45" s="58"/>
+      <c r="N45" s="61"/>
+      <c r="O45" s="61"/>
+      <c r="P45" s="61"/>
+      <c r="Q45" s="61"/>
+      <c r="R45" s="61"/>
+      <c r="S45" s="61"/>
+      <c r="T45" s="61"/>
+      <c r="U45" s="61"/>
     </row>
     <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -5267,7 +5267,7 @@
         <v>29</v>
       </c>
       <c r="F47" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>104</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="M47" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,W47,IF(AF48=1,W48,IF(AF49=1,W49,IF(AF50=1,W50,"")))),"")</f>
-        <v>Tunisia</v>
+        <v>Nederland</v>
       </c>
       <c r="N47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,X47,IF(AF48=1,X48,IF(AF49=1,X49,IF(AF50=1,X50,"")))),"")</f>
@@ -5294,11 +5294,11 @@
       </c>
       <c r="O47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,Y47,IF(AF48=1,Y48,IF(AF49=1,Y49,IF(AF50=1,Y50,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,Z47,IF(AF48=1,Z48,IF(AF49=1,Z49,IF(AF50=1,Z50,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,AA47,IF(AF48=1,AA48,IF(AF49=1,AA49,IF(AF50=1,AA50,"")))),"")</f>
@@ -5306,19 +5306,19 @@
       </c>
       <c r="R47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,AB47,IF(AF48=1,AB48,IF(AF49=1,AB49,IF(AF50=1,AB50,"")))),"")</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,AC47,IF(AF48=1,AC48,IF(AF49=1,AC49,IF(AF50=1,AC50,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,AD47,IF(AF48=1,AD48,IF(AF49=1,AD49,IF(AF50=1,AD50,"")))),"")</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U47" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,AE47,IF(AF48=1,AE48,IF(AF49=1,AE49,IF(AF50=1,AE50,"")))),"")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W47" t="s">
         <v>103</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Y47">
         <f>((C47="Nederland")*ISNUMBER(D47)*(D47&gt;F47))+((G47="Nederland")*ISNUMBER(D47)*(F47&gt;D47))+((C48="Nederland")*ISNUMBER(D48)*(D48&gt;F48))+((G48="Nederland")*ISNUMBER(D48)*(F48&gt;D48))+((C49="Nederland")*ISNUMBER(D49)*(D49&gt;F49))+((G49="Nederland")*ISNUMBER(D49)*(F49&gt;D49))+((C50="Nederland")*ISNUMBER(D50)*(D50&gt;F50))+((G50="Nederland")*ISNUMBER(D50)*(F50&gt;D50))+((C51="Nederland")*ISNUMBER(D51)*(D51&gt;F51))+((G51="Nederland")*ISNUMBER(D51)*(F51&gt;D51))+((C52="Nederland")*ISNUMBER(D52)*(D52&gt;F52))+((G52="Nederland")*ISNUMBER(D52)*(F52&gt;D52))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z47">
         <f>((C47="Nederland")*ISNUMBER(D47)*(D47=F47))+((G47="Nederland")*ISNUMBER(D47)*(F47=D47))+((C48="Nederland")*ISNUMBER(D48)*(D48=F48))+((G48="Nederland")*ISNUMBER(D48)*(F48=D48))+((C49="Nederland")*ISNUMBER(D49)*(D49=F49))+((G49="Nederland")*ISNUMBER(D49)*(F49=D49))+((C50="Nederland")*ISNUMBER(D50)*(D50=F50))+((G50="Nederland")*ISNUMBER(D50)*(F50=D50))+((C51="Nederland")*ISNUMBER(D51)*(D51=F51))+((G51="Nederland")*ISNUMBER(D51)*(F51=D51))+((C52="Nederland")*ISNUMBER(D52)*(D52=F52))+((G52="Nederland")*ISNUMBER(D52)*(F52=D52))</f>
@@ -5337,27 +5337,27 @@
       </c>
       <c r="AA47">
         <f>((C47="Nederland")*ISNUMBER(D47)*(D47&lt;F47))+((G47="Nederland")*ISNUMBER(D47)*(F47&lt;D47))+((C48="Nederland")*ISNUMBER(D48)*(D48&lt;F48))+((G48="Nederland")*ISNUMBER(D48)*(F48&lt;D48))+((C49="Nederland")*ISNUMBER(D49)*(D49&lt;F49))+((G49="Nederland")*ISNUMBER(D49)*(F49&lt;D49))+((C50="Nederland")*ISNUMBER(D50)*(D50&lt;F50))+((G50="Nederland")*ISNUMBER(D50)*(F50&lt;D50))+((C51="Nederland")*ISNUMBER(D51)*(D51&lt;F51))+((G51="Nederland")*ISNUMBER(D51)*(F51&lt;D51))+((C52="Nederland")*ISNUMBER(D52)*(D52&lt;F52))+((G52="Nederland")*ISNUMBER(D52)*(F52&lt;D52))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47">
         <f>IF((C47="Nederland")*ISNUMBER(D47),D47,0)+IF((G47="Nederland")*ISNUMBER(D47),F47,0)+IF((C48="Nederland")*ISNUMBER(D48),D48,0)+IF((G48="Nederland")*ISNUMBER(D48),F48,0)+IF((C49="Nederland")*ISNUMBER(D49),D49,0)+IF((G49="Nederland")*ISNUMBER(D49),F49,0)+IF((C50="Nederland")*ISNUMBER(D50),D50,0)+IF((G50="Nederland")*ISNUMBER(D50),F50,0)+IF((C51="Nederland")*ISNUMBER(D51),D51,0)+IF((G51="Nederland")*ISNUMBER(D51),F51,0)+IF((C52="Nederland")*ISNUMBER(D52),D52,0)+IF((G52="Nederland")*ISNUMBER(D52),F52,0)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC47">
         <f>IF((C47="Nederland")*ISNUMBER(D47),F47,0)+IF((G47="Nederland")*ISNUMBER(D47),D47,0)+IF((C48="Nederland")*ISNUMBER(D48),F48,0)+IF((G48="Nederland")*ISNUMBER(D48),D48,0)+IF((C49="Nederland")*ISNUMBER(D49),F49,0)+IF((G49="Nederland")*ISNUMBER(D49),D49,0)+IF((C50="Nederland")*ISNUMBER(D50),F50,0)+IF((G50="Nederland")*ISNUMBER(D50),D50,0)+IF((C51="Nederland")*ISNUMBER(D51),F51,0)+IF((G51="Nederland")*ISNUMBER(D51),D51,0)+IF((C52="Nederland")*ISNUMBER(D52),F52,0)+IF((G52="Nederland")*ISNUMBER(D52),D52,0)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD47">
         <f>AB47-AC47</f>
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="AE47">
         <f>3*Y47+Z47</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF47">
         <f>1+((AE48&gt;AE47)+(AE48=AE47)*(AD48&gt;AD47)+(AE48=AE47)*(AD48=AD47)*(AB48&gt;AB47)&gt;0)*1+((AE49&gt;AE47)+(AE49=AE47)*(AD49&gt;AD47)+(AE49=AE47)*(AD49=AD47)*(AB49&gt;AB47)&gt;0)*1+((AE50&gt;AE47)+(AE50=AE47)*(AD50&gt;AD47)+(AE50=AE47)*(AD50=AD47)*(AB50&gt;AB47)&gt;0)*1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M48" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,W47,IF(AF48=2,W48,IF(AF49=2,W49,IF(AF50=2,W50,"")))),"")</f>
-        <v>Japan</v>
+        <v>Sverige</v>
       </c>
       <c r="N48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,X47,IF(AF48=2,X48,IF(AF49=2,X49,IF(AF50=2,X50,"")))),"")</f>
@@ -5404,11 +5404,11 @@
       </c>
       <c r="O48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,Y47,IF(AF48=2,Y48,IF(AF49=2,Y49,IF(AF50=2,Y50,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,Z47,IF(AF48=2,Z48,IF(AF49=2,Z49,IF(AF50=2,Z50,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,AA47,IF(AF48=2,AA48,IF(AF49=2,AA49,IF(AF50=2,AA50,"")))),"")</f>
@@ -5416,19 +5416,19 @@
       </c>
       <c r="R48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,AB47,IF(AF48=2,AB48,IF(AF49=2,AB49,IF(AF50=2,AB50,"")))),"")</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,AC47,IF(AF48=2,AC48,IF(AF49=2,AC49,IF(AF50=2,AC50,"")))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,AD47,IF(AF48=2,AD48,IF(AF49=2,AD49,IF(AF50=2,AD50,"")))),"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U48" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,AE47,IF(AF48=2,AE48,IF(AF49=2,AE49,IF(AF50=2,AE50,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W48" t="s">
         <v>104</v>
@@ -5439,35 +5439,35 @@
       </c>
       <c r="Y48">
         <f>((C47="Japan")*ISNUMBER(D47)*(D47&gt;F47))+((G47="Japan")*ISNUMBER(D47)*(F47&gt;D47))+((C48="Japan")*ISNUMBER(D48)*(D48&gt;F48))+((G48="Japan")*ISNUMBER(D48)*(F48&gt;D48))+((C49="Japan")*ISNUMBER(D49)*(D49&gt;F49))+((G49="Japan")*ISNUMBER(D49)*(F49&gt;D49))+((C50="Japan")*ISNUMBER(D50)*(D50&gt;F50))+((G50="Japan")*ISNUMBER(D50)*(F50&gt;D50))+((C51="Japan")*ISNUMBER(D51)*(D51&gt;F51))+((G51="Japan")*ISNUMBER(D51)*(F51&gt;D51))+((C52="Japan")*ISNUMBER(D52)*(D52&gt;F52))+((G52="Japan")*ISNUMBER(D52)*(F52&gt;D52))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z48">
         <f>((C47="Japan")*ISNUMBER(D47)*(D47=F47))+((G47="Japan")*ISNUMBER(D47)*(F47=D47))+((C48="Japan")*ISNUMBER(D48)*(D48=F48))+((G48="Japan")*ISNUMBER(D48)*(F48=D48))+((C49="Japan")*ISNUMBER(D49)*(D49=F49))+((G49="Japan")*ISNUMBER(D49)*(F49=D49))+((C50="Japan")*ISNUMBER(D50)*(D50=F50))+((G50="Japan")*ISNUMBER(D50)*(F50=D50))+((C51="Japan")*ISNUMBER(D51)*(D51=F51))+((G51="Japan")*ISNUMBER(D51)*(F51=D51))+((C52="Japan")*ISNUMBER(D52)*(D52=F52))+((G52="Japan")*ISNUMBER(D52)*(F52=D52))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48">
         <f>((C47="Japan")*ISNUMBER(D47)*(D47&lt;F47))+((G47="Japan")*ISNUMBER(D47)*(F47&lt;D47))+((C48="Japan")*ISNUMBER(D48)*(D48&lt;F48))+((G48="Japan")*ISNUMBER(D48)*(F48&lt;D48))+((C49="Japan")*ISNUMBER(D49)*(D49&lt;F49))+((G49="Japan")*ISNUMBER(D49)*(F49&lt;D49))+((C50="Japan")*ISNUMBER(D50)*(D50&lt;F50))+((G50="Japan")*ISNUMBER(D50)*(F50&lt;D50))+((C51="Japan")*ISNUMBER(D51)*(D51&lt;F51))+((G51="Japan")*ISNUMBER(D51)*(F51&lt;D51))+((C52="Japan")*ISNUMBER(D52)*(D52&lt;F52))+((G52="Japan")*ISNUMBER(D52)*(F52&lt;D52))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB48">
         <f>IF((C47="Japan")*ISNUMBER(D47),D47,0)+IF((G47="Japan")*ISNUMBER(D47),F47,0)+IF((C48="Japan")*ISNUMBER(D48),D48,0)+IF((G48="Japan")*ISNUMBER(D48),F48,0)+IF((C49="Japan")*ISNUMBER(D49),D49,0)+IF((G49="Japan")*ISNUMBER(D49),F49,0)+IF((C50="Japan")*ISNUMBER(D50),D50,0)+IF((G50="Japan")*ISNUMBER(D50),F50,0)+IF((C51="Japan")*ISNUMBER(D51),D51,0)+IF((G51="Japan")*ISNUMBER(D51),F51,0)+IF((C52="Japan")*ISNUMBER(D52),D52,0)+IF((G52="Japan")*ISNUMBER(D52),F52,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC48">
         <f>IF((C47="Japan")*ISNUMBER(D47),F47,0)+IF((G47="Japan")*ISNUMBER(D47),D47,0)+IF((C48="Japan")*ISNUMBER(D48),F48,0)+IF((G48="Japan")*ISNUMBER(D48),D48,0)+IF((C49="Japan")*ISNUMBER(D49),F49,0)+IF((G49="Japan")*ISNUMBER(D49),D49,0)+IF((C50="Japan")*ISNUMBER(D50),F50,0)+IF((G50="Japan")*ISNUMBER(D50),D50,0)+IF((C51="Japan")*ISNUMBER(D51),F51,0)+IF((G51="Japan")*ISNUMBER(D51),D51,0)+IF((C52="Japan")*ISNUMBER(D52),F52,0)+IF((G52="Japan")*ISNUMBER(D52),D52,0)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD48">
         <f>AB48-AC48</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AE48">
         <f>3*Y48+Z48</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF48">
         <f>1+((AE47&gt;AE48)+(AE47=AE48)*(AD47&gt;AD48)+(AE47=AE48)*(AD47=AD48)*(AB47&gt;AB48)&gt;0)*1+((AE49&gt;AE48)+(AE49=AE48)*(AD49&gt;AD48)+(AE49=AE48)*(AD49=AD48)*(AB49&gt;AB48)&gt;0)*1+((AE50&gt;AE48)+(AE50=AE48)*(AD50&gt;AD48)+(AE50=AE48)*(AD50=AD48)*(AB50&gt;AB48)&gt;0)*1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5481,13 +5481,13 @@
         <v>103</v>
       </c>
       <c r="D49" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>106</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M49" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,W47,IF(AF48=3,W48,IF(AF49=3,W49,IF(AF50=3,W50,"")))),"")</f>
-        <v>Nederland</v>
+        <v>Tunisia</v>
       </c>
       <c r="N49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,X47,IF(AF48=3,X48,IF(AF49=3,X49,IF(AF50=3,X50,"")))),"")</f>
@@ -5514,31 +5514,31 @@
       </c>
       <c r="O49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,Y47,IF(AF48=3,Y48,IF(AF49=3,Y49,IF(AF50=3,Y50,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,Z47,IF(AF48=3,Z48,IF(AF49=3,Z49,IF(AF50=3,Z50,"")))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,AA47,IF(AF48=3,AA48,IF(AF49=3,AA49,IF(AF50=3,AA50,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,AB47,IF(AF48=3,AB48,IF(AF49=3,AB49,IF(AF50=3,AB50,"")))),"")</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,AC47,IF(AF48=3,AC48,IF(AF49=3,AC49,IF(AF50=3,AC50,"")))),"")</f>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,AD47,IF(AF48=3,AD48,IF(AF49=3,AD49,IF(AF50=3,AD50,"")))),"")</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="U49" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,AE47,IF(AF48=3,AE48,IF(AF49=3,AE49,IF(AF50=3,AE50,"")))),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W49" t="s">
         <v>106</v>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="Y49">
         <f>((C47="Sverige")*ISNUMBER(D47)*(D47&gt;F47))+((G47="Sverige")*ISNUMBER(D47)*(F47&gt;D47))+((C48="Sverige")*ISNUMBER(D48)*(D48&gt;F48))+((G48="Sverige")*ISNUMBER(D48)*(F48&gt;D48))+((C49="Sverige")*ISNUMBER(D49)*(D49&gt;F49))+((G49="Sverige")*ISNUMBER(D49)*(F49&gt;D49))+((C50="Sverige")*ISNUMBER(D50)*(D50&gt;F50))+((G50="Sverige")*ISNUMBER(D50)*(F50&gt;D50))+((C51="Sverige")*ISNUMBER(D51)*(D51&gt;F51))+((G51="Sverige")*ISNUMBER(D51)*(F51&gt;D51))+((C52="Sverige")*ISNUMBER(D52)*(D52&gt;F52))+((G52="Sverige")*ISNUMBER(D52)*(F52&gt;D52))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49">
         <f>((C47="Sverige")*ISNUMBER(D47)*(D47=F47))+((G47="Sverige")*ISNUMBER(D47)*(F47=D47))+((C48="Sverige")*ISNUMBER(D48)*(D48=F48))+((G48="Sverige")*ISNUMBER(D48)*(F48=D48))+((C49="Sverige")*ISNUMBER(D49)*(D49=F49))+((G49="Sverige")*ISNUMBER(D49)*(F49=D49))+((C50="Sverige")*ISNUMBER(D50)*(D50=F50))+((G50="Sverige")*ISNUMBER(D50)*(F50=D50))+((C51="Sverige")*ISNUMBER(D51)*(D51=F51))+((G51="Sverige")*ISNUMBER(D51)*(F51=D51))+((C52="Sverige")*ISNUMBER(D52)*(D52=F52))+((G52="Sverige")*ISNUMBER(D52)*(F52=D52))</f>
@@ -5557,27 +5557,27 @@
       </c>
       <c r="AA49">
         <f>((C47="Sverige")*ISNUMBER(D47)*(D47&lt;F47))+((G47="Sverige")*ISNUMBER(D47)*(F47&lt;D47))+((C48="Sverige")*ISNUMBER(D48)*(D48&lt;F48))+((G48="Sverige")*ISNUMBER(D48)*(F48&lt;D48))+((C49="Sverige")*ISNUMBER(D49)*(D49&lt;F49))+((G49="Sverige")*ISNUMBER(D49)*(F49&lt;D49))+((C50="Sverige")*ISNUMBER(D50)*(D50&lt;F50))+((G50="Sverige")*ISNUMBER(D50)*(F50&lt;D50))+((C51="Sverige")*ISNUMBER(D51)*(D51&lt;F51))+((G51="Sverige")*ISNUMBER(D51)*(F51&lt;D51))+((C52="Sverige")*ISNUMBER(D52)*(D52&lt;F52))+((G52="Sverige")*ISNUMBER(D52)*(F52&lt;D52))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB49">
         <f>IF((C47="Sverige")*ISNUMBER(D47),D47,0)+IF((G47="Sverige")*ISNUMBER(D47),F47,0)+IF((C48="Sverige")*ISNUMBER(D48),D48,0)+IF((G48="Sverige")*ISNUMBER(D48),F48,0)+IF((C49="Sverige")*ISNUMBER(D49),D49,0)+IF((G49="Sverige")*ISNUMBER(D49),F49,0)+IF((C50="Sverige")*ISNUMBER(D50),D50,0)+IF((G50="Sverige")*ISNUMBER(D50),F50,0)+IF((C51="Sverige")*ISNUMBER(D51),D51,0)+IF((G51="Sverige")*ISNUMBER(D51),F51,0)+IF((C52="Sverige")*ISNUMBER(D52),D52,0)+IF((G52="Sverige")*ISNUMBER(D52),F52,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC49">
         <f>IF((C47="Sverige")*ISNUMBER(D47),F47,0)+IF((G47="Sverige")*ISNUMBER(D47),D47,0)+IF((C48="Sverige")*ISNUMBER(D48),F48,0)+IF((G48="Sverige")*ISNUMBER(D48),D48,0)+IF((C49="Sverige")*ISNUMBER(D49),F49,0)+IF((G49="Sverige")*ISNUMBER(D49),D49,0)+IF((C50="Sverige")*ISNUMBER(D50),F50,0)+IF((G50="Sverige")*ISNUMBER(D50),D50,0)+IF((C51="Sverige")*ISNUMBER(D51),F51,0)+IF((G51="Sverige")*ISNUMBER(D51),D51,0)+IF((C52="Sverige")*ISNUMBER(D52),F52,0)+IF((G52="Sverige")*ISNUMBER(D52),D52,0)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD49">
         <f>AB49-AC49</f>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="AE49">
         <f>3*Y49+Z49</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF49">
         <f>1+((AE47&gt;AE49)+(AE47=AE49)*(AD47&gt;AD49)+(AE47=AE49)*(AD47=AD49)*(AB47&gt;AB49)&gt;0)*1+((AE48&gt;AE49)+(AE48=AE49)*(AD48&gt;AD49)+(AE48=AE49)*(AD48=AD49)*(AB48&gt;AB49)&gt;0)*1+((AE50&gt;AE49)+(AE50=AE49)*(AD50&gt;AD49)+(AE50=AE49)*(AD50=AD49)*(AB50&gt;AB49)&gt;0)*1</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5591,7 +5591,7 @@
         <v>107</v>
       </c>
       <c r="D50" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>29</v>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="M50" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,W47,IF(AF48=4,W48,IF(AF49=4,W49,IF(AF50=4,W50,"")))),"")</f>
-        <v>Sverige</v>
+        <v>Japan</v>
       </c>
       <c r="N50" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,X47,IF(AF48=4,X48,IF(AF49=4,X49,IF(AF50=4,X50,"")))),"")</f>
@@ -5636,15 +5636,15 @@
       </c>
       <c r="R50" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,AB47,IF(AF48=4,AB48,IF(AF49=4,AB49,IF(AF50=4,AB50,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S50" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,AC47,IF(AF48=4,AC48,IF(AF49=4,AC49,IF(AF50=4,AC50,"")))),"")</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T50" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,AD47,IF(AF48=4,AD48,IF(AF49=4,AD49,IF(AF50=4,AD50,"")))),"")</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="U50" s="3">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,AE47,IF(AF48=4,AE48,IF(AF49=4,AE49,IF(AF50=4,AE50,"")))),"")</f>
@@ -5659,35 +5659,35 @@
       </c>
       <c r="Y50">
         <f>((C47="Tunisia")*ISNUMBER(D47)*(D47&gt;F47))+((G47="Tunisia")*ISNUMBER(D47)*(F47&gt;D47))+((C48="Tunisia")*ISNUMBER(D48)*(D48&gt;F48))+((G48="Tunisia")*ISNUMBER(D48)*(F48&gt;D48))+((C49="Tunisia")*ISNUMBER(D49)*(D49&gt;F49))+((G49="Tunisia")*ISNUMBER(D49)*(F49&gt;D49))+((C50="Tunisia")*ISNUMBER(D50)*(D50&gt;F50))+((G50="Tunisia")*ISNUMBER(D50)*(F50&gt;D50))+((C51="Tunisia")*ISNUMBER(D51)*(D51&gt;F51))+((G51="Tunisia")*ISNUMBER(D51)*(F51&gt;D51))+((C52="Tunisia")*ISNUMBER(D52)*(D52&gt;F52))+((G52="Tunisia")*ISNUMBER(D52)*(F52&gt;D52))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z50">
         <f>((C47="Tunisia")*ISNUMBER(D47)*(D47=F47))+((G47="Tunisia")*ISNUMBER(D47)*(F47=D47))+((C48="Tunisia")*ISNUMBER(D48)*(D48=F48))+((G48="Tunisia")*ISNUMBER(D48)*(F48=D48))+((C49="Tunisia")*ISNUMBER(D49)*(D49=F49))+((G49="Tunisia")*ISNUMBER(D49)*(F49=D49))+((C50="Tunisia")*ISNUMBER(D50)*(D50=F50))+((G50="Tunisia")*ISNUMBER(D50)*(F50=D50))+((C51="Tunisia")*ISNUMBER(D51)*(D51=F51))+((G51="Tunisia")*ISNUMBER(D51)*(F51=D51))+((C52="Tunisia")*ISNUMBER(D52)*(D52=F52))+((G52="Tunisia")*ISNUMBER(D52)*(F52=D52))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA50">
         <f>((C47="Tunisia")*ISNUMBER(D47)*(D47&lt;F47))+((G47="Tunisia")*ISNUMBER(D47)*(F47&lt;D47))+((C48="Tunisia")*ISNUMBER(D48)*(D48&lt;F48))+((G48="Tunisia")*ISNUMBER(D48)*(F48&lt;D48))+((C49="Tunisia")*ISNUMBER(D49)*(D49&lt;F49))+((G49="Tunisia")*ISNUMBER(D49)*(F49&lt;D49))+((C50="Tunisia")*ISNUMBER(D50)*(D50&lt;F50))+((G50="Tunisia")*ISNUMBER(D50)*(F50&lt;D50))+((C51="Tunisia")*ISNUMBER(D51)*(D51&lt;F51))+((G51="Tunisia")*ISNUMBER(D51)*(F51&lt;D51))+((C52="Tunisia")*ISNUMBER(D52)*(D52&lt;F52))+((G52="Tunisia")*ISNUMBER(D52)*(F52&lt;D52))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50">
         <f>IF((C47="Tunisia")*ISNUMBER(D47),D47,0)+IF((G47="Tunisia")*ISNUMBER(D47),F47,0)+IF((C48="Tunisia")*ISNUMBER(D48),D48,0)+IF((G48="Tunisia")*ISNUMBER(D48),F48,0)+IF((C49="Tunisia")*ISNUMBER(D49),D49,0)+IF((G49="Tunisia")*ISNUMBER(D49),F49,0)+IF((C50="Tunisia")*ISNUMBER(D50),D50,0)+IF((G50="Tunisia")*ISNUMBER(D50),F50,0)+IF((C51="Tunisia")*ISNUMBER(D51),D51,0)+IF((G51="Tunisia")*ISNUMBER(D51),F51,0)+IF((C52="Tunisia")*ISNUMBER(D52),D52,0)+IF((G52="Tunisia")*ISNUMBER(D52),F52,0)</f>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AC50">
         <f>IF((C47="Tunisia")*ISNUMBER(D47),F47,0)+IF((G47="Tunisia")*ISNUMBER(D47),D47,0)+IF((C48="Tunisia")*ISNUMBER(D48),F48,0)+IF((G48="Tunisia")*ISNUMBER(D48),D48,0)+IF((C49="Tunisia")*ISNUMBER(D49),F49,0)+IF((G49="Tunisia")*ISNUMBER(D49),D49,0)+IF((C50="Tunisia")*ISNUMBER(D50),F50,0)+IF((G50="Tunisia")*ISNUMBER(D50),D50,0)+IF((C51="Tunisia")*ISNUMBER(D51),F51,0)+IF((G51="Tunisia")*ISNUMBER(D51),D51,0)+IF((C52="Tunisia")*ISNUMBER(D52),F52,0)+IF((G52="Tunisia")*ISNUMBER(D52),D52,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD50">
         <f>AB50-AC50</f>
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="AE50">
         <f>3*Y50+Z50</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AF50">
         <f>1+((AE47&gt;AE50)+(AE47=AE50)*(AD47&gt;AD50)+(AE47=AE50)*(AD47=AD50)*(AB47&gt;AB50)&gt;0)*1+((AE48&gt;AE50)+(AE48=AE50)*(AD48&gt;AD50)+(AE48=AE50)*(AD48=AD50)*(AB48&gt;AB50)&gt;0)*1+((AE49&gt;AE50)+(AE49=AE50)*(AD49&gt;AD50)+(AE49=AE50)*(AD49=AD50)*(AB49&gt;AB50)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5701,13 +5701,13 @@
         <v>107</v>
       </c>
       <c r="D51" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>103</v>
@@ -5736,13 +5736,13 @@
         <v>104</v>
       </c>
       <c r="D52" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>106</v>
@@ -5761,30 +5761,30 @@
       </c>
     </row>
     <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="57" t="s">
+      <c r="A53" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
-      <c r="M53" s="58" t="s">
+      <c r="B53" s="60"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="60"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="60"/>
+      <c r="I53" s="60"/>
+      <c r="J53" s="60"/>
+      <c r="K53" s="60"/>
+      <c r="M53" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="N53" s="58"/>
-      <c r="O53" s="58"/>
-      <c r="P53" s="58"/>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="58"/>
-      <c r="S53" s="58"/>
-      <c r="T53" s="58"/>
-      <c r="U53" s="58"/>
+      <c r="N53" s="61"/>
+      <c r="O53" s="61"/>
+      <c r="P53" s="61"/>
+      <c r="Q53" s="61"/>
+      <c r="R53" s="61"/>
+      <c r="S53" s="61"/>
+      <c r="T53" s="61"/>
+      <c r="U53" s="61"/>
     </row>
     <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
@@ -5857,7 +5857,7 @@
         <v>111</v>
       </c>
       <c r="D55" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="M55" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,W55,IF(AF56=1,W56,IF(AF57=1,W57,IF(AF58=1,W58,"")))),"")</f>
-        <v>New Zealand</v>
+        <v>Belgia</v>
       </c>
       <c r="N55" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,X55,IF(AF56=1,X56,IF(AF57=1,X57,IF(AF58=1,X58,"")))),"")</f>
@@ -5902,15 +5902,15 @@
       </c>
       <c r="R55" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,AB55,IF(AF56=1,AB56,IF(AF57=1,AB57,IF(AF58=1,AB58,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S55" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,AC55,IF(AF56=1,AC56,IF(AF57=1,AC57,IF(AF58=1,AC58,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T55" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,AD55,IF(AF56=1,AD56,IF(AF57=1,AD57,IF(AF58=1,AD58,"")))),"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U55" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,AE55,IF(AF56=1,AE56,IF(AF57=1,AE57,IF(AF58=1,AE58,"")))),"")</f>
@@ -5929,31 +5929,31 @@
       </c>
       <c r="Z55">
         <f>((C55="Belgia")*ISNUMBER(D55)*(D55=F55))+((G55="Belgia")*ISNUMBER(D55)*(F55=D55))+((C56="Belgia")*ISNUMBER(D56)*(D56=F56))+((G56="Belgia")*ISNUMBER(D56)*(F56=D56))+((C57="Belgia")*ISNUMBER(D57)*(D57=F57))+((G57="Belgia")*ISNUMBER(D57)*(F57=D57))+((C58="Belgia")*ISNUMBER(D58)*(D58=F58))+((G58="Belgia")*ISNUMBER(D58)*(F58=D58))+((C59="Belgia")*ISNUMBER(D59)*(D59=F59))+((G59="Belgia")*ISNUMBER(D59)*(F59=D59))+((C60="Belgia")*ISNUMBER(D60)*(D60=F60))+((G60="Belgia")*ISNUMBER(D60)*(F60=D60))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA55">
         <f>((C55="Belgia")*ISNUMBER(D55)*(D55&lt;F55))+((G55="Belgia")*ISNUMBER(D55)*(F55&lt;D55))+((C56="Belgia")*ISNUMBER(D56)*(D56&lt;F56))+((G56="Belgia")*ISNUMBER(D56)*(F56&lt;D56))+((C57="Belgia")*ISNUMBER(D57)*(D57&lt;F57))+((G57="Belgia")*ISNUMBER(D57)*(F57&lt;D57))+((C58="Belgia")*ISNUMBER(D58)*(D58&lt;F58))+((G58="Belgia")*ISNUMBER(D58)*(F58&lt;D58))+((C59="Belgia")*ISNUMBER(D59)*(D59&lt;F59))+((G59="Belgia")*ISNUMBER(D59)*(F59&lt;D59))+((C60="Belgia")*ISNUMBER(D60)*(D60&lt;F60))+((G60="Belgia")*ISNUMBER(D60)*(F60&lt;D60))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55">
         <f>IF((C55="Belgia")*ISNUMBER(D55),D55,0)+IF((G55="Belgia")*ISNUMBER(D55),F55,0)+IF((C56="Belgia")*ISNUMBER(D56),D56,0)+IF((G56="Belgia")*ISNUMBER(D56),F56,0)+IF((C57="Belgia")*ISNUMBER(D57),D57,0)+IF((G57="Belgia")*ISNUMBER(D57),F57,0)+IF((C58="Belgia")*ISNUMBER(D58),D58,0)+IF((G58="Belgia")*ISNUMBER(D58),F58,0)+IF((C59="Belgia")*ISNUMBER(D59),D59,0)+IF((G59="Belgia")*ISNUMBER(D59),F59,0)+IF((C60="Belgia")*ISNUMBER(D60),D60,0)+IF((G60="Belgia")*ISNUMBER(D60),F60,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC55">
         <f>IF((C55="Belgia")*ISNUMBER(D55),F55,0)+IF((G55="Belgia")*ISNUMBER(D55),D55,0)+IF((C56="Belgia")*ISNUMBER(D56),F56,0)+IF((G56="Belgia")*ISNUMBER(D56),D56,0)+IF((C57="Belgia")*ISNUMBER(D57),F57,0)+IF((G57="Belgia")*ISNUMBER(D57),D57,0)+IF((C58="Belgia")*ISNUMBER(D58),F58,0)+IF((G58="Belgia")*ISNUMBER(D58),D58,0)+IF((C59="Belgia")*ISNUMBER(D59),F59,0)+IF((G59="Belgia")*ISNUMBER(D59),D59,0)+IF((C60="Belgia")*ISNUMBER(D60),F60,0)+IF((G60="Belgia")*ISNUMBER(D60),D60,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD55">
         <f>AB55-AC55</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE55">
         <f>3*Y55+Z55</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF55">
         <f>1+((AE56&gt;AE55)+(AE56=AE55)*(AD56&gt;AD55)+(AE56=AE55)*(AD56=AD55)*(AB56&gt;AB55)&gt;0)*1+((AE57&gt;AE55)+(AE57=AE55)*(AD57&gt;AD55)+(AE57=AE55)*(AD57=AD55)*(AB57&gt;AB55)&gt;0)*1+((AE58&gt;AE55)+(AE58=AE55)*(AD58&gt;AD55)+(AE58=AE55)*(AD58=AD55)*(AB58&gt;AB55)&gt;0)*1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5967,7 +5967,7 @@
         <v>113</v>
       </c>
       <c r="D56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>29</v>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="M56" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,W55,IF(AF56=2,W56,IF(AF57=2,W57,IF(AF58=2,W58,"")))),"")</f>
-        <v>Belgia</v>
+        <v>Egypt</v>
       </c>
       <c r="N56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,X55,IF(AF56=2,X56,IF(AF57=2,X57,IF(AF58=2,X58,"")))),"")</f>
@@ -6004,11 +6004,11 @@
       </c>
       <c r="P56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,Z55,IF(AF56=2,Z56,IF(AF57=2,Z57,IF(AF58=2,Z58,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,AA55,IF(AF56=2,AA56,IF(AF57=2,AA57,IF(AF58=2,AA58,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,AB55,IF(AF56=2,AB56,IF(AF57=2,AB57,IF(AF58=2,AB58,"")))),"")</f>
@@ -6016,15 +6016,15 @@
       </c>
       <c r="S56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,AC55,IF(AF56=2,AC56,IF(AF57=2,AC57,IF(AF58=2,AC58,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,AD55,IF(AF56=2,AD56,IF(AF57=2,AD57,IF(AF58=2,AD58,"")))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U56" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,AE55,IF(AF56=2,AE56,IF(AF57=2,AE57,IF(AF58=2,AE58,"")))),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W56" t="s">
         <v>112</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="Y56">
         <f>((C55="Egypt")*ISNUMBER(D55)*(D55&gt;F55))+((G55="Egypt")*ISNUMBER(D55)*(F55&gt;D55))+((C56="Egypt")*ISNUMBER(D56)*(D56&gt;F56))+((G56="Egypt")*ISNUMBER(D56)*(F56&gt;D56))+((C57="Egypt")*ISNUMBER(D57)*(D57&gt;F57))+((G57="Egypt")*ISNUMBER(D57)*(F57&gt;D57))+((C58="Egypt")*ISNUMBER(D58)*(D58&gt;F58))+((G58="Egypt")*ISNUMBER(D58)*(F58&gt;D58))+((C59="Egypt")*ISNUMBER(D59)*(D59&gt;F59))+((G59="Egypt")*ISNUMBER(D59)*(F59&gt;D59))+((C60="Egypt")*ISNUMBER(D60)*(D60&gt;F60))+((G60="Egypt")*ISNUMBER(D60)*(F60&gt;D60))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z56">
         <f>((C55="Egypt")*ISNUMBER(D55)*(D55=F55))+((G55="Egypt")*ISNUMBER(D55)*(F55=D55))+((C56="Egypt")*ISNUMBER(D56)*(D56=F56))+((G56="Egypt")*ISNUMBER(D56)*(F56=D56))+((C57="Egypt")*ISNUMBER(D57)*(D57=F57))+((G57="Egypt")*ISNUMBER(D57)*(F57=D57))+((C58="Egypt")*ISNUMBER(D58)*(D58=F58))+((G58="Egypt")*ISNUMBER(D58)*(F58=D58))+((C59="Egypt")*ISNUMBER(D59)*(D59=F59))+((G59="Egypt")*ISNUMBER(D59)*(F59=D59))+((C60="Egypt")*ISNUMBER(D60)*(D60=F60))+((G60="Egypt")*ISNUMBER(D60)*(F60=D60))</f>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="AA56">
         <f>((C55="Egypt")*ISNUMBER(D55)*(D55&lt;F55))+((G55="Egypt")*ISNUMBER(D55)*(F55&lt;D55))+((C56="Egypt")*ISNUMBER(D56)*(D56&lt;F56))+((G56="Egypt")*ISNUMBER(D56)*(F56&lt;D56))+((C57="Egypt")*ISNUMBER(D57)*(D57&lt;F57))+((G57="Egypt")*ISNUMBER(D57)*(F57&lt;D57))+((C58="Egypt")*ISNUMBER(D58)*(D58&lt;F58))+((G58="Egypt")*ISNUMBER(D58)*(F58&lt;D58))+((C59="Egypt")*ISNUMBER(D59)*(D59&lt;F59))+((G59="Egypt")*ISNUMBER(D59)*(F59&lt;D59))+((C60="Egypt")*ISNUMBER(D60)*(D60&lt;F60))+((G60="Egypt")*ISNUMBER(D60)*(F60&lt;D60))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56">
         <f>IF((C55="Egypt")*ISNUMBER(D55),D55,0)+IF((G55="Egypt")*ISNUMBER(D55),F55,0)+IF((C56="Egypt")*ISNUMBER(D56),D56,0)+IF((G56="Egypt")*ISNUMBER(D56),F56,0)+IF((C57="Egypt")*ISNUMBER(D57),D57,0)+IF((G57="Egypt")*ISNUMBER(D57),F57,0)+IF((C58="Egypt")*ISNUMBER(D58),D58,0)+IF((G58="Egypt")*ISNUMBER(D58),F58,0)+IF((C59="Egypt")*ISNUMBER(D59),D59,0)+IF((G59="Egypt")*ISNUMBER(D59),F59,0)+IF((C60="Egypt")*ISNUMBER(D60),D60,0)+IF((G60="Egypt")*ISNUMBER(D60),F60,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC56">
         <f>IF((C55="Egypt")*ISNUMBER(D55),F55,0)+IF((G55="Egypt")*ISNUMBER(D55),D55,0)+IF((C56="Egypt")*ISNUMBER(D56),F56,0)+IF((G56="Egypt")*ISNUMBER(D56),D56,0)+IF((C57="Egypt")*ISNUMBER(D57),F57,0)+IF((G57="Egypt")*ISNUMBER(D57),D57,0)+IF((C58="Egypt")*ISNUMBER(D58),F58,0)+IF((G58="Egypt")*ISNUMBER(D58),D58,0)+IF((C59="Egypt")*ISNUMBER(D59),F59,0)+IF((G59="Egypt")*ISNUMBER(D59),D59,0)+IF((C60="Egypt")*ISNUMBER(D60),F60,0)+IF((G60="Egypt")*ISNUMBER(D60),D60,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD56">
         <f>AB56-AC56</f>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AE56">
         <f>3*Y56+Z56</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF56">
         <f>1+((AE55&gt;AE56)+(AE55=AE56)*(AD55&gt;AD56)+(AE55=AE56)*(AD55=AD56)*(AB55&gt;AB56)&gt;0)*1+((AE57&gt;AE56)+(AE57=AE56)*(AD57&gt;AD56)+(AE57=AE56)*(AD57=AD56)*(AB57&gt;AB56)&gt;0)*1+((AE58&gt;AE56)+(AE58=AE56)*(AD58&gt;AD56)+(AE58=AE56)*(AD58=AD56)*(AB58&gt;AB56)&gt;0)*1</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6077,13 +6077,13 @@
         <v>111</v>
       </c>
       <c r="D57" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>113</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="M57" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,W55,IF(AF56=3,W56,IF(AF57=3,W57,IF(AF58=3,W58,"")))),"")</f>
-        <v>Iran</v>
+        <v>New Zealand</v>
       </c>
       <c r="N57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,X55,IF(AF56=3,X56,IF(AF57=3,X57,IF(AF58=3,X58,"")))),"")</f>
@@ -6110,19 +6110,19 @@
       </c>
       <c r="O57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,Y55,IF(AF56=3,Y56,IF(AF57=3,Y57,IF(AF58=3,Y58,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,Z55,IF(AF56=3,Z56,IF(AF57=3,Z57,IF(AF58=3,Z58,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,AA55,IF(AF56=3,AA56,IF(AF57=3,AA57,IF(AF58=3,AA58,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,AB55,IF(AF56=3,AB56,IF(AF57=3,AB57,IF(AF58=3,AB58,"")))),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,AC55,IF(AF56=3,AC56,IF(AF57=3,AC57,IF(AF58=3,AC58,"")))),"")</f>
@@ -6130,11 +6130,11 @@
       </c>
       <c r="T57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,AD55,IF(AF56=3,AD56,IF(AF57=3,AD57,IF(AF58=3,AD58,"")))),"")</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U57" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,AE55,IF(AF56=3,AE56,IF(AF57=3,AE57,IF(AF58=3,AE58,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" t="s">
         <v>113</v>
@@ -6149,31 +6149,31 @@
       </c>
       <c r="Z57">
         <f>((C55="Iran")*ISNUMBER(D55)*(D55=F55))+((G55="Iran")*ISNUMBER(D55)*(F55=D55))+((C56="Iran")*ISNUMBER(D56)*(D56=F56))+((G56="Iran")*ISNUMBER(D56)*(F56=D56))+((C57="Iran")*ISNUMBER(D57)*(D57=F57))+((G57="Iran")*ISNUMBER(D57)*(F57=D57))+((C58="Iran")*ISNUMBER(D58)*(D58=F58))+((G58="Iran")*ISNUMBER(D58)*(F58=D58))+((C59="Iran")*ISNUMBER(D59)*(D59=F59))+((G59="Iran")*ISNUMBER(D59)*(F59=D59))+((C60="Iran")*ISNUMBER(D60)*(D60=F60))+((G60="Iran")*ISNUMBER(D60)*(F60=D60))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA57">
         <f>((C55="Iran")*ISNUMBER(D55)*(D55&lt;F55))+((G55="Iran")*ISNUMBER(D55)*(F55&lt;D55))+((C56="Iran")*ISNUMBER(D56)*(D56&lt;F56))+((G56="Iran")*ISNUMBER(D56)*(F56&lt;D56))+((C57="Iran")*ISNUMBER(D57)*(D57&lt;F57))+((G57="Iran")*ISNUMBER(D57)*(F57&lt;D57))+((C58="Iran")*ISNUMBER(D58)*(D58&lt;F58))+((G58="Iran")*ISNUMBER(D58)*(F58&lt;D58))+((C59="Iran")*ISNUMBER(D59)*(D59&lt;F59))+((G59="Iran")*ISNUMBER(D59)*(F59&lt;D59))+((C60="Iran")*ISNUMBER(D60)*(D60&lt;F60))+((G60="Iran")*ISNUMBER(D60)*(F60&lt;D60))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB57">
         <f>IF((C55="Iran")*ISNUMBER(D55),D55,0)+IF((G55="Iran")*ISNUMBER(D55),F55,0)+IF((C56="Iran")*ISNUMBER(D56),D56,0)+IF((G56="Iran")*ISNUMBER(D56),F56,0)+IF((C57="Iran")*ISNUMBER(D57),D57,0)+IF((G57="Iran")*ISNUMBER(D57),F57,0)+IF((C58="Iran")*ISNUMBER(D58),D58,0)+IF((G58="Iran")*ISNUMBER(D58),F58,0)+IF((C59="Iran")*ISNUMBER(D59),D59,0)+IF((G59="Iran")*ISNUMBER(D59),F59,0)+IF((C60="Iran")*ISNUMBER(D60),D60,0)+IF((G60="Iran")*ISNUMBER(D60),F60,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC57">
         <f>IF((C55="Iran")*ISNUMBER(D55),F55,0)+IF((G55="Iran")*ISNUMBER(D55),D55,0)+IF((C56="Iran")*ISNUMBER(D56),F56,0)+IF((G56="Iran")*ISNUMBER(D56),D56,0)+IF((C57="Iran")*ISNUMBER(D57),F57,0)+IF((G57="Iran")*ISNUMBER(D57),D57,0)+IF((C58="Iran")*ISNUMBER(D58),F58,0)+IF((G58="Iran")*ISNUMBER(D58),D58,0)+IF((C59="Iran")*ISNUMBER(D59),F59,0)+IF((G59="Iran")*ISNUMBER(D59),D59,0)+IF((C60="Iran")*ISNUMBER(D60),F60,0)+IF((G60="Iran")*ISNUMBER(D60),D60,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD57">
         <f>AB57-AC57</f>
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="AE57">
         <f>3*Y57+Z57</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF57">
         <f>1+((AE55&gt;AE57)+(AE55=AE57)*(AD55&gt;AD57)+(AE55=AE57)*(AD55=AD57)*(AB55&gt;AB57)&gt;0)*1+((AE56&gt;AE57)+(AE56=AE57)*(AD56&gt;AD57)+(AE56=AE57)*(AD56=AD57)*(AB56&gt;AB57)&gt;0)*1+((AE58&gt;AE57)+(AE58=AE57)*(AD58&gt;AD57)+(AE58=AE57)*(AD58=AD57)*(AB58&gt;AB57)&gt;0)*1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>114</v>
       </c>
       <c r="D58" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>29</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="M58" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,W55,IF(AF56=4,W56,IF(AF57=4,W57,IF(AF58=4,W58,"")))),"")</f>
-        <v>Egypt</v>
+        <v>Iran</v>
       </c>
       <c r="N58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,X55,IF(AF56=4,X56,IF(AF57=4,X57,IF(AF58=4,X58,"")))),"")</f>
@@ -6224,15 +6224,15 @@
       </c>
       <c r="P58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,Z55,IF(AF56=4,Z56,IF(AF57=4,Z57,IF(AF58=4,Z58,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,AA55,IF(AF56=4,AA56,IF(AF57=4,AA57,IF(AF58=4,AA58,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,AB55,IF(AF56=4,AB56,IF(AF57=4,AB57,IF(AF58=4,AB58,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,AC55,IF(AF56=4,AC56,IF(AF57=4,AC57,IF(AF58=4,AC58,"")))),"")</f>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="T58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,AD55,IF(AF56=4,AD56,IF(AF57=4,AD57,IF(AF58=4,AD58,"")))),"")</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="U58" s="3">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,AE55,IF(AF56=4,AE56,IF(AF57=4,AE57,IF(AF58=4,AE58,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" t="s">
         <v>114</v>
@@ -6255,35 +6255,35 @@
       </c>
       <c r="Y58">
         <f>((C55="New Zealand")*ISNUMBER(D55)*(D55&gt;F55))+((G55="New Zealand")*ISNUMBER(D55)*(F55&gt;D55))+((C56="New Zealand")*ISNUMBER(D56)*(D56&gt;F56))+((G56="New Zealand")*ISNUMBER(D56)*(F56&gt;D56))+((C57="New Zealand")*ISNUMBER(D57)*(D57&gt;F57))+((G57="New Zealand")*ISNUMBER(D57)*(F57&gt;D57))+((C58="New Zealand")*ISNUMBER(D58)*(D58&gt;F58))+((G58="New Zealand")*ISNUMBER(D58)*(F58&gt;D58))+((C59="New Zealand")*ISNUMBER(D59)*(D59&gt;F59))+((G59="New Zealand")*ISNUMBER(D59)*(F59&gt;D59))+((C60="New Zealand")*ISNUMBER(D60)*(D60&gt;F60))+((G60="New Zealand")*ISNUMBER(D60)*(F60&gt;D60))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z58">
         <f>((C55="New Zealand")*ISNUMBER(D55)*(D55=F55))+((G55="New Zealand")*ISNUMBER(D55)*(F55=D55))+((C56="New Zealand")*ISNUMBER(D56)*(D56=F56))+((G56="New Zealand")*ISNUMBER(D56)*(F56=D56))+((C57="New Zealand")*ISNUMBER(D57)*(D57=F57))+((G57="New Zealand")*ISNUMBER(D57)*(F57=D57))+((C58="New Zealand")*ISNUMBER(D58)*(D58=F58))+((G58="New Zealand")*ISNUMBER(D58)*(F58=D58))+((C59="New Zealand")*ISNUMBER(D59)*(D59=F59))+((G59="New Zealand")*ISNUMBER(D59)*(F59=D59))+((C60="New Zealand")*ISNUMBER(D60)*(D60=F60))+((G60="New Zealand")*ISNUMBER(D60)*(F60=D60))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58">
         <f>((C55="New Zealand")*ISNUMBER(D55)*(D55&lt;F55))+((G55="New Zealand")*ISNUMBER(D55)*(F55&lt;D55))+((C56="New Zealand")*ISNUMBER(D56)*(D56&lt;F56))+((G56="New Zealand")*ISNUMBER(D56)*(F56&lt;D56))+((C57="New Zealand")*ISNUMBER(D57)*(D57&lt;F57))+((G57="New Zealand")*ISNUMBER(D57)*(F57&lt;D57))+((C58="New Zealand")*ISNUMBER(D58)*(D58&lt;F58))+((G58="New Zealand")*ISNUMBER(D58)*(F58&lt;D58))+((C59="New Zealand")*ISNUMBER(D59)*(D59&lt;F59))+((G59="New Zealand")*ISNUMBER(D59)*(F59&lt;D59))+((C60="New Zealand")*ISNUMBER(D60)*(D60&lt;F60))+((G60="New Zealand")*ISNUMBER(D60)*(F60&lt;D60))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58">
         <f>IF((C55="New Zealand")*ISNUMBER(D55),D55,0)+IF((G55="New Zealand")*ISNUMBER(D55),F55,0)+IF((C56="New Zealand")*ISNUMBER(D56),D56,0)+IF((G56="New Zealand")*ISNUMBER(D56),F56,0)+IF((C57="New Zealand")*ISNUMBER(D57),D57,0)+IF((G57="New Zealand")*ISNUMBER(D57),F57,0)+IF((C58="New Zealand")*ISNUMBER(D58),D58,0)+IF((G58="New Zealand")*ISNUMBER(D58),F58,0)+IF((C59="New Zealand")*ISNUMBER(D59),D59,0)+IF((G59="New Zealand")*ISNUMBER(D59),F59,0)+IF((C60="New Zealand")*ISNUMBER(D60),D60,0)+IF((G60="New Zealand")*ISNUMBER(D60),F60,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC58">
         <f>IF((C55="New Zealand")*ISNUMBER(D55),F55,0)+IF((G55="New Zealand")*ISNUMBER(D55),D55,0)+IF((C56="New Zealand")*ISNUMBER(D56),F56,0)+IF((G56="New Zealand")*ISNUMBER(D56),D56,0)+IF((C57="New Zealand")*ISNUMBER(D57),F57,0)+IF((G57="New Zealand")*ISNUMBER(D57),D57,0)+IF((C58="New Zealand")*ISNUMBER(D58),F58,0)+IF((G58="New Zealand")*ISNUMBER(D58),D58,0)+IF((C59="New Zealand")*ISNUMBER(D59),F59,0)+IF((G59="New Zealand")*ISNUMBER(D59),D59,0)+IF((C60="New Zealand")*ISNUMBER(D60),F60,0)+IF((G60="New Zealand")*ISNUMBER(D60),D60,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD58">
         <f>AB58-AC58</f>
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="AE58">
         <f>3*Y58+Z58</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AF58">
         <f>1+((AE55&gt;AE58)+(AE55=AE58)*(AD55&gt;AD58)+(AE55=AE58)*(AD55=AD58)*(AB55&gt;AB58)&gt;0)*1+((AE56&gt;AE58)+(AE56=AE58)*(AD56&gt;AD58)+(AE56=AE58)*(AD56=AD58)*(AB56&gt;AB58)&gt;0)*1+((AE57&gt;AE58)+(AE57=AE58)*(AD57&gt;AD58)+(AE57=AE58)*(AD57=AD58)*(AB57&gt;AB58)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6297,13 +6297,13 @@
         <v>112</v>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>113</v>
@@ -6332,13 +6332,13 @@
         <v>114</v>
       </c>
       <c r="D60" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>111</v>
@@ -6357,30 +6357,30 @@
       </c>
     </row>
     <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="57" t="s">
+      <c r="A61" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57"/>
-      <c r="K61" s="57"/>
-      <c r="M61" s="58" t="s">
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
+      <c r="J61" s="60"/>
+      <c r="K61" s="60"/>
+      <c r="M61" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="N61" s="58"/>
-      <c r="O61" s="58"/>
-      <c r="P61" s="58"/>
-      <c r="Q61" s="58"/>
-      <c r="R61" s="58"/>
-      <c r="S61" s="58"/>
-      <c r="T61" s="58"/>
-      <c r="U61" s="58"/>
+      <c r="N61" s="61"/>
+      <c r="O61" s="61"/>
+      <c r="P61" s="61"/>
+      <c r="Q61" s="61"/>
+      <c r="R61" s="61"/>
+      <c r="S61" s="61"/>
+      <c r="T61" s="61"/>
+      <c r="U61" s="61"/>
     </row>
     <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -6453,7 +6453,7 @@
         <v>122</v>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="M63" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,W63,IF(AF64=1,W64,IF(AF65=1,W65,IF(AF66=1,W66,"")))),"")</f>
-        <v>Saudi Arabia</v>
+        <v>Spania</v>
       </c>
       <c r="N63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,X63,IF(AF64=1,X64,IF(AF65=1,X65,IF(AF66=1,X66,"")))),"")</f>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="O63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,Y63,IF(AF64=1,Y64,IF(AF65=1,Y65,IF(AF66=1,Y66,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,Z63,IF(AF64=1,Z64,IF(AF65=1,Z65,IF(AF66=1,Z66,"")))),"")</f>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Q63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,AA63,IF(AF64=1,AA64,IF(AF65=1,AA65,IF(AF66=1,AA66,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,AB63,IF(AF64=1,AB64,IF(AF65=1,AB65,IF(AF66=1,AB66,"")))),"")</f>
@@ -6502,15 +6502,15 @@
       </c>
       <c r="S63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,AC63,IF(AF64=1,AC64,IF(AF65=1,AC65,IF(AF66=1,AC66,"")))),"")</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,AD63,IF(AF64=1,AD64,IF(AF65=1,AD65,IF(AF66=1,AD66,"")))),"")</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U63" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,AE63,IF(AF64=1,AE64,IF(AF65=1,AE65,IF(AF66=1,AE66,"")))),"")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W63" t="s">
         <v>122</v>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Y63">
         <f>((C63="Spania")*ISNUMBER(D63)*(D63&gt;F63))+((G63="Spania")*ISNUMBER(D63)*(F63&gt;D63))+((C64="Spania")*ISNUMBER(D64)*(D64&gt;F64))+((G64="Spania")*ISNUMBER(D64)*(F64&gt;D64))+((C65="Spania")*ISNUMBER(D65)*(D65&gt;F65))+((G65="Spania")*ISNUMBER(D65)*(F65&gt;D65))+((C66="Spania")*ISNUMBER(D66)*(D66&gt;F66))+((G66="Spania")*ISNUMBER(D66)*(F66&gt;D66))+((C67="Spania")*ISNUMBER(D67)*(D67&gt;F67))+((G67="Spania")*ISNUMBER(D67)*(F67&gt;D67))+((C68="Spania")*ISNUMBER(D68)*(D68&gt;F68))+((G68="Spania")*ISNUMBER(D68)*(F68&gt;D68))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z63">
         <f>((C63="Spania")*ISNUMBER(D63)*(D63=F63))+((G63="Spania")*ISNUMBER(D63)*(F63=D63))+((C64="Spania")*ISNUMBER(D64)*(D64=F64))+((G64="Spania")*ISNUMBER(D64)*(F64=D64))+((C65="Spania")*ISNUMBER(D65)*(D65=F65))+((G65="Spania")*ISNUMBER(D65)*(F65=D65))+((C66="Spania")*ISNUMBER(D66)*(D66=F66))+((G66="Spania")*ISNUMBER(D66)*(F66=D66))+((C67="Spania")*ISNUMBER(D67)*(D67=F67))+((G67="Spania")*ISNUMBER(D67)*(F67=D67))+((C68="Spania")*ISNUMBER(D68)*(D68=F68))+((G68="Spania")*ISNUMBER(D68)*(F68=D68))</f>
@@ -6529,27 +6529,27 @@
       </c>
       <c r="AA63">
         <f>((C63="Spania")*ISNUMBER(D63)*(D63&lt;F63))+((G63="Spania")*ISNUMBER(D63)*(F63&lt;D63))+((C64="Spania")*ISNUMBER(D64)*(D64&lt;F64))+((G64="Spania")*ISNUMBER(D64)*(F64&lt;D64))+((C65="Spania")*ISNUMBER(D65)*(D65&lt;F65))+((G65="Spania")*ISNUMBER(D65)*(F65&lt;D65))+((C66="Spania")*ISNUMBER(D66)*(D66&lt;F66))+((G66="Spania")*ISNUMBER(D66)*(F66&lt;D66))+((C67="Spania")*ISNUMBER(D67)*(D67&lt;F67))+((G67="Spania")*ISNUMBER(D67)*(F67&lt;D67))+((C68="Spania")*ISNUMBER(D68)*(D68&lt;F68))+((G68="Spania")*ISNUMBER(D68)*(F68&lt;D68))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB63">
         <f>IF((C63="Spania")*ISNUMBER(D63),D63,0)+IF((G63="Spania")*ISNUMBER(D63),F63,0)+IF((C64="Spania")*ISNUMBER(D64),D64,0)+IF((G64="Spania")*ISNUMBER(D64),F64,0)+IF((C65="Spania")*ISNUMBER(D65),D65,0)+IF((G65="Spania")*ISNUMBER(D65),F65,0)+IF((C66="Spania")*ISNUMBER(D66),D66,0)+IF((G66="Spania")*ISNUMBER(D66),F66,0)+IF((C67="Spania")*ISNUMBER(D67),D67,0)+IF((G67="Spania")*ISNUMBER(D67),F67,0)+IF((C68="Spania")*ISNUMBER(D68),D68,0)+IF((G68="Spania")*ISNUMBER(D68),F68,0)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AC63">
         <f>IF((C63="Spania")*ISNUMBER(D63),F63,0)+IF((G63="Spania")*ISNUMBER(D63),D63,0)+IF((C64="Spania")*ISNUMBER(D64),F64,0)+IF((G64="Spania")*ISNUMBER(D64),D64,0)+IF((C65="Spania")*ISNUMBER(D65),F65,0)+IF((G65="Spania")*ISNUMBER(D65),D65,0)+IF((C66="Spania")*ISNUMBER(D66),F66,0)+IF((G66="Spania")*ISNUMBER(D66),D66,0)+IF((C67="Spania")*ISNUMBER(D67),F67,0)+IF((G67="Spania")*ISNUMBER(D67),D67,0)+IF((C68="Spania")*ISNUMBER(D68),F68,0)+IF((G68="Spania")*ISNUMBER(D68),D68,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD63">
         <f>AB63-AC63</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE63">
         <f>3*Y63+Z63</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF63">
         <f>1+((AE64&gt;AE63)+(AE64=AE63)*(AD64&gt;AD63)+(AE64=AE63)*(AD64=AD63)*(AB64&gt;AB63)&gt;0)*1+((AE65&gt;AE63)+(AE65=AE63)*(AD65&gt;AD63)+(AE65=AE63)*(AD65=AD63)*(AB65&gt;AB63)&gt;0)*1+((AE66&gt;AE63)+(AE66=AE63)*(AD66&gt;AD63)+(AE66=AE63)*(AD66=AD63)*(AB66&gt;AB63)&gt;0)*1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6563,7 +6563,7 @@
         <v>124</v>
       </c>
       <c r="D64" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>29</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="M64" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,W63,IF(AF64=2,W64,IF(AF65=2,W65,IF(AF66=2,W66,"")))),"")</f>
-        <v>Kapp Verde</v>
+        <v>Uruguay</v>
       </c>
       <c r="N64" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,X63,IF(AF64=2,X64,IF(AF65=2,X65,IF(AF66=2,X66,"")))),"")</f>
@@ -6608,15 +6608,15 @@
       </c>
       <c r="R64" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,AB63,IF(AF64=2,AB64,IF(AF65=2,AB65,IF(AF66=2,AB66,"")))),"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S64" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,AC63,IF(AF64=2,AC64,IF(AF65=2,AC65,IF(AF66=2,AC66,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T64" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,AD63,IF(AF64=2,AD64,IF(AF65=2,AD65,IF(AF66=2,AD66,"")))),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U64" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,AE63,IF(AF64=2,AE64,IF(AF65=2,AE65,IF(AF66=2,AE66,"")))),"")</f>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="Y64">
         <f>((C63="Kapp Verde")*ISNUMBER(D63)*(D63&gt;F63))+((G63="Kapp Verde")*ISNUMBER(D63)*(F63&gt;D63))+((C64="Kapp Verde")*ISNUMBER(D64)*(D64&gt;F64))+((G64="Kapp Verde")*ISNUMBER(D64)*(F64&gt;D64))+((C65="Kapp Verde")*ISNUMBER(D65)*(D65&gt;F65))+((G65="Kapp Verde")*ISNUMBER(D65)*(F65&gt;D65))+((C66="Kapp Verde")*ISNUMBER(D66)*(D66&gt;F66))+((G66="Kapp Verde")*ISNUMBER(D66)*(F66&gt;D66))+((C67="Kapp Verde")*ISNUMBER(D67)*(D67&gt;F67))+((G67="Kapp Verde")*ISNUMBER(D67)*(F67&gt;D67))+((C68="Kapp Verde")*ISNUMBER(D68)*(D68&gt;F68))+((G68="Kapp Verde")*ISNUMBER(D68)*(F68&gt;D68))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z64">
         <f>((C63="Kapp Verde")*ISNUMBER(D63)*(D63=F63))+((G63="Kapp Verde")*ISNUMBER(D63)*(F63=D63))+((C64="Kapp Verde")*ISNUMBER(D64)*(D64=F64))+((G64="Kapp Verde")*ISNUMBER(D64)*(F64=D64))+((C65="Kapp Verde")*ISNUMBER(D65)*(D65=F65))+((G65="Kapp Verde")*ISNUMBER(D65)*(F65=D65))+((C66="Kapp Verde")*ISNUMBER(D66)*(D66=F66))+((G66="Kapp Verde")*ISNUMBER(D66)*(F66=D66))+((C67="Kapp Verde")*ISNUMBER(D67)*(D67=F67))+((G67="Kapp Verde")*ISNUMBER(D67)*(F67=D67))+((C68="Kapp Verde")*ISNUMBER(D68)*(D68=F68))+((G68="Kapp Verde")*ISNUMBER(D68)*(F68=D68))</f>
@@ -6639,27 +6639,27 @@
       </c>
       <c r="AA64">
         <f>((C63="Kapp Verde")*ISNUMBER(D63)*(D63&lt;F63))+((G63="Kapp Verde")*ISNUMBER(D63)*(F63&lt;D63))+((C64="Kapp Verde")*ISNUMBER(D64)*(D64&lt;F64))+((G64="Kapp Verde")*ISNUMBER(D64)*(F64&lt;D64))+((C65="Kapp Verde")*ISNUMBER(D65)*(D65&lt;F65))+((G65="Kapp Verde")*ISNUMBER(D65)*(F65&lt;D65))+((C66="Kapp Verde")*ISNUMBER(D66)*(D66&lt;F66))+((G66="Kapp Verde")*ISNUMBER(D66)*(F66&lt;D66))+((C67="Kapp Verde")*ISNUMBER(D67)*(D67&lt;F67))+((G67="Kapp Verde")*ISNUMBER(D67)*(F67&lt;D67))+((C68="Kapp Verde")*ISNUMBER(D68)*(D68&lt;F68))+((G68="Kapp Verde")*ISNUMBER(D68)*(F68&lt;D68))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB64">
         <f>IF((C63="Kapp Verde")*ISNUMBER(D63),D63,0)+IF((G63="Kapp Verde")*ISNUMBER(D63),F63,0)+IF((C64="Kapp Verde")*ISNUMBER(D64),D64,0)+IF((G64="Kapp Verde")*ISNUMBER(D64),F64,0)+IF((C65="Kapp Verde")*ISNUMBER(D65),D65,0)+IF((G65="Kapp Verde")*ISNUMBER(D65),F65,0)+IF((C66="Kapp Verde")*ISNUMBER(D66),D66,0)+IF((G66="Kapp Verde")*ISNUMBER(D66),F66,0)+IF((C67="Kapp Verde")*ISNUMBER(D67),D67,0)+IF((G67="Kapp Verde")*ISNUMBER(D67),F67,0)+IF((C68="Kapp Verde")*ISNUMBER(D68),D68,0)+IF((G68="Kapp Verde")*ISNUMBER(D68),F68,0)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <f>IF((C63="Kapp Verde")*ISNUMBER(D63),F63,0)+IF((G63="Kapp Verde")*ISNUMBER(D63),D63,0)+IF((C64="Kapp Verde")*ISNUMBER(D64),F64,0)+IF((G64="Kapp Verde")*ISNUMBER(D64),D64,0)+IF((C65="Kapp Verde")*ISNUMBER(D65),F65,0)+IF((G65="Kapp Verde")*ISNUMBER(D65),D65,0)+IF((C66="Kapp Verde")*ISNUMBER(D66),F66,0)+IF((G66="Kapp Verde")*ISNUMBER(D66),D66,0)+IF((C67="Kapp Verde")*ISNUMBER(D67),F67,0)+IF((G67="Kapp Verde")*ISNUMBER(D67),D67,0)+IF((C68="Kapp Verde")*ISNUMBER(D68),F68,0)+IF((G68="Kapp Verde")*ISNUMBER(D68),D68,0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AD64">
         <f>AB64-AC64</f>
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="AE64">
         <f>3*Y64+Z64</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF64">
         <f>1+((AE63&gt;AE64)+(AE63=AE64)*(AD63&gt;AD64)+(AE63=AE64)*(AD63=AD64)*(AB63&gt;AB64)&gt;0)*1+((AE65&gt;AE64)+(AE65=AE64)*(AD65&gt;AD64)+(AE65=AE64)*(AD65=AD64)*(AB65&gt;AB64)&gt;0)*1+((AE66&gt;AE64)+(AE66=AE64)*(AD66&gt;AD64)+(AE66=AE64)*(AD66=AD64)*(AB66&gt;AB64)&gt;0)*1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6673,13 +6673,13 @@
         <v>122</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>124</v>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M65" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,W63,IF(AF64=3,W64,IF(AF65=3,W65,IF(AF66=3,W66,"")))),"")</f>
-        <v>Spania</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="N65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,X63,IF(AF64=3,X64,IF(AF65=3,X65,IF(AF66=3,X66,"")))),"")</f>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,Y63,IF(AF64=3,Y64,IF(AF65=3,Y65,IF(AF66=3,Y66,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,Z63,IF(AF64=3,Z64,IF(AF65=3,Z65,IF(AF66=3,Z66,"")))),"")</f>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="Q65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,AA63,IF(AF64=3,AA64,IF(AF65=3,AA65,IF(AF66=3,AA66,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,AB63,IF(AF64=3,AB64,IF(AF65=3,AB65,IF(AF66=3,AB66,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,AC63,IF(AF64=3,AC64,IF(AF65=3,AC65,IF(AF66=3,AC66,"")))),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,AD63,IF(AF64=3,AD64,IF(AF65=3,AD65,IF(AF66=3,AD66,"")))),"")</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="U65" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,AE63,IF(AF64=3,AE64,IF(AF65=3,AE65,IF(AF66=3,AE66,"")))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W65" t="s">
         <v>124</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Y65">
         <f>((C63="Saudi Arabia")*ISNUMBER(D63)*(D63&gt;F63))+((G63="Saudi Arabia")*ISNUMBER(D63)*(F63&gt;D63))+((C64="Saudi Arabia")*ISNUMBER(D64)*(D64&gt;F64))+((G64="Saudi Arabia")*ISNUMBER(D64)*(F64&gt;D64))+((C65="Saudi Arabia")*ISNUMBER(D65)*(D65&gt;F65))+((G65="Saudi Arabia")*ISNUMBER(D65)*(F65&gt;D65))+((C66="Saudi Arabia")*ISNUMBER(D66)*(D66&gt;F66))+((G66="Saudi Arabia")*ISNUMBER(D66)*(F66&gt;D66))+((C67="Saudi Arabia")*ISNUMBER(D67)*(D67&gt;F67))+((G67="Saudi Arabia")*ISNUMBER(D67)*(F67&gt;D67))+((C68="Saudi Arabia")*ISNUMBER(D68)*(D68&gt;F68))+((G68="Saudi Arabia")*ISNUMBER(D68)*(F68&gt;D68))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z65">
         <f>((C63="Saudi Arabia")*ISNUMBER(D63)*(D63=F63))+((G63="Saudi Arabia")*ISNUMBER(D63)*(F63=D63))+((C64="Saudi Arabia")*ISNUMBER(D64)*(D64=F64))+((G64="Saudi Arabia")*ISNUMBER(D64)*(F64=D64))+((C65="Saudi Arabia")*ISNUMBER(D65)*(D65=F65))+((G65="Saudi Arabia")*ISNUMBER(D65)*(F65=D65))+((C66="Saudi Arabia")*ISNUMBER(D66)*(D66=F66))+((G66="Saudi Arabia")*ISNUMBER(D66)*(F66=D66))+((C67="Saudi Arabia")*ISNUMBER(D67)*(D67=F67))+((G67="Saudi Arabia")*ISNUMBER(D67)*(F67=D67))+((C68="Saudi Arabia")*ISNUMBER(D68)*(D68=F68))+((G68="Saudi Arabia")*ISNUMBER(D68)*(F68=D68))</f>
@@ -6749,27 +6749,27 @@
       </c>
       <c r="AA65">
         <f>((C63="Saudi Arabia")*ISNUMBER(D63)*(D63&lt;F63))+((G63="Saudi Arabia")*ISNUMBER(D63)*(F63&lt;D63))+((C64="Saudi Arabia")*ISNUMBER(D64)*(D64&lt;F64))+((G64="Saudi Arabia")*ISNUMBER(D64)*(F64&lt;D64))+((C65="Saudi Arabia")*ISNUMBER(D65)*(D65&lt;F65))+((G65="Saudi Arabia")*ISNUMBER(D65)*(F65&lt;D65))+((C66="Saudi Arabia")*ISNUMBER(D66)*(D66&lt;F66))+((G66="Saudi Arabia")*ISNUMBER(D66)*(F66&lt;D66))+((C67="Saudi Arabia")*ISNUMBER(D67)*(D67&lt;F67))+((G67="Saudi Arabia")*ISNUMBER(D67)*(F67&lt;D67))+((C68="Saudi Arabia")*ISNUMBER(D68)*(D68&lt;F68))+((G68="Saudi Arabia")*ISNUMBER(D68)*(F68&lt;D68))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB65">
         <f>IF((C63="Saudi Arabia")*ISNUMBER(D63),D63,0)+IF((G63="Saudi Arabia")*ISNUMBER(D63),F63,0)+IF((C64="Saudi Arabia")*ISNUMBER(D64),D64,0)+IF((G64="Saudi Arabia")*ISNUMBER(D64),F64,0)+IF((C65="Saudi Arabia")*ISNUMBER(D65),D65,0)+IF((G65="Saudi Arabia")*ISNUMBER(D65),F65,0)+IF((C66="Saudi Arabia")*ISNUMBER(D66),D66,0)+IF((G66="Saudi Arabia")*ISNUMBER(D66),F66,0)+IF((C67="Saudi Arabia")*ISNUMBER(D67),D67,0)+IF((G67="Saudi Arabia")*ISNUMBER(D67),F67,0)+IF((C68="Saudi Arabia")*ISNUMBER(D68),D68,0)+IF((G68="Saudi Arabia")*ISNUMBER(D68),F68,0)</f>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC65">
         <f>IF((C63="Saudi Arabia")*ISNUMBER(D63),F63,0)+IF((G63="Saudi Arabia")*ISNUMBER(D63),D63,0)+IF((C64="Saudi Arabia")*ISNUMBER(D64),F64,0)+IF((G64="Saudi Arabia")*ISNUMBER(D64),D64,0)+IF((C65="Saudi Arabia")*ISNUMBER(D65),F65,0)+IF((G65="Saudi Arabia")*ISNUMBER(D65),D65,0)+IF((C66="Saudi Arabia")*ISNUMBER(D66),F66,0)+IF((G66="Saudi Arabia")*ISNUMBER(D66),D66,0)+IF((C67="Saudi Arabia")*ISNUMBER(D67),F67,0)+IF((G67="Saudi Arabia")*ISNUMBER(D67),D67,0)+IF((C68="Saudi Arabia")*ISNUMBER(D68),F68,0)+IF((G68="Saudi Arabia")*ISNUMBER(D68),D68,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AD65">
         <f>AB65-AC65</f>
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="AE65">
         <f>3*Y65+Z65</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF65">
         <f>1+((AE63&gt;AE65)+(AE63=AE65)*(AD63&gt;AD65)+(AE63=AE65)*(AD63=AD65)*(AB63&gt;AB65)&gt;0)*1+((AE64&gt;AE65)+(AE64=AE65)*(AD64&gt;AD65)+(AE64=AE65)*(AD64=AD65)*(AB64&gt;AB65)&gt;0)*1+((AE66&gt;AE65)+(AE66=AE65)*(AD66&gt;AD65)+(AE66=AE65)*(AD66=AD65)*(AB66&gt;AB65)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6783,13 +6783,13 @@
         <v>125</v>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>123</v>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="M66" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,W63,IF(AF64=4,W64,IF(AF65=4,W65,IF(AF66=4,W66,"")))),"")</f>
-        <v>Uruguay</v>
+        <v>Kapp Verde</v>
       </c>
       <c r="N66" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,X63,IF(AF64=4,X64,IF(AF65=4,X65,IF(AF66=4,X66,"")))),"")</f>
@@ -6828,15 +6828,15 @@
       </c>
       <c r="R66" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,AB63,IF(AF64=4,AB64,IF(AF65=4,AB65,IF(AF66=4,AB66,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S66" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,AC63,IF(AF64=4,AC64,IF(AF65=4,AC65,IF(AF66=4,AC66,"")))),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,AD63,IF(AF64=4,AD64,IF(AF65=4,AD65,IF(AF66=4,AD66,"")))),"")</f>
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="U66" s="3">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,AE63,IF(AF64=4,AE64,IF(AF65=4,AE65,IF(AF66=4,AE66,"")))),"")</f>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Y66">
         <f>((C63="Uruguay")*ISNUMBER(D63)*(D63&gt;F63))+((G63="Uruguay")*ISNUMBER(D63)*(F63&gt;D63))+((C64="Uruguay")*ISNUMBER(D64)*(D64&gt;F64))+((G64="Uruguay")*ISNUMBER(D64)*(F64&gt;D64))+((C65="Uruguay")*ISNUMBER(D65)*(D65&gt;F65))+((G65="Uruguay")*ISNUMBER(D65)*(F65&gt;D65))+((C66="Uruguay")*ISNUMBER(D66)*(D66&gt;F66))+((G66="Uruguay")*ISNUMBER(D66)*(F66&gt;D66))+((C67="Uruguay")*ISNUMBER(D67)*(D67&gt;F67))+((G67="Uruguay")*ISNUMBER(D67)*(F67&gt;D67))+((C68="Uruguay")*ISNUMBER(D68)*(D68&gt;F68))+((G68="Uruguay")*ISNUMBER(D68)*(F68&gt;D68))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z66">
         <f>((C63="Uruguay")*ISNUMBER(D63)*(D63=F63))+((G63="Uruguay")*ISNUMBER(D63)*(F63=D63))+((C64="Uruguay")*ISNUMBER(D64)*(D64=F64))+((G64="Uruguay")*ISNUMBER(D64)*(F64=D64))+((C65="Uruguay")*ISNUMBER(D65)*(D65=F65))+((G65="Uruguay")*ISNUMBER(D65)*(F65=D65))+((C66="Uruguay")*ISNUMBER(D66)*(D66=F66))+((G66="Uruguay")*ISNUMBER(D66)*(F66=D66))+((C67="Uruguay")*ISNUMBER(D67)*(D67=F67))+((G67="Uruguay")*ISNUMBER(D67)*(F67=D67))+((C68="Uruguay")*ISNUMBER(D68)*(D68=F68))+((G68="Uruguay")*ISNUMBER(D68)*(F68=D68))</f>
@@ -6859,27 +6859,27 @@
       </c>
       <c r="AA66">
         <f>((C63="Uruguay")*ISNUMBER(D63)*(D63&lt;F63))+((G63="Uruguay")*ISNUMBER(D63)*(F63&lt;D63))+((C64="Uruguay")*ISNUMBER(D64)*(D64&lt;F64))+((G64="Uruguay")*ISNUMBER(D64)*(F64&lt;D64))+((C65="Uruguay")*ISNUMBER(D65)*(D65&lt;F65))+((G65="Uruguay")*ISNUMBER(D65)*(F65&lt;D65))+((C66="Uruguay")*ISNUMBER(D66)*(D66&lt;F66))+((G66="Uruguay")*ISNUMBER(D66)*(F66&lt;D66))+((C67="Uruguay")*ISNUMBER(D67)*(D67&lt;F67))+((G67="Uruguay")*ISNUMBER(D67)*(F67&lt;D67))+((C68="Uruguay")*ISNUMBER(D68)*(D68&lt;F68))+((G68="Uruguay")*ISNUMBER(D68)*(F68&lt;D68))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB66">
         <f>IF((C63="Uruguay")*ISNUMBER(D63),D63,0)+IF((G63="Uruguay")*ISNUMBER(D63),F63,0)+IF((C64="Uruguay")*ISNUMBER(D64),D64,0)+IF((G64="Uruguay")*ISNUMBER(D64),F64,0)+IF((C65="Uruguay")*ISNUMBER(D65),D65,0)+IF((G65="Uruguay")*ISNUMBER(D65),F65,0)+IF((C66="Uruguay")*ISNUMBER(D66),D66,0)+IF((G66="Uruguay")*ISNUMBER(D66),F66,0)+IF((C67="Uruguay")*ISNUMBER(D67),D67,0)+IF((G67="Uruguay")*ISNUMBER(D67),F67,0)+IF((C68="Uruguay")*ISNUMBER(D68),D68,0)+IF((G68="Uruguay")*ISNUMBER(D68),F68,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC66">
         <f>IF((C63="Uruguay")*ISNUMBER(D63),F63,0)+IF((G63="Uruguay")*ISNUMBER(D63),D63,0)+IF((C64="Uruguay")*ISNUMBER(D64),F64,0)+IF((G64="Uruguay")*ISNUMBER(D64),D64,0)+IF((C65="Uruguay")*ISNUMBER(D65),F65,0)+IF((G65="Uruguay")*ISNUMBER(D65),D65,0)+IF((C66="Uruguay")*ISNUMBER(D66),F66,0)+IF((G66="Uruguay")*ISNUMBER(D66),D66,0)+IF((C67="Uruguay")*ISNUMBER(D67),F67,0)+IF((G67="Uruguay")*ISNUMBER(D67),D67,0)+IF((C68="Uruguay")*ISNUMBER(D68),F68,0)+IF((G68="Uruguay")*ISNUMBER(D68),D68,0)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AD66">
         <f>AB66-AC66</f>
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AE66">
         <f>3*Y66+Z66</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF66">
         <f>1+((AE63&gt;AE66)+(AE63=AE66)*(AD63&gt;AD66)+(AE63=AE66)*(AD63=AD66)*(AB63&gt;AB66)&gt;0)*1+((AE64&gt;AE66)+(AE64=AE66)*(AD64&gt;AD66)+(AE64=AE66)*(AD64=AD66)*(AB64&gt;AB66)&gt;0)*1+((AE65&gt;AE66)+(AE65=AE66)*(AD65&gt;AD66)+(AE65=AE66)*(AD65=AD66)*(AB65&gt;AB66)&gt;0)*1</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6893,13 +6893,13 @@
         <v>123</v>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>124</v>
@@ -6928,13 +6928,13 @@
         <v>125</v>
       </c>
       <c r="D68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>122</v>
@@ -6953,30 +6953,30 @@
       </c>
     </row>
     <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="61" t="s">
+      <c r="A69" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="61"/>
-      <c r="K69" s="61"/>
-      <c r="M69" s="62" t="s">
+      <c r="B69" s="64"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="64"/>
+      <c r="J69" s="64"/>
+      <c r="K69" s="64"/>
+      <c r="M69" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="N69" s="62"/>
-      <c r="O69" s="62"/>
-      <c r="P69" s="62"/>
-      <c r="Q69" s="62"/>
-      <c r="R69" s="62"/>
-      <c r="S69" s="62"/>
-      <c r="T69" s="62"/>
-      <c r="U69" s="62"/>
+      <c r="N69" s="65"/>
+      <c r="O69" s="65"/>
+      <c r="P69" s="65"/>
+      <c r="Q69" s="65"/>
+      <c r="R69" s="65"/>
+      <c r="S69" s="65"/>
+      <c r="T69" s="65"/>
+      <c r="U69" s="65"/>
     </row>
     <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
@@ -7049,13 +7049,13 @@
         <v>129</v>
       </c>
       <c r="D71" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>130</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M71" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,W71,IF(AF72=1,W72,IF(AF73=1,W73,IF(AF74=1,W74,"")))),"")</f>
-        <v>Norge</v>
+        <v>Frankrike</v>
       </c>
       <c r="N71" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,X71,IF(AF72=1,X72,IF(AF73=1,X73,IF(AF74=1,X74,"")))),"")</f>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="R71" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,AB71,IF(AF72=1,AB72,IF(AF73=1,AB73,IF(AF74=1,AB74,"")))),"")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S71" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,AC71,IF(AF72=1,AC72,IF(AF73=1,AC73,IF(AF74=1,AC74,"")))),"")</f>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="T71" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,AD71,IF(AF72=1,AD72,IF(AF73=1,AD73,IF(AF74=1,AD74,"")))),"")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U71" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,AE71,IF(AF72=1,AE72,IF(AF73=1,AE73,IF(AF74=1,AE74,"")))),"")</f>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="Y71">
         <f>((C71="Frankrike")*ISNUMBER(D71)*(D71&gt;F71))+((G71="Frankrike")*ISNUMBER(D71)*(F71&gt;D71))+((C72="Frankrike")*ISNUMBER(D72)*(D72&gt;F72))+((G72="Frankrike")*ISNUMBER(D72)*(F72&gt;D72))+((C73="Frankrike")*ISNUMBER(D73)*(D73&gt;F73))+((G73="Frankrike")*ISNUMBER(D73)*(F73&gt;D73))+((C74="Frankrike")*ISNUMBER(D74)*(D74&gt;F74))+((G74="Frankrike")*ISNUMBER(D74)*(F74&gt;D74))+((C75="Frankrike")*ISNUMBER(D75)*(D75&gt;F75))+((G75="Frankrike")*ISNUMBER(D75)*(F75&gt;D75))+((C76="Frankrike")*ISNUMBER(D76)*(D76&gt;F76))+((G76="Frankrike")*ISNUMBER(D76)*(F76&gt;D76))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z71">
         <f>((C71="Frankrike")*ISNUMBER(D71)*(D71=F71))+((G71="Frankrike")*ISNUMBER(D71)*(F71=D71))+((C72="Frankrike")*ISNUMBER(D72)*(D72=F72))+((G72="Frankrike")*ISNUMBER(D72)*(F72=D72))+((C73="Frankrike")*ISNUMBER(D73)*(D73=F73))+((G73="Frankrike")*ISNUMBER(D73)*(F73=D73))+((C74="Frankrike")*ISNUMBER(D74)*(D74=F74))+((G74="Frankrike")*ISNUMBER(D74)*(F74=D74))+((C75="Frankrike")*ISNUMBER(D75)*(D75=F75))+((G75="Frankrike")*ISNUMBER(D75)*(F75=D75))+((C76="Frankrike")*ISNUMBER(D76)*(D76=F76))+((G76="Frankrike")*ISNUMBER(D76)*(F76=D76))</f>
@@ -7125,27 +7125,27 @@
       </c>
       <c r="AA71">
         <f>((C71="Frankrike")*ISNUMBER(D71)*(D71&lt;F71))+((G71="Frankrike")*ISNUMBER(D71)*(F71&lt;D71))+((C72="Frankrike")*ISNUMBER(D72)*(D72&lt;F72))+((G72="Frankrike")*ISNUMBER(D72)*(F72&lt;D72))+((C73="Frankrike")*ISNUMBER(D73)*(D73&lt;F73))+((G73="Frankrike")*ISNUMBER(D73)*(F73&lt;D73))+((C74="Frankrike")*ISNUMBER(D74)*(D74&lt;F74))+((G74="Frankrike")*ISNUMBER(D74)*(F74&lt;D74))+((C75="Frankrike")*ISNUMBER(D75)*(D75&lt;F75))+((G75="Frankrike")*ISNUMBER(D75)*(F75&lt;D75))+((C76="Frankrike")*ISNUMBER(D76)*(D76&lt;F76))+((G76="Frankrike")*ISNUMBER(D76)*(F76&lt;D76))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB71">
         <f>IF((C71="Frankrike")*ISNUMBER(D71),D71,0)+IF((G71="Frankrike")*ISNUMBER(D71),F71,0)+IF((C72="Frankrike")*ISNUMBER(D72),D72,0)+IF((G72="Frankrike")*ISNUMBER(D72),F72,0)+IF((C73="Frankrike")*ISNUMBER(D73),D73,0)+IF((G73="Frankrike")*ISNUMBER(D73),F73,0)+IF((C74="Frankrike")*ISNUMBER(D74),D74,0)+IF((G74="Frankrike")*ISNUMBER(D74),F74,0)+IF((C75="Frankrike")*ISNUMBER(D75),D75,0)+IF((G75="Frankrike")*ISNUMBER(D75),F75,0)+IF((C76="Frankrike")*ISNUMBER(D76),D76,0)+IF((G76="Frankrike")*ISNUMBER(D76),F76,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AC71">
         <f>IF((C71="Frankrike")*ISNUMBER(D71),F71,0)+IF((G71="Frankrike")*ISNUMBER(D71),D71,0)+IF((C72="Frankrike")*ISNUMBER(D72),F72,0)+IF((G72="Frankrike")*ISNUMBER(D72),D72,0)+IF((C73="Frankrike")*ISNUMBER(D73),F73,0)+IF((G73="Frankrike")*ISNUMBER(D73),D73,0)+IF((C74="Frankrike")*ISNUMBER(D74),F74,0)+IF((G74="Frankrike")*ISNUMBER(D74),D74,0)+IF((C75="Frankrike")*ISNUMBER(D75),F75,0)+IF((G75="Frankrike")*ISNUMBER(D75),D75,0)+IF((C76="Frankrike")*ISNUMBER(D76),F76,0)+IF((G76="Frankrike")*ISNUMBER(D76),D76,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD71">
         <f>AB71-AC71</f>
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="AE71">
         <f>3*Y71+Z71</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF71">
         <f>1+((AE72&gt;AE71)+(AE72=AE71)*(AD72&gt;AD71)+(AE72=AE71)*(AD72=AD71)*(AB72&gt;AB71)&gt;0)*1+((AE73&gt;AE71)+(AE73=AE71)*(AD73&gt;AD71)+(AE73=AE71)*(AD73=AD71)*(AB73&gt;AB71)&gt;0)*1+((AE74&gt;AE71)+(AE74=AE71)*(AD74&gt;AD71)+(AE74=AE71)*(AD74=AD71)*(AB74&gt;AB71)&gt;0)*1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>29</v>
       </c>
       <c r="F72" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>132</v>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="M72" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,W71,IF(AF72=2,W72,IF(AF73=2,W73,IF(AF74=2,W74,"")))),"")</f>
-        <v>Senegal</v>
+        <v>Norge</v>
       </c>
       <c r="N72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,X71,IF(AF72=2,X72,IF(AF73=2,X73,IF(AF74=2,X74,"")))),"")</f>
@@ -7192,11 +7192,11 @@
       </c>
       <c r="O72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,Y71,IF(AF72=2,Y72,IF(AF73=2,Y73,IF(AF74=2,Y74,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,Z71,IF(AF72=2,Z72,IF(AF73=2,Z73,IF(AF74=2,Z74,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,AA71,IF(AF72=2,AA72,IF(AF73=2,AA73,IF(AF74=2,AA74,"")))),"")</f>
@@ -7204,19 +7204,19 @@
       </c>
       <c r="R72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,AB71,IF(AF72=2,AB72,IF(AF73=2,AB73,IF(AF74=2,AB74,"")))),"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,AC71,IF(AF72=2,AC72,IF(AF73=2,AC73,IF(AF74=2,AC74,"")))),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,AD71,IF(AF72=2,AD72,IF(AF73=2,AD73,IF(AF74=2,AD74,"")))),"")</f>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="U72" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,AE71,IF(AF72=2,AE72,IF(AF73=2,AE73,IF(AF74=2,AE74,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W72" t="s">
         <v>130</v>
@@ -7227,11 +7227,11 @@
       </c>
       <c r="Y72">
         <f>((C71="Senegal")*ISNUMBER(D71)*(D71&gt;F71))+((G71="Senegal")*ISNUMBER(D71)*(F71&gt;D71))+((C72="Senegal")*ISNUMBER(D72)*(D72&gt;F72))+((G72="Senegal")*ISNUMBER(D72)*(F72&gt;D72))+((C73="Senegal")*ISNUMBER(D73)*(D73&gt;F73))+((G73="Senegal")*ISNUMBER(D73)*(F73&gt;D73))+((C74="Senegal")*ISNUMBER(D74)*(D74&gt;F74))+((G74="Senegal")*ISNUMBER(D74)*(F74&gt;D74))+((C75="Senegal")*ISNUMBER(D75)*(D75&gt;F75))+((G75="Senegal")*ISNUMBER(D75)*(F75&gt;D75))+((C76="Senegal")*ISNUMBER(D76)*(D76&gt;F76))+((G76="Senegal")*ISNUMBER(D76)*(F76&gt;D76))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z72">
         <f>((C71="Senegal")*ISNUMBER(D71)*(D71=F71))+((G71="Senegal")*ISNUMBER(D71)*(F71=D71))+((C72="Senegal")*ISNUMBER(D72)*(D72=F72))+((G72="Senegal")*ISNUMBER(D72)*(F72=D72))+((C73="Senegal")*ISNUMBER(D73)*(D73=F73))+((G73="Senegal")*ISNUMBER(D73)*(F73=D73))+((C74="Senegal")*ISNUMBER(D74)*(D74=F74))+((G74="Senegal")*ISNUMBER(D74)*(F74=D74))+((C75="Senegal")*ISNUMBER(D75)*(D75=F75))+((G75="Senegal")*ISNUMBER(D75)*(F75=D75))+((C76="Senegal")*ISNUMBER(D76)*(D76=F76))+((G76="Senegal")*ISNUMBER(D76)*(F76=D76))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA72">
         <f>((C71="Senegal")*ISNUMBER(D71)*(D71&lt;F71))+((G71="Senegal")*ISNUMBER(D71)*(F71&lt;D71))+((C72="Senegal")*ISNUMBER(D72)*(D72&lt;F72))+((G72="Senegal")*ISNUMBER(D72)*(F72&lt;D72))+((C73="Senegal")*ISNUMBER(D73)*(D73&lt;F73))+((G73="Senegal")*ISNUMBER(D73)*(F73&lt;D73))+((C74="Senegal")*ISNUMBER(D74)*(D74&lt;F74))+((G74="Senegal")*ISNUMBER(D74)*(F74&lt;D74))+((C75="Senegal")*ISNUMBER(D75)*(D75&lt;F75))+((G75="Senegal")*ISNUMBER(D75)*(F75&lt;D75))+((C76="Senegal")*ISNUMBER(D76)*(D76&lt;F76))+((G76="Senegal")*ISNUMBER(D76)*(F76&lt;D76))</f>
@@ -7243,19 +7243,19 @@
       </c>
       <c r="AC72">
         <f>IF((C71="Senegal")*ISNUMBER(D71),F71,0)+IF((G71="Senegal")*ISNUMBER(D71),D71,0)+IF((C72="Senegal")*ISNUMBER(D72),F72,0)+IF((G72="Senegal")*ISNUMBER(D72),D72,0)+IF((C73="Senegal")*ISNUMBER(D73),F73,0)+IF((G73="Senegal")*ISNUMBER(D73),D73,0)+IF((C74="Senegal")*ISNUMBER(D74),F74,0)+IF((G74="Senegal")*ISNUMBER(D74),D74,0)+IF((C75="Senegal")*ISNUMBER(D75),F75,0)+IF((G75="Senegal")*ISNUMBER(D75),D75,0)+IF((C76="Senegal")*ISNUMBER(D76),F76,0)+IF((G76="Senegal")*ISNUMBER(D76),D76,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD72">
         <f>AB72-AC72</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE72">
         <f>3*Y72+Z72</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF72">
         <f>1+((AE71&gt;AE72)+(AE71=AE72)*(AD71&gt;AD72)+(AE71=AE72)*(AD71=AD72)*(AB71&gt;AB72)&gt;0)*1+((AE73&gt;AE72)+(AE73=AE72)*(AD73&gt;AD72)+(AE73=AE72)*(AD73=AD72)*(AB73&gt;AB72)&gt;0)*1+((AE74&gt;AE72)+(AE74=AE72)*(AD74&gt;AD72)+(AE74=AE72)*(AD74=AD72)*(AB74&gt;AB72)&gt;0)*1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7269,13 +7269,13 @@
         <v>129</v>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>131</v>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M73" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,W71,IF(AF72=3,W72,IF(AF73=3,W73,IF(AF74=3,W74,"")))),"")</f>
-        <v>Irak</v>
+        <v>Senegal</v>
       </c>
       <c r="N73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,X71,IF(AF72=3,X72,IF(AF73=3,X73,IF(AF74=3,X74,"")))),"")</f>
@@ -7306,11 +7306,11 @@
       </c>
       <c r="P73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,Z71,IF(AF72=3,Z72,IF(AF73=3,Z73,IF(AF74=3,Z74,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,AA71,IF(AF72=3,AA72,IF(AF73=3,AA73,IF(AF74=3,AA74,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,AB71,IF(AF72=3,AB72,IF(AF73=3,AB73,IF(AF74=3,AB74,"")))),"")</f>
@@ -7318,15 +7318,15 @@
       </c>
       <c r="S73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,AC71,IF(AF72=3,AC72,IF(AF73=3,AC73,IF(AF74=3,AC74,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,AD71,IF(AF72=3,AD72,IF(AF73=3,AD73,IF(AF74=3,AD74,"")))),"")</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="U73" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,AE71,IF(AF72=3,AE72,IF(AF73=3,AE73,IF(AF74=3,AE74,"")))),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W73" t="s">
         <v>131</v>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="Y73">
         <f>((C71="Irak")*ISNUMBER(D71)*(D71&gt;F71))+((G71="Irak")*ISNUMBER(D71)*(F71&gt;D71))+((C72="Irak")*ISNUMBER(D72)*(D72&gt;F72))+((G72="Irak")*ISNUMBER(D72)*(F72&gt;D72))+((C73="Irak")*ISNUMBER(D73)*(D73&gt;F73))+((G73="Irak")*ISNUMBER(D73)*(F73&gt;D73))+((C74="Irak")*ISNUMBER(D74)*(D74&gt;F74))+((G74="Irak")*ISNUMBER(D74)*(F74&gt;D74))+((C75="Irak")*ISNUMBER(D75)*(D75&gt;F75))+((G75="Irak")*ISNUMBER(D75)*(F75&gt;D75))+((C76="Irak")*ISNUMBER(D76)*(D76&gt;F76))+((G76="Irak")*ISNUMBER(D76)*(F76&gt;D76))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73">
         <f>((C71="Irak")*ISNUMBER(D71)*(D71=F71))+((G71="Irak")*ISNUMBER(D71)*(F71=D71))+((C72="Irak")*ISNUMBER(D72)*(D72=F72))+((G72="Irak")*ISNUMBER(D72)*(F72=D72))+((C73="Irak")*ISNUMBER(D73)*(D73=F73))+((G73="Irak")*ISNUMBER(D73)*(F73=D73))+((C74="Irak")*ISNUMBER(D74)*(D74=F74))+((G74="Irak")*ISNUMBER(D74)*(F74=D74))+((C75="Irak")*ISNUMBER(D75)*(D75=F75))+((G75="Irak")*ISNUMBER(D75)*(F75=D75))+((C76="Irak")*ISNUMBER(D76)*(D76=F76))+((G76="Irak")*ISNUMBER(D76)*(F76=D76))</f>
@@ -7345,27 +7345,27 @@
       </c>
       <c r="AA73">
         <f>((C71="Irak")*ISNUMBER(D71)*(D71&lt;F71))+((G71="Irak")*ISNUMBER(D71)*(F71&lt;D71))+((C72="Irak")*ISNUMBER(D72)*(D72&lt;F72))+((G72="Irak")*ISNUMBER(D72)*(F72&lt;D72))+((C73="Irak")*ISNUMBER(D73)*(D73&lt;F73))+((G73="Irak")*ISNUMBER(D73)*(F73&lt;D73))+((C74="Irak")*ISNUMBER(D74)*(D74&lt;F74))+((G74="Irak")*ISNUMBER(D74)*(F74&lt;D74))+((C75="Irak")*ISNUMBER(D75)*(D75&lt;F75))+((G75="Irak")*ISNUMBER(D75)*(F75&lt;D75))+((C76="Irak")*ISNUMBER(D76)*(D76&lt;F76))+((G76="Irak")*ISNUMBER(D76)*(F76&lt;D76))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB73">
         <f>IF((C71="Irak")*ISNUMBER(D71),D71,0)+IF((G71="Irak")*ISNUMBER(D71),F71,0)+IF((C72="Irak")*ISNUMBER(D72),D72,0)+IF((G72="Irak")*ISNUMBER(D72),F72,0)+IF((C73="Irak")*ISNUMBER(D73),D73,0)+IF((G73="Irak")*ISNUMBER(D73),F73,0)+IF((C74="Irak")*ISNUMBER(D74),D74,0)+IF((G74="Irak")*ISNUMBER(D74),F74,0)+IF((C75="Irak")*ISNUMBER(D75),D75,0)+IF((G75="Irak")*ISNUMBER(D75),F75,0)+IF((C76="Irak")*ISNUMBER(D76),D76,0)+IF((G76="Irak")*ISNUMBER(D76),F76,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73">
         <f>IF((C71="Irak")*ISNUMBER(D71),F71,0)+IF((G71="Irak")*ISNUMBER(D71),D71,0)+IF((C72="Irak")*ISNUMBER(D72),F72,0)+IF((G72="Irak")*ISNUMBER(D72),D72,0)+IF((C73="Irak")*ISNUMBER(D73),F73,0)+IF((G73="Irak")*ISNUMBER(D73),D73,0)+IF((C74="Irak")*ISNUMBER(D74),F74,0)+IF((G74="Irak")*ISNUMBER(D74),D74,0)+IF((C75="Irak")*ISNUMBER(D75),F75,0)+IF((G75="Irak")*ISNUMBER(D75),D75,0)+IF((C76="Irak")*ISNUMBER(D76),F76,0)+IF((G76="Irak")*ISNUMBER(D76),D76,0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD73">
         <f>AB73-AC73</f>
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="AE73">
         <f>3*Y73+Z73</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF73">
         <f>1+((AE71&gt;AE73)+(AE71=AE73)*(AD71&gt;AD73)+(AE71=AE73)*(AD71=AD73)*(AB71&gt;AB73)&gt;0)*1+((AE72&gt;AE73)+(AE72=AE73)*(AD72&gt;AD73)+(AE72=AE73)*(AD72=AD73)*(AB72&gt;AB73)&gt;0)*1+((AE74&gt;AE73)+(AE74=AE73)*(AD74&gt;AD73)+(AE74=AE73)*(AD74=AD73)*(AB74&gt;AB73)&gt;0)*1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7379,13 +7379,13 @@
         <v>132</v>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="11" t="s">
         <v>130</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M74" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,W71,IF(AF72=4,W72,IF(AF73=4,W73,IF(AF74=4,W74,"")))),"")</f>
-        <v>Frankrike</v>
+        <v>Irak</v>
       </c>
       <c r="N74" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,X71,IF(AF72=4,X72,IF(AF73=4,X73,IF(AF74=4,X74,"")))),"")</f>
@@ -7424,15 +7424,15 @@
       </c>
       <c r="R74" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,AB71,IF(AF72=4,AB72,IF(AF73=4,AB73,IF(AF74=4,AB74,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S74" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,AC71,IF(AF72=4,AC72,IF(AF73=4,AC73,IF(AF74=4,AC74,"")))),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T74" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,AD71,IF(AF72=4,AD72,IF(AF73=4,AD73,IF(AF74=4,AD74,"")))),"")</f>
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="U74" s="3">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,AE71,IF(AF72=4,AE72,IF(AF73=4,AE73,IF(AF74=4,AE74,"")))),"")</f>
@@ -7447,35 +7447,35 @@
       </c>
       <c r="Y74">
         <f>((C71="Norge")*ISNUMBER(D71)*(D71&gt;F71))+((G71="Norge")*ISNUMBER(D71)*(F71&gt;D71))+((C72="Norge")*ISNUMBER(D72)*(D72&gt;F72))+((G72="Norge")*ISNUMBER(D72)*(F72&gt;D72))+((C73="Norge")*ISNUMBER(D73)*(D73&gt;F73))+((G73="Norge")*ISNUMBER(D73)*(F73&gt;D73))+((C74="Norge")*ISNUMBER(D74)*(D74&gt;F74))+((G74="Norge")*ISNUMBER(D74)*(F74&gt;D74))+((C75="Norge")*ISNUMBER(D75)*(D75&gt;F75))+((G75="Norge")*ISNUMBER(D75)*(F75&gt;D75))+((C76="Norge")*ISNUMBER(D76)*(D76&gt;F76))+((G76="Norge")*ISNUMBER(D76)*(F76&gt;D76))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z74">
         <f>((C71="Norge")*ISNUMBER(D71)*(D71=F71))+((G71="Norge")*ISNUMBER(D71)*(F71=D71))+((C72="Norge")*ISNUMBER(D72)*(D72=F72))+((G72="Norge")*ISNUMBER(D72)*(F72=D72))+((C73="Norge")*ISNUMBER(D73)*(D73=F73))+((G73="Norge")*ISNUMBER(D73)*(F73=D73))+((C74="Norge")*ISNUMBER(D74)*(D74=F74))+((G74="Norge")*ISNUMBER(D74)*(F74=D74))+((C75="Norge")*ISNUMBER(D75)*(D75=F75))+((G75="Norge")*ISNUMBER(D75)*(F75=D75))+((C76="Norge")*ISNUMBER(D76)*(D76=F76))+((G76="Norge")*ISNUMBER(D76)*(F76=D76))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA74">
         <f>((C71="Norge")*ISNUMBER(D71)*(D71&lt;F71))+((G71="Norge")*ISNUMBER(D71)*(F71&lt;D71))+((C72="Norge")*ISNUMBER(D72)*(D72&lt;F72))+((G72="Norge")*ISNUMBER(D72)*(F72&lt;D72))+((C73="Norge")*ISNUMBER(D73)*(D73&lt;F73))+((G73="Norge")*ISNUMBER(D73)*(F73&lt;D73))+((C74="Norge")*ISNUMBER(D74)*(D74&lt;F74))+((G74="Norge")*ISNUMBER(D74)*(F74&lt;D74))+((C75="Norge")*ISNUMBER(D75)*(D75&lt;F75))+((G75="Norge")*ISNUMBER(D75)*(F75&lt;D75))+((C76="Norge")*ISNUMBER(D76)*(D76&lt;F76))+((G76="Norge")*ISNUMBER(D76)*(F76&lt;D76))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB74">
         <f>IF((C71="Norge")*ISNUMBER(D71),D71,0)+IF((G71="Norge")*ISNUMBER(D71),F71,0)+IF((C72="Norge")*ISNUMBER(D72),D72,0)+IF((G72="Norge")*ISNUMBER(D72),F72,0)+IF((C73="Norge")*ISNUMBER(D73),D73,0)+IF((G73="Norge")*ISNUMBER(D73),F73,0)+IF((C74="Norge")*ISNUMBER(D74),D74,0)+IF((G74="Norge")*ISNUMBER(D74),F74,0)+IF((C75="Norge")*ISNUMBER(D75),D75,0)+IF((G75="Norge")*ISNUMBER(D75),F75,0)+IF((C76="Norge")*ISNUMBER(D76),D76,0)+IF((G76="Norge")*ISNUMBER(D76),F76,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC74">
         <f>IF((C71="Norge")*ISNUMBER(D71),F71,0)+IF((G71="Norge")*ISNUMBER(D71),D71,0)+IF((C72="Norge")*ISNUMBER(D72),F72,0)+IF((G72="Norge")*ISNUMBER(D72),D72,0)+IF((C73="Norge")*ISNUMBER(D73),F73,0)+IF((G73="Norge")*ISNUMBER(D73),D73,0)+IF((C74="Norge")*ISNUMBER(D74),F74,0)+IF((G74="Norge")*ISNUMBER(D74),D74,0)+IF((C75="Norge")*ISNUMBER(D75),F75,0)+IF((G75="Norge")*ISNUMBER(D75),D75,0)+IF((C76="Norge")*ISNUMBER(D76),F76,0)+IF((G76="Norge")*ISNUMBER(D76),D76,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD74">
         <f>AB74-AC74</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE74">
         <f>3*Y74+Z74</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF74">
         <f>1+((AE71&gt;AE74)+(AE71=AE74)*(AD71&gt;AD74)+(AE71=AE74)*(AD71=AD74)*(AB71&gt;AB74)&gt;0)*1+((AE72&gt;AE74)+(AE72=AE74)*(AD72&gt;AD74)+(AE72=AE74)*(AD72=AD74)*(AB72&gt;AB74)&gt;0)*1+((AE73&gt;AE74)+(AE73=AE74)*(AD73&gt;AD74)+(AE73=AE74)*(AD73=AD74)*(AB73&gt;AB74)&gt;0)*1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7489,13 +7489,13 @@
         <v>132</v>
       </c>
       <c r="D75" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>129</v>
@@ -7549,30 +7549,30 @@
       </c>
     </row>
     <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="57" t="s">
+      <c r="A77" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="B77" s="57"/>
-      <c r="C77" s="57"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
-      <c r="K77" s="57"/>
-      <c r="M77" s="58" t="s">
+      <c r="B77" s="60"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
+      <c r="J77" s="60"/>
+      <c r="K77" s="60"/>
+      <c r="M77" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="N77" s="58"/>
-      <c r="O77" s="58"/>
-      <c r="P77" s="58"/>
-      <c r="Q77" s="58"/>
-      <c r="R77" s="58"/>
-      <c r="S77" s="58"/>
-      <c r="T77" s="58"/>
-      <c r="U77" s="58"/>
+      <c r="N77" s="61"/>
+      <c r="O77" s="61"/>
+      <c r="P77" s="61"/>
+      <c r="Q77" s="61"/>
+      <c r="R77" s="61"/>
+      <c r="S77" s="61"/>
+      <c r="T77" s="61"/>
+      <c r="U77" s="61"/>
     </row>
     <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
@@ -7645,13 +7645,13 @@
         <v>139</v>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>140</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="M79" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,W79,IF(AF80=1,W80,IF(AF81=1,W81,IF(AF82=1,W82,"")))),"")</f>
-        <v>Algerie</v>
+        <v>Argentina</v>
       </c>
       <c r="N79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,X79,IF(AF80=1,X80,IF(AF81=1,X81,IF(AF82=1,X82,"")))),"")</f>
@@ -7678,11 +7678,11 @@
       </c>
       <c r="O79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,Y79,IF(AF80=1,Y80,IF(AF81=1,Y81,IF(AF82=1,Y82,"")))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,Z79,IF(AF80=1,Z80,IF(AF81=1,Z81,IF(AF82=1,Z82,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,AA79,IF(AF80=1,AA80,IF(AF81=1,AA81,IF(AF82=1,AA82,"")))),"")</f>
@@ -7690,19 +7690,19 @@
       </c>
       <c r="R79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,AB79,IF(AF80=1,AB80,IF(AF81=1,AB81,IF(AF82=1,AB82,"")))),"")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,AC79,IF(AF80=1,AC80,IF(AF81=1,AC81,IF(AF82=1,AC82,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,AD79,IF(AF80=1,AD80,IF(AF81=1,AD81,IF(AF82=1,AD82,"")))),"")</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U79" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,AE79,IF(AF80=1,AE80,IF(AF81=1,AE81,IF(AF82=1,AE82,"")))),"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W79" t="s">
         <v>139</v>
@@ -7713,35 +7713,35 @@
       </c>
       <c r="Y79">
         <f>((C79="Argentina")*ISNUMBER(D79)*(D79&gt;F79))+((G79="Argentina")*ISNUMBER(D79)*(F79&gt;D79))+((C80="Argentina")*ISNUMBER(D80)*(D80&gt;F80))+((G80="Argentina")*ISNUMBER(D80)*(F80&gt;D80))+((C81="Argentina")*ISNUMBER(D81)*(D81&gt;F81))+((G81="Argentina")*ISNUMBER(D81)*(F81&gt;D81))+((C82="Argentina")*ISNUMBER(D82)*(D82&gt;F82))+((G82="Argentina")*ISNUMBER(D82)*(F82&gt;D82))+((C83="Argentina")*ISNUMBER(D83)*(D83&gt;F83))+((G83="Argentina")*ISNUMBER(D83)*(F83&gt;D83))+((C84="Argentina")*ISNUMBER(D84)*(D84&gt;F84))+((G84="Argentina")*ISNUMBER(D84)*(F84&gt;D84))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z79">
         <f>((C79="Argentina")*ISNUMBER(D79)*(D79=F79))+((G79="Argentina")*ISNUMBER(D79)*(F79=D79))+((C80="Argentina")*ISNUMBER(D80)*(D80=F80))+((G80="Argentina")*ISNUMBER(D80)*(F80=D80))+((C81="Argentina")*ISNUMBER(D81)*(D81=F81))+((G81="Argentina")*ISNUMBER(D81)*(F81=D81))+((C82="Argentina")*ISNUMBER(D82)*(D82=F82))+((G82="Argentina")*ISNUMBER(D82)*(F82=D82))+((C83="Argentina")*ISNUMBER(D83)*(D83=F83))+((G83="Argentina")*ISNUMBER(D83)*(F83=D83))+((C84="Argentina")*ISNUMBER(D84)*(D84=F84))+((G84="Argentina")*ISNUMBER(D84)*(F84=D84))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA79">
         <f>((C79="Argentina")*ISNUMBER(D79)*(D79&lt;F79))+((G79="Argentina")*ISNUMBER(D79)*(F79&lt;D79))+((C80="Argentina")*ISNUMBER(D80)*(D80&lt;F80))+((G80="Argentina")*ISNUMBER(D80)*(F80&lt;D80))+((C81="Argentina")*ISNUMBER(D81)*(D81&lt;F81))+((G81="Argentina")*ISNUMBER(D81)*(F81&lt;D81))+((C82="Argentina")*ISNUMBER(D82)*(D82&lt;F82))+((G82="Argentina")*ISNUMBER(D82)*(F82&lt;D82))+((C83="Argentina")*ISNUMBER(D83)*(D83&lt;F83))+((G83="Argentina")*ISNUMBER(D83)*(F83&lt;D83))+((C84="Argentina")*ISNUMBER(D84)*(D84&lt;F84))+((G84="Argentina")*ISNUMBER(D84)*(F84&lt;D84))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB79">
         <f>IF((C79="Argentina")*ISNUMBER(D79),D79,0)+IF((G79="Argentina")*ISNUMBER(D79),F79,0)+IF((C80="Argentina")*ISNUMBER(D80),D80,0)+IF((G80="Argentina")*ISNUMBER(D80),F80,0)+IF((C81="Argentina")*ISNUMBER(D81),D81,0)+IF((G81="Argentina")*ISNUMBER(D81),F81,0)+IF((C82="Argentina")*ISNUMBER(D82),D82,0)+IF((G82="Argentina")*ISNUMBER(D82),F82,0)+IF((C83="Argentina")*ISNUMBER(D83),D83,0)+IF((G83="Argentina")*ISNUMBER(D83),F83,0)+IF((C84="Argentina")*ISNUMBER(D84),D84,0)+IF((G84="Argentina")*ISNUMBER(D84),F84,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC79">
         <f>IF((C79="Argentina")*ISNUMBER(D79),F79,0)+IF((G79="Argentina")*ISNUMBER(D79),D79,0)+IF((C80="Argentina")*ISNUMBER(D80),F80,0)+IF((G80="Argentina")*ISNUMBER(D80),D80,0)+IF((C81="Argentina")*ISNUMBER(D81),F81,0)+IF((G81="Argentina")*ISNUMBER(D81),D81,0)+IF((C82="Argentina")*ISNUMBER(D82),F82,0)+IF((G82="Argentina")*ISNUMBER(D82),D82,0)+IF((C83="Argentina")*ISNUMBER(D83),F83,0)+IF((G83="Argentina")*ISNUMBER(D83),D83,0)+IF((C84="Argentina")*ISNUMBER(D84),F84,0)+IF((G84="Argentina")*ISNUMBER(D84),D84,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD79">
         <f>AB79-AC79</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE79">
         <f>3*Y79+Z79</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AF79">
         <f>1+((AE80&gt;AE79)+(AE80=AE79)*(AD80&gt;AD79)+(AE80=AE79)*(AD80=AD79)*(AB80&gt;AB79)&gt;0)*1+((AE81&gt;AE79)+(AE81=AE79)*(AD81&gt;AD79)+(AE81=AE79)*(AD81=AD79)*(AB81&gt;AB79)&gt;0)*1+((AE82&gt;AE79)+(AE82=AE79)*(AD82&gt;AD79)+(AE82=AE79)*(AD82=AD79)*(AB82&gt;AB79)&gt;0)*1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7761,7 +7761,7 @@
         <v>29</v>
       </c>
       <c r="F80" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>142</v>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="M80" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,W79,IF(AF80=2,W80,IF(AF81=2,W81,IF(AF82=2,W82,"")))),"")</f>
-        <v>Argentina</v>
+        <v>Østerrike</v>
       </c>
       <c r="N80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,X79,IF(AF80=2,X80,IF(AF81=2,X81,IF(AF82=2,X82,"")))),"")</f>
@@ -7788,11 +7788,11 @@
       </c>
       <c r="O80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,Y79,IF(AF80=2,Y80,IF(AF81=2,Y81,IF(AF82=2,Y82,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,Z79,IF(AF80=2,Z80,IF(AF81=2,Z81,IF(AF82=2,Z82,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,AA79,IF(AF80=2,AA80,IF(AF81=2,AA81,IF(AF82=2,AA82,"")))),"")</f>
@@ -7800,19 +7800,19 @@
       </c>
       <c r="R80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,AB79,IF(AF80=2,AB80,IF(AF81=2,AB81,IF(AF82=2,AB82,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,AC79,IF(AF80=2,AC80,IF(AF81=2,AC81,IF(AF82=2,AC82,"")))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,AD79,IF(AF80=2,AD80,IF(AF81=2,AD81,IF(AF82=2,AD82,"")))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U80" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,AE79,IF(AF80=2,AE80,IF(AF81=2,AE81,IF(AF82=2,AE82,"")))),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W80" t="s">
         <v>140</v>
@@ -7823,35 +7823,35 @@
       </c>
       <c r="Y80">
         <f>((C79="Algerie")*ISNUMBER(D79)*(D79&gt;F79))+((G79="Algerie")*ISNUMBER(D79)*(F79&gt;D79))+((C80="Algerie")*ISNUMBER(D80)*(D80&gt;F80))+((G80="Algerie")*ISNUMBER(D80)*(F80&gt;D80))+((C81="Algerie")*ISNUMBER(D81)*(D81&gt;F81))+((G81="Algerie")*ISNUMBER(D81)*(F81&gt;D81))+((C82="Algerie")*ISNUMBER(D82)*(D82&gt;F82))+((G82="Algerie")*ISNUMBER(D82)*(F82&gt;D82))+((C83="Algerie")*ISNUMBER(D83)*(D83&gt;F83))+((G83="Algerie")*ISNUMBER(D83)*(F83&gt;D83))+((C84="Algerie")*ISNUMBER(D84)*(D84&gt;F84))+((G84="Algerie")*ISNUMBER(D84)*(F84&gt;D84))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z80">
         <f>((C79="Algerie")*ISNUMBER(D79)*(D79=F79))+((G79="Algerie")*ISNUMBER(D79)*(F79=D79))+((C80="Algerie")*ISNUMBER(D80)*(D80=F80))+((G80="Algerie")*ISNUMBER(D80)*(F80=D80))+((C81="Algerie")*ISNUMBER(D81)*(D81=F81))+((G81="Algerie")*ISNUMBER(D81)*(F81=D81))+((C82="Algerie")*ISNUMBER(D82)*(D82=F82))+((G82="Algerie")*ISNUMBER(D82)*(F82=D82))+((C83="Algerie")*ISNUMBER(D83)*(D83=F83))+((G83="Algerie")*ISNUMBER(D83)*(F83=D83))+((C84="Algerie")*ISNUMBER(D84)*(D84=F84))+((G84="Algerie")*ISNUMBER(D84)*(F84=D84))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA80">
         <f>((C79="Algerie")*ISNUMBER(D79)*(D79&lt;F79))+((G79="Algerie")*ISNUMBER(D79)*(F79&lt;D79))+((C80="Algerie")*ISNUMBER(D80)*(D80&lt;F80))+((G80="Algerie")*ISNUMBER(D80)*(F80&lt;D80))+((C81="Algerie")*ISNUMBER(D81)*(D81&lt;F81))+((G81="Algerie")*ISNUMBER(D81)*(F81&lt;D81))+((C82="Algerie")*ISNUMBER(D82)*(D82&lt;F82))+((G82="Algerie")*ISNUMBER(D82)*(F82&lt;D82))+((C83="Algerie")*ISNUMBER(D83)*(D83&lt;F83))+((G83="Algerie")*ISNUMBER(D83)*(F83&lt;D83))+((C84="Algerie")*ISNUMBER(D84)*(D84&lt;F84))+((G84="Algerie")*ISNUMBER(D84)*(F84&lt;D84))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80">
         <f>IF((C79="Algerie")*ISNUMBER(D79),D79,0)+IF((G79="Algerie")*ISNUMBER(D79),F79,0)+IF((C80="Algerie")*ISNUMBER(D80),D80,0)+IF((G80="Algerie")*ISNUMBER(D80),F80,0)+IF((C81="Algerie")*ISNUMBER(D81),D81,0)+IF((G81="Algerie")*ISNUMBER(D81),F81,0)+IF((C82="Algerie")*ISNUMBER(D82),D82,0)+IF((G82="Algerie")*ISNUMBER(D82),F82,0)+IF((C83="Algerie")*ISNUMBER(D83),D83,0)+IF((G83="Algerie")*ISNUMBER(D83),F83,0)+IF((C84="Algerie")*ISNUMBER(D84),D84,0)+IF((G84="Algerie")*ISNUMBER(D84),F84,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC80">
         <f>IF((C79="Algerie")*ISNUMBER(D79),F79,0)+IF((G79="Algerie")*ISNUMBER(D79),D79,0)+IF((C80="Algerie")*ISNUMBER(D80),F80,0)+IF((G80="Algerie")*ISNUMBER(D80),D80,0)+IF((C81="Algerie")*ISNUMBER(D81),F81,0)+IF((G81="Algerie")*ISNUMBER(D81),D81,0)+IF((C82="Algerie")*ISNUMBER(D82),F82,0)+IF((G82="Algerie")*ISNUMBER(D82),D82,0)+IF((C83="Algerie")*ISNUMBER(D83),F83,0)+IF((G83="Algerie")*ISNUMBER(D83),D83,0)+IF((C84="Algerie")*ISNUMBER(D84),F84,0)+IF((G84="Algerie")*ISNUMBER(D84),D84,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD80">
         <f>AB80-AC80</f>
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="AE80">
         <f>3*Y80+Z80</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF80">
         <f>1+((AE79&gt;AE80)+(AE79=AE80)*(AD79&gt;AD80)+(AE79=AE80)*(AD79=AD80)*(AB79&gt;AB80)&gt;0)*1+((AE81&gt;AE80)+(AE81=AE80)*(AD81&gt;AD80)+(AE81=AE80)*(AD81=AD80)*(AB81&gt;AB80)&gt;0)*1+((AE82&gt;AE80)+(AE82=AE80)*(AD82&gt;AD80)+(AE82=AE80)*(AD82=AD80)*(AB82&gt;AB80)&gt;0)*1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7865,7 +7865,7 @@
         <v>139</v>
       </c>
       <c r="D81" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="M81" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,W79,IF(AF80=3,W80,IF(AF81=3,W81,IF(AF82=3,W82,"")))),"")</f>
-        <v>Østerrike</v>
+        <v>Algerie</v>
       </c>
       <c r="N81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,X79,IF(AF80=3,X80,IF(AF81=3,X81,IF(AF82=3,X82,"")))),"")</f>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="O81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,Y79,IF(AF80=3,Y80,IF(AF81=3,Y81,IF(AF82=3,Y82,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,Z79,IF(AF80=3,Z80,IF(AF81=3,Z81,IF(AF82=3,Z82,"")))),"")</f>
@@ -7906,23 +7906,23 @@
       </c>
       <c r="Q81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,AA79,IF(AF80=3,AA80,IF(AF81=3,AA81,IF(AF82=3,AA82,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,AB79,IF(AF80=3,AB80,IF(AF81=3,AB81,IF(AF82=3,AB82,"")))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,AC79,IF(AF80=3,AC80,IF(AF81=3,AC81,IF(AF82=3,AC82,"")))),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,AD79,IF(AF80=3,AD80,IF(AF81=3,AD81,IF(AF82=3,AD82,"")))),"")</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="U81" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,AE79,IF(AF80=3,AE80,IF(AF81=3,AE81,IF(AF82=3,AE82,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W81" t="s">
         <v>141</v>
@@ -7933,11 +7933,11 @@
       </c>
       <c r="Y81">
         <f>((C79="Østerrike")*ISNUMBER(D79)*(D79&gt;F79))+((G79="Østerrike")*ISNUMBER(D79)*(F79&gt;D79))+((C80="Østerrike")*ISNUMBER(D80)*(D80&gt;F80))+((G80="Østerrike")*ISNUMBER(D80)*(F80&gt;D80))+((C81="Østerrike")*ISNUMBER(D81)*(D81&gt;F81))+((G81="Østerrike")*ISNUMBER(D81)*(F81&gt;D81))+((C82="Østerrike")*ISNUMBER(D82)*(D82&gt;F82))+((G82="Østerrike")*ISNUMBER(D82)*(F82&gt;D82))+((C83="Østerrike")*ISNUMBER(D83)*(D83&gt;F83))+((G83="Østerrike")*ISNUMBER(D83)*(F83&gt;D83))+((C84="Østerrike")*ISNUMBER(D84)*(D84&gt;F84))+((G84="Østerrike")*ISNUMBER(D84)*(F84&gt;D84))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z81">
         <f>((C79="Østerrike")*ISNUMBER(D79)*(D79=F79))+((G79="Østerrike")*ISNUMBER(D79)*(F79=D79))+((C80="Østerrike")*ISNUMBER(D80)*(D80=F80))+((G80="Østerrike")*ISNUMBER(D80)*(F80=D80))+((C81="Østerrike")*ISNUMBER(D81)*(D81=F81))+((G81="Østerrike")*ISNUMBER(D81)*(F81=D81))+((C82="Østerrike")*ISNUMBER(D82)*(D82=F82))+((G82="Østerrike")*ISNUMBER(D82)*(F82=D82))+((C83="Østerrike")*ISNUMBER(D83)*(D83=F83))+((G83="Østerrike")*ISNUMBER(D83)*(F83=D83))+((C84="Østerrike")*ISNUMBER(D84)*(D84=F84))+((G84="Østerrike")*ISNUMBER(D84)*(F84=D84))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA81">
         <f>((C79="Østerrike")*ISNUMBER(D79)*(D79&lt;F79))+((G79="Østerrike")*ISNUMBER(D79)*(F79&lt;D79))+((C80="Østerrike")*ISNUMBER(D80)*(D80&lt;F80))+((G80="Østerrike")*ISNUMBER(D80)*(F80&lt;D80))+((C81="Østerrike")*ISNUMBER(D81)*(D81&lt;F81))+((G81="Østerrike")*ISNUMBER(D81)*(F81&lt;D81))+((C82="Østerrike")*ISNUMBER(D82)*(D82&lt;F82))+((G82="Østerrike")*ISNUMBER(D82)*(F82&lt;D82))+((C83="Østerrike")*ISNUMBER(D83)*(D83&lt;F83))+((G83="Østerrike")*ISNUMBER(D83)*(F83&lt;D83))+((C84="Østerrike")*ISNUMBER(D84)*(D84&lt;F84))+((G84="Østerrike")*ISNUMBER(D84)*(F84&lt;D84))</f>
@@ -7945,23 +7945,23 @@
       </c>
       <c r="AB81">
         <f>IF((C79="Østerrike")*ISNUMBER(D79),D79,0)+IF((G79="Østerrike")*ISNUMBER(D79),F79,0)+IF((C80="Østerrike")*ISNUMBER(D80),D80,0)+IF((G80="Østerrike")*ISNUMBER(D80),F80,0)+IF((C81="Østerrike")*ISNUMBER(D81),D81,0)+IF((G81="Østerrike")*ISNUMBER(D81),F81,0)+IF((C82="Østerrike")*ISNUMBER(D82),D82,0)+IF((G82="Østerrike")*ISNUMBER(D82),F82,0)+IF((C83="Østerrike")*ISNUMBER(D83),D83,0)+IF((G83="Østerrike")*ISNUMBER(D83),F83,0)+IF((C84="Østerrike")*ISNUMBER(D84),D84,0)+IF((G84="Østerrike")*ISNUMBER(D84),F84,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC81">
         <f>IF((C79="Østerrike")*ISNUMBER(D79),F79,0)+IF((G79="Østerrike")*ISNUMBER(D79),D79,0)+IF((C80="Østerrike")*ISNUMBER(D80),F80,0)+IF((G80="Østerrike")*ISNUMBER(D80),D80,0)+IF((C81="Østerrike")*ISNUMBER(D81),F81,0)+IF((G81="Østerrike")*ISNUMBER(D81),D81,0)+IF((C82="Østerrike")*ISNUMBER(D82),F82,0)+IF((G82="Østerrike")*ISNUMBER(D82),D82,0)+IF((C83="Østerrike")*ISNUMBER(D83),F83,0)+IF((G83="Østerrike")*ISNUMBER(D83),D83,0)+IF((C84="Østerrike")*ISNUMBER(D84),F84,0)+IF((G84="Østerrike")*ISNUMBER(D84),D84,0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD81">
         <f>AB81-AC81</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AE81">
         <f>3*Y81+Z81</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF81">
         <f>1+((AE79&gt;AE81)+(AE79=AE81)*(AD79&gt;AD81)+(AE79=AE81)*(AD79=AD81)*(AB79&gt;AB81)&gt;0)*1+((AE80&gt;AE81)+(AE80=AE81)*(AD80&gt;AD81)+(AE80=AE81)*(AD80=AD81)*(AB80&gt;AB81)&gt;0)*1+((AE82&gt;AE81)+(AE82=AE81)*(AD82&gt;AD81)+(AE82=AE81)*(AD82=AD81)*(AB82&gt;AB81)&gt;0)*1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7981,7 +7981,7 @@
         <v>29</v>
       </c>
       <c r="F82" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="8" t="s">
         <v>140</v>
@@ -8008,11 +8008,11 @@
       </c>
       <c r="O82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,Y79,IF(AF80=4,Y80,IF(AF81=4,Y81,IF(AF82=4,Y82,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,Z79,IF(AF80=4,Z80,IF(AF81=4,Z81,IF(AF82=4,Z82,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,AA79,IF(AF80=4,AA80,IF(AF81=4,AA81,IF(AF82=4,AA82,"")))),"")</f>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="R82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,AB79,IF(AF80=4,AB80,IF(AF81=4,AB81,IF(AF82=4,AB82,"")))),"")</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,AC79,IF(AF80=4,AC80,IF(AF81=4,AC81,IF(AF82=4,AC82,"")))),"")</f>
@@ -8028,11 +8028,11 @@
       </c>
       <c r="T82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,AD79,IF(AF80=4,AD80,IF(AF81=4,AD81,IF(AF82=4,AD82,"")))),"")</f>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U82" s="3">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,AE79,IF(AF80=4,AE80,IF(AF81=4,AE81,IF(AF82=4,AE82,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W82" t="s">
         <v>142</v>
@@ -8043,11 +8043,11 @@
       </c>
       <c r="Y82">
         <f>((C79="Jordan")*ISNUMBER(D79)*(D79&gt;F79))+((G79="Jordan")*ISNUMBER(D79)*(F79&gt;D79))+((C80="Jordan")*ISNUMBER(D80)*(D80&gt;F80))+((G80="Jordan")*ISNUMBER(D80)*(F80&gt;D80))+((C81="Jordan")*ISNUMBER(D81)*(D81&gt;F81))+((G81="Jordan")*ISNUMBER(D81)*(F81&gt;D81))+((C82="Jordan")*ISNUMBER(D82)*(D82&gt;F82))+((G82="Jordan")*ISNUMBER(D82)*(F82&gt;D82))+((C83="Jordan")*ISNUMBER(D83)*(D83&gt;F83))+((G83="Jordan")*ISNUMBER(D83)*(F83&gt;D83))+((C84="Jordan")*ISNUMBER(D84)*(D84&gt;F84))+((G84="Jordan")*ISNUMBER(D84)*(F84&gt;D84))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z82">
         <f>((C79="Jordan")*ISNUMBER(D79)*(D79=F79))+((G79="Jordan")*ISNUMBER(D79)*(F79=D79))+((C80="Jordan")*ISNUMBER(D80)*(D80=F80))+((G80="Jordan")*ISNUMBER(D80)*(F80=D80))+((C81="Jordan")*ISNUMBER(D81)*(D81=F81))+((G81="Jordan")*ISNUMBER(D81)*(F81=D81))+((C82="Jordan")*ISNUMBER(D82)*(D82=F82))+((G82="Jordan")*ISNUMBER(D82)*(F82=D82))+((C83="Jordan")*ISNUMBER(D83)*(D83=F83))+((G83="Jordan")*ISNUMBER(D83)*(F83=D83))+((C84="Jordan")*ISNUMBER(D84)*(D84=F84))+((G84="Jordan")*ISNUMBER(D84)*(F84=D84))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA82">
         <f>((C79="Jordan")*ISNUMBER(D79)*(D79&lt;F79))+((G79="Jordan")*ISNUMBER(D79)*(F79&lt;D79))+((C80="Jordan")*ISNUMBER(D80)*(D80&lt;F80))+((G80="Jordan")*ISNUMBER(D80)*(F80&lt;D80))+((C81="Jordan")*ISNUMBER(D81)*(D81&lt;F81))+((G81="Jordan")*ISNUMBER(D81)*(F81&lt;D81))+((C82="Jordan")*ISNUMBER(D82)*(D82&lt;F82))+((G82="Jordan")*ISNUMBER(D82)*(F82&lt;D82))+((C83="Jordan")*ISNUMBER(D83)*(D83&lt;F83))+((G83="Jordan")*ISNUMBER(D83)*(F83&lt;D83))+((C84="Jordan")*ISNUMBER(D84)*(D84&lt;F84))+((G84="Jordan")*ISNUMBER(D84)*(F84&lt;D84))</f>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AB82">
         <f>IF((C79="Jordan")*ISNUMBER(D79),D79,0)+IF((G79="Jordan")*ISNUMBER(D79),F79,0)+IF((C80="Jordan")*ISNUMBER(D80),D80,0)+IF((G80="Jordan")*ISNUMBER(D80),F80,0)+IF((C81="Jordan")*ISNUMBER(D81),D81,0)+IF((G81="Jordan")*ISNUMBER(D81),F81,0)+IF((C82="Jordan")*ISNUMBER(D82),D82,0)+IF((G82="Jordan")*ISNUMBER(D82),F82,0)+IF((C83="Jordan")*ISNUMBER(D83),D83,0)+IF((G83="Jordan")*ISNUMBER(D83),F83,0)+IF((C84="Jordan")*ISNUMBER(D84),D84,0)+IF((G84="Jordan")*ISNUMBER(D84),F84,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC82">
         <f>IF((C79="Jordan")*ISNUMBER(D79),F79,0)+IF((G79="Jordan")*ISNUMBER(D79),D79,0)+IF((C80="Jordan")*ISNUMBER(D80),F80,0)+IF((G80="Jordan")*ISNUMBER(D80),D80,0)+IF((C81="Jordan")*ISNUMBER(D81),F81,0)+IF((G81="Jordan")*ISNUMBER(D81),D81,0)+IF((C82="Jordan")*ISNUMBER(D82),F82,0)+IF((G82="Jordan")*ISNUMBER(D82),D82,0)+IF((C83="Jordan")*ISNUMBER(D83),F83,0)+IF((G83="Jordan")*ISNUMBER(D83),D83,0)+IF((C84="Jordan")*ISNUMBER(D84),F84,0)+IF((G84="Jordan")*ISNUMBER(D84),D84,0)</f>
@@ -8063,11 +8063,11 @@
       </c>
       <c r="AD82">
         <f>AB82-AC82</f>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AE82">
         <f>3*Y82+Z82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF82">
         <f>1+((AE79&gt;AE82)+(AE79=AE82)*(AD79&gt;AD82)+(AE79=AE82)*(AD79=AD82)*(AB79&gt;AB82)&gt;0)*1+((AE80&gt;AE82)+(AE80=AE82)*(AD80&gt;AD82)+(AE80=AE82)*(AD80=AD82)*(AB80&gt;AB82)&gt;0)*1+((AE81&gt;AE82)+(AE81=AE82)*(AD81&gt;AD82)+(AE81=AE82)*(AD81=AD82)*(AB81&gt;AB82)&gt;0)*1</f>
@@ -8085,13 +8085,13 @@
         <v>142</v>
       </c>
       <c r="D83" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>139</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="F84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>141</v>
@@ -8145,30 +8145,30 @@
       </c>
     </row>
     <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="57" t="s">
+      <c r="A85" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="B85" s="57"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57"/>
-      <c r="E85" s="57"/>
-      <c r="F85" s="57"/>
-      <c r="G85" s="57"/>
-      <c r="H85" s="57"/>
-      <c r="I85" s="57"/>
-      <c r="J85" s="57"/>
-      <c r="K85" s="57"/>
-      <c r="M85" s="58" t="s">
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="60"/>
+      <c r="I85" s="60"/>
+      <c r="J85" s="60"/>
+      <c r="K85" s="60"/>
+      <c r="M85" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="N85" s="58"/>
-      <c r="O85" s="58"/>
-      <c r="P85" s="58"/>
-      <c r="Q85" s="58"/>
-      <c r="R85" s="58"/>
-      <c r="S85" s="58"/>
-      <c r="T85" s="58"/>
-      <c r="U85" s="58"/>
+      <c r="N85" s="61"/>
+      <c r="O85" s="61"/>
+      <c r="P85" s="61"/>
+      <c r="Q85" s="61"/>
+      <c r="R85" s="61"/>
+      <c r="S85" s="61"/>
+      <c r="T85" s="61"/>
+      <c r="U85" s="61"/>
     </row>
     <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
@@ -8241,13 +8241,13 @@
         <v>146</v>
       </c>
       <c r="D87" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>147</v>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="M87" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,W87,IF(AF88=1,W88,IF(AF89=1,W89,IF(AF90=1,W90,"")))),"")</f>
-        <v>DR Kongo</v>
+        <v>Portugal</v>
       </c>
       <c r="N87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,X87,IF(AF88=1,X88,IF(AF89=1,X89,IF(AF90=1,X90,"")))),"")</f>
@@ -8274,11 +8274,11 @@
       </c>
       <c r="O87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,Y87,IF(AF88=1,Y88,IF(AF89=1,Y89,IF(AF90=1,Y90,"")))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,Z87,IF(AF88=1,Z88,IF(AF89=1,Z89,IF(AF90=1,Z90,"")))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,AA87,IF(AF88=1,AA88,IF(AF89=1,AA89,IF(AF90=1,AA90,"")))),"")</f>
@@ -8286,19 +8286,19 @@
       </c>
       <c r="R87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,AB87,IF(AF88=1,AB88,IF(AF89=1,AB89,IF(AF90=1,AB90,"")))),"")</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,AC87,IF(AF88=1,AC88,IF(AF89=1,AC89,IF(AF90=1,AC90,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,AD87,IF(AF88=1,AD88,IF(AF89=1,AD89,IF(AF90=1,AD90,"")))),"")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U87" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,AE87,IF(AF88=1,AE88,IF(AF89=1,AE89,IF(AF90=1,AE90,"")))),"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W87" t="s">
         <v>146</v>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="Y87">
         <f>((C87="Portugal")*ISNUMBER(D87)*(D87&gt;F87))+((G87="Portugal")*ISNUMBER(D87)*(F87&gt;D87))+((C88="Portugal")*ISNUMBER(D88)*(D88&gt;F88))+((G88="Portugal")*ISNUMBER(D88)*(F88&gt;D88))+((C89="Portugal")*ISNUMBER(D89)*(D89&gt;F89))+((G89="Portugal")*ISNUMBER(D89)*(F89&gt;D89))+((C90="Portugal")*ISNUMBER(D90)*(D90&gt;F90))+((G90="Portugal")*ISNUMBER(D90)*(F90&gt;D90))+((C91="Portugal")*ISNUMBER(D91)*(D91&gt;F91))+((G91="Portugal")*ISNUMBER(D91)*(F91&gt;D91))+((C92="Portugal")*ISNUMBER(D92)*(D92&gt;F92))+((G92="Portugal")*ISNUMBER(D92)*(F92&gt;D92))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z87">
         <f>((C87="Portugal")*ISNUMBER(D87)*(D87=F87))+((G87="Portugal")*ISNUMBER(D87)*(F87=D87))+((C88="Portugal")*ISNUMBER(D88)*(D88=F88))+((G88="Portugal")*ISNUMBER(D88)*(F88=D88))+((C89="Portugal")*ISNUMBER(D89)*(D89=F89))+((G89="Portugal")*ISNUMBER(D89)*(F89=D89))+((C90="Portugal")*ISNUMBER(D90)*(D90=F90))+((G90="Portugal")*ISNUMBER(D90)*(F90=D90))+((C91="Portugal")*ISNUMBER(D91)*(D91=F91))+((G91="Portugal")*ISNUMBER(D91)*(F91=D91))+((C92="Portugal")*ISNUMBER(D92)*(D92=F92))+((G92="Portugal")*ISNUMBER(D92)*(F92=D92))</f>
@@ -8317,27 +8317,27 @@
       </c>
       <c r="AA87">
         <f>((C87="Portugal")*ISNUMBER(D87)*(D87&lt;F87))+((G87="Portugal")*ISNUMBER(D87)*(F87&lt;D87))+((C88="Portugal")*ISNUMBER(D88)*(D88&lt;F88))+((G88="Portugal")*ISNUMBER(D88)*(F88&lt;D88))+((C89="Portugal")*ISNUMBER(D89)*(D89&lt;F89))+((G89="Portugal")*ISNUMBER(D89)*(F89&lt;D89))+((C90="Portugal")*ISNUMBER(D90)*(D90&lt;F90))+((G90="Portugal")*ISNUMBER(D90)*(F90&lt;D90))+((C91="Portugal")*ISNUMBER(D91)*(D91&lt;F91))+((G91="Portugal")*ISNUMBER(D91)*(F91&lt;D91))+((C92="Portugal")*ISNUMBER(D92)*(D92&lt;F92))+((G92="Portugal")*ISNUMBER(D92)*(F92&lt;D92))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB87">
         <f>IF((C87="Portugal")*ISNUMBER(D87),D87,0)+IF((G87="Portugal")*ISNUMBER(D87),F87,0)+IF((C88="Portugal")*ISNUMBER(D88),D88,0)+IF((G88="Portugal")*ISNUMBER(D88),F88,0)+IF((C89="Portugal")*ISNUMBER(D89),D89,0)+IF((G89="Portugal")*ISNUMBER(D89),F89,0)+IF((C90="Portugal")*ISNUMBER(D90),D90,0)+IF((G90="Portugal")*ISNUMBER(D90),F90,0)+IF((C91="Portugal")*ISNUMBER(D91),D91,0)+IF((G91="Portugal")*ISNUMBER(D91),F91,0)+IF((C92="Portugal")*ISNUMBER(D92),D92,0)+IF((G92="Portugal")*ISNUMBER(D92),F92,0)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC87">
         <f>IF((C87="Portugal")*ISNUMBER(D87),F87,0)+IF((G87="Portugal")*ISNUMBER(D87),D87,0)+IF((C88="Portugal")*ISNUMBER(D88),F88,0)+IF((G88="Portugal")*ISNUMBER(D88),D88,0)+IF((C89="Portugal")*ISNUMBER(D89),F89,0)+IF((G89="Portugal")*ISNUMBER(D89),D89,0)+IF((C90="Portugal")*ISNUMBER(D90),F90,0)+IF((G90="Portugal")*ISNUMBER(D90),D90,0)+IF((C91="Portugal")*ISNUMBER(D91),F91,0)+IF((G91="Portugal")*ISNUMBER(D91),D91,0)+IF((C92="Portugal")*ISNUMBER(D92),F92,0)+IF((G92="Portugal")*ISNUMBER(D92),D92,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD87">
         <f>AB87-AC87</f>
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="AE87">
         <f>3*Y87+Z87</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF87">
         <f>1+((AE88&gt;AE87)+(AE88=AE87)*(AD88&gt;AD87)+(AE88=AE87)*(AD88=AD87)*(AB88&gt;AB87)&gt;0)*1+((AE89&gt;AE87)+(AE89=AE87)*(AD89&gt;AD87)+(AE89=AE87)*(AD89=AD87)*(AB89&gt;AB87)&gt;0)*1+((AE90&gt;AE87)+(AE90=AE87)*(AD90&gt;AD87)+(AE90=AE87)*(AD90=AD87)*(AB90&gt;AB87)&gt;0)*1</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8357,7 +8357,7 @@
         <v>29</v>
       </c>
       <c r="F88" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>149</v>
@@ -8384,11 +8384,11 @@
       </c>
       <c r="O88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,Y87,IF(AF88=2,Y88,IF(AF89=2,Y89,IF(AF90=2,Y90,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,Z87,IF(AF88=2,Z88,IF(AF89=2,Z89,IF(AF90=2,Z90,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,AA87,IF(AF88=2,AA88,IF(AF89=2,AA89,IF(AF90=2,AA90,"")))),"")</f>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="R88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,AB87,IF(AF88=2,AB88,IF(AF89=2,AB89,IF(AF90=2,AB90,"")))),"")</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,AC87,IF(AF88=2,AC88,IF(AF89=2,AC89,IF(AF90=2,AC90,"")))),"")</f>
@@ -8404,11 +8404,11 @@
       </c>
       <c r="T88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,AD87,IF(AF88=2,AD88,IF(AF89=2,AD89,IF(AF90=2,AD90,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U88" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,AE87,IF(AF88=2,AE88,IF(AF89=2,AE89,IF(AF90=2,AE90,"")))),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W88" t="s">
         <v>147</v>
@@ -8419,35 +8419,35 @@
       </c>
       <c r="Y88">
         <f>((C87="DR Kongo")*ISNUMBER(D87)*(D87&gt;F87))+((G87="DR Kongo")*ISNUMBER(D87)*(F87&gt;D87))+((C88="DR Kongo")*ISNUMBER(D88)*(D88&gt;F88))+((G88="DR Kongo")*ISNUMBER(D88)*(F88&gt;D88))+((C89="DR Kongo")*ISNUMBER(D89)*(D89&gt;F89))+((G89="DR Kongo")*ISNUMBER(D89)*(F89&gt;D89))+((C90="DR Kongo")*ISNUMBER(D90)*(D90&gt;F90))+((G90="DR Kongo")*ISNUMBER(D90)*(F90&gt;D90))+((C91="DR Kongo")*ISNUMBER(D91)*(D91&gt;F91))+((G91="DR Kongo")*ISNUMBER(D91)*(F91&gt;D91))+((C92="DR Kongo")*ISNUMBER(D92)*(D92&gt;F92))+((G92="DR Kongo")*ISNUMBER(D92)*(F92&gt;D92))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z88">
         <f>((C87="DR Kongo")*ISNUMBER(D87)*(D87=F87))+((G87="DR Kongo")*ISNUMBER(D87)*(F87=D87))+((C88="DR Kongo")*ISNUMBER(D88)*(D88=F88))+((G88="DR Kongo")*ISNUMBER(D88)*(F88=D88))+((C89="DR Kongo")*ISNUMBER(D89)*(D89=F89))+((G89="DR Kongo")*ISNUMBER(D89)*(F89=D89))+((C90="DR Kongo")*ISNUMBER(D90)*(D90=F90))+((G90="DR Kongo")*ISNUMBER(D90)*(F90=D90))+((C91="DR Kongo")*ISNUMBER(D91)*(D91=F91))+((G91="DR Kongo")*ISNUMBER(D91)*(F91=D91))+((C92="DR Kongo")*ISNUMBER(D92)*(D92=F92))+((G92="DR Kongo")*ISNUMBER(D92)*(F92=D92))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA88">
         <f>((C87="DR Kongo")*ISNUMBER(D87)*(D87&lt;F87))+((G87="DR Kongo")*ISNUMBER(D87)*(F87&lt;D87))+((C88="DR Kongo")*ISNUMBER(D88)*(D88&lt;F88))+((G88="DR Kongo")*ISNUMBER(D88)*(F88&lt;D88))+((C89="DR Kongo")*ISNUMBER(D89)*(D89&lt;F89))+((G89="DR Kongo")*ISNUMBER(D89)*(F89&lt;D89))+((C90="DR Kongo")*ISNUMBER(D90)*(D90&lt;F90))+((G90="DR Kongo")*ISNUMBER(D90)*(F90&lt;D90))+((C91="DR Kongo")*ISNUMBER(D91)*(D91&lt;F91))+((G91="DR Kongo")*ISNUMBER(D91)*(F91&lt;D91))+((C92="DR Kongo")*ISNUMBER(D92)*(D92&lt;F92))+((G92="DR Kongo")*ISNUMBER(D92)*(F92&lt;D92))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB88">
         <f>IF((C87="DR Kongo")*ISNUMBER(D87),D87,0)+IF((G87="DR Kongo")*ISNUMBER(D87),F87,0)+IF((C88="DR Kongo")*ISNUMBER(D88),D88,0)+IF((G88="DR Kongo")*ISNUMBER(D88),F88,0)+IF((C89="DR Kongo")*ISNUMBER(D89),D89,0)+IF((G89="DR Kongo")*ISNUMBER(D89),F89,0)+IF((C90="DR Kongo")*ISNUMBER(D90),D90,0)+IF((G90="DR Kongo")*ISNUMBER(D90),F90,0)+IF((C91="DR Kongo")*ISNUMBER(D91),D91,0)+IF((G91="DR Kongo")*ISNUMBER(D91),F91,0)+IF((C92="DR Kongo")*ISNUMBER(D92),D92,0)+IF((G92="DR Kongo")*ISNUMBER(D92),F92,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC88">
         <f>IF((C87="DR Kongo")*ISNUMBER(D87),F87,0)+IF((G87="DR Kongo")*ISNUMBER(D87),D87,0)+IF((C88="DR Kongo")*ISNUMBER(D88),F88,0)+IF((G88="DR Kongo")*ISNUMBER(D88),D88,0)+IF((C89="DR Kongo")*ISNUMBER(D89),F89,0)+IF((G89="DR Kongo")*ISNUMBER(D89),D89,0)+IF((C90="DR Kongo")*ISNUMBER(D90),F90,0)+IF((G90="DR Kongo")*ISNUMBER(D90),D90,0)+IF((C91="DR Kongo")*ISNUMBER(D91),F91,0)+IF((G91="DR Kongo")*ISNUMBER(D91),D91,0)+IF((C92="DR Kongo")*ISNUMBER(D92),F92,0)+IF((G92="DR Kongo")*ISNUMBER(D92),D92,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD88">
         <f>AB88-AC88</f>
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AE88">
         <f>3*Y88+Z88</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF88">
         <f>1+((AE87&gt;AE88)+(AE87=AE88)*(AD87&gt;AD88)+(AE87=AE88)*(AD87=AD88)*(AB87&gt;AB88)&gt;0)*1+((AE89&gt;AE88)+(AE89=AE88)*(AD89&gt;AD88)+(AE89=AE88)*(AD89=AD88)*(AB89&gt;AB88)&gt;0)*1+((AE90&gt;AE88)+(AE90=AE88)*(AD90&gt;AD88)+(AE90=AE88)*(AD90=AD88)*(AB90&gt;AB88)&gt;0)*1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8461,13 +8461,13 @@
         <v>146</v>
       </c>
       <c r="D89" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F89" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>148</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,Y87,IF(AF88=3,Y88,IF(AF89=3,Y89,IF(AF90=3,Y90,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,Z87,IF(AF88=3,Z88,IF(AF89=3,Z89,IF(AF90=3,Z90,"")))),"")</f>
@@ -8502,23 +8502,23 @@
       </c>
       <c r="Q89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,AA87,IF(AF88=3,AA88,IF(AF89=3,AA89,IF(AF90=3,AA90,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,AB87,IF(AF88=3,AB88,IF(AF89=3,AB89,IF(AF90=3,AB90,"")))),"")</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,AC87,IF(AF88=3,AC88,IF(AF89=3,AC89,IF(AF90=3,AC90,"")))),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,AD87,IF(AF88=3,AD88,IF(AF89=3,AD89,IF(AF90=3,AD90,"")))),"")</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="U89" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,AE87,IF(AF88=3,AE88,IF(AF89=3,AE89,IF(AF90=3,AE90,"")))),"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W89" t="s">
         <v>148</v>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="Y89">
         <f>((C87="Usbekistan")*ISNUMBER(D87)*(D87&gt;F87))+((G87="Usbekistan")*ISNUMBER(D87)*(F87&gt;D87))+((C88="Usbekistan")*ISNUMBER(D88)*(D88&gt;F88))+((G88="Usbekistan")*ISNUMBER(D88)*(F88&gt;D88))+((C89="Usbekistan")*ISNUMBER(D89)*(D89&gt;F89))+((G89="Usbekistan")*ISNUMBER(D89)*(F89&gt;D89))+((C90="Usbekistan")*ISNUMBER(D90)*(D90&gt;F90))+((G90="Usbekistan")*ISNUMBER(D90)*(F90&gt;D90))+((C91="Usbekistan")*ISNUMBER(D91)*(D91&gt;F91))+((G91="Usbekistan")*ISNUMBER(D91)*(F91&gt;D91))+((C92="Usbekistan")*ISNUMBER(D92)*(D92&gt;F92))+((G92="Usbekistan")*ISNUMBER(D92)*(F92&gt;D92))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z89">
         <f>((C87="Usbekistan")*ISNUMBER(D87)*(D87=F87))+((G87="Usbekistan")*ISNUMBER(D87)*(F87=D87))+((C88="Usbekistan")*ISNUMBER(D88)*(D88=F88))+((G88="Usbekistan")*ISNUMBER(D88)*(F88=D88))+((C89="Usbekistan")*ISNUMBER(D89)*(D89=F89))+((G89="Usbekistan")*ISNUMBER(D89)*(F89=D89))+((C90="Usbekistan")*ISNUMBER(D90)*(D90=F90))+((G90="Usbekistan")*ISNUMBER(D90)*(F90=D90))+((C91="Usbekistan")*ISNUMBER(D91)*(D91=F91))+((G91="Usbekistan")*ISNUMBER(D91)*(F91=D91))+((C92="Usbekistan")*ISNUMBER(D92)*(D92=F92))+((G92="Usbekistan")*ISNUMBER(D92)*(F92=D92))</f>
@@ -8537,23 +8537,23 @@
       </c>
       <c r="AA89">
         <f>((C87="Usbekistan")*ISNUMBER(D87)*(D87&lt;F87))+((G87="Usbekistan")*ISNUMBER(D87)*(F87&lt;D87))+((C88="Usbekistan")*ISNUMBER(D88)*(D88&lt;F88))+((G88="Usbekistan")*ISNUMBER(D88)*(F88&lt;D88))+((C89="Usbekistan")*ISNUMBER(D89)*(D89&lt;F89))+((G89="Usbekistan")*ISNUMBER(D89)*(F89&lt;D89))+((C90="Usbekistan")*ISNUMBER(D90)*(D90&lt;F90))+((G90="Usbekistan")*ISNUMBER(D90)*(F90&lt;D90))+((C91="Usbekistan")*ISNUMBER(D91)*(D91&lt;F91))+((G91="Usbekistan")*ISNUMBER(D91)*(F91&lt;D91))+((C92="Usbekistan")*ISNUMBER(D92)*(D92&lt;F92))+((G92="Usbekistan")*ISNUMBER(D92)*(F92&lt;D92))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB89">
         <f>IF((C87="Usbekistan")*ISNUMBER(D87),D87,0)+IF((G87="Usbekistan")*ISNUMBER(D87),F87,0)+IF((C88="Usbekistan")*ISNUMBER(D88),D88,0)+IF((G88="Usbekistan")*ISNUMBER(D88),F88,0)+IF((C89="Usbekistan")*ISNUMBER(D89),D89,0)+IF((G89="Usbekistan")*ISNUMBER(D89),F89,0)+IF((C90="Usbekistan")*ISNUMBER(D90),D90,0)+IF((G90="Usbekistan")*ISNUMBER(D90),F90,0)+IF((C91="Usbekistan")*ISNUMBER(D91),D91,0)+IF((G91="Usbekistan")*ISNUMBER(D91),F91,0)+IF((C92="Usbekistan")*ISNUMBER(D92),D92,0)+IF((G92="Usbekistan")*ISNUMBER(D92),F92,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC89">
         <f>IF((C87="Usbekistan")*ISNUMBER(D87),F87,0)+IF((G87="Usbekistan")*ISNUMBER(D87),D87,0)+IF((C88="Usbekistan")*ISNUMBER(D88),F88,0)+IF((G88="Usbekistan")*ISNUMBER(D88),D88,0)+IF((C89="Usbekistan")*ISNUMBER(D89),F89,0)+IF((G89="Usbekistan")*ISNUMBER(D89),D89,0)+IF((C90="Usbekistan")*ISNUMBER(D90),F90,0)+IF((G90="Usbekistan")*ISNUMBER(D90),D90,0)+IF((C91="Usbekistan")*ISNUMBER(D91),F91,0)+IF((G91="Usbekistan")*ISNUMBER(D91),D91,0)+IF((C92="Usbekistan")*ISNUMBER(D92),F92,0)+IF((G92="Usbekistan")*ISNUMBER(D92),D92,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD89">
         <f>AB89-AC89</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AE89">
         <f>3*Y89+Z89</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF89">
         <f>1+((AE87&gt;AE89)+(AE87=AE89)*(AD87&gt;AD89)+(AE87=AE89)*(AD87=AD89)*(AB87&gt;AB89)&gt;0)*1+((AE88&gt;AE89)+(AE88=AE89)*(AD88&gt;AD89)+(AE88=AE89)*(AD88=AD89)*(AB88&gt;AB89)&gt;0)*1+((AE90&gt;AE89)+(AE90=AE89)*(AD90&gt;AD89)+(AE90=AE89)*(AD90=AD89)*(AB90&gt;AB89)&gt;0)*1</f>
@@ -8577,7 +8577,7 @@
         <v>29</v>
       </c>
       <c r="F90" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>147</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="M90" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,W87,IF(AF88=4,W88,IF(AF89=4,W89,IF(AF90=4,W90,"")))),"")</f>
-        <v>Portugal</v>
+        <v>DR Kongo</v>
       </c>
       <c r="N90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,X87,IF(AF88=4,X88,IF(AF89=4,X89,IF(AF90=4,X90,"")))),"")</f>
@@ -8604,11 +8604,11 @@
       </c>
       <c r="O90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,Y87,IF(AF88=4,Y88,IF(AF89=4,Y89,IF(AF90=4,Y90,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,Z87,IF(AF88=4,Z88,IF(AF89=4,Z89,IF(AF90=4,Z90,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,AA87,IF(AF88=4,AA88,IF(AF89=4,AA89,IF(AF90=4,AA90,"")))),"")</f>
@@ -8616,19 +8616,19 @@
       </c>
       <c r="R90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,AB87,IF(AF88=4,AB88,IF(AF89=4,AB89,IF(AF90=4,AB90,"")))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,AC87,IF(AF88=4,AC88,IF(AF89=4,AC89,IF(AF90=4,AC90,"")))),"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,AD87,IF(AF88=4,AD88,IF(AF89=4,AD89,IF(AF90=4,AD90,"")))),"")</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="U90" s="3">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,AE87,IF(AF88=4,AE88,IF(AF89=4,AE89,IF(AF90=4,AE90,"")))),"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W90" t="s">
         <v>149</v>
@@ -8639,11 +8639,11 @@
       </c>
       <c r="Y90">
         <f>((C87="Colombia")*ISNUMBER(D87)*(D87&gt;F87))+((G87="Colombia")*ISNUMBER(D87)*(F87&gt;D87))+((C88="Colombia")*ISNUMBER(D88)*(D88&gt;F88))+((G88="Colombia")*ISNUMBER(D88)*(F88&gt;D88))+((C89="Colombia")*ISNUMBER(D89)*(D89&gt;F89))+((G89="Colombia")*ISNUMBER(D89)*(F89&gt;D89))+((C90="Colombia")*ISNUMBER(D90)*(D90&gt;F90))+((G90="Colombia")*ISNUMBER(D90)*(F90&gt;D90))+((C91="Colombia")*ISNUMBER(D91)*(D91&gt;F91))+((G91="Colombia")*ISNUMBER(D91)*(F91&gt;D91))+((C92="Colombia")*ISNUMBER(D92)*(D92&gt;F92))+((G92="Colombia")*ISNUMBER(D92)*(F92&gt;D92))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z90">
         <f>((C87="Colombia")*ISNUMBER(D87)*(D87=F87))+((G87="Colombia")*ISNUMBER(D87)*(F87=D87))+((C88="Colombia")*ISNUMBER(D88)*(D88=F88))+((G88="Colombia")*ISNUMBER(D88)*(F88=D88))+((C89="Colombia")*ISNUMBER(D89)*(D89=F89))+((G89="Colombia")*ISNUMBER(D89)*(F89=D89))+((C90="Colombia")*ISNUMBER(D90)*(D90=F90))+((G90="Colombia")*ISNUMBER(D90)*(F90=D90))+((C91="Colombia")*ISNUMBER(D91)*(D91=F91))+((G91="Colombia")*ISNUMBER(D91)*(F91=D91))+((C92="Colombia")*ISNUMBER(D92)*(D92=F92))+((G92="Colombia")*ISNUMBER(D92)*(F92=D92))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA90">
         <f>((C87="Colombia")*ISNUMBER(D87)*(D87&lt;F87))+((G87="Colombia")*ISNUMBER(D87)*(F87&lt;D87))+((C88="Colombia")*ISNUMBER(D88)*(D88&lt;F88))+((G88="Colombia")*ISNUMBER(D88)*(F88&lt;D88))+((C89="Colombia")*ISNUMBER(D89)*(D89&lt;F89))+((G89="Colombia")*ISNUMBER(D89)*(F89&lt;D89))+((C90="Colombia")*ISNUMBER(D90)*(D90&lt;F90))+((G90="Colombia")*ISNUMBER(D90)*(F90&lt;D90))+((C91="Colombia")*ISNUMBER(D91)*(D91&lt;F91))+((G91="Colombia")*ISNUMBER(D91)*(F91&lt;D91))+((C92="Colombia")*ISNUMBER(D92)*(D92&lt;F92))+((G92="Colombia")*ISNUMBER(D92)*(F92&lt;D92))</f>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AB90">
         <f>IF((C87="Colombia")*ISNUMBER(D87),D87,0)+IF((G87="Colombia")*ISNUMBER(D87),F87,0)+IF((C88="Colombia")*ISNUMBER(D88),D88,0)+IF((G88="Colombia")*ISNUMBER(D88),F88,0)+IF((C89="Colombia")*ISNUMBER(D89),D89,0)+IF((G89="Colombia")*ISNUMBER(D89),F89,0)+IF((C90="Colombia")*ISNUMBER(D90),D90,0)+IF((G90="Colombia")*ISNUMBER(D90),F90,0)+IF((C91="Colombia")*ISNUMBER(D91),D91,0)+IF((G91="Colombia")*ISNUMBER(D91),F91,0)+IF((C92="Colombia")*ISNUMBER(D92),D92,0)+IF((G92="Colombia")*ISNUMBER(D92),F92,0)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC90">
         <f>IF((C87="Colombia")*ISNUMBER(D87),F87,0)+IF((G87="Colombia")*ISNUMBER(D87),D87,0)+IF((C88="Colombia")*ISNUMBER(D88),F88,0)+IF((G88="Colombia")*ISNUMBER(D88),D88,0)+IF((C89="Colombia")*ISNUMBER(D89),F89,0)+IF((G89="Colombia")*ISNUMBER(D89),D89,0)+IF((C90="Colombia")*ISNUMBER(D90),F90,0)+IF((G90="Colombia")*ISNUMBER(D90),D90,0)+IF((C91="Colombia")*ISNUMBER(D91),F91,0)+IF((G91="Colombia")*ISNUMBER(D91),D91,0)+IF((C92="Colombia")*ISNUMBER(D92),F92,0)+IF((G92="Colombia")*ISNUMBER(D92),D92,0)</f>
@@ -8659,11 +8659,11 @@
       </c>
       <c r="AD90">
         <f>AB90-AC90</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE90">
         <f>3*Y90+Z90</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF90">
         <f>1+((AE87&gt;AE90)+(AE87=AE90)*(AD87&gt;AD90)+(AE87=AE90)*(AD87=AD90)*(AB87&gt;AB90)&gt;0)*1+((AE88&gt;AE90)+(AE88=AE90)*(AD88&gt;AD90)+(AE88=AE90)*(AD88=AD90)*(AB88&gt;AB90)&gt;0)*1+((AE89&gt;AE90)+(AE89=AE90)*(AD89&gt;AD90)+(AE89=AE90)*(AD89=AD90)*(AB89&gt;AB90)&gt;0)*1</f>
@@ -8687,7 +8687,7 @@
         <v>29</v>
       </c>
       <c r="F91" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>146</v>
@@ -8741,30 +8741,30 @@
       </c>
     </row>
     <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="57" t="s">
+      <c r="A93" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B93" s="57"/>
-      <c r="C93" s="57"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="57"/>
-      <c r="M93" s="58" t="s">
+      <c r="B93" s="60"/>
+      <c r="C93" s="60"/>
+      <c r="D93" s="60"/>
+      <c r="E93" s="60"/>
+      <c r="F93" s="60"/>
+      <c r="G93" s="60"/>
+      <c r="H93" s="60"/>
+      <c r="I93" s="60"/>
+      <c r="J93" s="60"/>
+      <c r="K93" s="60"/>
+      <c r="M93" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="N93" s="58"/>
-      <c r="O93" s="58"/>
-      <c r="P93" s="58"/>
-      <c r="Q93" s="58"/>
-      <c r="R93" s="58"/>
-      <c r="S93" s="58"/>
-      <c r="T93" s="58"/>
-      <c r="U93" s="58"/>
+      <c r="N93" s="61"/>
+      <c r="O93" s="61"/>
+      <c r="P93" s="61"/>
+      <c r="Q93" s="61"/>
+      <c r="R93" s="61"/>
+      <c r="S93" s="61"/>
+      <c r="T93" s="61"/>
+      <c r="U93" s="61"/>
     </row>
     <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
@@ -8837,13 +8837,13 @@
         <v>154</v>
       </c>
       <c r="D95" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F95" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>155</v>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="M95" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,W95,IF(AF96=1,W96,IF(AF97=1,W97,IF(AF98=1,W98,"")))),"")</f>
-        <v>Panama</v>
+        <v>England</v>
       </c>
       <c r="N95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,X95,IF(AF96=1,X96,IF(AF97=1,X97,IF(AF98=1,X98,"")))),"")</f>
@@ -8882,11 +8882,11 @@
       </c>
       <c r="R95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AB95,IF(AF96=1,AB96,IF(AF97=1,AB97,IF(AF98=1,AB98,"")))),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AC95,IF(AF96=1,AC96,IF(AF97=1,AC97,IF(AF98=1,AC98,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AD95,IF(AF96=1,AD96,IF(AF97=1,AD97,IF(AF98=1,AD98,"")))),"")</f>
@@ -8905,11 +8905,11 @@
       </c>
       <c r="Y95">
         <f>((C95="England")*ISNUMBER(D95)*(D95&gt;F95))+((G95="England")*ISNUMBER(D95)*(F95&gt;D95))+((C96="England")*ISNUMBER(D96)*(D96&gt;F96))+((G96="England")*ISNUMBER(D96)*(F96&gt;D96))+((C97="England")*ISNUMBER(D97)*(D97&gt;F97))+((G97="England")*ISNUMBER(D97)*(F97&gt;D97))+((C98="England")*ISNUMBER(D98)*(D98&gt;F98))+((G98="England")*ISNUMBER(D98)*(F98&gt;D98))+((C99="England")*ISNUMBER(D99)*(D99&gt;F99))+((G99="England")*ISNUMBER(D99)*(F99&gt;D99))+((C100="England")*ISNUMBER(D100)*(D100&gt;F100))+((G100="England")*ISNUMBER(D100)*(F100&gt;D100))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z95">
         <f>((C95="England")*ISNUMBER(D95)*(D95=F95))+((G95="England")*ISNUMBER(D95)*(F95=D95))+((C96="England")*ISNUMBER(D96)*(D96=F96))+((G96="England")*ISNUMBER(D96)*(F96=D96))+((C97="England")*ISNUMBER(D97)*(D97=F97))+((G97="England")*ISNUMBER(D97)*(F97=D97))+((C98="England")*ISNUMBER(D98)*(D98=F98))+((G98="England")*ISNUMBER(D98)*(F98=D98))+((C99="England")*ISNUMBER(D99)*(D99=F99))+((G99="England")*ISNUMBER(D99)*(F99=D99))+((C100="England")*ISNUMBER(D100)*(D100=F100))+((G100="England")*ISNUMBER(D100)*(F100=D100))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA95">
         <f>((C95="England")*ISNUMBER(D95)*(D95&lt;F95))+((G95="England")*ISNUMBER(D95)*(F95&lt;D95))+((C96="England")*ISNUMBER(D96)*(D96&lt;F96))+((G96="England")*ISNUMBER(D96)*(F96&lt;D96))+((C97="England")*ISNUMBER(D97)*(D97&lt;F97))+((G97="England")*ISNUMBER(D97)*(F97&lt;D97))+((C98="England")*ISNUMBER(D98)*(D98&lt;F98))+((G98="England")*ISNUMBER(D98)*(F98&lt;D98))+((C99="England")*ISNUMBER(D99)*(D99&lt;F99))+((G99="England")*ISNUMBER(D99)*(F99&lt;D99))+((C100="England")*ISNUMBER(D100)*(D100&lt;F100))+((G100="England")*ISNUMBER(D100)*(F100&lt;D100))</f>
@@ -8917,23 +8917,23 @@
       </c>
       <c r="AB95">
         <f>IF((C95="England")*ISNUMBER(D95),D95,0)+IF((G95="England")*ISNUMBER(D95),F95,0)+IF((C96="England")*ISNUMBER(D96),D96,0)+IF((G96="England")*ISNUMBER(D96),F96,0)+IF((C97="England")*ISNUMBER(D97),D97,0)+IF((G97="England")*ISNUMBER(D97),F97,0)+IF((C98="England")*ISNUMBER(D98),D98,0)+IF((G98="England")*ISNUMBER(D98),F98,0)+IF((C99="England")*ISNUMBER(D99),D99,0)+IF((G99="England")*ISNUMBER(D99),F99,0)+IF((C100="England")*ISNUMBER(D100),D100,0)+IF((G100="England")*ISNUMBER(D100),F100,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC95">
         <f>IF((C95="England")*ISNUMBER(D95),F95,0)+IF((G95="England")*ISNUMBER(D95),D95,0)+IF((C96="England")*ISNUMBER(D96),F96,0)+IF((G96="England")*ISNUMBER(D96),D96,0)+IF((C97="England")*ISNUMBER(D97),F97,0)+IF((G97="England")*ISNUMBER(D97),D97,0)+IF((C98="England")*ISNUMBER(D98),F98,0)+IF((G98="England")*ISNUMBER(D98),D98,0)+IF((C99="England")*ISNUMBER(D99),F99,0)+IF((G99="England")*ISNUMBER(D99),D99,0)+IF((C100="England")*ISNUMBER(D100),F100,0)+IF((G100="England")*ISNUMBER(D100),D100,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD95">
         <f>AB95-AC95</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE95">
         <f>3*Y95+Z95</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF95">
         <f>1+((AE96&gt;AE95)+(AE96=AE95)*(AD96&gt;AD95)+(AE96=AE95)*(AD96=AD95)*(AB96&gt;AB95)&gt;0)*1+((AE97&gt;AE95)+(AE97=AE95)*(AD97&gt;AD95)+(AE97=AE95)*(AD97=AD95)*(AB97&gt;AB95)&gt;0)*1+((AE98&gt;AE95)+(AE98=AE95)*(AD98&gt;AD95)+(AE98=AE95)*(AD98=AD95)*(AB98&gt;AB95)&gt;0)*1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8947,13 +8947,13 @@
         <v>156</v>
       </c>
       <c r="D96" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F96" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>157</v>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="O96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,Y95,IF(AF96=2,Y96,IF(AF97=2,Y97,IF(AF98=2,Y98,"")))),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,Z95,IF(AF96=2,Z96,IF(AF97=2,Z97,IF(AF98=2,Z98,"")))),"")</f>
@@ -8988,23 +8988,23 @@
       </c>
       <c r="Q96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,AA95,IF(AF96=2,AA96,IF(AF97=2,AA97,IF(AF98=2,AA98,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,AB95,IF(AF96=2,AB96,IF(AF97=2,AB97,IF(AF98=2,AB98,"")))),"")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,AC95,IF(AF96=2,AC96,IF(AF97=2,AC97,IF(AF98=2,AC98,"")))),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,AD95,IF(AF96=2,AD96,IF(AF97=2,AD97,IF(AF98=2,AD98,"")))),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U96" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,AE95,IF(AF96=2,AE96,IF(AF97=2,AE97,IF(AF98=2,AE98,"")))),"")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W96" t="s">
         <v>155</v>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="Y96">
         <f>((C95="Kroatia")*ISNUMBER(D95)*(D95&gt;F95))+((G95="Kroatia")*ISNUMBER(D95)*(F95&gt;D95))+((C96="Kroatia")*ISNUMBER(D96)*(D96&gt;F96))+((G96="Kroatia")*ISNUMBER(D96)*(F96&gt;D96))+((C97="Kroatia")*ISNUMBER(D97)*(D97&gt;F97))+((G97="Kroatia")*ISNUMBER(D97)*(F97&gt;D97))+((C98="Kroatia")*ISNUMBER(D98)*(D98&gt;F98))+((G98="Kroatia")*ISNUMBER(D98)*(F98&gt;D98))+((C99="Kroatia")*ISNUMBER(D99)*(D99&gt;F99))+((G99="Kroatia")*ISNUMBER(D99)*(F99&gt;D99))+((C100="Kroatia")*ISNUMBER(D100)*(D100&gt;F100))+((G100="Kroatia")*ISNUMBER(D100)*(F100&gt;D100))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z96">
         <f>((C95="Kroatia")*ISNUMBER(D95)*(D95=F95))+((G95="Kroatia")*ISNUMBER(D95)*(F95=D95))+((C96="Kroatia")*ISNUMBER(D96)*(D96=F96))+((G96="Kroatia")*ISNUMBER(D96)*(F96=D96))+((C97="Kroatia")*ISNUMBER(D97)*(D97=F97))+((G97="Kroatia")*ISNUMBER(D97)*(F97=D97))+((C98="Kroatia")*ISNUMBER(D98)*(D98=F98))+((G98="Kroatia")*ISNUMBER(D98)*(F98=D98))+((C99="Kroatia")*ISNUMBER(D99)*(D99=F99))+((G99="Kroatia")*ISNUMBER(D99)*(F99=D99))+((C100="Kroatia")*ISNUMBER(D100)*(D100=F100))+((G100="Kroatia")*ISNUMBER(D100)*(F100=D100))</f>
@@ -9023,23 +9023,23 @@
       </c>
       <c r="AA96">
         <f>((C95="Kroatia")*ISNUMBER(D95)*(D95&lt;F95))+((G95="Kroatia")*ISNUMBER(D95)*(F95&lt;D95))+((C96="Kroatia")*ISNUMBER(D96)*(D96&lt;F96))+((G96="Kroatia")*ISNUMBER(D96)*(F96&lt;D96))+((C97="Kroatia")*ISNUMBER(D97)*(D97&lt;F97))+((G97="Kroatia")*ISNUMBER(D97)*(F97&lt;D97))+((C98="Kroatia")*ISNUMBER(D98)*(D98&lt;F98))+((G98="Kroatia")*ISNUMBER(D98)*(F98&lt;D98))+((C99="Kroatia")*ISNUMBER(D99)*(D99&lt;F99))+((G99="Kroatia")*ISNUMBER(D99)*(F99&lt;D99))+((C100="Kroatia")*ISNUMBER(D100)*(D100&lt;F100))+((G100="Kroatia")*ISNUMBER(D100)*(F100&lt;D100))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB96">
         <f>IF((C95="Kroatia")*ISNUMBER(D95),D95,0)+IF((G95="Kroatia")*ISNUMBER(D95),F95,0)+IF((C96="Kroatia")*ISNUMBER(D96),D96,0)+IF((G96="Kroatia")*ISNUMBER(D96),F96,0)+IF((C97="Kroatia")*ISNUMBER(D97),D97,0)+IF((G97="Kroatia")*ISNUMBER(D97),F97,0)+IF((C98="Kroatia")*ISNUMBER(D98),D98,0)+IF((G98="Kroatia")*ISNUMBER(D98),F98,0)+IF((C99="Kroatia")*ISNUMBER(D99),D99,0)+IF((G99="Kroatia")*ISNUMBER(D99),F99,0)+IF((C100="Kroatia")*ISNUMBER(D100),D100,0)+IF((G100="Kroatia")*ISNUMBER(D100),F100,0)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC96">
         <f>IF((C95="Kroatia")*ISNUMBER(D95),F95,0)+IF((G95="Kroatia")*ISNUMBER(D95),D95,0)+IF((C96="Kroatia")*ISNUMBER(D96),F96,0)+IF((G96="Kroatia")*ISNUMBER(D96),D96,0)+IF((C97="Kroatia")*ISNUMBER(D97),F97,0)+IF((G97="Kroatia")*ISNUMBER(D97),D97,0)+IF((C98="Kroatia")*ISNUMBER(D98),F98,0)+IF((G98="Kroatia")*ISNUMBER(D98),D98,0)+IF((C99="Kroatia")*ISNUMBER(D99),F99,0)+IF((G99="Kroatia")*ISNUMBER(D99),D99,0)+IF((C100="Kroatia")*ISNUMBER(D100),F100,0)+IF((G100="Kroatia")*ISNUMBER(D100),D100,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD96">
         <f>AB96-AC96</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE96">
         <f>3*Y96+Z96</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF96">
         <f>1+((AE95&gt;AE96)+(AE95=AE96)*(AD95&gt;AD96)+(AE95=AE96)*(AD95=AD96)*(AB95&gt;AB96)&gt;0)*1+((AE97&gt;AE96)+(AE97=AE96)*(AD97&gt;AD96)+(AE97=AE96)*(AD97=AD96)*(AB97&gt;AB96)&gt;0)*1+((AE98&gt;AE96)+(AE98=AE96)*(AD98&gt;AD96)+(AE98=AE96)*(AD98=AD96)*(AB98&gt;AB96)&gt;0)*1</f>
@@ -9057,13 +9057,13 @@
         <v>154</v>
       </c>
       <c r="D97" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F97" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>156</v>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="M97" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,W95,IF(AF96=3,W96,IF(AF97=3,W97,IF(AF98=3,W98,"")))),"")</f>
-        <v>England</v>
+        <v>Ghana</v>
       </c>
       <c r="N97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,X95,IF(AF96=3,X96,IF(AF97=3,X97,IF(AF98=3,X98,"")))),"")</f>
@@ -9090,27 +9090,27 @@
       </c>
       <c r="O97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,Y95,IF(AF96=3,Y96,IF(AF97=3,Y97,IF(AF98=3,Y98,"")))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,Z95,IF(AF96=3,Z96,IF(AF97=3,Z97,IF(AF98=3,Z98,"")))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AA95,IF(AF96=3,AA96,IF(AF97=3,AA97,IF(AF98=3,AA98,"")))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AB95,IF(AF96=3,AB96,IF(AF97=3,AB97,IF(AF98=3,AB98,"")))),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AC95,IF(AF96=3,AC96,IF(AF97=3,AC97,IF(AF98=3,AC98,"")))),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AD95,IF(AF96=3,AD96,IF(AF97=3,AD97,IF(AF98=3,AD98,"")))),"")</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AE95,IF(AF96=3,AE96,IF(AF97=3,AE97,IF(AF98=3,AE98,"")))),"")</f>
@@ -9125,11 +9125,11 @@
       </c>
       <c r="Y97">
         <f>((C95="Ghana")*ISNUMBER(D95)*(D95&gt;F95))+((G95="Ghana")*ISNUMBER(D95)*(F95&gt;D95))+((C96="Ghana")*ISNUMBER(D96)*(D96&gt;F96))+((G96="Ghana")*ISNUMBER(D96)*(F96&gt;D96))+((C97="Ghana")*ISNUMBER(D97)*(D97&gt;F97))+((G97="Ghana")*ISNUMBER(D97)*(F97&gt;D97))+((C98="Ghana")*ISNUMBER(D98)*(D98&gt;F98))+((G98="Ghana")*ISNUMBER(D98)*(F98&gt;D98))+((C99="Ghana")*ISNUMBER(D99)*(D99&gt;F99))+((G99="Ghana")*ISNUMBER(D99)*(F99&gt;D99))+((C100="Ghana")*ISNUMBER(D100)*(D100&gt;F100))+((G100="Ghana")*ISNUMBER(D100)*(F100&gt;D100))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z97">
         <f>((C95="Ghana")*ISNUMBER(D95)*(D95=F95))+((G95="Ghana")*ISNUMBER(D95)*(F95=D95))+((C96="Ghana")*ISNUMBER(D96)*(D96=F96))+((G96="Ghana")*ISNUMBER(D96)*(F96=D96))+((C97="Ghana")*ISNUMBER(D97)*(D97=F97))+((G97="Ghana")*ISNUMBER(D97)*(F97=D97))+((C98="Ghana")*ISNUMBER(D98)*(D98=F98))+((G98="Ghana")*ISNUMBER(D98)*(F98=D98))+((C99="Ghana")*ISNUMBER(D99)*(D99=F99))+((G99="Ghana")*ISNUMBER(D99)*(F99=D99))+((C100="Ghana")*ISNUMBER(D100)*(D100=F100))+((G100="Ghana")*ISNUMBER(D100)*(F100=D100))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA97">
         <f>((C95="Ghana")*ISNUMBER(D95)*(D95&lt;F95))+((G95="Ghana")*ISNUMBER(D95)*(F95&lt;D95))+((C96="Ghana")*ISNUMBER(D96)*(D96&lt;F96))+((G96="Ghana")*ISNUMBER(D96)*(F96&lt;D96))+((C97="Ghana")*ISNUMBER(D97)*(D97&lt;F97))+((G97="Ghana")*ISNUMBER(D97)*(F97&lt;D97))+((C98="Ghana")*ISNUMBER(D98)*(D98&lt;F98))+((G98="Ghana")*ISNUMBER(D98)*(F98&lt;D98))+((C99="Ghana")*ISNUMBER(D99)*(D99&lt;F99))+((G99="Ghana")*ISNUMBER(D99)*(F99&lt;D99))+((C100="Ghana")*ISNUMBER(D100)*(D100&lt;F100))+((G100="Ghana")*ISNUMBER(D100)*(F100&lt;D100))</f>
@@ -9137,23 +9137,23 @@
       </c>
       <c r="AB97">
         <f>IF((C95="Ghana")*ISNUMBER(D95),D95,0)+IF((G95="Ghana")*ISNUMBER(D95),F95,0)+IF((C96="Ghana")*ISNUMBER(D96),D96,0)+IF((G96="Ghana")*ISNUMBER(D96),F96,0)+IF((C97="Ghana")*ISNUMBER(D97),D97,0)+IF((G97="Ghana")*ISNUMBER(D97),F97,0)+IF((C98="Ghana")*ISNUMBER(D98),D98,0)+IF((G98="Ghana")*ISNUMBER(D98),F98,0)+IF((C99="Ghana")*ISNUMBER(D99),D99,0)+IF((G99="Ghana")*ISNUMBER(D99),F99,0)+IF((C100="Ghana")*ISNUMBER(D100),D100,0)+IF((G100="Ghana")*ISNUMBER(D100),F100,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC97">
         <f>IF((C95="Ghana")*ISNUMBER(D95),F95,0)+IF((G95="Ghana")*ISNUMBER(D95),D95,0)+IF((C96="Ghana")*ISNUMBER(D96),F96,0)+IF((G96="Ghana")*ISNUMBER(D96),D96,0)+IF((C97="Ghana")*ISNUMBER(D97),F97,0)+IF((G97="Ghana")*ISNUMBER(D97),D97,0)+IF((C98="Ghana")*ISNUMBER(D98),F98,0)+IF((G98="Ghana")*ISNUMBER(D98),D98,0)+IF((C99="Ghana")*ISNUMBER(D99),F99,0)+IF((G99="Ghana")*ISNUMBER(D99),D99,0)+IF((C100="Ghana")*ISNUMBER(D100),F100,0)+IF((G100="Ghana")*ISNUMBER(D100),D100,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD97">
         <f>AB97-AC97</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AE97">
         <f>3*Y97+Z97</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF97">
         <f>1+((AE95&gt;AE97)+(AE95=AE97)*(AD95&gt;AD97)+(AE95=AE97)*(AD95=AD97)*(AB95&gt;AB97)&gt;0)*1+((AE96&gt;AE97)+(AE96=AE97)*(AD96&gt;AD97)+(AE96=AE97)*(AD96=AD97)*(AB96&gt;AB97)&gt;0)*1+((AE98&gt;AE97)+(AE98=AE97)*(AD98&gt;AD97)+(AE98=AE97)*(AD98=AD97)*(AB98&gt;AB97)&gt;0)*1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9173,7 +9173,7 @@
         <v>29</v>
       </c>
       <c r="F98" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>155</v>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="M98" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,W95,IF(AF96=4,W96,IF(AF97=4,W97,IF(AF98=4,W98,"")))),"")</f>
-        <v>Ghana</v>
+        <v>Panama</v>
       </c>
       <c r="N98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,X95,IF(AF96=4,X96,IF(AF97=4,X97,IF(AF98=4,X98,"")))),"")</f>
@@ -9204,11 +9204,11 @@
       </c>
       <c r="P98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,Z95,IF(AF96=4,Z96,IF(AF97=4,Z97,IF(AF98=4,Z98,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,AA95,IF(AF96=4,AA96,IF(AF97=4,AA97,IF(AF98=4,AA98,"")))),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,AB95,IF(AF96=4,AB96,IF(AF97=4,AB97,IF(AF98=4,AB98,"")))),"")</f>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="S98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,AC95,IF(AF96=4,AC96,IF(AF97=4,AC97,IF(AF98=4,AC98,"")))),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,AD95,IF(AF96=4,AD96,IF(AF97=4,AD97,IF(AF98=4,AD98,"")))),"")</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="U98" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,AE95,IF(AF96=4,AE96,IF(AF97=4,AE97,IF(AF98=4,AE98,"")))),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W98" t="s">
         <v>157</v>
@@ -9235,35 +9235,35 @@
       </c>
       <c r="Y98">
         <f>((C95="Panama")*ISNUMBER(D95)*(D95&gt;F95))+((G95="Panama")*ISNUMBER(D95)*(F95&gt;D95))+((C96="Panama")*ISNUMBER(D96)*(D96&gt;F96))+((G96="Panama")*ISNUMBER(D96)*(F96&gt;D96))+((C97="Panama")*ISNUMBER(D97)*(D97&gt;F97))+((G97="Panama")*ISNUMBER(D97)*(F97&gt;D97))+((C98="Panama")*ISNUMBER(D98)*(D98&gt;F98))+((G98="Panama")*ISNUMBER(D98)*(F98&gt;D98))+((C99="Panama")*ISNUMBER(D99)*(D99&gt;F99))+((G99="Panama")*ISNUMBER(D99)*(F99&gt;D99))+((C100="Panama")*ISNUMBER(D100)*(D100&gt;F100))+((G100="Panama")*ISNUMBER(D100)*(F100&gt;D100))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z98">
         <f>((C95="Panama")*ISNUMBER(D95)*(D95=F95))+((G95="Panama")*ISNUMBER(D95)*(F95=D95))+((C96="Panama")*ISNUMBER(D96)*(D96=F96))+((G96="Panama")*ISNUMBER(D96)*(F96=D96))+((C97="Panama")*ISNUMBER(D97)*(D97=F97))+((G97="Panama")*ISNUMBER(D97)*(F97=D97))+((C98="Panama")*ISNUMBER(D98)*(D98=F98))+((G98="Panama")*ISNUMBER(D98)*(F98=D98))+((C99="Panama")*ISNUMBER(D99)*(D99=F99))+((G99="Panama")*ISNUMBER(D99)*(F99=D99))+((C100="Panama")*ISNUMBER(D100)*(D100=F100))+((G100="Panama")*ISNUMBER(D100)*(F100=D100))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA98">
         <f>((C95="Panama")*ISNUMBER(D95)*(D95&lt;F95))+((G95="Panama")*ISNUMBER(D95)*(F95&lt;D95))+((C96="Panama")*ISNUMBER(D96)*(D96&lt;F96))+((G96="Panama")*ISNUMBER(D96)*(F96&lt;D96))+((C97="Panama")*ISNUMBER(D97)*(D97&lt;F97))+((G97="Panama")*ISNUMBER(D97)*(F97&lt;D97))+((C98="Panama")*ISNUMBER(D98)*(D98&lt;F98))+((G98="Panama")*ISNUMBER(D98)*(F98&lt;D98))+((C99="Panama")*ISNUMBER(D99)*(D99&lt;F99))+((G99="Panama")*ISNUMBER(D99)*(F99&lt;D99))+((C100="Panama")*ISNUMBER(D100)*(D100&lt;F100))+((G100="Panama")*ISNUMBER(D100)*(F100&lt;D100))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB98">
         <f>IF((C95="Panama")*ISNUMBER(D95),D95,0)+IF((G95="Panama")*ISNUMBER(D95),F95,0)+IF((C96="Panama")*ISNUMBER(D96),D96,0)+IF((G96="Panama")*ISNUMBER(D96),F96,0)+IF((C97="Panama")*ISNUMBER(D97),D97,0)+IF((G97="Panama")*ISNUMBER(D97),F97,0)+IF((C98="Panama")*ISNUMBER(D98),D98,0)+IF((G98="Panama")*ISNUMBER(D98),F98,0)+IF((C99="Panama")*ISNUMBER(D99),D99,0)+IF((G99="Panama")*ISNUMBER(D99),F99,0)+IF((C100="Panama")*ISNUMBER(D100),D100,0)+IF((G100="Panama")*ISNUMBER(D100),F100,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC98">
         <f>IF((C95="Panama")*ISNUMBER(D95),F95,0)+IF((G95="Panama")*ISNUMBER(D95),D95,0)+IF((C96="Panama")*ISNUMBER(D96),F96,0)+IF((G96="Panama")*ISNUMBER(D96),D96,0)+IF((C97="Panama")*ISNUMBER(D97),F97,0)+IF((G97="Panama")*ISNUMBER(D97),D97,0)+IF((C98="Panama")*ISNUMBER(D98),F98,0)+IF((G98="Panama")*ISNUMBER(D98),D98,0)+IF((C99="Panama")*ISNUMBER(D99),F99,0)+IF((G99="Panama")*ISNUMBER(D99),D99,0)+IF((C100="Panama")*ISNUMBER(D100),F100,0)+IF((G100="Panama")*ISNUMBER(D100),D100,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD98">
         <f>AB98-AC98</f>
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="AE98">
         <f>3*Y98+Z98</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF98">
         <f>1+((AE95&gt;AE98)+(AE95=AE98)*(AD95&gt;AD98)+(AE95=AE98)*(AD95=AD98)*(AB95&gt;AB98)&gt;0)*1+((AE96&gt;AE98)+(AE96=AE98)*(AD96&gt;AD98)+(AE96=AE98)*(AD96=AD98)*(AB96&gt;AB98)&gt;0)*1+((AE97&gt;AE98)+(AE97=AE98)*(AD97&gt;AD98)+(AE97=AE98)*(AD97=AD98)*(AB97&gt;AB98)&gt;0)*1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9277,13 +9277,13 @@
         <v>157</v>
       </c>
       <c r="D99" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F99" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>154</v>
@@ -9312,13 +9312,13 @@
         <v>155</v>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F100" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>156</v>
@@ -9344,12 +9344,12 @@
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
-      <c r="H101" s="59" t="s">
+      <c r="H101" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="I101" s="59"/>
-      <c r="J101" s="59"/>
-      <c r="K101" s="59"/>
+      <c r="I101" s="62"/>
+      <c r="J101" s="62"/>
+      <c r="K101" s="62"/>
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
@@ -9415,11 +9415,11 @@
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="13"/>
-      <c r="I103" s="60" t="s">
+      <c r="I103" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="J103" s="60"/>
-      <c r="K103" s="60"/>
+      <c r="J103" s="63"/>
+      <c r="K103" s="63"/>
       <c r="L103" s="12"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
@@ -9451,7 +9451,7 @@
       <c r="G104" s="12"/>
       <c r="H104" s="14" t="str">
         <f>COUNTIF(H105:H136,1)&amp;"/16"</f>
-        <v>0/16</v>
+        <v>16/16</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>18</v>
@@ -9487,14 +9487,16 @@
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
       <c r="G105" s="12"/>
-      <c r="H105" s="17"/>
+      <c r="H105" s="17">
+        <v>1</v>
+      </c>
       <c r="I105" s="18" t="str">
         <f>IFERROR(M7,"A1")</f>
-        <v>Sør-Afrika</v>
-      </c>
-      <c r="J105" s="12" t="str">
+        <v>Mexico</v>
+      </c>
+      <c r="J105" s="12">
         <f>IF(H105=1,COUNTIF($H$105:H105,1),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K105" s="19"/>
       <c r="L105" s="12"/>
@@ -9529,7 +9531,7 @@
       <c r="H106" s="20"/>
       <c r="I106" s="21" t="str">
         <f>IFERROR(M8,"A2")</f>
-        <v>Tsjekkia</v>
+        <v>Sør-Korea</v>
       </c>
       <c r="J106" s="12" t="str">
         <f>IF(H106=1,COUNTIF($H$105:H106,1),"")</f>
@@ -9568,7 +9570,7 @@
       <c r="H107" s="17"/>
       <c r="I107" s="18" t="str">
         <f>IFERROR(M15,"B1")</f>
-        <v>Sveits</v>
+        <v>Bosnia-Hercegovina</v>
       </c>
       <c r="J107" s="12" t="str">
         <f>IF(H107=1,COUNTIF($H$105:H107,1),"")</f>
@@ -9643,14 +9645,16 @@
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
-      <c r="H109" s="17"/>
+      <c r="H109" s="17">
+        <v>1</v>
+      </c>
       <c r="I109" s="18" t="str">
         <f>IFERROR(M23,"C1")</f>
-        <v>Skottland</v>
-      </c>
-      <c r="J109" s="12" t="str">
+        <v>Brasil</v>
+      </c>
+      <c r="J109" s="12">
         <f>IF(H109=1,COUNTIF($H$105:H109,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K109" s="19"/>
       <c r="L109" s="12"/>
@@ -9682,14 +9686,16 @@
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
-      <c r="H110" s="20"/>
+      <c r="H110" s="20">
+        <v>1</v>
+      </c>
       <c r="I110" s="21" t="str">
         <f>IFERROR(M24,"C2")</f>
-        <v>Haiti</v>
-      </c>
-      <c r="J110" s="12" t="str">
+        <v>Skottland</v>
+      </c>
+      <c r="J110" s="12">
         <f>IF(H110=1,COUNTIF($H$105:H110,1),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K110" s="22"/>
       <c r="L110" s="12"/>
@@ -9721,14 +9727,16 @@
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
       <c r="G111" s="12"/>
-      <c r="H111" s="17"/>
+      <c r="H111" s="17">
+        <v>1</v>
+      </c>
       <c r="I111" s="18" t="str">
         <f>IFERROR(M31,"D1")</f>
-        <v>Paraguay</v>
-      </c>
-      <c r="J111" s="12" t="str">
+        <v>Tyrkia</v>
+      </c>
+      <c r="J111" s="12">
         <f>IF(H111=1,COUNTIF($H$105:H111,1),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K111" s="19"/>
       <c r="L111" s="12"/>
@@ -9799,14 +9807,16 @@
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
-      <c r="H113" s="17"/>
+      <c r="H113" s="17">
+        <v>1</v>
+      </c>
       <c r="I113" s="18" t="str">
         <f>IFERROR(M39,"E1")</f>
-        <v>Elfenbenskysten</v>
-      </c>
-      <c r="J113" s="12" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="J113" s="12">
         <f>IF(H113=1,COUNTIF($H$105:H113,1),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K113" s="19"/>
       <c r="L113" s="12"/>
@@ -9841,7 +9851,7 @@
       <c r="H114" s="20"/>
       <c r="I114" s="21" t="str">
         <f>IFERROR(M40,"E2")</f>
-        <v>Tyskland</v>
+        <v>Elfenbenskysten</v>
       </c>
       <c r="J114" s="12" t="str">
         <f>IF(H114=1,COUNTIF($H$105:H114,1),"")</f>
@@ -9877,14 +9887,16 @@
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
-      <c r="H115" s="17"/>
+      <c r="H115" s="17">
+        <v>1</v>
+      </c>
       <c r="I115" s="18" t="str">
         <f>IFERROR(M47,"F1")</f>
-        <v>Tunisia</v>
-      </c>
-      <c r="J115" s="12" t="str">
+        <v>Nederland</v>
+      </c>
+      <c r="J115" s="12">
         <f>IF(H115=1,COUNTIF($H$105:H115,1),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K115" s="19"/>
       <c r="L115" s="12"/>
@@ -9919,7 +9931,7 @@
       <c r="H116" s="20"/>
       <c r="I116" s="21" t="str">
         <f>IFERROR(M48,"F2")</f>
-        <v>Japan</v>
+        <v>Sverige</v>
       </c>
       <c r="J116" s="12" t="str">
         <f>IF(H116=1,COUNTIF($H$105:H116,1),"")</f>
@@ -9955,14 +9967,16 @@
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
-      <c r="H117" s="17"/>
+      <c r="H117" s="17">
+        <v>1</v>
+      </c>
       <c r="I117" s="18" t="str">
         <f>IFERROR(M55,"G1")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="J117" s="12" t="str">
+        <v>Belgia</v>
+      </c>
+      <c r="J117" s="12">
         <f>IF(H117=1,COUNTIF($H$105:H117,1),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K117" s="19"/>
       <c r="L117" s="12"/>
@@ -9994,14 +10008,16 @@
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
-      <c r="H118" s="20"/>
+      <c r="H118" s="20">
+        <v>1</v>
+      </c>
       <c r="I118" s="21" t="str">
         <f>IFERROR(M56,"G2")</f>
-        <v>Belgia</v>
-      </c>
-      <c r="J118" s="12" t="str">
+        <v>Egypt</v>
+      </c>
+      <c r="J118" s="12">
         <f>IF(H118=1,COUNTIF($H$105:H118,1),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="K118" s="22"/>
       <c r="L118" s="12"/>
@@ -10033,14 +10049,16 @@
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
-      <c r="H119" s="17"/>
+      <c r="H119" s="17">
+        <v>1</v>
+      </c>
       <c r="I119" s="18" t="str">
         <f>IFERROR(M63,"H1")</f>
-        <v>Saudi Arabia</v>
-      </c>
-      <c r="J119" s="12" t="str">
+        <v>Spania</v>
+      </c>
+      <c r="J119" s="12">
         <f>IF(H119=1,COUNTIF($H$105:H119,1),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="K119" s="19"/>
       <c r="L119" s="12"/>
@@ -10075,7 +10093,7 @@
       <c r="H120" s="20"/>
       <c r="I120" s="21" t="str">
         <f>IFERROR(M64,"H2")</f>
-        <v>Kapp Verde</v>
+        <v>Uruguay</v>
       </c>
       <c r="J120" s="12" t="str">
         <f>IF(H120=1,COUNTIF($H$105:H120,1),"")</f>
@@ -10111,14 +10129,16 @@
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
-      <c r="H121" s="17"/>
+      <c r="H121" s="17">
+        <v>1</v>
+      </c>
       <c r="I121" s="18" t="str">
         <f>IFERROR(M71,"I1")</f>
-        <v>Norge</v>
-      </c>
-      <c r="J121" s="12" t="str">
+        <v>Frankrike</v>
+      </c>
+      <c r="J121" s="12">
         <f>IF(H121=1,COUNTIF($H$105:H121,1),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K121" s="19"/>
       <c r="L121" s="12"/>
@@ -10150,14 +10170,16 @@
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
       <c r="G122" s="12"/>
-      <c r="H122" s="20"/>
+      <c r="H122" s="20">
+        <v>1</v>
+      </c>
       <c r="I122" s="21" t="str">
         <f>IFERROR(M72,"I2")</f>
-        <v>Senegal</v>
-      </c>
-      <c r="J122" s="12" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="J122" s="12">
         <f>IF(H122=1,COUNTIF($H$105:H122,1),"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="K122" s="22"/>
       <c r="L122" s="12"/>
@@ -10189,14 +10211,16 @@
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
-      <c r="H123" s="17"/>
+      <c r="H123" s="17">
+        <v>1</v>
+      </c>
       <c r="I123" s="18" t="str">
         <f>IFERROR(M79,"J1")</f>
-        <v>Algerie</v>
-      </c>
-      <c r="J123" s="12" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="J123" s="12">
         <f>IF(H123=1,COUNTIF($H$105:H123,1),"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="K123" s="19"/>
       <c r="L123" s="12"/>
@@ -10231,7 +10255,7 @@
       <c r="H124" s="20"/>
       <c r="I124" s="21" t="str">
         <f>IFERROR(M80,"J2")</f>
-        <v>Argentina</v>
+        <v>Østerrike</v>
       </c>
       <c r="J124" s="12" t="str">
         <f>IF(H124=1,COUNTIF($H$105:H124,1),"")</f>
@@ -10267,14 +10291,16 @@
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
-      <c r="H125" s="17"/>
+      <c r="H125" s="17">
+        <v>1</v>
+      </c>
       <c r="I125" s="18" t="str">
         <f>IFERROR(M87,"K1")</f>
-        <v>DR Kongo</v>
-      </c>
-      <c r="J125" s="12" t="str">
+        <v>Portugal</v>
+      </c>
+      <c r="J125" s="12">
         <f>IF(H125=1,COUNTIF($H$105:H125,1),"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="K125" s="19"/>
       <c r="L125" s="12"/>
@@ -10345,14 +10371,16 @@
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
-      <c r="H127" s="17"/>
+      <c r="H127" s="17">
+        <v>1</v>
+      </c>
       <c r="I127" s="18" t="str">
         <f>IFERROR(M95,"L1")</f>
-        <v>Panama</v>
-      </c>
-      <c r="J127" s="12" t="str">
+        <v>England</v>
+      </c>
+      <c r="J127" s="12">
         <f>IF(H127=1,COUNTIF($H$105:H127,1),"")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="K127" s="19"/>
       <c r="L127" s="12"/>
@@ -10384,14 +10412,16 @@
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
-      <c r="H128" s="20"/>
+      <c r="H128" s="20">
+        <v>1</v>
+      </c>
       <c r="I128" s="21" t="str">
         <f>IFERROR(M96,"L2")</f>
         <v>Kroatia</v>
       </c>
-      <c r="J128" s="12" t="str">
+      <c r="J128" s="12">
         <f>IF(H128=1,COUNTIF($H$105:H128,1),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="K128" s="22"/>
       <c r="L128" s="12"/>
@@ -10426,7 +10456,7 @@
       <c r="H129" s="17"/>
       <c r="I129" s="18" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(1,$E$300:$E$311,0)),"")</f>
-        <v>Spania</v>
+        <v>Marokko</v>
       </c>
       <c r="J129" s="12" t="str">
         <f>IF(H129=1,COUNTIF($H$105:H129,1),"")</f>
@@ -10462,14 +10492,16 @@
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
       <c r="G130" s="12"/>
-      <c r="H130" s="20"/>
+      <c r="H130" s="20">
+        <v>1</v>
+      </c>
       <c r="I130" s="21" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(2,$E$300:$E$311,0)),"")</f>
-        <v>Marokko</v>
-      </c>
-      <c r="J130" s="12" t="str">
+        <v>Senegal</v>
+      </c>
+      <c r="J130" s="12">
         <f>IF(H130=1,COUNTIF($H$105:H130,1),"")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="K130" s="22"/>
       <c r="L130" s="12"/>
@@ -10504,7 +10536,7 @@
       <c r="H131" s="17"/>
       <c r="I131" s="18" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(3,$E$300:$E$311,0)),"")</f>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="J131" s="12" t="str">
         <f>IF(H131=1,COUNTIF($H$105:H131,1),"")</f>
@@ -10543,7 +10575,7 @@
       <c r="H132" s="20"/>
       <c r="I132" s="21" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(4,$E$300:$E$311,0)),"")</f>
-        <v>Sør-Korea</v>
+        <v>Sør-Afrika</v>
       </c>
       <c r="J132" s="12" t="str">
         <f>IF(H132=1,COUNTIF($H$105:H132,1),"")</f>
@@ -10621,7 +10653,7 @@
       <c r="H134" s="20"/>
       <c r="I134" s="21" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(6,$E$300:$E$311,0)),"")</f>
-        <v>Ecuador</v>
+        <v/>
       </c>
       <c r="J134" s="12" t="str">
         <f>IF(H134=1,COUNTIF($H$105:H134,1),"")</f>
@@ -10660,7 +10692,7 @@
       <c r="H135" s="17"/>
       <c r="I135" s="18" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(7,$E$300:$E$311,0)),"")</f>
-        <v>England</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="J135" s="12" t="str">
         <f>IF(H135=1,COUNTIF($H$105:H135,1),"")</f>
@@ -10699,7 +10731,7 @@
       <c r="H136" s="20"/>
       <c r="I136" s="21" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(8,$E$300:$E$311,0)),"")</f>
-        <v>Irak</v>
+        <v>Tunisia</v>
       </c>
       <c r="J136" s="12" t="str">
         <f>IF(H136=1,COUNTIF($H$105:H136,1),"")</f>
@@ -10769,11 +10801,11 @@
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="24"/>
-      <c r="I138" s="53" t="s">
+      <c r="I138" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="J138" s="53"/>
-      <c r="K138" s="53"/>
+      <c r="J138" s="66"/>
+      <c r="K138" s="66"/>
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
       <c r="N138" s="12"/>
@@ -10805,7 +10837,7 @@
       <c r="G139" s="12"/>
       <c r="H139" s="14" t="str">
         <f>COUNTIF(H140:H155,1)&amp;"/8"</f>
-        <v>0/8</v>
+        <v>8/8</v>
       </c>
       <c r="I139" s="15" t="s">
         <v>18</v>
@@ -10844,7 +10876,7 @@
       <c r="H140" s="25"/>
       <c r="I140" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(1,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Mexico</v>
       </c>
       <c r="J140" s="12" t="str">
         <f>IF(H140=1,COUNTIF($H$140:H140,1),"")</f>
@@ -10880,14 +10912,16 @@
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
       <c r="G141" s="12"/>
-      <c r="H141" s="28"/>
+      <c r="H141" s="28">
+        <v>1</v>
+      </c>
       <c r="I141" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(2,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J141" s="12" t="str">
+        <v>Brasil</v>
+      </c>
+      <c r="J141" s="12">
         <f>IF(H141=1,COUNTIF($H$140:H141,1),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K141" s="30"/>
       <c r="L141" s="12"/>
@@ -10922,7 +10956,7 @@
       <c r="H142" s="25"/>
       <c r="I142" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(3,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Skottland</v>
       </c>
       <c r="J142" s="12" t="str">
         <f>IF(H142=1,COUNTIF($H$140:H142,1),"")</f>
@@ -10961,7 +10995,7 @@
       <c r="H143" s="28"/>
       <c r="I143" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(4,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Tyrkia</v>
       </c>
       <c r="J143" s="12" t="str">
         <f>IF(H143=1,COUNTIF($H$140:H143,1),"")</f>
@@ -10997,14 +11031,16 @@
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
       <c r="G144" s="12"/>
-      <c r="H144" s="25"/>
+      <c r="H144" s="25">
+        <v>1</v>
+      </c>
       <c r="I144" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(5,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J144" s="12" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="J144" s="12">
         <f>IF(H144=1,COUNTIF($H$140:H144,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K144" s="27"/>
       <c r="L144" s="12"/>
@@ -11039,7 +11075,7 @@
       <c r="H145" s="28"/>
       <c r="I145" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(6,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Nederland</v>
       </c>
       <c r="J145" s="12" t="str">
         <f>IF(H145=1,COUNTIF($H$140:H145,1),"")</f>
@@ -11078,7 +11114,7 @@
       <c r="H146" s="25"/>
       <c r="I146" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(7,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Belgia</v>
       </c>
       <c r="J146" s="12" t="str">
         <f>IF(H146=1,COUNTIF($H$140:H146,1),"")</f>
@@ -11117,7 +11153,7 @@
       <c r="H147" s="28"/>
       <c r="I147" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(8,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Egypt</v>
       </c>
       <c r="J147" s="12" t="str">
         <f>IF(H147=1,COUNTIF($H$140:H147,1),"")</f>
@@ -11153,14 +11189,16 @@
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
       <c r="G148" s="12"/>
-      <c r="H148" s="25"/>
+      <c r="H148" s="25">
+        <v>1</v>
+      </c>
       <c r="I148" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(9,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J148" s="12" t="str">
+        <v>Spania</v>
+      </c>
+      <c r="J148" s="12">
         <f>IF(H148=1,COUNTIF($H$140:H148,1),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K148" s="27"/>
       <c r="L148" s="12"/>
@@ -11192,14 +11230,16 @@
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
       <c r="G149" s="12"/>
-      <c r="H149" s="28"/>
+      <c r="H149" s="28">
+        <v>1</v>
+      </c>
       <c r="I149" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(10,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J149" s="12" t="str">
+        <v>Frankrike</v>
+      </c>
+      <c r="J149" s="12">
         <f>IF(H149=1,COUNTIF($H$140:H149,1),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K149" s="30"/>
       <c r="L149" s="12"/>
@@ -11234,7 +11274,7 @@
       <c r="H150" s="25"/>
       <c r="I150" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(11,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Norge</v>
       </c>
       <c r="J150" s="12" t="str">
         <f>IF(H150=1,COUNTIF($H$140:H150,1),"")</f>
@@ -11270,14 +11310,16 @@
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
       <c r="G151" s="12"/>
-      <c r="H151" s="28"/>
+      <c r="H151" s="28">
+        <v>1</v>
+      </c>
       <c r="I151" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(12,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J151" s="12" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="J151" s="12">
         <f>IF(H151=1,COUNTIF($H$140:H151,1),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K151" s="30"/>
       <c r="L151" s="12"/>
@@ -11309,14 +11351,16 @@
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
       <c r="G152" s="12"/>
-      <c r="H152" s="25"/>
+      <c r="H152" s="25">
+        <v>1</v>
+      </c>
       <c r="I152" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(13,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J152" s="12" t="str">
+        <v>Portugal</v>
+      </c>
+      <c r="J152" s="12">
         <f>IF(H152=1,COUNTIF($H$140:H152,1),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K152" s="27"/>
       <c r="L152" s="12"/>
@@ -11348,14 +11392,16 @@
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
       <c r="G153" s="12"/>
-      <c r="H153" s="28"/>
+      <c r="H153" s="28">
+        <v>1</v>
+      </c>
       <c r="I153" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(14,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J153" s="12" t="str">
+        <v>England</v>
+      </c>
+      <c r="J153" s="12">
         <f>IF(H153=1,COUNTIF($H$140:H153,1),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K153" s="30"/>
       <c r="L153" s="12"/>
@@ -11387,14 +11433,16 @@
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
       <c r="G154" s="12"/>
-      <c r="H154" s="25"/>
+      <c r="H154" s="25">
+        <v>1</v>
+      </c>
       <c r="I154" s="26" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(15,$J$105:$J$136,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J154" s="12" t="str">
+        <v>Kroatia</v>
+      </c>
+      <c r="J154" s="12">
         <f>IF(H154=1,COUNTIF($H$140:H154,1),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="K154" s="27"/>
       <c r="L154" s="12"/>
@@ -11429,7 +11477,7 @@
       <c r="H155" s="28"/>
       <c r="I155" s="29" t="str">
         <f>IFERROR(INDEX($I$105:$I$136,MATCH(16,$J$105:$J$136,0)),"")</f>
-        <v/>
+        <v>Senegal</v>
       </c>
       <c r="J155" s="12" t="str">
         <f>IF(H155=1,COUNTIF($H$140:H155,1),"")</f>
@@ -11499,11 +11547,11 @@
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
       <c r="H157" s="31"/>
-      <c r="I157" s="54" t="s">
+      <c r="I157" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="J157" s="54"/>
-      <c r="K157" s="54"/>
+      <c r="J157" s="67"/>
+      <c r="K157" s="67"/>
       <c r="L157" s="12"/>
       <c r="M157" s="12"/>
       <c r="N157" s="12"/>
@@ -11535,7 +11583,7 @@
       <c r="G158" s="12"/>
       <c r="H158" s="14" t="str">
         <f>COUNTIF(H159:H166,1)&amp;"/4"</f>
-        <v>0/4</v>
+        <v>4/4</v>
       </c>
       <c r="I158" s="15" t="s">
         <v>18</v>
@@ -11571,14 +11619,16 @@
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
       <c r="G159" s="12"/>
-      <c r="H159" s="32"/>
+      <c r="H159" s="32">
+        <v>1</v>
+      </c>
       <c r="I159" s="33" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(1,$J$140:$J$155,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J159" s="12" t="str">
+        <v>Brasil</v>
+      </c>
+      <c r="J159" s="12">
         <f>IF(H159=1,COUNTIF($H$159:H159,1),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K159" s="34"/>
       <c r="L159" s="12"/>
@@ -11610,14 +11660,16 @@
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
       <c r="G160" s="12"/>
-      <c r="H160" s="35"/>
+      <c r="H160" s="35">
+        <v>1</v>
+      </c>
       <c r="I160" s="36" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(2,$J$140:$J$155,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J160" s="12" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="J160" s="12">
         <f>IF(H160=1,COUNTIF($H$159:H160,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K160" s="37"/>
       <c r="L160" s="12"/>
@@ -11649,14 +11701,16 @@
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
       <c r="G161" s="12"/>
-      <c r="H161" s="32"/>
+      <c r="H161" s="32">
+        <v>1</v>
+      </c>
       <c r="I161" s="33" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(3,$J$140:$J$155,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J161" s="12" t="str">
+        <v>Spania</v>
+      </c>
+      <c r="J161" s="12">
         <f>IF(H161=1,COUNTIF($H$159:H161,1),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K161" s="34"/>
       <c r="L161" s="12"/>
@@ -11691,7 +11745,7 @@
       <c r="H162" s="35"/>
       <c r="I162" s="36" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(4,$J$140:$J$155,0)),"")</f>
-        <v/>
+        <v>Frankrike</v>
       </c>
       <c r="J162" s="12" t="str">
         <f>IF(H162=1,COUNTIF($H$159:H162,1),"")</f>
@@ -11727,14 +11781,16 @@
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
       <c r="G163" s="12"/>
-      <c r="H163" s="32"/>
+      <c r="H163" s="32">
+        <v>1</v>
+      </c>
       <c r="I163" s="33" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(5,$J$140:$J$155,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J163" s="12" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="J163" s="12">
         <f>IF(H163=1,COUNTIF($H$159:H163,1),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K163" s="34"/>
       <c r="L163" s="12"/>
@@ -11769,7 +11825,7 @@
       <c r="H164" s="35"/>
       <c r="I164" s="36" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(6,$J$140:$J$155,0)),"")</f>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="J164" s="12" t="str">
         <f>IF(H164=1,COUNTIF($H$159:H164,1),"")</f>
@@ -11808,7 +11864,7 @@
       <c r="H165" s="32"/>
       <c r="I165" s="33" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(7,$J$140:$J$155,0)),"")</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="J165" s="12" t="str">
         <f>IF(H165=1,COUNTIF($H$159:H165,1),"")</f>
@@ -11847,7 +11903,7 @@
       <c r="H166" s="35"/>
       <c r="I166" s="36" t="str">
         <f>IFERROR(INDEX($I$140:$I$155,MATCH(8,$J$140:$J$155,0)),"")</f>
-        <v/>
+        <v>Kroatia</v>
       </c>
       <c r="J166" s="12" t="str">
         <f>IF(H166=1,COUNTIF($H$159:H166,1),"")</f>
@@ -11917,11 +11973,11 @@
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
       <c r="H168" s="38"/>
-      <c r="I168" s="55" t="s">
+      <c r="I168" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="J168" s="55"/>
-      <c r="K168" s="55"/>
+      <c r="J168" s="68"/>
+      <c r="K168" s="68"/>
       <c r="L168" s="12"/>
       <c r="M168" s="12"/>
       <c r="N168" s="12"/>
@@ -11953,7 +12009,7 @@
       <c r="G169" s="12"/>
       <c r="H169" s="14" t="str">
         <f>COUNTIF(H170:H173,1)&amp;"/2"</f>
-        <v>0/2</v>
+        <v>2/2</v>
       </c>
       <c r="I169" s="15" t="s">
         <v>18</v>
@@ -11992,7 +12048,7 @@
       <c r="H170" s="39"/>
       <c r="I170" s="40" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(1,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Brasil</v>
       </c>
       <c r="J170" s="12" t="str">
         <f>IF(H170=1,COUNTIF($H$170:H170,1),"")</f>
@@ -12031,7 +12087,7 @@
       <c r="H171" s="42"/>
       <c r="I171" s="43" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(2,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Tyskland</v>
       </c>
       <c r="J171" s="12" t="str">
         <f>IF(H171=1,COUNTIF($H$170:H171,1),"")</f>
@@ -12067,14 +12123,16 @@
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
       <c r="G172" s="12"/>
-      <c r="H172" s="39"/>
+      <c r="H172" s="39">
+        <v>1</v>
+      </c>
       <c r="I172" s="40" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(3,$J$159:$J$166,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J172" s="12" t="str">
+        <v>Spania</v>
+      </c>
+      <c r="J172" s="12">
         <f>IF(H172=1,COUNTIF($H$170:H172,1),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K172" s="41"/>
       <c r="L172" s="12"/>
@@ -12106,14 +12164,16 @@
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
       <c r="G173" s="12"/>
-      <c r="H173" s="42"/>
+      <c r="H173" s="42">
+        <v>1</v>
+      </c>
       <c r="I173" s="43" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(4,$J$159:$J$166,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J173" s="12" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="J173" s="12">
         <f>IF(H173=1,COUNTIF($H$170:H173,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K173" s="44"/>
       <c r="L173" s="12"/>
@@ -12179,11 +12239,11 @@
       <c r="F175" s="12"/>
       <c r="G175" s="12"/>
       <c r="H175" s="45"/>
-      <c r="I175" s="56" t="s">
+      <c r="I175" s="69" t="s">
         <v>164</v>
       </c>
-      <c r="J175" s="56"/>
-      <c r="K175" s="56"/>
+      <c r="J175" s="69"/>
+      <c r="K175" s="69"/>
       <c r="L175" s="12"/>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -12215,7 +12275,7 @@
       <c r="G176" s="12"/>
       <c r="H176" s="14" t="str">
         <f>COUNTIF(H177:H178,1)&amp;"/1"</f>
-        <v>0/1</v>
+        <v>1/1</v>
       </c>
       <c r="I176" s="15" t="s">
         <v>18</v>
@@ -12251,14 +12311,16 @@
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
       <c r="G177" s="12"/>
-      <c r="H177" s="46"/>
+      <c r="H177" s="46">
+        <v>1</v>
+      </c>
       <c r="I177" s="47" t="str">
         <f>IFERROR(INDEX($I$170:$I$173,MATCH(1,$J$170:$J$173,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J177" s="12" t="str">
+        <v>Spania</v>
+      </c>
+      <c r="J177" s="12">
         <f>IF(H177=1,COUNTIF($H$177:H177,1),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K177" s="48"/>
       <c r="L177" s="12"/>
@@ -12293,7 +12355,7 @@
       <c r="H178" s="49"/>
       <c r="I178" s="50" t="str">
         <f>IFERROR(INDEX($I$170:$I$173,MATCH(2,$J$170:$J$173,0)),"")</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="J178" s="12" t="str">
         <f>IF(H178=1,COUNTIF($H$177:H178,1),"")</f>
@@ -16317,19 +16379,19 @@
     <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="str">
         <f>M9</f>
-        <v>Sør-Korea</v>
+        <v>Sør-Afrika</v>
       </c>
       <c r="B300" s="12">
         <f>IFERROR(INDEX(AE7:AE10,MATCH(3,AF7:AF10,0)),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C300" s="12">
         <f>IFERROR(INDEX(AD7:AD10,MATCH(3,AF7:AF10,0)),0)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D300" s="12">
         <f>IFERROR(INDEX(AB7:AB10,MATCH(3,AF7:AF10,0)),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E300" s="12">
         <f>1+((B301&gt;B300)+((B301=B300)*(C301&gt;C300))+((B301=B300)*(C301=C300)*(D301&gt;D300))&gt;0)*1+((B302&gt;B300)+((B302=B300)*(C302&gt;C300))+((B302=B300)*(C302=C300)*(D302&gt;D300))&gt;0)*1+((B303&gt;B300)+((B303=B300)*(C303&gt;C300))+((B303=B300)*(C303=C300)*(D303&gt;D300))&gt;0)*1+((B304&gt;B300)+((B304=B300)*(C304&gt;C300))+((B304=B300)*(C304=C300)*(D304&gt;D300))&gt;0)*1+((B305&gt;B300)+((B305=B300)*(C305&gt;C300))+((B305=B300)*(C305=C300)*(D305&gt;D300))&gt;0)*1+((B306&gt;B300)+((B306=B300)*(C306&gt;C300))+((B306=B300)*(C306=C300)*(D306&gt;D300))&gt;0)*1+((B307&gt;B300)+((B307=B300)*(C307&gt;C300))+((B307=B300)*(C307=C300)*(D307&gt;D300))&gt;0)*1+((B308&gt;B300)+((B308=B300)*(C308&gt;C300))+((B308=B300)*(C308=C300)*(D308&gt;D300))&gt;0)*1+((B309&gt;B300)+((B309=B300)*(C309&gt;C300))+((B309=B300)*(C309=C300)*(D309&gt;D300))&gt;0)*1+((B310&gt;B300)+((B310=B300)*(C310&gt;C300))+((B310=B300)*(C310=C300)*(D310&gt;D300))&gt;0)*1+((B311&gt;B300)+((B311=B300)*(C311&gt;C300))+((B311=B300)*(C311=C300)*(D311&gt;D300))&gt;0)*1</f>
@@ -16365,19 +16427,19 @@
     <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="str">
         <f>M17</f>
-        <v>Bosnia-Hercegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="B301" s="12">
         <f>IFERROR(INDEX(AE15:AE18,MATCH(3,AF15:AF18,0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C301" s="12">
         <f>IFERROR(INDEX(AD15:AD18,MATCH(3,AF15:AF18,0)),0)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D301" s="12">
         <f>IFERROR(INDEX(AB15:AB18,MATCH(3,AF15:AF18,0)),0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E301" s="12">
         <f>1+((B300&gt;B301)+((B300=B301)*(C300&gt;C301))+((B300=B301)*(C300=C301)*(D300&gt;D301))&gt;0)*1+((B302&gt;B301)+((B302=B301)*(C302&gt;C301))+((B302=B301)*(C302=C301)*(D302&gt;D301))&gt;0)*1+((B303&gt;B301)+((B303=B301)*(C303&gt;C301))+((B303=B301)*(C303=C301)*(D303&gt;D301))&gt;0)*1+((B304&gt;B301)+((B304=B301)*(C304&gt;C301))+((B304=B301)*(C304=C301)*(D304&gt;D301))&gt;0)*1+((B305&gt;B301)+((B305=B301)*(C305&gt;C301))+((B305=B301)*(C305=C301)*(D305&gt;D301))&gt;0)*1+((B306&gt;B301)+((B306=B301)*(C306&gt;C301))+((B306=B301)*(C306=C301)*(D306&gt;D301))&gt;0)*1+((B307&gt;B301)+((B307=B301)*(C307&gt;C301))+((B307=B301)*(C307=C301)*(D307&gt;D301))&gt;0)*1+((B308&gt;B301)+((B308=B301)*(C308&gt;C301))+((B308=B301)*(C308=C301)*(D308&gt;D301))&gt;0)*1+((B309&gt;B301)+((B309=B301)*(C309&gt;C301))+((B309=B301)*(C309=C301)*(D309&gt;D301))&gt;0)*1+((B310&gt;B301)+((B310=B301)*(C310&gt;C301))+((B310=B301)*(C310=C301)*(D310&gt;D301))&gt;0)*1+((B311&gt;B301)+((B311=B301)*(C311&gt;C301))+((B311=B301)*(C311=C301)*(D311&gt;D301))&gt;0)*1</f>
@@ -16421,15 +16483,15 @@
       </c>
       <c r="C302" s="12">
         <f>IFERROR(INDEX(AD23:AD26,MATCH(3,AF23:AF26,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302" s="12">
         <f>IFERROR(INDEX(AB23:AB26,MATCH(3,AF23:AF26,0)),0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E302" s="12">
         <f>1+((B300&gt;B302)+((B300=B302)*(C300&gt;C302))+((B300=B302)*(C300=C302)*(D300&gt;D302))&gt;0)*1+((B301&gt;B302)+((B301=B302)*(C301&gt;C302))+((B301=B302)*(C301=C302)*(D301&gt;D302))&gt;0)*1+((B303&gt;B302)+((B303=B302)*(C303&gt;C302))+((B303=B302)*(C303=C302)*(D303&gt;D302))&gt;0)*1+((B304&gt;B302)+((B304=B302)*(C304&gt;C302))+((B304=B302)*(C304=C302)*(D304&gt;D302))&gt;0)*1+((B305&gt;B302)+((B305=B302)*(C305&gt;C302))+((B305=B302)*(C305=C302)*(D305&gt;D302))&gt;0)*1+((B306&gt;B302)+((B306=B302)*(C306&gt;C302))+((B306=B302)*(C306=C302)*(D306&gt;D302))&gt;0)*1+((B307&gt;B302)+((B307=B302)*(C307&gt;C302))+((B307=B302)*(C307=C302)*(D307&gt;D302))&gt;0)*1+((B308&gt;B302)+((B308=B302)*(C308&gt;C302))+((B308=B302)*(C308=C302)*(D308&gt;D302))&gt;0)*1+((B309&gt;B302)+((B309=B302)*(C309&gt;C302))+((B309=B302)*(C309=C302)*(D309&gt;D302))&gt;0)*1+((B310&gt;B302)+((B310=B302)*(C310&gt;C302))+((B310=B302)*(C310=C302)*(D310&gt;D302))&gt;0)*1+((B311&gt;B302)+((B311=B302)*(C311&gt;C302))+((B311=B302)*(C311=C302)*(D311&gt;D302))&gt;0)*1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F302" s="12"/>
       <c r="G302" s="12"/>
@@ -16461,7 +16523,7 @@
     <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="str">
         <f>M33</f>
-        <v>Australia</v>
+        <v>Paraguay</v>
       </c>
       <c r="B303" s="12">
         <f>IFERROR(INDEX(AE31:AE34,MATCH(3,AF31:AF34,0)),0)</f>
@@ -16469,15 +16531,15 @@
       </c>
       <c r="C303" s="12">
         <f>IFERROR(INDEX(AD31:AD34,MATCH(3,AF31:AF34,0)),0)</f>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D303" s="12">
         <f>IFERROR(INDEX(AB31:AB34,MATCH(3,AF31:AF34,0)),0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E303" s="12">
         <f>1+((B300&gt;B303)+((B300=B303)*(C300&gt;C303))+((B300=B303)*(C300=C303)*(D300&gt;D303))&gt;0)*1+((B301&gt;B303)+((B301=B303)*(C301&gt;C303))+((B301=B303)*(C301=C303)*(D301&gt;D303))&gt;0)*1+((B302&gt;B303)+((B302=B303)*(C302&gt;C303))+((B302=B303)*(C302=C303)*(D302&gt;D303))&gt;0)*1+((B304&gt;B303)+((B304=B303)*(C304&gt;C303))+((B304=B303)*(C304=C303)*(D304&gt;D303))&gt;0)*1+((B305&gt;B303)+((B305=B303)*(C305&gt;C303))+((B305=B303)*(C305=C303)*(D305&gt;D303))&gt;0)*1+((B306&gt;B303)+((B306=B303)*(C306&gt;C303))+((B306=B303)*(C306=C303)*(D306&gt;D303))&gt;0)*1+((B307&gt;B303)+((B307=B303)*(C307&gt;C303))+((B307=B303)*(C307=C303)*(D307&gt;D303))&gt;0)*1+((B308&gt;B303)+((B308=B303)*(C308&gt;C303))+((B308=B303)*(C308=C303)*(D308&gt;D303))&gt;0)*1+((B309&gt;B303)+((B309=B303)*(C309&gt;C303))+((B309=B303)*(C309=C303)*(D309&gt;D303))&gt;0)*1+((B310&gt;B303)+((B310=B303)*(C310&gt;C303))+((B310=B303)*(C310=C303)*(D310&gt;D303))&gt;0)*1+((B311&gt;B303)+((B311=B303)*(C311&gt;C303))+((B311=B303)*(C311=C303)*(D311&gt;D303))&gt;0)*1</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F303" s="12"/>
       <c r="G303" s="12"/>
@@ -16513,19 +16575,19 @@
       </c>
       <c r="B304" s="12">
         <f>IFERROR(INDEX(AE39:AE42,MATCH(3,AF39:AF42,0)),0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C304" s="12">
         <f>IFERROR(INDEX(AD39:AD42,MATCH(3,AF39:AF42,0)),0)</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D304" s="12">
         <f>IFERROR(INDEX(AB39:AB42,MATCH(3,AF39:AF42,0)),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E304" s="12">
         <f>1+((B300&gt;B304)+((B300=B304)*(C300&gt;C304))+((B300=B304)*(C300=C304)*(D300&gt;D304))&gt;0)*1+((B301&gt;B304)+((B301=B304)*(C301&gt;C304))+((B301=B304)*(C301=C304)*(D301&gt;D304))&gt;0)*1+((B302&gt;B304)+((B302=B304)*(C302&gt;C304))+((B302=B304)*(C302=C304)*(D302&gt;D304))&gt;0)*1+((B303&gt;B304)+((B303=B304)*(C303&gt;C304))+((B303=B304)*(C303=C304)*(D303&gt;D304))&gt;0)*1+((B305&gt;B304)+((B305=B304)*(C305&gt;C304))+((B305=B304)*(C305=C304)*(D305&gt;D304))&gt;0)*1+((B306&gt;B304)+((B306=B304)*(C306&gt;C304))+((B306=B304)*(C306=C304)*(D306&gt;D304))&gt;0)*1+((B307&gt;B304)+((B307=B304)*(C307&gt;C304))+((B307=B304)*(C307=C304)*(D307&gt;D304))&gt;0)*1+((B308&gt;B304)+((B308=B304)*(C308&gt;C304))+((B308=B304)*(C308=C304)*(D308&gt;D304))&gt;0)*1+((B309&gt;B304)+((B309=B304)*(C309&gt;C304))+((B309=B304)*(C309=C304)*(D309&gt;D304))&gt;0)*1+((B310&gt;B304)+((B310=B304)*(C310&gt;C304))+((B310=B304)*(C310=C304)*(D310&gt;D304))&gt;0)*1+((B311&gt;B304)+((B311=B304)*(C311&gt;C304))+((B311=B304)*(C311=C304)*(D311&gt;D304))&gt;0)*1</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F304" s="12"/>
       <c r="G304" s="12"/>
@@ -16557,23 +16619,23 @@
     <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="str">
         <f>M49</f>
-        <v>Nederland</v>
+        <v>Tunisia</v>
       </c>
       <c r="B305" s="12">
         <f>IFERROR(INDEX(AE47:AE50,MATCH(3,AF47:AF50,0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C305" s="12">
         <f>IFERROR(INDEX(AD47:AD50,MATCH(3,AF47:AF50,0)),0)</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D305" s="12">
         <f>IFERROR(INDEX(AB47:AB50,MATCH(3,AF47:AF50,0)),0)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E305" s="12">
         <f>1+((B300&gt;B305)+((B300=B305)*(C300&gt;C305))+((B300=B305)*(C300=C305)*(D300&gt;D305))&gt;0)*1+((B301&gt;B305)+((B301=B305)*(C301&gt;C305))+((B301=B305)*(C301=C305)*(D301&gt;D305))&gt;0)*1+((B302&gt;B305)+((B302=B305)*(C302&gt;C305))+((B302=B305)*(C302=C305)*(D302&gt;D305))&gt;0)*1+((B303&gt;B305)+((B303=B305)*(C303&gt;C305))+((B303=B305)*(C303=C305)*(D303&gt;D305))&gt;0)*1+((B304&gt;B305)+((B304=B305)*(C304&gt;C305))+((B304=B305)*(C304=C305)*(D304&gt;D305))&gt;0)*1+((B306&gt;B305)+((B306=B305)*(C306&gt;C305))+((B306=B305)*(C306=C305)*(D306&gt;D305))&gt;0)*1+((B307&gt;B305)+((B307=B305)*(C307&gt;C305))+((B307=B305)*(C307=C305)*(D307&gt;D305))&gt;0)*1+((B308&gt;B305)+((B308=B305)*(C308&gt;C305))+((B308=B305)*(C308=C305)*(D308&gt;D305))&gt;0)*1+((B309&gt;B305)+((B309=B305)*(C309&gt;C305))+((B309=B305)*(C309=C305)*(D309&gt;D305))&gt;0)*1+((B310&gt;B305)+((B310=B305)*(C310&gt;C305))+((B310=B305)*(C310=C305)*(D310&gt;D305))&gt;0)*1+((B311&gt;B305)+((B311=B305)*(C311&gt;C305))+((B311=B305)*(C311=C305)*(D311&gt;D305))&gt;0)*1</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F305" s="12"/>
       <c r="G305" s="12"/>
@@ -16605,23 +16667,23 @@
     <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12" t="str">
         <f>M57</f>
-        <v>Iran</v>
+        <v>New Zealand</v>
       </c>
       <c r="B306" s="12">
         <f>IFERROR(INDEX(AE55:AE58,MATCH(3,AF55:AF58,0)),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C306" s="12">
         <f>IFERROR(INDEX(AD55:AD58,MATCH(3,AF55:AF58,0)),0)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D306" s="12">
         <f>IFERROR(INDEX(AB55:AB58,MATCH(3,AF55:AF58,0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E306" s="12">
         <f>1+((B300&gt;B306)+((B300=B306)*(C300&gt;C306))+((B300=B306)*(C300=C306)*(D300&gt;D306))&gt;0)*1+((B301&gt;B306)+((B301=B306)*(C301&gt;C306))+((B301=B306)*(C301=C306)*(D301&gt;D306))&gt;0)*1+((B302&gt;B306)+((B302=B306)*(C302&gt;C306))+((B302=B306)*(C302=C306)*(D302&gt;D306))&gt;0)*1+((B303&gt;B306)+((B303=B306)*(C303&gt;C306))+((B303=B306)*(C303=C306)*(D303&gt;D306))&gt;0)*1+((B304&gt;B306)+((B304=B306)*(C304&gt;C306))+((B304=B306)*(C304=C306)*(D304&gt;D306))&gt;0)*1+((B305&gt;B306)+((B305=B306)*(C305&gt;C306))+((B305=B306)*(C305=C306)*(D305&gt;D306))&gt;0)*1+((B307&gt;B306)+((B307=B306)*(C307&gt;C306))+((B307=B306)*(C307=C306)*(D307&gt;D306))&gt;0)*1+((B308&gt;B306)+((B308=B306)*(C308&gt;C306))+((B308=B306)*(C308=C306)*(D308&gt;D306))&gt;0)*1+((B309&gt;B306)+((B309=B306)*(C309&gt;C306))+((B309=B306)*(C309=C306)*(D309&gt;D306))&gt;0)*1+((B310&gt;B306)+((B310=B306)*(C310&gt;C306))+((B310=B306)*(C310=C306)*(D310&gt;D306))&gt;0)*1+((B311&gt;B306)+((B311=B306)*(C311&gt;C306))+((B311=B306)*(C311=C306)*(D311&gt;D306))&gt;0)*1</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F306" s="12"/>
       <c r="G306" s="12"/>
@@ -16653,23 +16715,23 @@
     <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="str">
         <f>M65</f>
-        <v>Spania</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="B307" s="12">
         <f>IFERROR(INDEX(AE63:AE66,MATCH(3,AF63:AF66,0)),0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C307" s="12">
         <f>IFERROR(INDEX(AD63:AD66,MATCH(3,AF63:AF66,0)),0)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D307" s="12">
         <f>IFERROR(INDEX(AB63:AB66,MATCH(3,AF63:AF66,0)),0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E307" s="12">
         <f>1+((B300&gt;B307)+((B300=B307)*(C300&gt;C307))+((B300=B307)*(C300=C307)*(D300&gt;D307))&gt;0)*1+((B301&gt;B307)+((B301=B307)*(C301&gt;C307))+((B301=B307)*(C301=C307)*(D301&gt;D307))&gt;0)*1+((B302&gt;B307)+((B302=B307)*(C302&gt;C307))+((B302=B307)*(C302=C307)*(D302&gt;D307))&gt;0)*1+((B303&gt;B307)+((B303=B307)*(C303&gt;C307))+((B303=B307)*(C303=C307)*(D303&gt;D307))&gt;0)*1+((B304&gt;B307)+((B304=B307)*(C304&gt;C307))+((B304=B307)*(C304=C307)*(D304&gt;D307))&gt;0)*1+((B305&gt;B307)+((B305=B307)*(C305&gt;C307))+((B305=B307)*(C305=C307)*(D305&gt;D307))&gt;0)*1+((B306&gt;B307)+((B306=B307)*(C306&gt;C307))+((B306=B307)*(C306=C307)*(D306&gt;D307))&gt;0)*1+((B308&gt;B307)+((B308=B307)*(C308&gt;C307))+((B308=B307)*(C308=C307)*(D308&gt;D307))&gt;0)*1+((B309&gt;B307)+((B309=B307)*(C309&gt;C307))+((B309=B307)*(C309=C307)*(D309&gt;D307))&gt;0)*1+((B310&gt;B307)+((B310=B307)*(C310&gt;C307))+((B310=B307)*(C310=C307)*(D310&gt;D307))&gt;0)*1+((B311&gt;B307)+((B311=B307)*(C311&gt;C307))+((B311=B307)*(C311=C307)*(D311&gt;D307))&gt;0)*1</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F307" s="12"/>
       <c r="G307" s="12"/>
@@ -16701,15 +16763,15 @@
     <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12" t="str">
         <f>M73</f>
-        <v>Irak</v>
+        <v>Senegal</v>
       </c>
       <c r="B308" s="12">
         <f>IFERROR(INDEX(AE71:AE74,MATCH(3,AF71:AF74,0)),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C308" s="12">
         <f>IFERROR(INDEX(AD71:AD74,MATCH(3,AF71:AF74,0)),0)</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D308" s="12">
         <f>IFERROR(INDEX(AB71:AB74,MATCH(3,AF71:AF74,0)),0)</f>
@@ -16717,7 +16779,7 @@
       </c>
       <c r="E308" s="12">
         <f>1+((B300&gt;B308)+((B300=B308)*(C300&gt;C308))+((B300=B308)*(C300=C308)*(D300&gt;D308))&gt;0)*1+((B301&gt;B308)+((B301=B308)*(C301&gt;C308))+((B301=B308)*(C301=C308)*(D301&gt;D308))&gt;0)*1+((B302&gt;B308)+((B302=B308)*(C302&gt;C308))+((B302=B308)*(C302=C308)*(D302&gt;D308))&gt;0)*1+((B303&gt;B308)+((B303=B308)*(C303&gt;C308))+((B303=B308)*(C303=C308)*(D303&gt;D308))&gt;0)*1+((B304&gt;B308)+((B304=B308)*(C304&gt;C308))+((B304=B308)*(C304=C308)*(D304&gt;D308))&gt;0)*1+((B305&gt;B308)+((B305=B308)*(C305&gt;C308))+((B305=B308)*(C305=C308)*(D305&gt;D308))&gt;0)*1+((B306&gt;B308)+((B306=B308)*(C306&gt;C308))+((B306=B308)*(C306=C308)*(D306&gt;D308))&gt;0)*1+((B307&gt;B308)+((B307=B308)*(C307&gt;C308))+((B307=B308)*(C307=C308)*(D307&gt;D308))&gt;0)*1+((B309&gt;B308)+((B309=B308)*(C309&gt;C308))+((B309=B308)*(C309=C308)*(D309&gt;D308))&gt;0)*1+((B310&gt;B308)+((B310=B308)*(C310&gt;C308))+((B310=B308)*(C310=C308)*(D310&gt;D308))&gt;0)*1+((B311&gt;B308)+((B311=B308)*(C311&gt;C308))+((B311=B308)*(C311=C308)*(D311&gt;D308))&gt;0)*1</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F308" s="12"/>
       <c r="G308" s="12"/>
@@ -16749,23 +16811,23 @@
     <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12" t="str">
         <f>M81</f>
-        <v>Østerrike</v>
+        <v>Algerie</v>
       </c>
       <c r="B309" s="12">
         <f>IFERROR(INDEX(AE79:AE82,MATCH(3,AF79:AF82,0)),0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C309" s="12">
         <f>IFERROR(INDEX(AD79:AD82,MATCH(3,AF79:AF82,0)),0)</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D309" s="12">
         <f>IFERROR(INDEX(AB79:AB82,MATCH(3,AF79:AF82,0)),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E309" s="12">
         <f>1+((B300&gt;B309)+((B300=B309)*(C300&gt;C309))+((B300=B309)*(C300=C309)*(D300&gt;D309))&gt;0)*1+((B301&gt;B309)+((B301=B309)*(C301&gt;C309))+((B301=B309)*(C301=C309)*(D301&gt;D309))&gt;0)*1+((B302&gt;B309)+((B302=B309)*(C302&gt;C309))+((B302=B309)*(C302=C309)*(D302&gt;D309))&gt;0)*1+((B303&gt;B309)+((B303=B309)*(C303&gt;C309))+((B303=B309)*(C303=C309)*(D303&gt;D309))&gt;0)*1+((B304&gt;B309)+((B304=B309)*(C304&gt;C309))+((B304=B309)*(C304=C309)*(D304&gt;D309))&gt;0)*1+((B305&gt;B309)+((B305=B309)*(C305&gt;C309))+((B305=B309)*(C305=C309)*(D305&gt;D309))&gt;0)*1+((B306&gt;B309)+((B306=B309)*(C306&gt;C309))+((B306=B309)*(C306=C309)*(D306&gt;D309))&gt;0)*1+((B307&gt;B309)+((B307=B309)*(C307&gt;C309))+((B307=B309)*(C307=C309)*(D307&gt;D309))&gt;0)*1+((B308&gt;B309)+((B308=B309)*(C308&gt;C309))+((B308=B309)*(C308=C309)*(D308&gt;D309))&gt;0)*1+((B310&gt;B309)+((B310=B309)*(C310&gt;C309))+((B310=B309)*(C310=C309)*(D310&gt;D309))&gt;0)*1+((B311&gt;B309)+((B311=B309)*(C311&gt;C309))+((B311=B309)*(C311=C309)*(D311&gt;D309))&gt;0)*1</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F309" s="12"/>
       <c r="G309" s="12"/>
@@ -16801,19 +16863,19 @@
       </c>
       <c r="B310" s="12">
         <f>IFERROR(INDEX(AE87:AE90,MATCH(3,AF87:AF90,0)),0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C310" s="12">
         <f>IFERROR(INDEX(AD87:AD90,MATCH(3,AF87:AF90,0)),0)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D310" s="12">
         <f>IFERROR(INDEX(AB87:AB90,MATCH(3,AF87:AF90,0)),0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E310" s="12">
         <f>1+((B300&gt;B310)+((B300=B310)*(C300&gt;C310))+((B300=B310)*(C300=C310)*(D300&gt;D310))&gt;0)*1+((B301&gt;B310)+((B301=B310)*(C301&gt;C310))+((B301=B310)*(C301=C310)*(D301&gt;D310))&gt;0)*1+((B302&gt;B310)+((B302=B310)*(C302&gt;C310))+((B302=B310)*(C302=C310)*(D302&gt;D310))&gt;0)*1+((B303&gt;B310)+((B303=B310)*(C303&gt;C310))+((B303=B310)*(C303=C310)*(D303&gt;D310))&gt;0)*1+((B304&gt;B310)+((B304=B310)*(C304&gt;C310))+((B304=B310)*(C304=C310)*(D304&gt;D310))&gt;0)*1+((B305&gt;B310)+((B305=B310)*(C305&gt;C310))+((B305=B310)*(C305=C310)*(D305&gt;D310))&gt;0)*1+((B306&gt;B310)+((B306=B310)*(C306&gt;C310))+((B306=B310)*(C306=C310)*(D306&gt;D310))&gt;0)*1+((B307&gt;B310)+((B307=B310)*(C307&gt;C310))+((B307=B310)*(C307=C310)*(D307&gt;D310))&gt;0)*1+((B308&gt;B310)+((B308=B310)*(C308&gt;C310))+((B308=B310)*(C308=C310)*(D308&gt;D310))&gt;0)*1+((B309&gt;B310)+((B309=B310)*(C309&gt;C310))+((B309=B310)*(C309=C310)*(D309&gt;D310))&gt;0)*1+((B311&gt;B310)+((B311=B310)*(C311&gt;C310))+((B311=B310)*(C311=C310)*(D311&gt;D310))&gt;0)*1</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F310" s="12"/>
       <c r="G310" s="12"/>
@@ -16845,7 +16907,7 @@
     <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="str">
         <f>M97</f>
-        <v>England</v>
+        <v>Ghana</v>
       </c>
       <c r="B311" s="12">
         <f>IFERROR(INDEX(AE95:AE98,MATCH(3,AF95:AF98,0)),0)</f>
@@ -16853,15 +16915,15 @@
       </c>
       <c r="C311" s="12">
         <f>IFERROR(INDEX(AD95:AD98,MATCH(3,AF95:AF98,0)),0)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D311" s="12">
         <f>IFERROR(INDEX(AB95:AB98,MATCH(3,AF95:AF98,0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E311" s="12">
         <f>1+((B300&gt;B311)+((B300=B311)*(C300&gt;C311))+((B300=B311)*(C300=C311)*(D300&gt;D311))&gt;0)*1+((B301&gt;B311)+((B301=B311)*(C301&gt;C311))+((B301=B311)*(C301=C311)*(D301&gt;D311))&gt;0)*1+((B302&gt;B311)+((B302=B311)*(C302&gt;C311))+((B302=B311)*(C302=C311)*(D302&gt;D311))&gt;0)*1+((B303&gt;B311)+((B303=B311)*(C303&gt;C311))+((B303=B311)*(C303=C311)*(D303&gt;D311))&gt;0)*1+((B304&gt;B311)+((B304=B311)*(C304&gt;C311))+((B304=B311)*(C304=C311)*(D304&gt;D311))&gt;0)*1+((B305&gt;B311)+((B305=B311)*(C305&gt;C311))+((B305=B311)*(C305=C311)*(D305&gt;D311))&gt;0)*1+((B306&gt;B311)+((B306=B311)*(C306&gt;C311))+((B306=B311)*(C306=C311)*(D306&gt;D311))&gt;0)*1+((B307&gt;B311)+((B307=B311)*(C307&gt;C311))+((B307=B311)*(C307=C311)*(D307&gt;D311))&gt;0)*1+((B308&gt;B311)+((B308=B311)*(C308&gt;C311))+((B308=B311)*(C308=C311)*(D308&gt;D311))&gt;0)*1+((B309&gt;B311)+((B309=B311)*(C309&gt;C311))+((B309=B311)*(C309=C311)*(D309&gt;D311))&gt;0)*1+((B310&gt;B311)+((B310=B311)*(C310&gt;C311))+((B310=B311)*(C310=C311)*(D310&gt;D311))&gt;0)*1</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F311" s="12"/>
       <c r="G311" s="12"/>
@@ -16892,29 +16954,11 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="M1:U1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="M2:U2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="M3:U3"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="M21:U21"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="M29:U29"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="M37:U37"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="M53:U53"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="M61:U61"/>
+    <mergeCell ref="I138:K138"/>
+    <mergeCell ref="I157:K157"/>
+    <mergeCell ref="I168:K168"/>
+    <mergeCell ref="I175:K175"/>
+    <mergeCell ref="A93:K93"/>
     <mergeCell ref="M93:U93"/>
     <mergeCell ref="H101:K101"/>
     <mergeCell ref="I103:K103"/>
@@ -16924,11 +16968,29 @@
     <mergeCell ref="M77:U77"/>
     <mergeCell ref="A85:K85"/>
     <mergeCell ref="M85:U85"/>
-    <mergeCell ref="I138:K138"/>
-    <mergeCell ref="I157:K157"/>
-    <mergeCell ref="I168:K168"/>
-    <mergeCell ref="I175:K175"/>
-    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="M53:U53"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="M61:U61"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="M21:U21"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="M29:U29"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="M37:U37"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="M3:U3"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="M2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="H105:H136">
     <cfRule type="expression" dxfId="19" priority="2">

--- a/VM2026_Tipping - Martin.xlsx
+++ b/VM2026_Tipping - Martin.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/Tipping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="8_{93E9AAE6-D14F-4877-B081-BFF986B62DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CACE6077-60F6-472C-96DB-8DE6FAA71042}"/>
+  <xr:revisionPtr revIDLastSave="344" documentId="8_{93E9AAE6-D14F-4877-B081-BFF986B62DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6EAD25-FE31-45B2-BC0A-7A84AF141D44}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="8172" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MINE TIPS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="166">
   <si>
     <t>⚽  VM 2026  –  MINE TIPS</t>
   </si>
@@ -2082,20 +2082,20 @@
     <tabColor rgb="FFE94560"/>
   </sheetPr>
   <dimension ref="A1:AF311"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="12" width="1.5703125" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="17" width="4" customWidth="1"/>
     <col min="18" max="21" width="5" customWidth="1"/>
@@ -2103,7 +2103,7 @@
     <col min="23" max="32" width="18" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="T1" s="54"/>
       <c r="U1" s="54"/>
     </row>
-    <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
         <v>2</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="T2" s="57"/>
       <c r="U2" s="57"/>
     </row>
-    <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>4</v>
       </c>
@@ -2183,8 +2183,8 @@
       <c r="T3" s="59"/>
       <c r="U3" s="59"/>
     </row>
-    <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="60" t="s">
         <v>6</v>
       </c>
@@ -2210,7 +2210,7 @@
       <c r="T5" s="61"/>
       <c r="U5" s="61"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="60" t="s">
         <v>48</v>
       </c>
@@ -2806,7 +2806,7 @@
       <c r="T13" s="61"/>
       <c r="U13" s="61"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>7</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>8</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>10</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>11</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>12</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="60" t="s">
         <v>63</v>
       </c>
@@ -3402,7 +3402,7 @@
       <c r="T21" s="61"/>
       <c r="U21" s="61"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>14</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>16</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>17</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>18</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="60" t="s">
         <v>76</v>
       </c>
@@ -3998,7 +3998,7 @@
       <c r="T29" s="61"/>
       <c r="U29" s="61"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>8</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>19</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>20</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>21</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>22</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>23</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>24</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="60" t="s">
         <v>85</v>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="T37" s="61"/>
       <c r="U37" s="61"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>8</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>25</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>26</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>27</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>28</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>29</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>30</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="60" t="s">
         <v>100</v>
       </c>
@@ -5190,7 +5190,7 @@
       <c r="T45" s="61"/>
       <c r="U45" s="61"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>31</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>32</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>33</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>34</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>35</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>36</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="60" t="s">
         <v>108</v>
       </c>
@@ -5786,7 +5786,7 @@
       <c r="T53" s="61"/>
       <c r="U53" s="61"/>
     </row>
-    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>37</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>38</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>39</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>40</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>41</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>42</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="60" t="s">
         <v>119</v>
       </c>
@@ -6382,7 +6382,7 @@
       <c r="T61" s="61"/>
       <c r="U61" s="61"/>
     </row>
-    <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>8</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>43</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>44</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>45</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>46</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>47</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>48</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="64" t="s">
         <v>126</v>
       </c>
@@ -6978,7 +6978,7 @@
       <c r="T69" s="65"/>
       <c r="U69" s="65"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>8</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>49</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>50</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>51</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>52</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>53</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>54</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="60" t="s">
         <v>136</v>
       </c>
@@ -7574,7 +7574,7 @@
       <c r="T77" s="61"/>
       <c r="U77" s="61"/>
     </row>
-    <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>8</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>55</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>56</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>57</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>58</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>59</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>60</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="60" t="s">
         <v>143</v>
       </c>
@@ -8170,7 +8170,7 @@
       <c r="T85" s="61"/>
       <c r="U85" s="61"/>
     </row>
-    <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>8</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>61</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>62</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>63</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>64</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>65</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>66</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="60" t="s">
         <v>151</v>
       </c>
@@ -8766,7 +8766,7 @@
       <c r="T93" s="61"/>
       <c r="U93" s="61"/>
     </row>
-    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>8</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>67</v>
       </c>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="R95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AB95,IF(AF96=1,AB96,IF(AF97=1,AB97,IF(AF98=1,AB98,"")))),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AC95,IF(AF96=1,AC96,IF(AF97=1,AC97,IF(AF98=1,AC98,"")))),"")</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="T95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AD95,IF(AF96=1,AD96,IF(AF97=1,AD97,IF(AF98=1,AD98,"")))),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U95" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,AE95,IF(AF96=1,AE96,IF(AF97=1,AE97,IF(AF98=1,AE98,"")))),"")</f>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="AB95">
         <f>IF((C95="England")*ISNUMBER(D95),D95,0)+IF((G95="England")*ISNUMBER(D95),F95,0)+IF((C96="England")*ISNUMBER(D96),D96,0)+IF((G96="England")*ISNUMBER(D96),F96,0)+IF((C97="England")*ISNUMBER(D97),D97,0)+IF((G97="England")*ISNUMBER(D97),F97,0)+IF((C98="England")*ISNUMBER(D98),D98,0)+IF((G98="England")*ISNUMBER(D98),F98,0)+IF((C99="England")*ISNUMBER(D99),D99,0)+IF((G99="England")*ISNUMBER(D99),F99,0)+IF((C100="England")*ISNUMBER(D100),D100,0)+IF((G100="England")*ISNUMBER(D100),F100,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC95">
         <f>IF((C95="England")*ISNUMBER(D95),F95,0)+IF((G95="England")*ISNUMBER(D95),D95,0)+IF((C96="England")*ISNUMBER(D96),F96,0)+IF((G96="England")*ISNUMBER(D96),D96,0)+IF((C97="England")*ISNUMBER(D97),F97,0)+IF((G97="England")*ISNUMBER(D97),D97,0)+IF((C98="England")*ISNUMBER(D98),F98,0)+IF((G98="England")*ISNUMBER(D98),D98,0)+IF((C99="England")*ISNUMBER(D99),F99,0)+IF((G99="England")*ISNUMBER(D99),D99,0)+IF((C100="England")*ISNUMBER(D100),F100,0)+IF((G100="England")*ISNUMBER(D100),D100,0)</f>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="AD95">
         <f>AB95-AC95</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE95">
         <f>3*Y95+Z95</f>
@@ -8936,7 +8936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>68</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>69</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>154</v>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>29</v>
@@ -9106,11 +9106,11 @@
       </c>
       <c r="S97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AC95,IF(AF96=3,AC96,IF(AF97=3,AC97,IF(AF98=3,AC98,"")))),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AD95,IF(AF96=3,AD96,IF(AF97=3,AD97,IF(AF98=3,AD98,"")))),"")</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="U97" s="3">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,AE95,IF(AF96=3,AE96,IF(AF97=3,AE97,IF(AF98=3,AE98,"")))),"")</f>
@@ -9141,11 +9141,11 @@
       </c>
       <c r="AC97">
         <f>IF((C95="Ghana")*ISNUMBER(D95),F95,0)+IF((G95="Ghana")*ISNUMBER(D95),D95,0)+IF((C96="Ghana")*ISNUMBER(D96),F96,0)+IF((G96="Ghana")*ISNUMBER(D96),D96,0)+IF((C97="Ghana")*ISNUMBER(D97),F97,0)+IF((G97="Ghana")*ISNUMBER(D97),D97,0)+IF((C98="Ghana")*ISNUMBER(D98),F98,0)+IF((G98="Ghana")*ISNUMBER(D98),D98,0)+IF((C99="Ghana")*ISNUMBER(D99),F99,0)+IF((G99="Ghana")*ISNUMBER(D99),D99,0)+IF((C100="Ghana")*ISNUMBER(D100),F100,0)+IF((G100="Ghana")*ISNUMBER(D100),D100,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD97">
         <f>AB97-AC97</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AE97">
         <f>3*Y97+Z97</f>
@@ -9156,7 +9156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>70</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>71</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>72</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -9371,7 +9371,7 @@
       <c r="AD101" s="12"/>
       <c r="AE101" s="12"/>
     </row>
-    <row r="102" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -9406,7 +9406,7 @@
       <c r="AD102" s="12"/>
       <c r="AE102" s="12"/>
     </row>
-    <row r="103" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -9441,7 +9441,7 @@
       <c r="AD103" s="12"/>
       <c r="AE103" s="12"/>
     </row>
-    <row r="104" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -9479,7 +9479,7 @@
       <c r="AD104" s="12"/>
       <c r="AE104" s="12"/>
     </row>
-    <row r="105" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -9520,7 +9520,7 @@
       <c r="AD105" s="12"/>
       <c r="AE105" s="12"/>
     </row>
-    <row r="106" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -9559,7 +9559,7 @@
       <c r="AD106" s="12"/>
       <c r="AE106" s="12"/>
     </row>
-    <row r="107" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -9598,7 +9598,7 @@
       <c r="AD107" s="12"/>
       <c r="AE107" s="12"/>
     </row>
-    <row r="108" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -9637,7 +9637,7 @@
       <c r="AD108" s="12"/>
       <c r="AE108" s="12"/>
     </row>
-    <row r="109" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -9678,7 +9678,7 @@
       <c r="AD109" s="12"/>
       <c r="AE109" s="12"/>
     </row>
-    <row r="110" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -9719,7 +9719,7 @@
       <c r="AD110" s="12"/>
       <c r="AE110" s="12"/>
     </row>
-    <row r="111" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -9760,7 +9760,7 @@
       <c r="AD111" s="12"/>
       <c r="AE111" s="12"/>
     </row>
-    <row r="112" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -9799,7 +9799,7 @@
       <c r="AD112" s="12"/>
       <c r="AE112" s="12"/>
     </row>
-    <row r="113" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -9840,7 +9840,7 @@
       <c r="AD113" s="12"/>
       <c r="AE113" s="12"/>
     </row>
-    <row r="114" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -9879,7 +9879,7 @@
       <c r="AD114" s="12"/>
       <c r="AE114" s="12"/>
     </row>
-    <row r="115" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -9920,7 +9920,7 @@
       <c r="AD115" s="12"/>
       <c r="AE115" s="12"/>
     </row>
-    <row r="116" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -9959,7 +9959,7 @@
       <c r="AD116" s="12"/>
       <c r="AE116" s="12"/>
     </row>
-    <row r="117" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -10000,7 +10000,7 @@
       <c r="AD117" s="12"/>
       <c r="AE117" s="12"/>
     </row>
-    <row r="118" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -10041,7 +10041,7 @@
       <c r="AD118" s="12"/>
       <c r="AE118" s="12"/>
     </row>
-    <row r="119" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -10082,7 +10082,7 @@
       <c r="AD119" s="12"/>
       <c r="AE119" s="12"/>
     </row>
-    <row r="120" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -10121,7 +10121,7 @@
       <c r="AD120" s="12"/>
       <c r="AE120" s="12"/>
     </row>
-    <row r="121" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -10162,7 +10162,7 @@
       <c r="AD121" s="12"/>
       <c r="AE121" s="12"/>
     </row>
-    <row r="122" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -10203,7 +10203,7 @@
       <c r="AD122" s="12"/>
       <c r="AE122" s="12"/>
     </row>
-    <row r="123" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -10244,7 +10244,7 @@
       <c r="AD123" s="12"/>
       <c r="AE123" s="12"/>
     </row>
-    <row r="124" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -10283,7 +10283,7 @@
       <c r="AD124" s="12"/>
       <c r="AE124" s="12"/>
     </row>
-    <row r="125" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -10324,7 +10324,7 @@
       <c r="AD125" s="12"/>
       <c r="AE125" s="12"/>
     </row>
-    <row r="126" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -10363,7 +10363,7 @@
       <c r="AD126" s="12"/>
       <c r="AE126" s="12"/>
     </row>
-    <row r="127" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -10404,7 +10404,7 @@
       <c r="AD127" s="12"/>
       <c r="AE127" s="12"/>
     </row>
-    <row r="128" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -10445,7 +10445,7 @@
       <c r="AD128" s="12"/>
       <c r="AE128" s="12"/>
     </row>
-    <row r="129" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -10484,7 +10484,7 @@
       <c r="AD129" s="12"/>
       <c r="AE129" s="12"/>
     </row>
-    <row r="130" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -10525,7 +10525,7 @@
       <c r="AD130" s="12"/>
       <c r="AE130" s="12"/>
     </row>
-    <row r="131" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -10564,7 +10564,7 @@
       <c r="AD131" s="12"/>
       <c r="AE131" s="12"/>
     </row>
-    <row r="132" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -10603,7 +10603,7 @@
       <c r="AD132" s="12"/>
       <c r="AE132" s="12"/>
     </row>
-    <row r="133" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -10612,9 +10612,8 @@
       <c r="F133" s="12"/>
       <c r="G133" s="12"/>
       <c r="H133" s="17"/>
-      <c r="I133" s="18" t="str">
-        <f>IFERROR(INDEX($A$300:$A$311,MATCH(5,$E$300:$E$311,0)),"")</f>
-        <v/>
+      <c r="I133" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="J133" s="12" t="str">
         <f>IF(H133=1,COUNTIF($H$105:H133,1),"")</f>
@@ -10642,7 +10641,7 @@
       <c r="AD133" s="12"/>
       <c r="AE133" s="12"/>
     </row>
-    <row r="134" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -10653,7 +10652,7 @@
       <c r="H134" s="20"/>
       <c r="I134" s="21" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(6,$E$300:$E$311,0)),"")</f>
-        <v/>
+        <v>Ghana</v>
       </c>
       <c r="J134" s="12" t="str">
         <f>IF(H134=1,COUNTIF($H$105:H134,1),"")</f>
@@ -10681,7 +10680,7 @@
       <c r="AD134" s="12"/>
       <c r="AE134" s="12"/>
     </row>
-    <row r="135" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -10720,7 +10719,7 @@
       <c r="AD135" s="12"/>
       <c r="AE135" s="12"/>
     </row>
-    <row r="136" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -10759,7 +10758,7 @@
       <c r="AD136" s="12"/>
       <c r="AE136" s="12"/>
     </row>
-    <row r="137" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -10792,7 +10791,7 @@
       <c r="AD137" s="12"/>
       <c r="AE137" s="12"/>
     </row>
-    <row r="138" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -10827,7 +10826,7 @@
       <c r="AD138" s="12"/>
       <c r="AE138" s="12"/>
     </row>
-    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -10865,7 +10864,7 @@
       <c r="AD139" s="12"/>
       <c r="AE139" s="12"/>
     </row>
-    <row r="140" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -10904,7 +10903,7 @@
       <c r="AD140" s="12"/>
       <c r="AE140" s="12"/>
     </row>
-    <row r="141" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -10945,7 +10944,7 @@
       <c r="AD141" s="12"/>
       <c r="AE141" s="12"/>
     </row>
-    <row r="142" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -10984,7 +10983,7 @@
       <c r="AD142" s="12"/>
       <c r="AE142" s="12"/>
     </row>
-    <row r="143" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -11023,7 +11022,7 @@
       <c r="AD143" s="12"/>
       <c r="AE143" s="12"/>
     </row>
-    <row r="144" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -11064,7 +11063,7 @@
       <c r="AD144" s="12"/>
       <c r="AE144" s="12"/>
     </row>
-    <row r="145" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -11103,7 +11102,7 @@
       <c r="AD145" s="12"/>
       <c r="AE145" s="12"/>
     </row>
-    <row r="146" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -11142,7 +11141,7 @@
       <c r="AD146" s="12"/>
       <c r="AE146" s="12"/>
     </row>
-    <row r="147" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
@@ -11181,7 +11180,7 @@
       <c r="AD147" s="12"/>
       <c r="AE147" s="12"/>
     </row>
-    <row r="148" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -11222,7 +11221,7 @@
       <c r="AD148" s="12"/>
       <c r="AE148" s="12"/>
     </row>
-    <row r="149" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -11263,7 +11262,7 @@
       <c r="AD149" s="12"/>
       <c r="AE149" s="12"/>
     </row>
-    <row r="150" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -11302,7 +11301,7 @@
       <c r="AD150" s="12"/>
       <c r="AE150" s="12"/>
     </row>
-    <row r="151" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -11343,7 +11342,7 @@
       <c r="AD151" s="12"/>
       <c r="AE151" s="12"/>
     </row>
-    <row r="152" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
@@ -11384,7 +11383,7 @@
       <c r="AD152" s="12"/>
       <c r="AE152" s="12"/>
     </row>
-    <row r="153" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
@@ -11425,7 +11424,7 @@
       <c r="AD153" s="12"/>
       <c r="AE153" s="12"/>
     </row>
-    <row r="154" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -11466,7 +11465,7 @@
       <c r="AD154" s="12"/>
       <c r="AE154" s="12"/>
     </row>
-    <row r="155" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -11505,7 +11504,7 @@
       <c r="AD155" s="12"/>
       <c r="AE155" s="12"/>
     </row>
-    <row r="156" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -11538,7 +11537,7 @@
       <c r="AD156" s="12"/>
       <c r="AE156" s="12"/>
     </row>
-    <row r="157" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
@@ -11573,7 +11572,7 @@
       <c r="AD157" s="12"/>
       <c r="AE157" s="12"/>
     </row>
-    <row r="158" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
@@ -11611,7 +11610,7 @@
       <c r="AD158" s="12"/>
       <c r="AE158" s="12"/>
     </row>
-    <row r="159" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
@@ -11652,7 +11651,7 @@
       <c r="AD159" s="12"/>
       <c r="AE159" s="12"/>
     </row>
-    <row r="160" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
@@ -11693,7 +11692,7 @@
       <c r="AD160" s="12"/>
       <c r="AE160" s="12"/>
     </row>
-    <row r="161" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -11734,7 +11733,7 @@
       <c r="AD161" s="12"/>
       <c r="AE161" s="12"/>
     </row>
-    <row r="162" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
@@ -11773,7 +11772,7 @@
       <c r="AD162" s="12"/>
       <c r="AE162" s="12"/>
     </row>
-    <row r="163" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
@@ -11814,7 +11813,7 @@
       <c r="AD163" s="12"/>
       <c r="AE163" s="12"/>
     </row>
-    <row r="164" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
@@ -11853,7 +11852,7 @@
       <c r="AD164" s="12"/>
       <c r="AE164" s="12"/>
     </row>
-    <row r="165" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -11892,7 +11891,7 @@
       <c r="AD165" s="12"/>
       <c r="AE165" s="12"/>
     </row>
-    <row r="166" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
@@ -11931,7 +11930,7 @@
       <c r="AD166" s="12"/>
       <c r="AE166" s="12"/>
     </row>
-    <row r="167" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
@@ -11964,7 +11963,7 @@
       <c r="AD167" s="12"/>
       <c r="AE167" s="12"/>
     </row>
-    <row r="168" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -11999,7 +11998,7 @@
       <c r="AD168" s="12"/>
       <c r="AE168" s="12"/>
     </row>
-    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
@@ -12037,7 +12036,7 @@
       <c r="AD169" s="12"/>
       <c r="AE169" s="12"/>
     </row>
-    <row r="170" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -12076,7 +12075,7 @@
       <c r="AD170" s="12"/>
       <c r="AE170" s="12"/>
     </row>
-    <row r="171" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -12115,7 +12114,7 @@
       <c r="AD171" s="12"/>
       <c r="AE171" s="12"/>
     </row>
-    <row r="172" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -12156,7 +12155,7 @@
       <c r="AD172" s="12"/>
       <c r="AE172" s="12"/>
     </row>
-    <row r="173" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
@@ -12197,7 +12196,7 @@
       <c r="AD173" s="12"/>
       <c r="AE173" s="12"/>
     </row>
-    <row r="174" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
@@ -12230,7 +12229,7 @@
       <c r="AD174" s="12"/>
       <c r="AE174" s="12"/>
     </row>
-    <row r="175" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
@@ -12265,7 +12264,7 @@
       <c r="AD175" s="12"/>
       <c r="AE175" s="12"/>
     </row>
-    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -12303,7 +12302,7 @@
       <c r="AD176" s="12"/>
       <c r="AE176" s="12"/>
     </row>
-    <row r="177" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -12344,7 +12343,7 @@
       <c r="AD177" s="12"/>
       <c r="AE177" s="12"/>
     </row>
-    <row r="178" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -12383,7 +12382,7 @@
       <c r="AD178" s="12"/>
       <c r="AE178" s="12"/>
     </row>
-    <row r="179" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
@@ -12416,7 +12415,7 @@
       <c r="AD179" s="12"/>
       <c r="AE179" s="12"/>
     </row>
-    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
@@ -12449,7 +12448,7 @@
       <c r="AD180" s="12"/>
       <c r="AE180" s="12"/>
     </row>
-    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
@@ -12482,7 +12481,7 @@
       <c r="AD181" s="12"/>
       <c r="AE181" s="12"/>
     </row>
-    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
@@ -12515,7 +12514,7 @@
       <c r="AD182" s="12"/>
       <c r="AE182" s="12"/>
     </row>
-    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
@@ -12548,7 +12547,7 @@
       <c r="AD183" s="12"/>
       <c r="AE183" s="12"/>
     </row>
-    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
@@ -12581,7 +12580,7 @@
       <c r="AD184" s="12"/>
       <c r="AE184" s="12"/>
     </row>
-    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
@@ -12614,7 +12613,7 @@
       <c r="AD185" s="12"/>
       <c r="AE185" s="12"/>
     </row>
-    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
@@ -12647,7 +12646,7 @@
       <c r="AD186" s="12"/>
       <c r="AE186" s="12"/>
     </row>
-    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
@@ -12680,7 +12679,7 @@
       <c r="AD187" s="12"/>
       <c r="AE187" s="12"/>
     </row>
-    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
@@ -12713,7 +12712,7 @@
       <c r="AD188" s="12"/>
       <c r="AE188" s="12"/>
     </row>
-    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
@@ -12746,7 +12745,7 @@
       <c r="AD189" s="12"/>
       <c r="AE189" s="12"/>
     </row>
-    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
@@ -12779,7 +12778,7 @@
       <c r="AD190" s="12"/>
       <c r="AE190" s="12"/>
     </row>
-    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
@@ -12812,7 +12811,7 @@
       <c r="AD191" s="12"/>
       <c r="AE191" s="12"/>
     </row>
-    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
@@ -12845,7 +12844,7 @@
       <c r="AD192" s="12"/>
       <c r="AE192" s="12"/>
     </row>
-    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
@@ -12878,7 +12877,7 @@
       <c r="AD193" s="12"/>
       <c r="AE193" s="12"/>
     </row>
-    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
@@ -12911,7 +12910,7 @@
       <c r="AD194" s="12"/>
       <c r="AE194" s="12"/>
     </row>
-    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
@@ -12944,7 +12943,7 @@
       <c r="AD195" s="12"/>
       <c r="AE195" s="12"/>
     </row>
-    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
@@ -12977,7 +12976,7 @@
       <c r="AD196" s="12"/>
       <c r="AE196" s="12"/>
     </row>
-    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
@@ -13010,7 +13009,7 @@
       <c r="AD197" s="12"/>
       <c r="AE197" s="12"/>
     </row>
-    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
@@ -13043,7 +13042,7 @@
       <c r="AD198" s="12"/>
       <c r="AE198" s="12"/>
     </row>
-    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="12"/>
@@ -13076,7 +13075,7 @@
       <c r="AD199" s="12"/>
       <c r="AE199" s="12"/>
     </row>
-    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="12"/>
@@ -13109,7 +13108,7 @@
       <c r="AD200" s="12"/>
       <c r="AE200" s="12"/>
     </row>
-    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="12"/>
@@ -13142,7 +13141,7 @@
       <c r="AD201" s="12"/>
       <c r="AE201" s="12"/>
     </row>
-    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="12"/>
@@ -13175,7 +13174,7 @@
       <c r="AD202" s="12"/>
       <c r="AE202" s="12"/>
     </row>
-    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="12"/>
@@ -13208,7 +13207,7 @@
       <c r="AD203" s="12"/>
       <c r="AE203" s="12"/>
     </row>
-    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="12"/>
@@ -13241,7 +13240,7 @@
       <c r="AD204" s="12"/>
       <c r="AE204" s="12"/>
     </row>
-    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="12"/>
@@ -13274,7 +13273,7 @@
       <c r="AD205" s="12"/>
       <c r="AE205" s="12"/>
     </row>
-    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="12"/>
@@ -13307,7 +13306,7 @@
       <c r="AD206" s="12"/>
       <c r="AE206" s="12"/>
     </row>
-    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12"/>
@@ -13340,7 +13339,7 @@
       <c r="AD207" s="12"/>
       <c r="AE207" s="12"/>
     </row>
-    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12"/>
@@ -13373,7 +13372,7 @@
       <c r="AD208" s="12"/>
       <c r="AE208" s="12"/>
     </row>
-    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12"/>
@@ -13406,7 +13405,7 @@
       <c r="AD209" s="12"/>
       <c r="AE209" s="12"/>
     </row>
-    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12"/>
@@ -13439,7 +13438,7 @@
       <c r="AD210" s="12"/>
       <c r="AE210" s="12"/>
     </row>
-    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12"/>
@@ -13472,7 +13471,7 @@
       <c r="AD211" s="12"/>
       <c r="AE211" s="12"/>
     </row>
-    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12"/>
@@ -13505,7 +13504,7 @@
       <c r="AD212" s="12"/>
       <c r="AE212" s="12"/>
     </row>
-    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -13538,7 +13537,7 @@
       <c r="AD213" s="12"/>
       <c r="AE213" s="12"/>
     </row>
-    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -13571,7 +13570,7 @@
       <c r="AD214" s="12"/>
       <c r="AE214" s="12"/>
     </row>
-    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="12"/>
@@ -13604,7 +13603,7 @@
       <c r="AD215" s="12"/>
       <c r="AE215" s="12"/>
     </row>
-    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -13637,7 +13636,7 @@
       <c r="AD216" s="12"/>
       <c r="AE216" s="12"/>
     </row>
-    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -13670,7 +13669,7 @@
       <c r="AD217" s="12"/>
       <c r="AE217" s="12"/>
     </row>
-    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
@@ -13703,7 +13702,7 @@
       <c r="AD218" s="12"/>
       <c r="AE218" s="12"/>
     </row>
-    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="12"/>
@@ -13736,7 +13735,7 @@
       <c r="AD219" s="12"/>
       <c r="AE219" s="12"/>
     </row>
-    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="12"/>
@@ -13769,7 +13768,7 @@
       <c r="AD220" s="12"/>
       <c r="AE220" s="12"/>
     </row>
-    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="12"/>
@@ -13802,7 +13801,7 @@
       <c r="AD221" s="12"/>
       <c r="AE221" s="12"/>
     </row>
-    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="12"/>
@@ -13835,7 +13834,7 @@
       <c r="AD222" s="12"/>
       <c r="AE222" s="12"/>
     </row>
-    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
@@ -13868,7 +13867,7 @@
       <c r="AD223" s="12"/>
       <c r="AE223" s="12"/>
     </row>
-    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="12"/>
@@ -13901,7 +13900,7 @@
       <c r="AD224" s="12"/>
       <c r="AE224" s="12"/>
     </row>
-    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="12"/>
@@ -13934,7 +13933,7 @@
       <c r="AD225" s="12"/>
       <c r="AE225" s="12"/>
     </row>
-    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="12"/>
@@ -13967,7 +13966,7 @@
       <c r="AD226" s="12"/>
       <c r="AE226" s="12"/>
     </row>
-    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="12"/>
@@ -14000,7 +13999,7 @@
       <c r="AD227" s="12"/>
       <c r="AE227" s="12"/>
     </row>
-    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="12"/>
@@ -14033,7 +14032,7 @@
       <c r="AD228" s="12"/>
       <c r="AE228" s="12"/>
     </row>
-    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="12"/>
@@ -14066,7 +14065,7 @@
       <c r="AD229" s="12"/>
       <c r="AE229" s="12"/>
     </row>
-    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="12"/>
@@ -14099,7 +14098,7 @@
       <c r="AD230" s="12"/>
       <c r="AE230" s="12"/>
     </row>
-    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="12"/>
@@ -14132,7 +14131,7 @@
       <c r="AD231" s="12"/>
       <c r="AE231" s="12"/>
     </row>
-    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="12"/>
@@ -14165,7 +14164,7 @@
       <c r="AD232" s="12"/>
       <c r="AE232" s="12"/>
     </row>
-    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="12"/>
@@ -14198,7 +14197,7 @@
       <c r="AD233" s="12"/>
       <c r="AE233" s="12"/>
     </row>
-    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="12"/>
@@ -14231,7 +14230,7 @@
       <c r="AD234" s="12"/>
       <c r="AE234" s="12"/>
     </row>
-    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="12"/>
@@ -14264,7 +14263,7 @@
       <c r="AD235" s="12"/>
       <c r="AE235" s="12"/>
     </row>
-    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="12"/>
@@ -14297,7 +14296,7 @@
       <c r="AD236" s="12"/>
       <c r="AE236" s="12"/>
     </row>
-    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -14330,7 +14329,7 @@
       <c r="AD237" s="12"/>
       <c r="AE237" s="12"/>
     </row>
-    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="12"/>
@@ -14363,7 +14362,7 @@
       <c r="AD238" s="12"/>
       <c r="AE238" s="12"/>
     </row>
-    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="12"/>
@@ -14396,7 +14395,7 @@
       <c r="AD239" s="12"/>
       <c r="AE239" s="12"/>
     </row>
-    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="12"/>
@@ -14429,7 +14428,7 @@
       <c r="AD240" s="12"/>
       <c r="AE240" s="12"/>
     </row>
-    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -14462,7 +14461,7 @@
       <c r="AD241" s="12"/>
       <c r="AE241" s="12"/>
     </row>
-    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="12"/>
@@ -14495,7 +14494,7 @@
       <c r="AD242" s="12"/>
       <c r="AE242" s="12"/>
     </row>
-    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="12"/>
@@ -14528,7 +14527,7 @@
       <c r="AD243" s="12"/>
       <c r="AE243" s="12"/>
     </row>
-    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="12"/>
@@ -14561,7 +14560,7 @@
       <c r="AD244" s="12"/>
       <c r="AE244" s="12"/>
     </row>
-    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
@@ -14594,7 +14593,7 @@
       <c r="AD245" s="12"/>
       <c r="AE245" s="12"/>
     </row>
-    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="12"/>
@@ -14627,7 +14626,7 @@
       <c r="AD246" s="12"/>
       <c r="AE246" s="12"/>
     </row>
-    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
@@ -14660,7 +14659,7 @@
       <c r="AD247" s="12"/>
       <c r="AE247" s="12"/>
     </row>
-    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
@@ -14693,7 +14692,7 @@
       <c r="AD248" s="12"/>
       <c r="AE248" s="12"/>
     </row>
-    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
@@ -14726,7 +14725,7 @@
       <c r="AD249" s="12"/>
       <c r="AE249" s="12"/>
     </row>
-    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -14759,7 +14758,7 @@
       <c r="AD250" s="12"/>
       <c r="AE250" s="12"/>
     </row>
-    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="12"/>
@@ -14792,7 +14791,7 @@
       <c r="AD251" s="12"/>
       <c r="AE251" s="12"/>
     </row>
-    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="12"/>
@@ -14825,7 +14824,7 @@
       <c r="AD252" s="12"/>
       <c r="AE252" s="12"/>
     </row>
-    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="12"/>
@@ -14858,7 +14857,7 @@
       <c r="AD253" s="12"/>
       <c r="AE253" s="12"/>
     </row>
-    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="12"/>
@@ -14891,7 +14890,7 @@
       <c r="AD254" s="12"/>
       <c r="AE254" s="12"/>
     </row>
-    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -14924,7 +14923,7 @@
       <c r="AD255" s="12"/>
       <c r="AE255" s="12"/>
     </row>
-    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="12"/>
@@ -14957,7 +14956,7 @@
       <c r="AD256" s="12"/>
       <c r="AE256" s="12"/>
     </row>
-    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
@@ -14990,7 +14989,7 @@
       <c r="AD257" s="12"/>
       <c r="AE257" s="12"/>
     </row>
-    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -15023,7 +15022,7 @@
       <c r="AD258" s="12"/>
       <c r="AE258" s="12"/>
     </row>
-    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -15056,7 +15055,7 @@
       <c r="AD259" s="12"/>
       <c r="AE259" s="12"/>
     </row>
-    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -15089,7 +15088,7 @@
       <c r="AD260" s="12"/>
       <c r="AE260" s="12"/>
     </row>
-    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -15122,7 +15121,7 @@
       <c r="AD261" s="12"/>
       <c r="AE261" s="12"/>
     </row>
-    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -15155,7 +15154,7 @@
       <c r="AD262" s="12"/>
       <c r="AE262" s="12"/>
     </row>
-    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -15188,7 +15187,7 @@
       <c r="AD263" s="12"/>
       <c r="AE263" s="12"/>
     </row>
-    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -15221,7 +15220,7 @@
       <c r="AD264" s="12"/>
       <c r="AE264" s="12"/>
     </row>
-    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="12"/>
@@ -15254,7 +15253,7 @@
       <c r="AD265" s="12"/>
       <c r="AE265" s="12"/>
     </row>
-    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
@@ -15287,7 +15286,7 @@
       <c r="AD266" s="12"/>
       <c r="AE266" s="12"/>
     </row>
-    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="12"/>
@@ -15320,7 +15319,7 @@
       <c r="AD267" s="12"/>
       <c r="AE267" s="12"/>
     </row>
-    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
@@ -15353,7 +15352,7 @@
       <c r="AD268" s="12"/>
       <c r="AE268" s="12"/>
     </row>
-    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
@@ -15386,7 +15385,7 @@
       <c r="AD269" s="12"/>
       <c r="AE269" s="12"/>
     </row>
-    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="12"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
@@ -15419,7 +15418,7 @@
       <c r="AD270" s="12"/>
       <c r="AE270" s="12"/>
     </row>
-    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="12"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -15452,7 +15451,7 @@
       <c r="AD271" s="12"/>
       <c r="AE271" s="12"/>
     </row>
-    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="12"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -15485,7 +15484,7 @@
       <c r="AD272" s="12"/>
       <c r="AE272" s="12"/>
     </row>
-    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="12"/>
       <c r="B273" s="12"/>
       <c r="C273" s="12"/>
@@ -15518,7 +15517,7 @@
       <c r="AD273" s="12"/>
       <c r="AE273" s="12"/>
     </row>
-    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -15551,7 +15550,7 @@
       <c r="AD274" s="12"/>
       <c r="AE274" s="12"/>
     </row>
-    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -15584,7 +15583,7 @@
       <c r="AD275" s="12"/>
       <c r="AE275" s="12"/>
     </row>
-    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -15617,7 +15616,7 @@
       <c r="AD276" s="12"/>
       <c r="AE276" s="12"/>
     </row>
-    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -15650,7 +15649,7 @@
       <c r="AD277" s="12"/>
       <c r="AE277" s="12"/>
     </row>
-    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -15683,7 +15682,7 @@
       <c r="AD278" s="12"/>
       <c r="AE278" s="12"/>
     </row>
-    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12"/>
@@ -15716,7 +15715,7 @@
       <c r="AD279" s="12"/>
       <c r="AE279" s="12"/>
     </row>
-    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -15749,7 +15748,7 @@
       <c r="AD280" s="12"/>
       <c r="AE280" s="12"/>
     </row>
-    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -15782,7 +15781,7 @@
       <c r="AD281" s="12"/>
       <c r="AE281" s="12"/>
     </row>
-    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -15815,7 +15814,7 @@
       <c r="AD282" s="12"/>
       <c r="AE282" s="12"/>
     </row>
-    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -15848,7 +15847,7 @@
       <c r="AD283" s="12"/>
       <c r="AE283" s="12"/>
     </row>
-    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -15881,7 +15880,7 @@
       <c r="AD284" s="12"/>
       <c r="AE284" s="12"/>
     </row>
-    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="12"/>
       <c r="B285" s="12"/>
       <c r="C285" s="12"/>
@@ -15914,7 +15913,7 @@
       <c r="AD285" s="12"/>
       <c r="AE285" s="12"/>
     </row>
-    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="12"/>
       <c r="B286" s="12"/>
       <c r="C286" s="12"/>
@@ -15947,7 +15946,7 @@
       <c r="AD286" s="12"/>
       <c r="AE286" s="12"/>
     </row>
-    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="12"/>
       <c r="B287" s="12"/>
       <c r="C287" s="12"/>
@@ -15980,7 +15979,7 @@
       <c r="AD287" s="12"/>
       <c r="AE287" s="12"/>
     </row>
-    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="12"/>
       <c r="B288" s="12"/>
       <c r="C288" s="12"/>
@@ -16013,7 +16012,7 @@
       <c r="AD288" s="12"/>
       <c r="AE288" s="12"/>
     </row>
-    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="12"/>
       <c r="B289" s="12"/>
       <c r="C289" s="12"/>
@@ -16046,7 +16045,7 @@
       <c r="AD289" s="12"/>
       <c r="AE289" s="12"/>
     </row>
-    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="12"/>
       <c r="B290" s="12"/>
       <c r="C290" s="12"/>
@@ -16079,7 +16078,7 @@
       <c r="AD290" s="12"/>
       <c r="AE290" s="12"/>
     </row>
-    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="12"/>
       <c r="B291" s="12"/>
       <c r="C291" s="12"/>
@@ -16112,7 +16111,7 @@
       <c r="AD291" s="12"/>
       <c r="AE291" s="12"/>
     </row>
-    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="12"/>
       <c r="B292" s="12"/>
       <c r="C292" s="12"/>
@@ -16145,7 +16144,7 @@
       <c r="AD292" s="12"/>
       <c r="AE292" s="12"/>
     </row>
-    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="12"/>
       <c r="B293" s="12"/>
       <c r="C293" s="12"/>
@@ -16178,7 +16177,7 @@
       <c r="AD293" s="12"/>
       <c r="AE293" s="12"/>
     </row>
-    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12"/>
       <c r="B294" s="12"/>
       <c r="C294" s="12"/>
@@ -16211,7 +16210,7 @@
       <c r="AD294" s="12"/>
       <c r="AE294" s="12"/>
     </row>
-    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12"/>
       <c r="C295" s="12"/>
@@ -16244,7 +16243,7 @@
       <c r="AD295" s="12"/>
       <c r="AE295" s="12"/>
     </row>
-    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12"/>
@@ -16277,7 +16276,7 @@
       <c r="AD296" s="12"/>
       <c r="AE296" s="12"/>
     </row>
-    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12"/>
@@ -16310,7 +16309,7 @@
       <c r="AD297" s="12"/>
       <c r="AE297" s="12"/>
     </row>
-    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12"/>
       <c r="C298" s="12"/>
@@ -16343,7 +16342,7 @@
       <c r="AD298" s="12"/>
       <c r="AE298" s="12"/>
     </row>
-    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12"/>
@@ -16376,7 +16375,7 @@
       <c r="AD299" s="12"/>
       <c r="AE299" s="12"/>
     </row>
-    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="12" t="str">
         <f>M9</f>
         <v>Sør-Afrika</v>
@@ -16424,7 +16423,7 @@
       <c r="AD300" s="12"/>
       <c r="AE300" s="12"/>
     </row>
-    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="12" t="str">
         <f>M17</f>
         <v>Qatar</v>
@@ -16472,7 +16471,7 @@
       <c r="AD301" s="12"/>
       <c r="AE301" s="12"/>
     </row>
-    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="12" t="str">
         <f>M25</f>
         <v>Marokko</v>
@@ -16520,7 +16519,7 @@
       <c r="AD302" s="12"/>
       <c r="AE302" s="12"/>
     </row>
-    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="str">
         <f>M33</f>
         <v>Paraguay</v>
@@ -16568,7 +16567,7 @@
       <c r="AD303" s="12"/>
       <c r="AE303" s="12"/>
     </row>
-    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="12" t="str">
         <f>M41</f>
         <v>Ecuador</v>
@@ -16616,7 +16615,7 @@
       <c r="AD304" s="12"/>
       <c r="AE304" s="12"/>
     </row>
-    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="str">
         <f>M49</f>
         <v>Tunisia</v>
@@ -16664,7 +16663,7 @@
       <c r="AD305" s="12"/>
       <c r="AE305" s="12"/>
     </row>
-    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="12" t="str">
         <f>M57</f>
         <v>New Zealand</v>
@@ -16712,7 +16711,7 @@
       <c r="AD306" s="12"/>
       <c r="AE306" s="12"/>
     </row>
-    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="str">
         <f>M65</f>
         <v>Saudi Arabia</v>
@@ -16760,7 +16759,7 @@
       <c r="AD307" s="12"/>
       <c r="AE307" s="12"/>
     </row>
-    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="12" t="str">
         <f>M73</f>
         <v>Senegal</v>
@@ -16808,7 +16807,7 @@
       <c r="AD308" s="12"/>
       <c r="AE308" s="12"/>
     </row>
-    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="str">
         <f>M81</f>
         <v>Algerie</v>
@@ -16856,7 +16855,7 @@
       <c r="AD309" s="12"/>
       <c r="AE309" s="12"/>
     </row>
-    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="12" t="str">
         <f>M89</f>
         <v>Usbekistan</v>
@@ -16904,7 +16903,7 @@
       <c r="AD310" s="12"/>
       <c r="AE310" s="12"/>
     </row>
-    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="12" t="str">
         <f>M97</f>
         <v>Ghana</v>
@@ -16915,7 +16914,7 @@
       </c>
       <c r="C311" s="12">
         <f>IFERROR(INDEX(AD95:AD98,MATCH(3,AF95:AF98,0)),0)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D311" s="12">
         <f>IFERROR(INDEX(AB95:AB98,MATCH(3,AF95:AF98,0)),0)</f>
@@ -16923,7 +16922,7 @@
       </c>
       <c r="E311" s="12">
         <f>1+((B300&gt;B311)+((B300=B311)*(C300&gt;C311))+((B300=B311)*(C300=C311)*(D300&gt;D311))&gt;0)*1+((B301&gt;B311)+((B301=B311)*(C301&gt;C311))+((B301=B311)*(C301=C311)*(D301&gt;D311))&gt;0)*1+((B302&gt;B311)+((B302=B311)*(C302&gt;C311))+((B302=B311)*(C302=C311)*(D302&gt;D311))&gt;0)*1+((B303&gt;B311)+((B303=B311)*(C303&gt;C311))+((B303=B311)*(C303=C311)*(D303&gt;D311))&gt;0)*1+((B304&gt;B311)+((B304=B311)*(C304&gt;C311))+((B304=B311)*(C304=C311)*(D304&gt;D311))&gt;0)*1+((B305&gt;B311)+((B305=B311)*(C305&gt;C311))+((B305=B311)*(C305=C311)*(D305&gt;D311))&gt;0)*1+((B306&gt;B311)+((B306=B311)*(C306&gt;C311))+((B306=B311)*(C306=C311)*(D306&gt;D311))&gt;0)*1+((B307&gt;B311)+((B307=B311)*(C307&gt;C311))+((B307=B311)*(C307=C311)*(D307&gt;D311))&gt;0)*1+((B308&gt;B311)+((B308=B311)*(C308&gt;C311))+((B308=B311)*(C308=C311)*(D308&gt;D311))&gt;0)*1+((B309&gt;B311)+((B309=B311)*(C309&gt;C311))+((B309=B311)*(C309=C311)*(D309&gt;D311))&gt;0)*1+((B310&gt;B311)+((B310=B311)*(C310&gt;C311))+((B310=B311)*(C310=C311)*(D310&gt;D311))&gt;0)*1</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F311" s="12"/>
       <c r="G311" s="12"/>
@@ -17032,7 +17031,7 @@
       <formula>AND(COUNTIF($H$177:$H$178,1)&gt;=1,H177&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I105:I136">
+  <conditionalFormatting sqref="I105:I132 I134:I136">
     <cfRule type="expression" dxfId="9" priority="4">
       <formula>$H105=1</formula>
     </cfRule>
